--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05249610417725045</v>
+        <v>0.05249610417725028</v>
       </c>
       <c r="C2" t="n">
         <v>0.04891039605956912</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05293181507703506</v>
+        <v>0.05293181507703493</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05868380316300064</v>
+        <v>0.0586838031630005</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05335322395595266</v>
+        <v>0.05335322395595251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05342514870240189</v>
+        <v>0.05342514870240177</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05463552461586208</v>
+        <v>0.05463552461586196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05312466403762534</v>
+        <v>0.05312466403762532</v>
       </c>
       <c r="J2" t="n">
         <v>0.05482069543842386</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05392924356860518</v>
+        <v>0.0539292435686051</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05258899138530485</v>
+        <v>0.05258899138530479</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0542446799964208</v>
+        <v>0.05424467999642074</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05367799778186952</v>
+        <v>0.05367799778186941</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05780080299884633</v>
+        <v>0.05780080299884615</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05719838627152814</v>
+        <v>0.05719838627152804</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05362037075720057</v>
+        <v>0.05362037075720044</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05365944233472157</v>
+        <v>0.05365944233472141</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05259388023921959</v>
+        <v>0.05259388023921946</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05538908790472793</v>
+        <v>0.05538908790472787</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196183443681799</v>
+        <v>0.21961834436818</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05613237589934681</v>
+        <v>0.05613237589934672</v>
       </c>
       <c r="W2" t="n">
         <v>0.242452720618676</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05254090302313218</v>
+        <v>0.05254090302313216</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05868017785546396</v>
+        <v>0.05868017785546387</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2053849525540616</v>
+        <v>0.2053849525540615</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05289112467221203</v>
+        <v>0.05289112467221206</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05283770303347421</v>
+        <v>0.05283770303347416</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02446036012354027</v>
+        <v>0.02446036012354033</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02009575958668367</v>
+        <v>0.02009575958668366</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02758511099094289</v>
+        <v>0.02758511099094287</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06861813400343414</v>
+        <v>0.06861813400343411</v>
       </c>
       <c r="F3" t="n">
         <v>0.03061181454401471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03107490567841466</v>
+        <v>0.03107490567841461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03982173802832301</v>
+        <v>0.03982173802832311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02896942796695336</v>
+        <v>0.02896942796695342</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04102792478522285</v>
+        <v>0.04102792478522283</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03471998430200673</v>
+        <v>0.03471998430200664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02512557582085719</v>
+        <v>0.02512557582085711</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03717677535500811</v>
+        <v>0.03717677535500812</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03291062044102214</v>
+        <v>0.03291062044102208</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04539446859125846</v>
+        <v>0.04539446859125845</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05791701706068326</v>
+        <v>0.0579170170606832</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03250303239211667</v>
+        <v>0.03250303239211665</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03280764366975197</v>
+        <v>0.03280764366975194</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0251575696508053</v>
+        <v>0.02515756965080526</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04518098988299147</v>
+        <v>0.04518098988299148</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3146208561827421</v>
+        <v>0.3146208561827423</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05032002483738877</v>
+        <v>0.05032002483738887</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3747921884789955</v>
+        <v>0.3747921884789957</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02478594433012629</v>
+        <v>0.02478594433012628</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06861120196268178</v>
+        <v>0.06861120196268169</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2989184813374882</v>
+        <v>0.2989184813374877</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02728472848669083</v>
+        <v>0.02728472848669081</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02719578020961437</v>
+        <v>0.02719578020961433</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0127590627712214</v>
+        <v>0.01275906277122135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01588550403979018</v>
+        <v>0.01588550403979021</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01768061782120562</v>
+        <v>0.01768061782120564</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08265196929743482</v>
+        <v>0.0826519692974348</v>
       </c>
       <c r="F4" t="n">
         <v>0.02244062496624134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02325304806440354</v>
+        <v>0.02325304806440359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03692480080736516</v>
+        <v>0.03692480080736532</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01985893554597818</v>
+        <v>0.01985893554597822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03912475679096036</v>
+        <v>0.03912475679096034</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02894703147326554</v>
+        <v>0.02894703147326563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0138082665164239</v>
+        <v>0.01380826651642402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03284608788626302</v>
+        <v>0.03284608788626307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02610909473331399</v>
+        <v>0.02610909473331412</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03800432417910667</v>
+        <v>0.03800432417910653</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06587350218272373</v>
+        <v>0.06587350218272374</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02545817097993667</v>
+        <v>0.02545817097993661</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02589950242185025</v>
+        <v>0.02589950242185027</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01386348837037368</v>
+        <v>0.01386348837037362</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04543664481134486</v>
+        <v>0.04543664481134485</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04261322872416948</v>
+        <v>0.04261322872416945</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05455633226977903</v>
+        <v>0.05455633226977899</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0884379485003958</v>
+        <v>0.08843794850039581</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01326508634394379</v>
+        <v>0.01326508634394386</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08298964860389803</v>
+        <v>0.08298964860389808</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0583803980606029</v>
+        <v>0.05838039806060288</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01722100098021944</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01712045745403572</v>
+        <v>0.01712045745403578</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0408418689640566</v>
+        <v>0.04084186896405664</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1093969912434258</v>
+        <v>0.1093969912434256</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1489025784742514</v>
+        <v>0.1489025784742497</v>
       </c>
       <c r="E5" t="n">
-        <v>1.445872725049495</v>
+        <v>1.445872725049494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2561034603328788</v>
+        <v>0.2561034603328768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2426041610984268</v>
+        <v>0.2426041610984272</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5823032892039639</v>
+        <v>0.5823032892039656</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1974909224549843</v>
+        <v>0.1974909224549836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5559517587580209</v>
+        <v>0.5559517587580203</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3853983801243481</v>
+        <v>0.3853983801243484</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06332275853671648</v>
+        <v>0.06332275853671569</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4775389607383539</v>
+        <v>0.4775389607383546</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6052756929387398</v>
+        <v>0.6052756929387425</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4991512286225432</v>
+        <v>0.4991512286225431</v>
       </c>
       <c r="P5" t="n">
-        <v>1.048779860824714</v>
+        <v>1.048779860824713</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3077041721960165</v>
+        <v>0.3077041721960157</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3318994008526346</v>
+        <v>0.3318994008526341</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06271228486907217</v>
+        <v>0.06271228486906963</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7424405446754735</v>
+        <v>0.7424405446754748</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6214011981067813</v>
+        <v>0.6214011981067808</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8136653808468981</v>
+        <v>0.8136653808468978</v>
       </c>
       <c r="W5" t="n">
-        <v>1.573968209658431</v>
+        <v>1.57396820965843</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05451059247112623</v>
+        <v>0.05451059247112628</v>
       </c>
       <c r="Y5" t="n">
         <v>1.456306238216784</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9168542154809177</v>
+        <v>0.9168542154809158</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1337194006536022</v>
+        <v>0.133719400653602</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1430471508626807</v>
+        <v>0.1430471508626802</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.04443524577101</v>
+        <v>7.735499563210245</v>
       </c>
       <c r="C6" t="n">
-        <v>7.738626004478821</v>
+        <v>7.738626004478817</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049356800820995</v>
+        <v>2.049356800820997</v>
       </c>
       <c r="E6" t="n">
-        <v>7.805392469736468</v>
+        <v>2.114328152297224</v>
       </c>
       <c r="F6" t="n">
-        <v>2.054116807966031</v>
+        <v>7.745181125405275</v>
       </c>
       <c r="G6" t="n">
-        <v>2.054929231064193</v>
+        <v>7.745993548503434</v>
       </c>
       <c r="H6" t="n">
-        <v>7.759665301246393</v>
+        <v>7.759665301246391</v>
       </c>
       <c r="I6" t="n">
-        <v>7.742599435985007</v>
+        <v>2.051535118545767</v>
       </c>
       <c r="J6" t="n">
-        <v>2.070800939790749</v>
+        <v>7.761865257229995</v>
       </c>
       <c r="K6" t="n">
-        <v>2.060623214473056</v>
+        <v>2.060623214473058</v>
       </c>
       <c r="L6" t="n">
-        <v>7.736548766955461</v>
+        <v>2.045484449516214</v>
       </c>
       <c r="M6" t="n">
-        <v>2.064522270886052</v>
+        <v>2.064522270886055</v>
       </c>
       <c r="N6" t="n">
-        <v>2.057548612566319</v>
+        <v>2.057548612566317</v>
       </c>
       <c r="O6" t="n">
-        <v>7.761205966900396</v>
+        <v>7.761205966900397</v>
       </c>
       <c r="P6" t="n">
         <v>7.789075211881581</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.057134353979726</v>
+        <v>2.057134353979727</v>
       </c>
       <c r="R6" t="n">
-        <v>7.748640002860886</v>
+        <v>2.05757568542164</v>
       </c>
       <c r="S6" t="n">
-        <v>7.736603988809404</v>
+        <v>7.736603988809405</v>
       </c>
       <c r="T6" t="n">
-        <v>2.077112827811133</v>
+        <v>2.077112827811136</v>
       </c>
       <c r="U6" t="n">
-        <v>2.073910782901146</v>
+        <v>2.073910782901148</v>
       </c>
       <c r="V6" t="n">
-        <v>7.777296832708809</v>
+        <v>7.777296832708805</v>
       </c>
       <c r="W6" t="n">
-        <v>2.223498674012015</v>
+        <v>7.811639640392536</v>
       </c>
       <c r="X6" t="n">
-        <v>7.73600558678298</v>
+        <v>7.736005586782984</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.203078679787434</v>
+        <v>2.203078679787432</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.090056581060393</v>
+        <v>2.090056581060394</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.739961501419256</v>
+        <v>2.048897183980009</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.048385592097509</v>
+        <v>2.04838559209751</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01639793128645259</v>
+        <v>0.0163979312864526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01952437255502138</v>
+        <v>0.01952437255502142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02131948633643683</v>
+        <v>0.02131948633643681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08629083781266589</v>
+        <v>0.08629083781266594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02607949348147254</v>
+        <v>0.02607949348147258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02689191657963472</v>
+        <v>0.02689191657963477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04056366932259634</v>
+        <v>0.04056366932259649</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02349780406120937</v>
+        <v>0.02349780406120933</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04276362530619152</v>
+        <v>0.04276362530619154</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03258589998849673</v>
+        <v>0.03258589998849679</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01744713503165508</v>
+        <v>0.01744713503165515</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03648495640149421</v>
+        <v>0.03648495640149423</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0297479632485452</v>
+        <v>0.02974796324854532</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04164304154710977</v>
+        <v>0.04164304154710981</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06951221955072687</v>
+        <v>0.06951221955072684</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02909703949516781</v>
+        <v>0.02909703949516786</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02953837093708142</v>
+        <v>0.02953837093708136</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01750235688560484</v>
+        <v>0.01750235688560479</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04907551332657607</v>
+        <v>0.04907551332657608</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04588791838705526</v>
+        <v>0.04588791838705528</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05819520078501022</v>
+        <v>0.05819520078501027</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09207681701562709</v>
+        <v>0.09207681701562707</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01690395485917496</v>
+        <v>0.01690395485917507</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08624988829631576</v>
+        <v>0.08624988829631575</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06201926657583407</v>
+        <v>0.06201926657583402</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02085986949545062</v>
+        <v>0.0208598694954506</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02075932596926693</v>
+        <v>0.02075932596926694</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01932663290072533</v>
+        <v>0.01932663290072536</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02745605649512762</v>
+        <v>0.02745605649512765</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02925117027654306</v>
+        <v>0.029251170276543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09422252175277214</v>
+        <v>0.09155858124474309</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02978760127000919</v>
+        <v>0.02978760127000929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.034823600519741</v>
+        <v>0.03586100149578629</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04849535326270258</v>
+        <v>0.04849535326270275</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03142948800131561</v>
+        <v>0.03142948800131563</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05069530924629782</v>
+        <v>0.05069530924629777</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04051758392860299</v>
+        <v>0.04051758392860297</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02537881897176134</v>
+        <v>0.02537881897176143</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04441664034160048</v>
+        <v>0.04441664034160101</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03380149890321732</v>
+        <v>0.03380149890321742</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04676247716680035</v>
+        <v>0.04676247716680038</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07437041438354924</v>
+        <v>0.07437041438354926</v>
       </c>
       <c r="Q8" t="n">
         <v>0.03104254089721304</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03747005487718764</v>
+        <v>0.03747005487718781</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02543404082571107</v>
+        <v>0.02543404082571101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0570071972666823</v>
+        <v>0.05700719726668237</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05073720262419405</v>
+        <v>0.05137457896016862</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06612688472511646</v>
+        <v>0.06477197488849611</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1000094841765277</v>
+        <v>0.1000094841765275</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01930798952719665</v>
+        <v>0.01930798952719657</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09917528122702177</v>
+        <v>0.09917528122702178</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.06995095051594029</v>
+        <v>0.06485503522559523</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02879155343555688</v>
+        <v>0.02879155343555691</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03391704328330439</v>
+        <v>0.0339170432833044</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03521353430976202</v>
+        <v>0.03521353430976212</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04491113437469263</v>
+        <v>0.0449111343746926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04670624815610806</v>
+        <v>0.046706248156108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1116775996323371</v>
+        <v>0.1101610109044725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05146625530114382</v>
+        <v>0.03631792739816705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05227867839930602</v>
+        <v>0.05227868869444979</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06595043114226767</v>
+        <v>0.06595043114226777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04888456588088064</v>
+        <v>0.04888456588088065</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0681503871258628</v>
+        <v>0.06815038712586284</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05797266180816802</v>
+        <v>0.05797266180816799</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04283389685132635</v>
+        <v>0.04283389685132647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06187171822116543</v>
+        <v>0.0618717182211654</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05513472506821646</v>
+        <v>0.05513472506821639</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06920764164186717</v>
+        <v>0.06920764164186706</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09755042699395743</v>
+        <v>0.09755042699395736</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05448381160998297</v>
+        <v>0.05448381160998286</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05492513275675266</v>
+        <v>0.05492513275675273</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04288911870527613</v>
+        <v>0.04288911870527597</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07446227514624734</v>
+        <v>0.07446227514624719</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07126023023625851</v>
+        <v>0.07126023023625838</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08358196260468151</v>
+        <v>0.09116494946503242</v>
       </c>
       <c r="W9" t="n">
         <v>0.1174635788352982</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04229071667884622</v>
+        <v>0.04229071667884626</v>
       </c>
       <c r="Y9" t="n">
         <v>0.1116366501159871</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08740602839550536</v>
+        <v>0.08344420805962628</v>
       </c>
       <c r="AA9" t="n">
         <v>0.0462466313151219</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04614608778893818</v>
+        <v>0.04614608778893822</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05135595151607759</v>
+        <v>0.05135595151607757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04769212650795215</v>
+        <v>0.04769212650795212</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05158521577176857</v>
+        <v>0.05158521577176855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0525607113048852</v>
+        <v>0.05256071130488514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05800167515682829</v>
+        <v>0.05800167515682826</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05423201848557905</v>
+        <v>0.05423201848557894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05298275238688765</v>
+        <v>0.05298275238688754</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05213115304356637</v>
+        <v>0.0521311530435663</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05418336254817884</v>
+        <v>0.05418336254817883</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05497714508468828</v>
+        <v>0.05497714508468824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05419970014624115</v>
+        <v>0.05419970014624108</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05609466934162926</v>
+        <v>0.05609466934162922</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05358130669221427</v>
+        <v>0.05358130669221419</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0700264069500927</v>
+        <v>0.07002640695009268</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0581005863248108</v>
+        <v>0.05810058632481069</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05301387805338367</v>
+        <v>0.0530138780533836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05231545746726538</v>
+        <v>0.05231545746726524</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05491755157324395</v>
+        <v>0.05491755157324389</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05581672818970093</v>
+        <v>0.05581672818970077</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2183113284743772</v>
+        <v>0.2183113284743774</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05231119641916454</v>
+        <v>0.05231119641916449</v>
       </c>
       <c r="W2" t="n">
         <v>0.2371478299067226</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05461928309826792</v>
+        <v>0.05461928309826788</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05400788585817793</v>
+        <v>0.0540078858581779</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1979646475575594</v>
+        <v>0.1979646475575593</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05209292221232743</v>
+        <v>0.05209292221232725</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05329412839015948</v>
+        <v>0.05329412839015947</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02300578572167103</v>
+        <v>0.02300578572167108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01842012141216426</v>
+        <v>0.01842012141216409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02464356821074958</v>
+        <v>0.02464356821074959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03156774045971157</v>
+        <v>0.03156774045971152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07048801965666823</v>
+        <v>0.07048801965666819</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04339811887326323</v>
+        <v>0.04339811887326307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03466598659536713</v>
+        <v>0.03466598659536714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02855014848564615</v>
+        <v>0.02855014848564627</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04312425375391452</v>
+        <v>0.04312425375391451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04872756429475764</v>
+        <v>0.04872756429475762</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04319777130449824</v>
+        <v>0.04319777130449836</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05668585053734732</v>
+        <v>0.05668585053734738</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03891265200073141</v>
+        <v>0.03891265200073132</v>
       </c>
       <c r="O3" t="n">
         <v>0.1106951633868654</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07085629885281729</v>
+        <v>0.07085629885281719</v>
       </c>
       <c r="Q3" t="n">
         <v>0.03481272726272187</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02988011928421848</v>
+        <v>0.02988011928421846</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0482800918968501</v>
+        <v>0.04828009189685013</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05492085221344346</v>
+        <v>0.05492085221344342</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3172016314701545</v>
+        <v>0.3172016314701546</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02978371752513687</v>
+        <v>0.02978371752513688</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3499344684522137</v>
+        <v>0.3499344684522135</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0462655728533994</v>
+        <v>0.04626557285339938</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04195029452357572</v>
+        <v>0.04195029452357563</v>
       </c>
       <c r="Z3" t="n">
         <v>0.2685341493860686</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02826900436895121</v>
+        <v>0.02826900436895122</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03691282434531972</v>
+        <v>0.03691282434531976</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00789690340106251</v>
+        <v>0.00789690340106252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.010881397096614</v>
+        <v>0.01088139709661391</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01048654863585986</v>
+        <v>0.01048654863585996</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02150521943252842</v>
+        <v>0.02150521943252855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08296340910725783</v>
+        <v>0.08296340910725787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04038340287775318</v>
+        <v>0.0403834028777534</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02627236760223545</v>
+        <v>0.02627236760223554</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01665316126436897</v>
+        <v>0.01665316126436905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.039919658691443</v>
+        <v>0.03991965869144302</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04879995058986262</v>
+        <v>0.04879995058986272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04001835236776115</v>
+        <v>0.04001835236776127</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06114363763333302</v>
+        <v>0.06114363763333309</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O4" t="n">
         <v>0.12597752491158</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08408065625100532</v>
+        <v>0.08408065625100528</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02662394632382238</v>
+        <v>0.0266239463238223</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01873496451427263</v>
+        <v>0.01873496451427276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04812681446372895</v>
+        <v>0.04812681446372894</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05828342798829027</v>
+        <v>0.05828342798829031</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04608176413705911</v>
+        <v>0.04608176413705906</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01925812855248242</v>
+        <v>0.01925812855248244</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04958598119983718</v>
+        <v>0.04958598119983722</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0447577348285975</v>
+        <v>0.04475773482859759</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03742329654051815</v>
+        <v>0.03742329654051813</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01522554955402957</v>
+        <v>0.01522554955402966</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01622132643847349</v>
+        <v>0.01622132643847366</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02981802043760632</v>
+        <v>0.02981802043760649</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01625649536466131</v>
+        <v>0.01625649536466141</v>
       </c>
       <c r="C5" t="n">
         <v>0.06886012431678827</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06284223499814331</v>
+        <v>0.06284223499814325</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2380392905695315</v>
+        <v>0.238039290569532</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3705542791688</v>
+        <v>1.370554279168798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5212361742673214</v>
+        <v>0.5212361742673212</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3669825901604908</v>
+        <v>0.3669825901604911</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1771941990012255</v>
+        <v>0.1771941990012251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5496365551586223</v>
+        <v>0.5496365551586216</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6760250633090598</v>
+        <v>0.6760250633090589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5304870592663203</v>
+        <v>0.5304870592663199</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9638837862354689</v>
+        <v>0.9638837862354679</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O5" t="n">
-        <v>1.854364798054283</v>
+        <v>1.854364798054281</v>
       </c>
       <c r="P5" t="n">
-        <v>1.215333619287994</v>
+        <v>1.215333619287988</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3341242293760341</v>
+        <v>0.3341242293760337</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2215705269826592</v>
+        <v>0.2215705269826594</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6526405858359859</v>
+        <v>0.6526405858359837</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9479924697708952</v>
+        <v>0.9479924697708962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6217426584466347</v>
+        <v>0.6217426584466327</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1870926764782083</v>
+        <v>0.1870926764782086</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7516232757962933</v>
+        <v>0.7516232757962934</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6522537684379885</v>
+        <v>0.6522537684379843</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5551368044461489</v>
+        <v>0.5551368044461478</v>
       </c>
       <c r="Z5" t="n">
         <v>0.1273454045945403</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1652610432592665</v>
+        <v>0.1652610432592668</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4343767603006611</v>
+        <v>0.4343767603006624</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739862814188994</v>
+        <v>1.777531555333758</v>
       </c>
       <c r="C6" t="n">
-        <v>6.742847307884541</v>
+        <v>1.780516049029311</v>
       </c>
       <c r="D6" t="n">
-        <v>6.74245245942379</v>
+        <v>6.742452459423792</v>
       </c>
       <c r="E6" t="n">
-        <v>6.753471130220467</v>
+        <v>1.791139871365224</v>
       </c>
       <c r="F6" t="n">
-        <v>6.814929319895188</v>
+        <v>1.852598061039954</v>
       </c>
       <c r="G6" t="n">
-        <v>1.810018054810447</v>
+        <v>6.772349313665681</v>
       </c>
       <c r="H6" t="n">
-        <v>1.795907019534932</v>
+        <v>6.758238278390166</v>
       </c>
       <c r="I6" t="n">
-        <v>1.786287813197064</v>
+        <v>6.748619072052306</v>
       </c>
       <c r="J6" t="n">
-        <v>1.809554310624135</v>
+        <v>6.771885569479376</v>
       </c>
       <c r="K6" t="n">
-        <v>6.780765861377782</v>
+        <v>1.818434602522559</v>
       </c>
       <c r="L6" t="n">
-        <v>1.809653004300457</v>
+        <v>6.771984263155688</v>
       </c>
       <c r="M6" t="n">
-        <v>1.830778289566027</v>
+        <v>6.793109548421269</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O6" t="n">
-        <v>6.858463589740738</v>
+        <v>6.85846358974074</v>
       </c>
       <c r="P6" t="n">
-        <v>1.751468474041534</v>
+        <v>6.816564344486061</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.758589857111759</v>
+        <v>6.758589857111757</v>
       </c>
       <c r="R6" t="n">
-        <v>1.788369616446967</v>
+        <v>6.750700875302212</v>
       </c>
       <c r="S6" t="n">
-        <v>1.817761466396423</v>
+        <v>6.780092725251661</v>
       </c>
       <c r="T6" t="n">
-        <v>6.790249338776229</v>
+        <v>1.827918079920986</v>
       </c>
       <c r="U6" t="n">
-        <v>1.816144841274391</v>
+        <v>6.778476100129628</v>
       </c>
       <c r="V6" t="n">
-        <v>1.788892780485177</v>
+        <v>6.751224039340417</v>
       </c>
       <c r="W6" t="n">
         <v>1.909413558208042</v>
       </c>
       <c r="X6" t="n">
-        <v>1.814392386761291</v>
+        <v>1.814392386761293</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.884970654671121</v>
+        <v>1.884970654671127</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.747191460341959</v>
+        <v>1.784860201486724</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.785855978371167</v>
+        <v>1.785855978371169</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.799499526058623</v>
+        <v>1.799499526058622</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01062181928233864</v>
+        <v>0.01062181928233875</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01360631297789017</v>
+        <v>0.01360631297789009</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01321146451713603</v>
+        <v>0.01321146451713614</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02423013531380463</v>
+        <v>0.02423013531380473</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08568832498853389</v>
+        <v>0.08568832498853404</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04310831875902926</v>
+        <v>0.04310831875902954</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02899728348351166</v>
+        <v>0.02899728348351165</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01937807714564512</v>
+        <v>0.01937807714564523</v>
       </c>
       <c r="J7" t="n">
         <v>0.04264457457271922</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05152486647113881</v>
+        <v>0.05152486647113896</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0427432682490373</v>
+        <v>0.04274326824903741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06386855351460921</v>
+        <v>0.06386855351460928</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1287023873601206</v>
+        <v>0.1287023873601207</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08680551869954575</v>
+        <v>0.08680551869954574</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02934886220509847</v>
+        <v>0.02934886220509851</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0214598803955488</v>
+        <v>0.02145988039554891</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0508517303450051</v>
+        <v>0.05085173034500513</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06100834386956647</v>
+        <v>0.06100834386956646</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04917522807669551</v>
+        <v>0.04917522807669552</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02198304443375857</v>
+        <v>0.02198304443375859</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05231089708111332</v>
+        <v>0.05231089708111342</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04748265070987376</v>
+        <v>0.04748265070987371</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04057663762643049</v>
+        <v>0.04057663762643052</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01795046543530574</v>
+        <v>0.01795046543530581</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01894624231974966</v>
+        <v>0.01894624231974978</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03254293631888249</v>
+        <v>0.03254293631888269</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01335716900768116</v>
+        <v>0.01335716900768132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0205846213103335</v>
+        <v>0.02058462131033353</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02018977284957939</v>
+        <v>0.02018977284957957</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03120844364624792</v>
+        <v>0.0289491933488455</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08908467807556486</v>
+        <v>0.08908467807556487</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0500866270914727</v>
+        <v>0.05096643219841858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03597559181595492</v>
+        <v>0.03597559181595508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02635638547808849</v>
+        <v>0.02635638547808866</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04962288290516251</v>
+        <v>0.0496228829051625</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0585031748035821</v>
+        <v>0.0585031748035823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04972157658148067</v>
+        <v>0.0497215765814808</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07084686184705249</v>
+        <v>0.0708468618470576</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O8" t="n">
         <v>0.1332955928825419</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09117716960249755</v>
+        <v>0.09117716960249768</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03125037372526997</v>
+        <v>0.03125037372527006</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02843818872799213</v>
+        <v>0.02843818872799231</v>
       </c>
       <c r="S8" t="n">
         <v>0.05783003867744849</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06798665220200979</v>
+        <v>0.06798665220200988</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05355898458846899</v>
+        <v>0.05409612017582094</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02896135276620191</v>
+        <v>0.02775055236940015</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05929003926946476</v>
+        <v>0.05929003926946488</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0497730378129496</v>
+        <v>0.04977303781294948</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.05169431138573971</v>
+        <v>0.05169431138573988</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0249287737677491</v>
+        <v>0.02060700002681502</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02592455065219303</v>
+        <v>0.02592455065219318</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04395336970027248</v>
+        <v>0.04395336970027252</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02361148620420015</v>
+        <v>0.02361148620420005</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03127862985126593</v>
+        <v>0.03127862985126594</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03088378139051189</v>
+        <v>0.03088378139051185</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04190245218718051</v>
+        <v>0.04082171287395146</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1033606418619098</v>
+        <v>0.09256586046641016</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0607806356324052</v>
+        <v>0.06078063198629722</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04666960035688753</v>
+        <v>0.04666960035688739</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03705039401902101</v>
+        <v>0.03705039401902097</v>
       </c>
       <c r="J9" t="n">
         <v>0.06031689144609498</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06919718334451466</v>
+        <v>0.0691971833445147</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06041558512241316</v>
+        <v>0.06041558512241312</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08154087038798509</v>
+        <v>0.08154087038798503</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4734777156772466</v>
+        <v>0.4734777156772439</v>
       </c>
       <c r="O9" t="n">
-        <v>0.147926576874334</v>
+        <v>0.1479265768743341</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1063672030597538</v>
+        <v>0.106367203059754</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0470211754323665</v>
+        <v>0.04702117543236651</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0391321972689247</v>
+        <v>0.03913219726892474</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06852404721838101</v>
+        <v>0.068524047218381</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07868066074294226</v>
+        <v>0.07868066074294239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06690742209634769</v>
+        <v>0.06690742209634762</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03965536130713439</v>
+        <v>0.04505902109038108</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06998321395448923</v>
+        <v>0.0699832139544892</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06515496758324953</v>
+        <v>0.0651549675832494</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05824895449980631</v>
+        <v>0.05824895449980634</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03562278230868149</v>
+        <v>0.03279955933756983</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03661855919312548</v>
+        <v>0.03661855919312554</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05021525319225837</v>
+        <v>0.05021525319225836</v>
       </c>
     </row>
   </sheetData>
@@ -2306,52 +2306,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05235143385993508</v>
+        <v>0.05235143385993509</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04900745160428303</v>
+        <v>0.04900745160428304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05245354864310587</v>
+        <v>0.05245354864310585</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05800278621248216</v>
+        <v>0.05800278621248221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05325222246388575</v>
+        <v>0.05325222246388581</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05312416637538395</v>
+        <v>0.05312416637538398</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05453006510080554</v>
+        <v>0.05453006510080555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05269789651306738</v>
+        <v>0.05269789651306735</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0544317759184697</v>
+        <v>0.05443177591846973</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05341361134424873</v>
+        <v>0.05341361134424869</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05238768462327512</v>
+        <v>0.05238768462327514</v>
       </c>
       <c r="M2" t="n">
         <v>0.05350422140764217</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05325754838989964</v>
+        <v>0.05325754838989961</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06410901643632545</v>
+        <v>0.0641090164363254</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05671509729809645</v>
+        <v>0.05671509729809648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0545866211717103</v>
+        <v>0.05458662117171032</v>
       </c>
       <c r="R2" t="n">
         <v>0.05283776846497273</v>
@@ -2360,13 +2360,13 @@
         <v>0.05248141590577368</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05474201501073939</v>
+        <v>0.05474201501073938</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2193219891599755</v>
+        <v>0.2193219891599754</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05646877712404481</v>
+        <v>0.05646877712404483</v>
       </c>
       <c r="W2" t="n">
         <v>0.2418283004362837</v>
@@ -2375,16 +2375,16 @@
         <v>0.05247268270900605</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05869395387384784</v>
+        <v>0.05869395387384788</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2051453525470995</v>
+        <v>0.2051453525470996</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05275450808016538</v>
+        <v>0.05275450808016543</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0527291801725509</v>
+        <v>0.05272918017255088</v>
       </c>
     </row>
     <row r="3">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02400593747347987</v>
+        <v>0.02400593747347993</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02125070214473235</v>
+        <v>0.02125070214473236</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0247399530338739</v>
+        <v>0.02473995303387399</v>
       </c>
       <c r="E3" t="n">
         <v>0.06432731721445098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03045863962048509</v>
+        <v>0.03045863962048511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02950449927394495</v>
+        <v>0.029504499273945</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03964100276886805</v>
+        <v>0.03964100276886808</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02649128496071644</v>
+        <v>0.02649128496071649</v>
       </c>
       <c r="J3" t="n">
         <v>0.03882128591381363</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03157996421032756</v>
+        <v>0.03157996421032764</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02426562805120916</v>
+        <v>0.02426562805120924</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03247925315175498</v>
+        <v>0.03247925315175501</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0304833167485877</v>
+        <v>0.03048331674858776</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07670513645603445</v>
+        <v>0.07670513645603444</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05504861795047623</v>
+        <v>0.05504861795047633</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03998402561979492</v>
+        <v>0.03998402561979493</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02749647137799265</v>
+        <v>0.02749647137799268</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02493138347895375</v>
+        <v>0.0249313834789538</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04112084497271715</v>
+        <v>0.0411208449727172</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3130439823228523</v>
+        <v>0.3130439823228524</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05322986608679051</v>
+        <v>0.05322986608679056</v>
       </c>
       <c r="W3" t="n">
-        <v>0.370957644882756</v>
+        <v>0.3709576448827557</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02487577039566575</v>
+        <v>0.02487577039566577</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06925857660399709</v>
+        <v>0.06925857660399704</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2978321261596272</v>
+        <v>0.2978321261596271</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02688485390349974</v>
+        <v>0.02688485390349976</v>
       </c>
       <c r="AB3" t="n">
         <v>0.02698248123121027</v>
@@ -2485,22 +2485,22 @@
         <v>0.01159352420449188</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01722538605802365</v>
+        <v>0.01722538605802366</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01274695765552655</v>
+        <v>0.01274695765552657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07542814877703548</v>
+        <v>0.07542814877703535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02176834586934523</v>
+        <v>0.02176834586934522</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02032189344100614</v>
+        <v>0.02032189344100612</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03620216629000942</v>
+        <v>0.03620216629000944</v>
       </c>
       <c r="I4" t="n">
         <v>0.01550697925231565</v>
@@ -2509,22 +2509,22 @@
         <v>0.03520414474441786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02359130751559795</v>
+        <v>0.02359130751559797</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01200299325259253</v>
+        <v>0.01200299325259255</v>
       </c>
       <c r="M4" t="n">
         <v>0.02500662059806242</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02182850465371877</v>
+        <v>0.02182850465371876</v>
       </c>
       <c r="O4" t="n">
         <v>0.08064910536258903</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06088311012288216</v>
+        <v>0.06088311012288215</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03684099312795695</v>
@@ -2533,31 +2533,31 @@
         <v>0.01708689729336351</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01306173120693386</v>
+        <v>0.01306173120693391</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03859623802448782</v>
+        <v>0.03859623802448783</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03972263662847163</v>
+        <v>0.03972263662847166</v>
       </c>
       <c r="V4" t="n">
         <v>0.05885073624002669</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08194837121677156</v>
+        <v>0.0819483712167715</v>
       </c>
       <c r="X4" t="n">
         <v>0.01296308573197451</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08368067087590969</v>
+        <v>0.08368067087590966</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05625791288910249</v>
+        <v>0.05625791288910251</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01614643294529562</v>
+        <v>0.01614643294529561</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01633617269458106</v>
@@ -2570,82 +2570,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02779469454024315</v>
+        <v>0.02779469454024236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1373151328460466</v>
+        <v>0.1373151328460463</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05250529625405471</v>
+        <v>0.05250529625405482</v>
       </c>
       <c r="E5" t="n">
         <v>1.22776408729117</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2333761735731734</v>
+        <v>0.2333761735731735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1836707705835698</v>
+        <v>0.1836707705835703</v>
       </c>
       <c r="H5" t="n">
         <v>0.5409580820324513</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1088120518014587</v>
+        <v>0.1088120518014586</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4543288540163238</v>
+        <v>0.4543288540163243</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2508730746583475</v>
+        <v>0.2508730746583471</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03607473580436775</v>
+        <v>0.03607473580436792</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2997189912110794</v>
+        <v>0.2997189912110799</v>
       </c>
       <c r="N5" t="n">
-        <v>0.520652678215655</v>
+        <v>0.5206526782156532</v>
       </c>
       <c r="O5" t="n">
         <v>1.194381353632407</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9035844221858983</v>
+        <v>0.9035844221858976</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5193226497958369</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1425298517583374</v>
+        <v>0.1425298517583375</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05430833238131816</v>
+        <v>0.05430833238131882</v>
       </c>
       <c r="T5" t="n">
-        <v>0.567952652134139</v>
+        <v>0.5679526521341388</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5381013447794913</v>
+        <v>0.5381013447794899</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8179392505256184</v>
+        <v>0.817939250525617</v>
       </c>
       <c r="W5" t="n">
         <v>1.365339852442644</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0561783703505063</v>
+        <v>0.05617837035050651</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37446782201767</v>
+        <v>1.374467822017672</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8265446744628961</v>
+        <v>0.8265446744628944</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1150795146031897</v>
+        <v>0.1150795146031898</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1297155196030829</v>
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.237972647355032</v>
+        <v>1.912766758513746</v>
       </c>
       <c r="C6" t="n">
-        <v>7.243604509208563</v>
+        <v>7.243604509208565</v>
       </c>
       <c r="D6" t="n">
-        <v>1.913920191964781</v>
+        <v>7.239126080806066</v>
       </c>
       <c r="E6" t="n">
         <v>1.976601383086291</v>
       </c>
       <c r="F6" t="n">
-        <v>7.248147469019878</v>
+        <v>1.922941580178599</v>
       </c>
       <c r="G6" t="n">
-        <v>7.246701016591538</v>
+        <v>1.921495127750262</v>
       </c>
       <c r="H6" t="n">
-        <v>1.937375400599264</v>
+        <v>7.262581289440543</v>
       </c>
       <c r="I6" t="n">
-        <v>1.916680213561571</v>
+        <v>1.916680213561573</v>
       </c>
       <c r="J6" t="n">
-        <v>7.261583267894951</v>
+        <v>7.26158326789495</v>
       </c>
       <c r="K6" t="n">
-        <v>1.924764541824852</v>
+        <v>7.249970430666129</v>
       </c>
       <c r="L6" t="n">
-        <v>1.913176227561847</v>
+        <v>1.913176227561848</v>
       </c>
       <c r="M6" t="n">
         <v>1.926179854907317</v>
       </c>
       <c r="N6" t="n">
-        <v>1.922826163402174</v>
+        <v>1.922826163402173</v>
       </c>
       <c r="O6" t="n">
-        <v>7.307452908335805</v>
+        <v>7.307452908335804</v>
       </c>
       <c r="P6" t="n">
-        <v>7.287686672201581</v>
+        <v>7.287686672201578</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93801422743721</v>
+        <v>7.263220116278496</v>
       </c>
       <c r="R6" t="n">
-        <v>1.918260131602618</v>
+        <v>7.243466020443903</v>
       </c>
       <c r="S6" t="n">
-        <v>1.914234965516188</v>
+        <v>7.239440854357469</v>
       </c>
       <c r="T6" t="n">
-        <v>7.264975361175025</v>
+        <v>1.939769472333744</v>
       </c>
       <c r="U6" t="n">
-        <v>7.265656294368083</v>
+        <v>1.94045040552681</v>
       </c>
       <c r="V6" t="n">
-        <v>7.285229859390559</v>
+        <v>7.285229859390562</v>
       </c>
       <c r="W6" t="n">
-        <v>7.308752063907008</v>
+        <v>7.308752063907009</v>
       </c>
       <c r="X6" t="n">
-        <v>1.914136320041227</v>
+        <v>7.239342208882511</v>
       </c>
       <c r="Y6" t="n">
         <v>2.067560862034366</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.957431147198357</v>
+        <v>7.282637036039643</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.242525556095832</v>
+        <v>1.91731966725455</v>
       </c>
       <c r="AB6" t="n">
         <v>1.917162532030277</v>
@@ -2749,76 +2749,76 @@
         <v>0.01488301905311738</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02051488090664914</v>
+        <v>0.02051488090664916</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01603645250415205</v>
+        <v>0.01603645250415207</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07871764362566079</v>
+        <v>0.07871764362566078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02505784071797072</v>
+        <v>0.02505784071797073</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02361138828963163</v>
+        <v>0.0236113882896316</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03949166113863489</v>
+        <v>0.03949166113863493</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01879647410094114</v>
+        <v>0.01879647410094115</v>
       </c>
       <c r="J7" t="n">
         <v>0.03849363959304337</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02688080236422347</v>
+        <v>0.02688080236422345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01529248810121803</v>
+        <v>0.01529248810121804</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02829611544668793</v>
+        <v>0.02829611544668791</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02511799950234426</v>
+        <v>0.02511799950234427</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08393844849073048</v>
+        <v>0.08393844849073047</v>
       </c>
       <c r="P7" t="n">
         <v>0.06417245325102358</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04013048797658246</v>
+        <v>0.04013048797658245</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02037639214198902</v>
+        <v>0.02037639214198901</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01635122605555939</v>
+        <v>0.01635122605555942</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04188573287311328</v>
+        <v>0.04188573287311329</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04258192512133795</v>
+        <v>0.04258192512133797</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0621402310886522</v>
+        <v>0.06214023108865217</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08523786606539714</v>
+        <v>0.08523786606539703</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0162525805806</v>
+        <v>0.01625258058060001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08652470031361895</v>
+        <v>0.08652470031361882</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05954740773772799</v>
+        <v>0.05954740773772802</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01943592779392111</v>
@@ -2840,79 +2840,79 @@
         <v>0.02752296117910178</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02304453277660467</v>
+        <v>0.0230445327766047</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08572572389811341</v>
+        <v>0.0833544557271651</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02830636567528809</v>
+        <v>0.0283063656752881</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03061946856208427</v>
+        <v>0.03154289605887983</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04649974141108752</v>
+        <v>0.0464997414110876</v>
       </c>
       <c r="I8" t="n">
         <v>0.02580455437339377</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04550171986549598</v>
+        <v>0.045501719865496</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03388888263667611</v>
+        <v>0.03388888263667614</v>
       </c>
       <c r="L8" t="n">
         <v>0.02230056837367065</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03530419571914056</v>
+        <v>0.03530419571913906</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02867400208602898</v>
+        <v>0.02867400208602896</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08844326371353421</v>
+        <v>0.0884432637135342</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06844472876024917</v>
+        <v>0.06844472876024919</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04181005431438374</v>
+        <v>0.04181005431438375</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02738447241444165</v>
+        <v>0.02738447241444162</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02335930632801201</v>
+        <v>0.02335930632801204</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04889381314556594</v>
+        <v>0.04889381314556593</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04684561169201435</v>
+        <v>0.04741307716845119</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06914831136110484</v>
+        <v>0.06794432119507117</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09224682153729512</v>
+        <v>0.09224682153729515</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01834030368283333</v>
+        <v>0.01834030368283336</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09798105864121164</v>
+        <v>0.09798105864121162</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.06655548801018064</v>
+        <v>0.0620194326089198</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02644400806637373</v>
+        <v>0.02644400806637372</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03128562594958726</v>
+        <v>0.03128562594958723</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03011246318732041</v>
+        <v>0.03011246318732042</v>
       </c>
       <c r="C9" t="n">
         <v>0.04118789547342244</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03670946707092531</v>
+        <v>0.03670946707092533</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09939065819243409</v>
+        <v>0.09813431201630603</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04573085528474398</v>
+        <v>0.03318192672119012</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04428440285640489</v>
+        <v>0.04428441283527682</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06016467570540816</v>
+        <v>0.06016467570540819</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0394694886677144</v>
+        <v>0.03946948866771442</v>
       </c>
       <c r="J9" t="n">
         <v>0.05916665415981665</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04755381693099674</v>
+        <v>0.04755381693099675</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0359655026679913</v>
+        <v>0.03596550266799134</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04896913001346121</v>
+        <v>0.04896913001346123</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0457910140691175</v>
+        <v>0.04579101406911752</v>
       </c>
       <c r="O9" t="n">
         <v>0.1064156201774524</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08704196299037546</v>
+        <v>0.08704196299037541</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06080351252222766</v>
+        <v>0.06080351252222765</v>
       </c>
       <c r="R9" t="n">
         <v>0.0410494067087623</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03702424062233265</v>
+        <v>0.03702424062233271</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06255874743988657</v>
+        <v>0.0625587474398866</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06323968063295408</v>
+        <v>0.06323968063295413</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08281324565542553</v>
+        <v>0.08909502212057183</v>
       </c>
       <c r="W9" t="n">
         <v>0.1059108806321704</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03692559514737329</v>
+        <v>0.03692559514737331</v>
       </c>
       <c r="Y9" t="n">
         <v>0.1071977148803921</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0802204223045013</v>
+        <v>0.07693843735733107</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04010894236069439</v>
+        <v>0.04010894236069441</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04029868210997986</v>
+        <v>0.04029868210997985</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05119234375408987</v>
+        <v>0.0511923437540899</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04763770281157614</v>
+        <v>0.04763770281157624</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05124014604808498</v>
+        <v>0.05124014604808502</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05419623881684752</v>
+        <v>0.05419623881684758</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05463800393394396</v>
+        <v>0.05463800393394402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0516832454205521</v>
+        <v>0.05168324542055212</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05312384100749783</v>
+        <v>0.05312384100749787</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05116560056256109</v>
+        <v>0.0511656005625611</v>
       </c>
       <c r="J2" t="n">
         <v>0.05267954093922524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05114136240850367</v>
+        <v>0.05114136240850365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05105436733448004</v>
+        <v>0.0510543673344801</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05203962381486717</v>
+        <v>0.05203962381486723</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05185021114771964</v>
+        <v>0.05185021114771966</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06626255440187506</v>
+        <v>0.06626255440187513</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05503431493931516</v>
+        <v>0.05503431493931527</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05537944425289683</v>
+        <v>0.05537944425289687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05158663436950713</v>
+        <v>0.05158663436950717</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05117266130352999</v>
+        <v>0.05117266130353006</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0546658716722995</v>
+        <v>0.05466587167229957</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2169750780984994</v>
+        <v>0.2169750780984996</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05415218083008102</v>
+        <v>0.05415218083008105</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2387280474613302</v>
+        <v>0.2387280474613304</v>
       </c>
       <c r="X2" t="n">
-        <v>0.051304570812354</v>
+        <v>0.05130457081235405</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05566113452388169</v>
+        <v>0.05566113452388176</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2011331829326758</v>
+        <v>0.2011331829326759</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05146738358843635</v>
+        <v>0.05146738358843636</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05136498338865177</v>
+        <v>0.0513649833886518</v>
       </c>
     </row>
     <row r="3">
@@ -3257,82 +3257,82 @@
         <v>0.02384769579505269</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01950890583039062</v>
+        <v>0.01950890583039064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.024197943556803</v>
+        <v>0.02419794355680306</v>
       </c>
       <c r="E3" t="n">
         <v>0.04528733097422024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0485022023720694</v>
+        <v>0.04850220237206941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0273377824364654</v>
+        <v>0.02733778243646543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03772329382316712</v>
+        <v>0.03772329382316719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02366565157105996</v>
+        <v>0.02366565157106</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03443815075414666</v>
+        <v>0.0344381507541467</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02348831780806574</v>
+        <v>0.02348831780806577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02286723212908741</v>
+        <v>0.02286723212908742</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03007840969820826</v>
+        <v>0.03007840969820828</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02855587266316362</v>
+        <v>0.02855587266316363</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09354441514175289</v>
+        <v>0.09354441514175306</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05116122990141875</v>
+        <v>0.05116122990141898</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05374392899896974</v>
+        <v>0.05374392899896975</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02668524442730331</v>
+        <v>0.02668524442730328</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02370823867012728</v>
+        <v>0.02370823867012749</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04872338591126271</v>
+        <v>0.04872338591126279</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3077525390133246</v>
+        <v>0.307752539013325</v>
       </c>
       <c r="V3" t="n">
         <v>0.04483893234557607</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3607757812351869</v>
+        <v>0.3607757812351871</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0246571961932157</v>
+        <v>0.02465719619321581</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05574026394498481</v>
+        <v>0.05574026394498482</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2835547195632572</v>
+        <v>0.2835547195632573</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02581631066059344</v>
+        <v>0.02581631066059349</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02529180771422947</v>
+        <v>0.02529180771422951</v>
       </c>
     </row>
     <row r="4">
@@ -3345,79 +3345,79 @@
         <v>0.01106053369422393</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01416739184638567</v>
+        <v>0.01416739184638568</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01160048259503987</v>
+        <v>0.01160048259503995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04499091028807151</v>
+        <v>0.0449909102880716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04998085050767072</v>
+        <v>0.04998085050767079</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01660549384283856</v>
+        <v>0.01660549384283857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03287768370410155</v>
+        <v>0.03287768370410153</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01075845704343007</v>
+        <v>0.01075845704343011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02796636114415665</v>
+        <v>0.0279663611441567</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0104846759432498</v>
+        <v>0.01048467594324987</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00950202656244222</v>
+        <v>0.009502026562442225</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02091042005058015</v>
+        <v>0.02091042005058017</v>
       </c>
       <c r="N4" t="n">
         <v>0.01849144853922466</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1040965608262806</v>
+        <v>0.1040965608262808</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05445736562540739</v>
+        <v>0.05445736562540784</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05835575998964055</v>
+        <v>0.05835575998964062</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0155142275780061</v>
+        <v>0.01551422757800612</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01083821136077555</v>
+        <v>0.0108382113607757</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05029562943218931</v>
+        <v>0.05029562943218938</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03248089711176258</v>
+        <v>0.03248089711176269</v>
       </c>
       <c r="V4" t="n">
         <v>0.04520963537167657</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06737178241382456</v>
+        <v>0.06737178241382444</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01232818994431483</v>
+        <v>0.01232818994431493</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06180273447719891</v>
+        <v>0.0618027344771989</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03638839971920824</v>
+        <v>0.03638839971920828</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01416723514774169</v>
+        <v>0.01416723514774175</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01336096587411163</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04644613962209262</v>
+        <v>0.04644613962209272</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1029146072681113</v>
+        <v>0.1029146072681114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06070171763724191</v>
+        <v>0.06070171763724296</v>
       </c>
       <c r="E5" t="n">
         <v>0.6469165311502593</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7672871400215726</v>
+        <v>0.7672871400215714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1375203092173385</v>
+        <v>0.1375203092173384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4791689768507008</v>
+        <v>0.4791689768506999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04567585036320367</v>
+        <v>0.0456758503632048</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3313584339500584</v>
+        <v>0.3313584339500591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03858197177177413</v>
+        <v>0.03858197177177513</v>
       </c>
       <c r="L5" t="n">
         <v>0.02109984722173362</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2371336233827216</v>
+        <v>0.2371336233827217</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3938455694775676</v>
+        <v>0.3938455694775696</v>
       </c>
       <c r="O5" t="n">
-        <v>1.501051827886849</v>
+        <v>1.50105182788685</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7586413357812763</v>
+        <v>0.758641335781282</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8895156028646699</v>
+        <v>0.8895156028646707</v>
       </c>
       <c r="R5" t="n">
         <v>0.1373833501627663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04304129897660977</v>
+        <v>0.04304129897660995</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7844058052889215</v>
+        <v>0.7844058052889237</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4075698647572485</v>
+        <v>0.4075698647572503</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5694124880700453</v>
+        <v>0.5694124880700452</v>
       </c>
       <c r="W5" t="n">
-        <v>1.050121901442329</v>
+        <v>1.050121901442328</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07328733826214659</v>
+        <v>0.07328733826214799</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9384830660772897</v>
+        <v>0.9384830660772878</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4426466056066009</v>
+        <v>0.4426466056066015</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1043170305770757</v>
+        <v>0.1043170305770769</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09832744085693297</v>
+        <v>0.09832744085693292</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.743404498327335</v>
+        <v>1.78189447581417</v>
       </c>
       <c r="C6" t="n">
-        <v>1.785001333966331</v>
+        <v>1.78500133396633</v>
       </c>
       <c r="D6" t="n">
-        <v>6.743944447228153</v>
+        <v>6.74394444722816</v>
       </c>
       <c r="E6" t="n">
         <v>1.815824852408018</v>
       </c>
       <c r="F6" t="n">
-        <v>1.820814792627617</v>
+        <v>6.782324815140783</v>
       </c>
       <c r="G6" t="n">
-        <v>6.748949458475953</v>
+        <v>1.787439435962785</v>
       </c>
       <c r="H6" t="n">
         <v>1.803711625824047</v>
       </c>
       <c r="I6" t="n">
-        <v>6.743102421676546</v>
+        <v>1.781592399163375</v>
       </c>
       <c r="J6" t="n">
-        <v>6.760310325777274</v>
+        <v>6.760310325777272</v>
       </c>
       <c r="K6" t="n">
-        <v>1.781318618063196</v>
+        <v>6.742828640576363</v>
       </c>
       <c r="L6" t="n">
-        <v>6.741845991195563</v>
+        <v>1.780335968682388</v>
       </c>
       <c r="M6" t="n">
-        <v>6.753254384683696</v>
+        <v>6.753254384683694</v>
       </c>
       <c r="N6" t="n">
         <v>1.789276663252452</v>
       </c>
       <c r="O6" t="n">
-        <v>6.836861186792305</v>
+        <v>1.874881775539508</v>
       </c>
       <c r="P6" t="n">
-        <v>6.787221135327254</v>
+        <v>6.787221135327251</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.79069972462276</v>
+        <v>6.790699724622761</v>
       </c>
       <c r="R6" t="n">
         <v>6.747858192211122</v>
       </c>
       <c r="S6" t="n">
-        <v>1.781672153480721</v>
+        <v>1.781672153480722</v>
       </c>
       <c r="T6" t="n">
-        <v>1.821129571552134</v>
+        <v>1.821129571552135</v>
       </c>
       <c r="U6" t="n">
-        <v>6.764559708452021</v>
+        <v>1.803049685938852</v>
       </c>
       <c r="V6" t="n">
         <v>6.777553600004792</v>
       </c>
       <c r="W6" t="n">
-        <v>6.800136428322591</v>
+        <v>1.928410239615256</v>
       </c>
       <c r="X6" t="n">
-        <v>1.78316213206426</v>
+        <v>1.783162132064261</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.909919627424361</v>
+        <v>1.90991962742436</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.768732364352327</v>
+        <v>1.807222341839154</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.785001177267687</v>
+        <v>6.746511199780857</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.784021501375305</v>
+        <v>1.784021501375306</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01361594668702945</v>
+        <v>0.01361594668702948</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0167228048391912</v>
+        <v>0.01672280483919122</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01415589558784539</v>
+        <v>0.01415589558784549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04754632328087711</v>
+        <v>0.04754632328087715</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05253626350047626</v>
+        <v>0.05253626350047624</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0191609068356441</v>
+        <v>0.01916090683564412</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03543309669690709</v>
+        <v>0.03543309669690708</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01331387003623559</v>
+        <v>0.01331387003623566</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03052177413696223</v>
+        <v>0.03052177413696226</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01304008893605532</v>
+        <v>0.01304008893605543</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01205743955524775</v>
+        <v>0.01205743955524776</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02346583304338569</v>
+        <v>0.0234658330433857</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02104686153203016</v>
+        <v>0.0210468615320302</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1066518619099579</v>
+        <v>0.106651861909958</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05701266670908487</v>
+        <v>0.05701266670908523</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06091117298244605</v>
+        <v>0.0609111729824461</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01806964057081164</v>
+        <v>0.01806964057081166</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01339362435358108</v>
+        <v>0.01339362435358125</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05285104242499484</v>
+        <v>0.05285104242499492</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03476390628292206</v>
+        <v>0.03476390628292219</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04776504836448214</v>
+        <v>0.04776504836448212</v>
       </c>
       <c r="W7" t="n">
         <v>0.06992719540663005</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01488360293712029</v>
+        <v>0.01488360293712046</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0640929941771472</v>
+        <v>0.06409299417714714</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03894381271201375</v>
+        <v>0.03894381271201383</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01672264814054724</v>
+        <v>0.01672264814054729</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01591637886691717</v>
+        <v>0.01591637886691718</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01571062711566832</v>
+        <v>0.01571062711566834</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02240839063535402</v>
+        <v>0.02240839063535403</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01984148138400823</v>
+        <v>0.01984148138400831</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05323190907703992</v>
+        <v>0.05131985789537843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05519036501674001</v>
+        <v>0.05519036501674002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02484649263180691</v>
+        <v>0.02559109025178586</v>
       </c>
       <c r="H8" t="n">
         <v>0.04111868249306991</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01899945583239844</v>
+        <v>0.01899945583239849</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03620735993312504</v>
+        <v>0.03620735993312507</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01872567473221806</v>
+        <v>0.01872567473221823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01774302535141055</v>
+        <v>0.01774302535141057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02915141883954848</v>
+        <v>0.02915141883954702</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02394889492112319</v>
+        <v>0.02394889492112322</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1103189515750736</v>
+        <v>0.1103189515750737</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06049225002662209</v>
+        <v>0.06049225002662238</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06230015854991269</v>
+        <v>0.06230015854991271</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02375522636697443</v>
+        <v>0.02375522636697446</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01907921014974387</v>
+        <v>0.01907921014974406</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05853662822115768</v>
+        <v>0.05853662822115774</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03824189170689506</v>
+        <v>0.03869853736594795</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0534506341606449</v>
+        <v>0.05246308365978315</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07561348691134696</v>
+        <v>0.07561348691134702</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01660170211231161</v>
+        <v>0.01660170211231181</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07333947136522355</v>
+        <v>0.07333947136522354</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.04462939850817653</v>
+        <v>0.04097179023051123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02240823393671004</v>
+        <v>0.02240823393671012</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02535296557931226</v>
+        <v>0.02535296557931228</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02436301013442425</v>
+        <v>0.02436301013442429</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0314256768686566</v>
+        <v>0.03142567686865663</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0288587676173108</v>
+        <v>0.0288587676173109</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06224919531034246</v>
+        <v>0.06133621559552842</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06723913552994161</v>
+        <v>0.05811990901058482</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03386377886510951</v>
+        <v>0.03386378506694613</v>
       </c>
       <c r="H9" t="n">
         <v>0.05013596872637249</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02801674206570102</v>
+        <v>0.02801674206570105</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04522464616642762</v>
+        <v>0.04522464616642765</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02774296096552071</v>
+        <v>0.02774296096552082</v>
       </c>
       <c r="L9" t="n">
         <v>0.02676031158471317</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03816870507285107</v>
+        <v>0.03816870507285108</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03574973356149554</v>
+        <v>0.03574973356149558</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1226658038900783</v>
+        <v>0.1226658038900784</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0733117182221923</v>
+        <v>0.0733117182221925</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07561405121374816</v>
+        <v>0.07561405121374817</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03277251260027703</v>
+        <v>0.03277251260027704</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02809649638304652</v>
+        <v>0.02809649638304666</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06755391445446027</v>
+        <v>0.06755391445446039</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04947402884117631</v>
+        <v>0.04947402884117637</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06246792039394748</v>
+        <v>0.06703284590902729</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08463006743609544</v>
+        <v>0.08463006743609548</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02958647496658584</v>
+        <v>0.02958647496658585</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.07879586620661265</v>
+        <v>0.07879586620661259</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05364668474147918</v>
+        <v>0.05126168639339556</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03142552017001261</v>
+        <v>0.03142552017001269</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03061925089638256</v>
+        <v>0.03061925089638258</v>
       </c>
     </row>
   </sheetData>
@@ -4026,13 +4026,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04955865337624058</v>
+        <v>0.04955865337624053</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04578556933925406</v>
+        <v>0.04578556933925401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05011900383672048</v>
+        <v>0.05011900383672049</v>
       </c>
       <c r="E2" t="n">
         <v>0.05028776957611272</v>
@@ -4044,7 +4044,7 @@
         <v>0.05002427434038705</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05131539801359265</v>
+        <v>0.05131539801359263</v>
       </c>
       <c r="I2" t="n">
         <v>0.05166079356014691</v>
@@ -4053,58 +4053,58 @@
         <v>0.05085205103802781</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05126754000349123</v>
+        <v>0.05126754000349119</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05114072177551886</v>
+        <v>0.05114072177551882</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05159539842929735</v>
+        <v>0.05159539842929734</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04992119320560125</v>
+        <v>0.04992119320560124</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06012219036226976</v>
+        <v>0.06012219036226973</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05226908202012879</v>
+        <v>0.05226908202012877</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05448181858885653</v>
+        <v>0.05448181858885654</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05059823823543562</v>
+        <v>0.05059823823543563</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05107622163962334</v>
+        <v>0.05107622163962333</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05323295386527795</v>
+        <v>0.05323295386527794</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2133048677904295</v>
+        <v>0.2133048677904296</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05022305843549667</v>
+        <v>0.05022305843549665</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2347456911701469</v>
+        <v>0.2347456911701473</v>
       </c>
       <c r="X2" t="n">
         <v>0.05007284683115331</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05047689912230485</v>
+        <v>0.05047689912230483</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1962822959993171</v>
+        <v>0.1962822959993168</v>
       </c>
       <c r="AA2" t="n">
         <v>0.04985911087389214</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04955802614708898</v>
+        <v>0.04955802614708894</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02328674586334169</v>
+        <v>0.02328674586334171</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01721691445350652</v>
+        <v>0.01721691445350653</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02729813334580147</v>
+        <v>0.02729813334580149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02847570548378381</v>
+        <v>0.02847570548378379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05876120867373569</v>
+        <v>0.05876120867373574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02659085405969776</v>
+        <v>0.02659085405969775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03592177031448008</v>
+        <v>0.03592177031448007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03834209378334899</v>
+        <v>0.038342093783349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03251144986903594</v>
+        <v>0.03251144986903596</v>
       </c>
       <c r="K3" t="n">
         <v>0.03544196037473013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03455418999924995</v>
+        <v>0.03455418999924996</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03783538810356524</v>
+        <v>0.03783538810356521</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0258922433950485</v>
+        <v>0.02589224339504851</v>
       </c>
       <c r="O3" t="n">
         <v>0.07216750572588136</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04252099354798188</v>
+        <v>0.04252099354798192</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05839173430281867</v>
+        <v>0.05839173430281868</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03076033273238978</v>
+        <v>0.03076033273238979</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03407623782977366</v>
+        <v>0.03407623782977367</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04961046791947084</v>
+        <v>0.0496104679194708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2973978355969518</v>
+        <v>0.2973978355969519</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02799459665788174</v>
+        <v>0.02799459665788173</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3487189098085826</v>
+        <v>0.3487189098085832</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0269674390251641</v>
+        <v>0.02696743902516414</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02985886101772343</v>
+        <v>0.02985886101772348</v>
       </c>
       <c r="Z3" t="n">
         <v>0.2679050109895053</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02544442445609795</v>
+        <v>0.02544442445609799</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02342132338821055</v>
+        <v>0.02342132338821054</v>
       </c>
     </row>
     <row r="4">
@@ -4202,82 +4202,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01073195766614993</v>
+        <v>0.01073195766614992</v>
       </c>
       <c r="C4" t="n">
         <v>0.01102020873113885</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01706137389121803</v>
+        <v>0.01706137389121805</v>
       </c>
       <c r="E4" t="n">
         <v>0.01896766055372924</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06675544836998508</v>
+        <v>0.06675544836998511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01599136065241069</v>
+        <v>0.01599136065241068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03057519648750189</v>
+        <v>0.03057519648750191</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03447659807563358</v>
+        <v>0.03447659807563357</v>
       </c>
       <c r="J4" t="n">
         <v>0.02543596743526444</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03003461824763376</v>
+        <v>0.03003461824763379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02860214802341867</v>
+        <v>0.02860214802341869</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03370640809542837</v>
+        <v>0.03370640809542833</v>
       </c>
       <c r="N4" t="n">
         <v>0.01482701181533999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07599160233058229</v>
+        <v>0.07599160233058228</v>
       </c>
       <c r="P4" t="n">
         <v>0.04134749605764563</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06634137351053737</v>
+        <v>0.06634137351053736</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02247454688342074</v>
+        <v>0.02247454688342073</v>
       </c>
       <c r="S4" t="n">
         <v>0.02787358931695061</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05223487195156069</v>
+        <v>0.05223487195156059</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01855278053540953</v>
+        <v>0.01855278053540952</v>
       </c>
       <c r="V4" t="n">
         <v>0.01886658244793683</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05134433334579752</v>
+        <v>0.05134433334579764</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01654000928006548</v>
+        <v>0.01654000928006549</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02102987203733635</v>
+        <v>0.0210298720373364</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01579432548172714</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0141257633194023</v>
+        <v>0.01412576331940232</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01093875513688091</v>
@@ -4290,25 +4290,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06463364552467345</v>
+        <v>0.06463364552467352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07418343467647105</v>
+        <v>0.07418343467647111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1828701883687111</v>
+        <v>0.1828701883687112</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2026367747678275</v>
+        <v>0.2026367747678278</v>
       </c>
       <c r="F5" t="n">
         <v>1.094862536988798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1477817340110609</v>
+        <v>0.147781734011061</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4658879788452144</v>
+        <v>0.4658879788452158</v>
       </c>
       <c r="I5" t="n">
         <v>0.5116836877341518</v>
@@ -4317,58 +4317,58 @@
         <v>0.3198363011762134</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3846850232998746</v>
+        <v>0.3846850232998753</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3683342163685777</v>
+        <v>0.3683342163685783</v>
       </c>
       <c r="M5" t="n">
         <v>0.4862197098629091</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1918722442124237</v>
+        <v>0.1918722442124238</v>
       </c>
       <c r="O5" t="n">
-        <v>1.087313915056428</v>
+        <v>1.087313915056429</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5490029648785965</v>
+        <v>0.5490029648785968</v>
       </c>
       <c r="Q5" t="n">
         <v>1.031653238987698</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3003141233497399</v>
+        <v>0.3003141233497406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3463217477357778</v>
+        <v>0.346321747735778</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8505328110367903</v>
+        <v>0.8505328110367895</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1956721066770177</v>
+        <v>0.1956721066770122</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1803565796906523</v>
+        <v>0.1803565796906526</v>
       </c>
       <c r="W5" t="n">
-        <v>0.793835571033998</v>
+        <v>0.7938355710339994</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1729911237589492</v>
+        <v>0.1729911237589503</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2576925268568269</v>
+        <v>0.2576925268568279</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1361190129573766</v>
+        <v>0.1361190129573767</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1315502855703002</v>
+        <v>0.1315502855703007</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.08013136056753026</v>
+        <v>0.08013136056753027</v>
       </c>
     </row>
     <row r="6">
@@ -4378,37 +4378,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.780291340863159</v>
+        <v>6.741345042744954</v>
       </c>
       <c r="C6" t="n">
         <v>1.780579591928148</v>
       </c>
       <c r="D6" t="n">
-        <v>1.786620757088227</v>
+        <v>1.786620757088228</v>
       </c>
       <c r="E6" t="n">
-        <v>1.788527043750739</v>
+        <v>6.749580745632532</v>
       </c>
       <c r="F6" t="n">
-        <v>1.836314831566994</v>
+        <v>1.836314831566993</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78555074384942</v>
+        <v>6.746604445731218</v>
       </c>
       <c r="H6" t="n">
-        <v>6.761188281566312</v>
+        <v>1.800134579684511</v>
       </c>
       <c r="I6" t="n">
-        <v>1.804035981272644</v>
+        <v>1.804035981272643</v>
       </c>
       <c r="J6" t="n">
-        <v>1.794995350632272</v>
+        <v>6.756049052514063</v>
       </c>
       <c r="K6" t="n">
-        <v>6.760647703326443</v>
+        <v>6.76064770332644</v>
       </c>
       <c r="L6" t="n">
-        <v>1.798161531220427</v>
+        <v>6.759215233102223</v>
       </c>
       <c r="M6" t="n">
         <v>1.803265791292437</v>
@@ -4417,46 +4417,46 @@
         <v>1.784390195185456</v>
       </c>
       <c r="O6" t="n">
-        <v>1.845554785700699</v>
+        <v>6.807047546331062</v>
       </c>
       <c r="P6" t="n">
-        <v>6.772401932446414</v>
+        <v>1.70866758196749</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.796954458589345</v>
+        <v>6.796954458589341</v>
       </c>
       <c r="R6" t="n">
-        <v>6.75308763196222</v>
+        <v>6.753087631962225</v>
       </c>
       <c r="S6" t="n">
-        <v>6.758486674395752</v>
+        <v>6.758486674395759</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82179425514857</v>
+        <v>6.782847957030363</v>
       </c>
       <c r="U6" t="n">
-        <v>6.749239959358734</v>
+        <v>1.788186257476942</v>
       </c>
       <c r="V6" t="n">
-        <v>6.749479667526741</v>
+        <v>1.788425965644946</v>
       </c>
       <c r="W6" t="n">
         <v>6.78240051021127</v>
       </c>
       <c r="X6" t="n">
-        <v>1.786099392477075</v>
+        <v>1.786099392477074</v>
       </c>
       <c r="Y6" t="n">
         <v>1.86815392715135</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.746407410560524</v>
+        <v>6.746407410560532</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.744738848398205</v>
+        <v>6.744738848398206</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78045353090406</v>
+        <v>1.780453530904061</v>
       </c>
     </row>
     <row r="7">
@@ -4466,19 +4466,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01276086673439796</v>
+        <v>0.01276086673439795</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01304911779938687</v>
+        <v>0.01304911779938688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01909028295946607</v>
+        <v>0.01909028295946606</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02099656962197728</v>
+        <v>0.02099656962197727</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0687843574382332</v>
+        <v>0.06878435743823318</v>
       </c>
       <c r="G7" t="n">
         <v>0.01802026972065872</v>
@@ -4487,61 +4487,61 @@
         <v>0.0326041055557499</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0365055071438816</v>
+        <v>0.03650550714388162</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02746487650351248</v>
+        <v>0.02746487650351247</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03206352731588179</v>
+        <v>0.03206352731588182</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03063105709166671</v>
+        <v>0.03063105709166673</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03573531716367634</v>
+        <v>0.03573531716367632</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01685592088358802</v>
+        <v>0.016855920883588</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07802046392497307</v>
+        <v>0.07802046392497301</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04337635765203642</v>
+        <v>0.04337635765203646</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0683702825787854</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02450345595166878</v>
+        <v>0.02450345595166877</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02990249838519867</v>
+        <v>0.02990249838519864</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05426378101980858</v>
+        <v>0.05426378101980855</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02059340864005825</v>
+        <v>0.02059340864005826</v>
       </c>
       <c r="V7" t="n">
         <v>0.02089549151618484</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05337324241404563</v>
+        <v>0.05337324241404565</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01856891834831351</v>
+        <v>0.01856891834831349</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02313287485010689</v>
+        <v>0.02313287485010696</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01782323454997518</v>
+        <v>0.01782323454997516</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01615467238765032</v>
+        <v>0.01615467238765033</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01296766420512894</v>
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01473456314113014</v>
+        <v>0.01473456314113013</v>
       </c>
       <c r="C8" t="n">
         <v>0.01817157317171366</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02421273833179288</v>
+        <v>0.02421273833179287</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02611902499430405</v>
+        <v>0.02444240372910705</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07124859369069067</v>
+        <v>0.07124859369069068</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02314272509298552</v>
+        <v>0.02379564077621449</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03772656092807668</v>
+        <v>0.03772656092807671</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04162796251620836</v>
+        <v>0.04162796251620839</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03258733187583929</v>
+        <v>0.03258733187583927</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03718598268820857</v>
+        <v>0.0371859826882086</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03575351246399355</v>
+        <v>0.0357535124639935</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04085777253600319</v>
+        <v>0.04085777253600108</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01953756127991307</v>
+        <v>0.01953756127991306</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08137290894021079</v>
+        <v>0.08137290894021078</v>
       </c>
       <c r="P8" t="n">
         <v>0.04656438388362585</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06972517598374817</v>
+        <v>0.06972517598374819</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02962591132399558</v>
+        <v>0.02962591132399556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03502495375752547</v>
+        <v>0.03502495375752548</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0593862363921355</v>
+        <v>0.05938623639213541</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02379530145140413</v>
+        <v>0.02419306941475881</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02601794688851164</v>
+        <v>0.02510406780479257</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05849631660080736</v>
+        <v>0.05849631660080738</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0202124017648981</v>
+        <v>0.02021240176489814</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03130343878994094</v>
+        <v>0.03130343878994102</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02294568992230198</v>
+        <v>0.01973844114296455</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02127712775997714</v>
+        <v>0.02127712775997713</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02137926160546758</v>
+        <v>0.02137926160546757</v>
       </c>
     </row>
     <row r="9">
@@ -4642,43 +4642,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01985043105676795</v>
+        <v>0.01985043105676794</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02292400947731196</v>
+        <v>0.02292400947731195</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02896517463739114</v>
+        <v>0.02896517463739113</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03087146129990235</v>
+        <v>0.03022861943693492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07865924911615822</v>
+        <v>0.07223830881442479</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02789516139858378</v>
+        <v>0.02789516182701503</v>
       </c>
       <c r="H9" t="n">
         <v>0.04247899723367498</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04638039882180665</v>
+        <v>0.04638039882180664</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03733976818143755</v>
+        <v>0.03733976818143753</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04193841899380686</v>
+        <v>0.04193841899380688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405059487695918</v>
+        <v>0.04050594876959179</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04561020884160148</v>
+        <v>0.04561020884160141</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02673081256151309</v>
+        <v>0.02673081256151308</v>
       </c>
       <c r="O9" t="n">
         <v>0.08881845748572471</v>
@@ -4687,40 +4687,40 @@
         <v>0.05437509961661584</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07824517468514183</v>
+        <v>0.07824517468514179</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03437834762959385</v>
+        <v>0.03437834762959383</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03977739006312372</v>
+        <v>0.0397773900631237</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06413867269773355</v>
+        <v>0.0641386726977337</v>
       </c>
       <c r="U9" t="n">
         <v>0.03053067502610516</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03077038319410993</v>
+        <v>0.03398458486905414</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06324813409197073</v>
+        <v>0.06324813409197079</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02844381002623857</v>
+        <v>0.02844381002623858</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03300776652803198</v>
+        <v>0.03300776652803201</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02769812622790026</v>
+        <v>0.02601882168359834</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02602956406557541</v>
+        <v>0.02602956406557543</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02284255588305401</v>
+        <v>0.022842555883054</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05476462004480829</v>
+        <v>0.05476462004480831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05112174510585898</v>
+        <v>0.05112174510585895</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05506081331632029</v>
+        <v>0.0550608133163203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06103762403830548</v>
+        <v>0.06103762403830547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05609639009151216</v>
+        <v>0.05609639009151215</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05714239924180282</v>
+        <v>0.05714239924180279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05566491574663515</v>
+        <v>0.05566491574663518</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05490277378320406</v>
+        <v>0.05490277378320403</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05849510050329135</v>
+        <v>0.05849510050329138</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05539092488481041</v>
+        <v>0.05539092488481036</v>
       </c>
       <c r="L2" t="n">
         <v>0.05488043762908965</v>
       </c>
       <c r="M2" t="n">
-        <v>0.059813685108851</v>
+        <v>0.05981368510885095</v>
       </c>
       <c r="N2" t="n">
         <v>0.05824158338655466</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0787166515645169</v>
+        <v>0.07871665156451688</v>
       </c>
       <c r="P2" t="n">
         <v>0.06330685032992169</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05962661072108812</v>
+        <v>0.05962661072108821</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05496075719334709</v>
+        <v>0.05496075719334706</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05496677650625372</v>
+        <v>0.05496677650625371</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05988616879709655</v>
+        <v>0.05988616879709657</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2229893791477368</v>
+        <v>0.2229893791477367</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05913268232325396</v>
+        <v>0.05913268232325398</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2472718602915497</v>
+        <v>0.2472718602915501</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05489241810879247</v>
+        <v>0.05489241810879256</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06258839687301873</v>
+        <v>0.06258839687301876</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2085488473118239</v>
+        <v>0.2085488473118235</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05499957003222156</v>
+        <v>0.05499957003222154</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05832310795411801</v>
+        <v>0.05832310795411799</v>
       </c>
     </row>
     <row r="3">
@@ -4974,16 +4974,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02614900832667232</v>
+        <v>0.02614900832667227</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02190532874652841</v>
+        <v>0.0219053287465284</v>
       </c>
       <c r="D3" t="n">
         <v>0.02827181386887816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07090440007417205</v>
+        <v>0.07090440007417202</v>
       </c>
       <c r="F3" t="n">
         <v>0.03567637788371768</v>
@@ -4992,67 +4992,67 @@
         <v>0.04298687527070839</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03261330025022231</v>
+        <v>0.03261330025022226</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02714291771155023</v>
+        <v>0.0271429177115502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0526583968263976</v>
+        <v>0.05265839682639769</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03061027602171925</v>
+        <v>0.03061027602171933</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02697381635605349</v>
+        <v>0.02697381635605348</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06213113416112792</v>
+        <v>0.06213113416112789</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05095452050228869</v>
+        <v>0.05095452050228868</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1364258114642597</v>
+        <v>0.1364258114642596</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08688431566729497</v>
+        <v>0.08688431566729492</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06080759680659635</v>
+        <v>0.06080759680659629</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02756056474932513</v>
+        <v>0.02756056474932514</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02757869413383934</v>
+        <v>0.02757869413383936</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06270089977204281</v>
+        <v>0.06270089977204284</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3235639677601994</v>
+        <v>0.3235639677601991</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05714478821671875</v>
+        <v>0.05714478821671882</v>
       </c>
       <c r="W3" t="n">
-        <v>0.393587144635402</v>
+        <v>0.3935871446354022</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02706616079584255</v>
+        <v>0.02706616079584256</v>
       </c>
       <c r="Y3" t="n">
         <v>0.08196258620286374</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3057985284199066</v>
+        <v>0.3057985284199067</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0278283097497822</v>
+        <v>0.02782830974978217</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0517083123850017</v>
+        <v>0.05170831238500168</v>
       </c>
     </row>
     <row r="4">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01605817351108134</v>
+        <v>0.01605817351108133</v>
       </c>
       <c r="C4" t="n">
         <v>0.01962240960958977</v>
@@ -5071,34 +5071,34 @@
         <v>0.01940381276844579</v>
       </c>
       <c r="E4" t="n">
-        <v>0.086914639342039</v>
+        <v>0.08691463934203897</v>
       </c>
       <c r="F4" t="n">
         <v>0.03110112883309078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04291628337360565</v>
+        <v>0.04291628337360556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02622742761970053</v>
+        <v>0.02622742761970056</v>
       </c>
       <c r="I4" t="n">
         <v>0.01761868354012102</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05830146734121568</v>
+        <v>0.0583014673412157</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02313257479336597</v>
+        <v>0.02313257479336596</v>
       </c>
       <c r="L4" t="n">
         <v>0.01736638640425983</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07313846826079044</v>
+        <v>0.07313846826079042</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05533207393826712</v>
+        <v>0.05533207393826711</v>
       </c>
       <c r="O4" t="n">
         <v>0.1629575783953481</v>
@@ -5107,22 +5107,22 @@
         <v>0.1125465942015126</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07097659482587493</v>
+        <v>0.07097659482587491</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01827363283137232</v>
+        <v>0.0182736328313723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01834162373967346</v>
+        <v>0.01834162373967345</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07390842269700393</v>
+        <v>0.0739084226970039</v>
       </c>
       <c r="U4" t="n">
         <v>0.05711216673411313</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06610428582627779</v>
+        <v>0.06610428582627767</v>
       </c>
       <c r="W4" t="n">
         <v>0.1182837729525474</v>
@@ -5131,16 +5131,16 @@
         <v>0.01750171143379663</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.104715730389806</v>
+        <v>0.1047157303898059</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06960923992011689</v>
+        <v>0.06960923992011694</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01871204170124805</v>
+        <v>0.01871204170124803</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.056388517886987</v>
+        <v>0.05638851788698701</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03885173956660029</v>
+        <v>0.03885173956660027</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1091205381967663</v>
+        <v>0.1091205381967662</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1070379410897503</v>
+        <v>0.1070379410897504</v>
       </c>
       <c r="E5" t="n">
         <v>1.370061827608238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3357738722841822</v>
+        <v>0.3357738722841847</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4730134311912925</v>
+        <v>0.4730134311912921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2527300977710522</v>
+        <v>0.2527300977710524</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07275090914764323</v>
+        <v>0.07275090914764321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7716001908149669</v>
+        <v>0.7716001908149662</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1677746678490457</v>
+        <v>0.1677746678490454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06259299091051945</v>
+        <v>0.06259299091051938</v>
       </c>
       <c r="M5" t="n">
-        <v>1.073735346376789</v>
+        <v>1.073735346376788</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7676180373436579</v>
+        <v>0.7676180373436583</v>
       </c>
       <c r="O5" t="n">
         <v>2.476293629864085</v>
       </c>
       <c r="P5" t="n">
-        <v>1.734765486956943</v>
+        <v>1.734765486956942</v>
       </c>
       <c r="Q5" t="n">
         <v>1.054062825211271</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08725721012279744</v>
+        <v>0.08725721012279741</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0747330972108483</v>
+        <v>0.07473309721084805</v>
       </c>
       <c r="T5" t="n">
-        <v>1.132201927010033</v>
+        <v>1.132201927010032</v>
       </c>
       <c r="U5" t="n">
-        <v>0.769113731650573</v>
+        <v>0.7691137316505728</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8727436585485721</v>
+        <v>0.8727436585485703</v>
       </c>
       <c r="W5" t="n">
-        <v>1.981320338200794</v>
+        <v>1.981320338200792</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0689553172686253</v>
+        <v>0.06895531726862497</v>
       </c>
       <c r="Y5" t="n">
         <v>1.695839454924724</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9345867814481765</v>
+        <v>0.9345867814481749</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09039431667307284</v>
+        <v>0.09039431667307275</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8506510957620295</v>
+        <v>0.8506510957620288</v>
       </c>
     </row>
     <row r="6">
@@ -5241,79 +5241,79 @@
         <v>1.917900814445127</v>
       </c>
       <c r="C6" t="n">
-        <v>7.247936091806273</v>
+        <v>7.247936091806275</v>
       </c>
       <c r="D6" t="n">
-        <v>7.247717494965138</v>
+        <v>1.92124645370249</v>
       </c>
       <c r="E6" t="n">
-        <v>7.315228321538722</v>
+        <v>1.988757280276084</v>
       </c>
       <c r="F6" t="n">
-        <v>7.259414811029769</v>
+        <v>7.259414811029768</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94475892430765</v>
+        <v>7.271229965570282</v>
       </c>
       <c r="H6" t="n">
-        <v>1.928070068553746</v>
+        <v>1.928070068553745</v>
       </c>
       <c r="I6" t="n">
-        <v>7.245932365736806</v>
+        <v>1.919461324474165</v>
       </c>
       <c r="J6" t="n">
         <v>1.96014410827526</v>
       </c>
       <c r="K6" t="n">
-        <v>7.251446256990054</v>
+        <v>1.92497521572741</v>
       </c>
       <c r="L6" t="n">
-        <v>7.245680068600945</v>
+        <v>1.919209027338305</v>
       </c>
       <c r="M6" t="n">
-        <v>1.974981109194834</v>
+        <v>7.301452150457468</v>
       </c>
       <c r="N6" t="n">
-        <v>1.956976005255685</v>
+        <v>1.956976005255684</v>
       </c>
       <c r="O6" t="n">
-        <v>7.391770501884145</v>
+        <v>7.39177050188415</v>
       </c>
       <c r="P6" t="n">
-        <v>7.341359270380657</v>
+        <v>1.904298364396518</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.299290277022551</v>
+        <v>7.299290277022544</v>
       </c>
       <c r="R6" t="n">
-        <v>7.246587315028052</v>
+        <v>1.920116273765417</v>
       </c>
       <c r="S6" t="n">
-        <v>7.246655305936359</v>
+        <v>1.920184264673717</v>
       </c>
       <c r="T6" t="n">
-        <v>1.975751063631049</v>
+        <v>7.302222104893683</v>
       </c>
       <c r="U6" t="n">
-        <v>7.285141450441872</v>
+        <v>1.958670409179227</v>
       </c>
       <c r="V6" t="n">
-        <v>1.967946926760322</v>
+        <v>7.294417968022956</v>
       </c>
       <c r="W6" t="n">
         <v>2.117067619261676</v>
       </c>
       <c r="X6" t="n">
-        <v>1.919344352367842</v>
+        <v>1.919344352367841</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.089414162466451</v>
+        <v>2.089414162466448</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.971451880854162</v>
+        <v>7.297922922116789</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.920554682635292</v>
+        <v>7.247025723897928</v>
       </c>
       <c r="AB6" t="n">
         <v>1.958054221754267</v>
@@ -5329,82 +5329,82 @@
         <v>0.02039515565203253</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02395939175054096</v>
+        <v>0.02395939175054095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02374079490939697</v>
+        <v>0.023740794909397</v>
       </c>
       <c r="E7" t="n">
         <v>0.09125162148299014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03543811097404197</v>
+        <v>0.0354381109740419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04725326551455675</v>
+        <v>0.04725326551455673</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03056440976065173</v>
+        <v>0.03056440976065171</v>
       </c>
       <c r="I7" t="n">
         <v>0.02195566568107222</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06263844948216687</v>
+        <v>0.06263844948216689</v>
       </c>
       <c r="K7" t="n">
         <v>0.02746955693431716</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02170336854521104</v>
+        <v>0.02170336854521103</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07747545040174171</v>
+        <v>0.07747545040174161</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05966905607921834</v>
+        <v>0.05966905607921832</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1672944230047295</v>
+        <v>0.1672944230047296</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1168834388108941</v>
+        <v>0.1168834388108942</v>
       </c>
       <c r="Q7" t="n">
         <v>0.07531357696682617</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02261061497232351</v>
+        <v>0.0226106149723235</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02267860588062465</v>
+        <v>0.02267860588062464</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07824540483795497</v>
+        <v>0.07824540483795506</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06115153054131814</v>
+        <v>0.06115153054131812</v>
       </c>
       <c r="V7" t="n">
-        <v>0.07044126796722891</v>
+        <v>0.07044126796722881</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1226207550934986</v>
+        <v>0.1226207550934987</v>
       </c>
       <c r="X7" t="n">
         <v>0.02183869357474783</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1087683140418262</v>
+        <v>0.1087683140418261</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.07394622206106814</v>
+        <v>0.07394622206106816</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02304902384219925</v>
+        <v>0.02304902384219923</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0607255000279382</v>
+        <v>0.06072550002793818</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02397661173278021</v>
+        <v>0.02397661173278022</v>
       </c>
       <c r="C8" t="n">
         <v>0.03351714729836543</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03329855045722147</v>
+        <v>0.03329855045722146</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1008093770308146</v>
+        <v>0.09762717385603543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03995060466431265</v>
+        <v>0.0399506046643128</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05681102106238117</v>
+        <v>0.05805024568822502</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04012216530847619</v>
+        <v>0.0401221653084762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03151342122889667</v>
+        <v>0.03151342122889669</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07219620502999136</v>
+        <v>0.07219620502999134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03702731248214159</v>
+        <v>0.0370273124821416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03126112409303548</v>
+        <v>0.0312611240930355</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08703320594956611</v>
+        <v>0.08703320594956232</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06459417972482534</v>
+        <v>0.06459417972482535</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1734927716488825</v>
+        <v>0.1734927716488824</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1227697229552378</v>
+        <v>0.1227697229552379</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07772055380210496</v>
+        <v>0.07772055380210499</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03216837052014799</v>
+        <v>0.03216837052014797</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03223636142844913</v>
+        <v>0.03223636142844909</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08780316038577958</v>
+        <v>0.0878031603857795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06703548253592308</v>
+        <v>0.06779541545235906</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07999902351505339</v>
+        <v>0.07835442831671377</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1321796851472297</v>
+        <v>0.1321796851472298</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02479341012625943</v>
+        <v>0.02479341012625939</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1242508241429555</v>
+        <v>0.1242508241429553</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0835039776088925</v>
+        <v>0.07741666531167257</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03260677939002368</v>
+        <v>0.03260677939002367</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07652600009154677</v>
+        <v>0.07652600009154674</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04048108618709811</v>
+        <v>0.04048108618709816</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05121092028814611</v>
+        <v>0.05121092028814612</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05099232344700208</v>
+        <v>0.05099232344700207</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1185031500205952</v>
+        <v>0.1168493621509918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06268963951164709</v>
+        <v>0.04617097548111957</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07450479405216184</v>
+        <v>0.0745047978501656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05781593829825677</v>
+        <v>0.05781593829825685</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04920719421867725</v>
+        <v>0.04920719421867729</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08988997801977201</v>
+        <v>0.08988997801977198</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05472108547192227</v>
+        <v>0.05472108547192224</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04895489708281617</v>
+        <v>0.04895489708281616</v>
       </c>
       <c r="M9" t="n">
         <v>0.1047269789393467</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08692058461682343</v>
+        <v>0.08692058461682345</v>
       </c>
       <c r="O9" t="n">
         <v>0.1969207639260548</v>
       </c>
       <c r="P9" t="n">
-        <v>0.147026229944002</v>
+        <v>0.1470262299440021</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1025651093024349</v>
+        <v>0.102565109302435</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04986214350992868</v>
+        <v>0.04986214350992865</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04993013441822977</v>
+        <v>0.04993013441822975</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1054969333755603</v>
+        <v>0.1054969333755602</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08841627892373848</v>
+        <v>0.0884162789237385</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09769279650483409</v>
+        <v>0.1059617367865413</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1498722836311037</v>
+        <v>0.1498722836311039</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04909022211235296</v>
+        <v>0.0490902221123529</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1360198425794313</v>
+        <v>0.1360198425794311</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1011977505986733</v>
+        <v>0.09687753370112354</v>
       </c>
       <c r="AA9" t="n">
         <v>0.05030055237980434</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08797702856554332</v>
+        <v>0.08797702856554335</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05224644245779662</v>
+        <v>0.05224644245779659</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04870811129489722</v>
+        <v>0.04870811129489727</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05234287276893894</v>
+        <v>0.05234287276893888</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05431262343931864</v>
+        <v>0.05431262343931862</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05570224205324363</v>
+        <v>0.05570224205324359</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05459022796173091</v>
+        <v>0.05459022796173085</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05284479479850882</v>
+        <v>0.05284479479850879</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0523415957619365</v>
+        <v>0.05234159576193651</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05505054985824692</v>
+        <v>0.05505054985824696</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0523919793374004</v>
+        <v>0.05239197933740036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05232976184277626</v>
+        <v>0.05232976184277619</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05651264803100282</v>
+        <v>0.05651264803100286</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05511926766556451</v>
+        <v>0.05511926766556454</v>
       </c>
       <c r="O2" t="n">
         <v>0.07587824528725078</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06058299338989674</v>
+        <v>0.06058299338989673</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05478153086662518</v>
+        <v>0.05478153086662514</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05240310259426179</v>
+        <v>0.05240310259426175</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05249609091374409</v>
+        <v>0.05249609091374408</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05615077250349584</v>
+        <v>0.0561507725034958</v>
       </c>
       <c r="U2" t="n">
         <v>0.2193880449732573</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0552506702052817</v>
+        <v>0.05525067020528171</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2399932476259692</v>
+        <v>0.2399932476259691</v>
       </c>
       <c r="X2" t="n">
         <v>0.05611723061194435</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05794229989510034</v>
+        <v>0.05794229989510033</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008282931579676</v>
+        <v>0.2008282931579675</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05286500760491838</v>
+        <v>0.05286500760491832</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05626068901134066</v>
+        <v>0.05626068901134068</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403593246573898</v>
+        <v>0.02403593246573893</v>
       </c>
       <c r="C3" t="n">
         <v>0.02020490796621777</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02472733239631383</v>
+        <v>0.02472733239631379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03877255617658958</v>
+        <v>0.03877255617658953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04871118696844818</v>
+        <v>0.04871118696844817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04060896687919262</v>
+        <v>0.0406089668791926</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02832895286352426</v>
+        <v>0.02832895286352425</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0247198367092349</v>
+        <v>0.02471983670923482</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04393512534180778</v>
+        <v>0.04393512534180776</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02507464223645698</v>
+        <v>0.02507464223645697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02462854878117091</v>
+        <v>0.02462854878117084</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05420779045780986</v>
+        <v>0.05420779045780989</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04450794227879459</v>
+        <v>0.04450794227879457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1349737565440346</v>
+        <v>0.1349737565440345</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08325672839772923</v>
+        <v>0.08325672839772925</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04202511003303593</v>
+        <v>0.04202511003303586</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02516114532529522</v>
+        <v>0.02516114532529519</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02580254901523678</v>
+        <v>0.02580254901523674</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05185989781360949</v>
+        <v>0.05185989781360947</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3192432821325461</v>
+        <v>0.319243282132546</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04532709388432292</v>
+        <v>0.04532709388432289</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3643795931528498</v>
+        <v>0.36437959315285</v>
       </c>
       <c r="X3" t="n">
         <v>0.05161100474281009</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06469665502596089</v>
+        <v>0.06469665502596088</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2781731162876745</v>
+        <v>0.2781731162876744</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02845251334599636</v>
+        <v>0.02845251334599629</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05255873604192051</v>
+        <v>0.0525587360419205</v>
       </c>
     </row>
     <row r="4">
@@ -5925,79 +5925,79 @@
         <v>0.01222246372387605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01633125882549744</v>
+        <v>0.01633125882549741</v>
       </c>
       <c r="D4" t="n">
         <v>0.01331168844836341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03556092840037841</v>
+        <v>0.03556092840037838</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05125730990080622</v>
+        <v>0.05125730990080628</v>
       </c>
       <c r="G4" t="n">
         <v>0.03869659918541415</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01898112866789643</v>
+        <v>0.01898112866789638</v>
       </c>
       <c r="I4" t="n">
         <v>0.0132972640668186</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04399732176835232</v>
+        <v>0.04399732176835231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01386636972927302</v>
+        <v>0.01386636972927299</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01316359450603161</v>
+        <v>0.01316359450603162</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06022555040735009</v>
+        <v>0.06022555040735018</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04467234601050276</v>
+        <v>0.04467234601050281</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1616306862703539</v>
+        <v>0.161630686270354</v>
       </c>
       <c r="P4" t="n">
         <v>0.1063876415048458</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04085745349987919</v>
+        <v>0.0408574534998792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01399201203247353</v>
+        <v>0.01399201203247352</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01504235787776652</v>
+        <v>0.0150423578777665</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05632366767060582</v>
+        <v>0.05632366767060581</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05252319489697697</v>
+        <v>0.05252319489697694</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04683185312058401</v>
+        <v>0.04683185312058406</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07512864965485375</v>
+        <v>0.07512864965485364</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05594479657549983</v>
+        <v>0.05594479657549992</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07664706368015053</v>
+        <v>0.07664706368015059</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03065935934182992</v>
+        <v>0.03065935934182988</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01920944161464233</v>
+        <v>0.0192094416146423</v>
       </c>
       <c r="AB4" t="n">
         <v>0.05728612783333682</v>
@@ -6010,40 +6010,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0266465105151143</v>
+        <v>0.02664651051511433</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09922410224405971</v>
+        <v>0.09922410224405973</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04755505203241211</v>
+        <v>0.047555052032412</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4343404531267356</v>
+        <v>0.434340453126736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7227636433328372</v>
+        <v>0.7227636433328365</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4147265113741323</v>
+        <v>0.4147265113741319</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1578705741764845</v>
+        <v>0.1578705741764844</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04813861519537823</v>
+        <v>0.04813861519537913</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5279432323135093</v>
+        <v>0.5279432323135089</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05572470953080012</v>
+        <v>0.05572470953080005</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0422356698283411</v>
+        <v>0.04223566982834114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7847705338420017</v>
+        <v>0.7847705338420018</v>
       </c>
       <c r="N5" t="n">
         <v>0.6147783570476287</v>
@@ -6052,43 +6052,43 @@
         <v>2.337250791553954</v>
       </c>
       <c r="P5" t="n">
-        <v>1.548262359655558</v>
+        <v>1.548262359655559</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4792730788506327</v>
+        <v>0.4792730788506325</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06163451011640821</v>
+        <v>0.06163451011640832</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06867666318657101</v>
+        <v>0.06867666318657088</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7851775617478379</v>
+        <v>0.7851775617478369</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6225419359560483</v>
+        <v>0.6225419359560487</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5496853874295994</v>
+        <v>0.5496853874296005</v>
       </c>
       <c r="W5" t="n">
         <v>1.076412547423271</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7735519542782362</v>
+        <v>0.7735519542782363</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.169276315386136</v>
+        <v>1.169276315386139</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3115729106214686</v>
+        <v>0.311572910621469</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1511817646032171</v>
+        <v>0.1511817646032168</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8364019575396233</v>
+        <v>0.8364019575396221</v>
       </c>
     </row>
     <row r="6">
@@ -6101,64 +6101,64 @@
         <v>1.782916781074871</v>
       </c>
       <c r="C6" t="n">
-        <v>6.749500972346045</v>
+        <v>1.787025576176492</v>
       </c>
       <c r="D6" t="n">
         <v>1.784006005799359</v>
       </c>
       <c r="E6" t="n">
-        <v>6.768730641920927</v>
+        <v>6.768730641920939</v>
       </c>
       <c r="F6" t="n">
-        <v>6.784427023421351</v>
+        <v>6.784427023421365</v>
       </c>
       <c r="G6" t="n">
-        <v>6.771866312705958</v>
+        <v>1.809390916536408</v>
       </c>
       <c r="H6" t="n">
-        <v>6.752150842188443</v>
+        <v>1.789675446018892</v>
       </c>
       <c r="I6" t="n">
-        <v>1.783991581417813</v>
+        <v>1.783991581417814</v>
       </c>
       <c r="J6" t="n">
-        <v>6.777167035288902</v>
+        <v>1.814691639119348</v>
       </c>
       <c r="K6" t="n">
         <v>1.784560687080268</v>
       </c>
       <c r="L6" t="n">
-        <v>6.746333308026571</v>
+        <v>6.746333308026584</v>
       </c>
       <c r="M6" t="n">
-        <v>1.830919867758345</v>
+        <v>6.793395263927906</v>
       </c>
       <c r="N6" t="n">
-        <v>1.815392363154693</v>
+        <v>1.815392363154694</v>
       </c>
       <c r="O6" t="n">
         <v>1.932350703414546</v>
       </c>
       <c r="P6" t="n">
-        <v>6.84005208930869</v>
+        <v>1.774789059626335</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.774027167020428</v>
+        <v>1.811551770850874</v>
       </c>
       <c r="R6" t="n">
-        <v>6.747161725553022</v>
+        <v>6.747161725553032</v>
       </c>
       <c r="S6" t="n">
-        <v>6.748212071398313</v>
+        <v>1.785736675228762</v>
       </c>
       <c r="T6" t="n">
-        <v>6.789493381191156</v>
+        <v>6.789493381191159</v>
       </c>
       <c r="U6" t="n">
-        <v>1.823130242269916</v>
+        <v>1.823130242269917</v>
       </c>
       <c r="V6" t="n">
-        <v>1.817526170471579</v>
+        <v>6.780001566641139</v>
       </c>
       <c r="W6" t="n">
         <v>1.936127635747726</v>
@@ -6167,16 +6167,16 @@
         <v>1.826639113926495</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.924855445912589</v>
+        <v>1.924855445912591</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.763829072862383</v>
+        <v>6.763829072862395</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.789903758965639</v>
+        <v>6.752379155135195</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.828101240879664</v>
+        <v>1.828101240879666</v>
       </c>
     </row>
     <row r="7">
@@ -6186,28 +6186,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01534032770184597</v>
+        <v>0.01534032770184595</v>
       </c>
       <c r="C7" t="n">
         <v>0.01944912280346733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01642955242633333</v>
+        <v>0.01642955242633331</v>
       </c>
       <c r="E7" t="n">
         <v>0.03867879237834827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05437517387877615</v>
+        <v>0.05437517387877614</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04181446316338402</v>
+        <v>0.041814463163384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02209899264586628</v>
+        <v>0.02209899264586629</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01641512804478851</v>
+        <v>0.0164151280447885</v>
       </c>
       <c r="J7" t="n">
         <v>0.04711518574632223</v>
@@ -6216,55 +6216,55 @@
         <v>0.01698423370724289</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01628145848400153</v>
+        <v>0.01628145848400151</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06334341438531996</v>
+        <v>0.06334341438532</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0477902099884727</v>
+        <v>0.04779020998847266</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1647484521525143</v>
+        <v>0.1647484521525142</v>
       </c>
       <c r="P7" t="n">
         <v>0.1095054073870061</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0439753174778491</v>
+        <v>0.04397531747784909</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01710987601044342</v>
+        <v>0.01710987601044341</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01816022185573643</v>
+        <v>0.01816022185573642</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05944153164857572</v>
+        <v>0.05944153164857569</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05552126071372839</v>
+        <v>0.05552126071372831</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04994971709855396</v>
+        <v>0.04994971709855395</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07824651363282367</v>
+        <v>0.07824651363282357</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05906266055346984</v>
+        <v>0.05906266055346985</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07967765768006606</v>
+        <v>0.0796776576800661</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03377722331979979</v>
+        <v>0.03377722331979981</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02232730559261222</v>
+        <v>0.0223273055926122</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06040399181130679</v>
+        <v>0.06040399181130678</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01801523900975875</v>
+        <v>0.01801523900975878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02656458156577201</v>
+        <v>0.02656458156577202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02354501118863803</v>
+        <v>0.02354501118863801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04579425114065295</v>
+        <v>0.04342979061049046</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05774187058153246</v>
+        <v>0.05774187058153254</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04892992192568878</v>
+        <v>0.04985069836731893</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02921445140817099</v>
+        <v>0.02921445140817098</v>
       </c>
       <c r="I8" t="n">
         <v>0.02353058680709319</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05423064450862692</v>
+        <v>0.05423064450862691</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02409969246954761</v>
+        <v>0.02409969246954759</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02339691724630622</v>
+        <v>0.02339691724630621</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07045887314762472</v>
+        <v>0.07045887314761644</v>
       </c>
       <c r="N8" t="n">
         <v>0.05146350158449648</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1693677792660185</v>
+        <v>0.1693677792660186</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1138928623817767</v>
+        <v>0.1138928623817766</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04577755986223515</v>
+        <v>0.04577755986223514</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0242253347727481</v>
+        <v>0.02422533477274811</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0252756806180411</v>
+        <v>0.02527568061804111</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06655699041088041</v>
+        <v>0.06655699041088045</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05991316689110696</v>
+        <v>0.06047674318844913</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05706517586085862</v>
+        <v>0.05582378684648619</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08536284508324776</v>
+        <v>0.08536284508324767</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06127188793144261</v>
+        <v>0.06127188793144268</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0911652572687755</v>
+        <v>0.09116525726877557</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.04089268208210447</v>
+        <v>0.03636964917954506</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02944276435491688</v>
+        <v>0.02944276435491689</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07215797369601556</v>
+        <v>0.07215797369601555</v>
       </c>
     </row>
     <row r="9">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02834564512668132</v>
+        <v>0.02834564512668131</v>
       </c>
       <c r="C9" t="n">
         <v>0.03724413436279569</v>
@@ -6371,34 +6371,34 @@
         <v>0.0342245639856617</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05647380393767659</v>
+        <v>0.05536835914283868</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07217018543810449</v>
+        <v>0.06112863819070161</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05960947472271241</v>
+        <v>0.05960947091955546</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03989400420519466</v>
+        <v>0.03989400420519464</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03421013960411688</v>
+        <v>0.03421013960411685</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06491019730565058</v>
+        <v>0.06491019730565056</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03477924526657129</v>
+        <v>0.03477924526657123</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03407647004332991</v>
+        <v>0.03407647004332993</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08113842594464839</v>
+        <v>0.08113842594464842</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06558522154780103</v>
+        <v>0.06558522154780101</v>
       </c>
       <c r="O9" t="n">
         <v>0.1841308551087364</v>
@@ -6407,40 +6407,40 @@
         <v>0.1292330202299685</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06177032523402055</v>
+        <v>0.0617703252340205</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03490488756977178</v>
+        <v>0.03490488756977177</v>
       </c>
       <c r="S9" t="n">
         <v>0.03595523341506476</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07723654320790403</v>
+        <v>0.07723654320790407</v>
       </c>
       <c r="U9" t="n">
         <v>0.0733488004562208</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06774472865788231</v>
+        <v>0.07327191962692094</v>
       </c>
       <c r="W9" t="n">
         <v>0.09604152519215192</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07685767211279816</v>
+        <v>0.07685767211279818</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09747266923939435</v>
+        <v>0.09747266923939436</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05157223487912813</v>
+        <v>0.04868447372205814</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04012231715194055</v>
+        <v>0.04012231715194054</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0781990033706351</v>
+        <v>0.07819900337063515</v>
       </c>
     </row>
   </sheetData>
@@ -6609,79 +6609,79 @@
         <v>0.04976031167560874</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04606111531670325</v>
+        <v>0.04606111531670323</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05004131149550302</v>
+        <v>0.05004131149550297</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0499125063897907</v>
+        <v>0.04991250638979065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05498716609493944</v>
+        <v>0.05498716609493946</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05081312042252191</v>
+        <v>0.05081312042252192</v>
       </c>
       <c r="H2" t="n">
         <v>0.05083143226455541</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05034375093451651</v>
+        <v>0.05034375093451644</v>
       </c>
       <c r="J2" t="n">
         <v>0.05166815168828642</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05064487454132702</v>
+        <v>0.05064487454132711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05030850924240214</v>
+        <v>0.05030850924240213</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05342323354076029</v>
+        <v>0.05342323354076023</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05127832466287917</v>
+        <v>0.05127832466287918</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06698891578138876</v>
+        <v>0.06698891578138882</v>
       </c>
       <c r="P2" t="n">
         <v>0.05726995579688791</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05087498527760226</v>
+        <v>0.05087498527760224</v>
       </c>
       <c r="R2" t="n">
         <v>0.05007903548137119</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05245019099364912</v>
+        <v>0.05245019099364915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05309657894306336</v>
+        <v>0.05309657894306335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2158128698926945</v>
+        <v>0.2158128698926944</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05121000719841218</v>
+        <v>0.0512100071984122</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2329403527853199</v>
+        <v>0.23294035278532</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05385981400574169</v>
+        <v>0.05385981400574167</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05363115920842453</v>
+        <v>0.05363115920842452</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1960739683458326</v>
+        <v>0.1960739683458327</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05069557200310319</v>
+        <v>0.05069557200310317</v>
       </c>
       <c r="AB2" t="n">
         <v>0.05279251602218554</v>
@@ -6694,34 +6694,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02206090500389543</v>
+        <v>0.02206090500389546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01712403049123479</v>
+        <v>0.01712403049123478</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0240693033941492</v>
+        <v>0.02406930339414918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02314354554270149</v>
+        <v>0.0231435455427015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05943553595181651</v>
+        <v>0.05943553595181652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02952425088377404</v>
+        <v>0.02952425088377405</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02973774252703945</v>
+        <v>0.02973774252703946</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02623684690635365</v>
+        <v>0.02623684690635363</v>
       </c>
       <c r="J3" t="n">
         <v>0.03563698546792728</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02836268075731683</v>
+        <v>0.02836268075731682</v>
       </c>
       <c r="L3" t="n">
         <v>0.0259432551486331</v>
@@ -6730,43 +6730,43 @@
         <v>0.04803200030149339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03289324790177358</v>
+        <v>0.03289324790177357</v>
       </c>
       <c r="O3" t="n">
         <v>0.1040474302755715</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07533327084085084</v>
+        <v>0.0753332708408508</v>
       </c>
       <c r="Q3" t="n">
         <v>0.02999637858357482</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02434750211319138</v>
+        <v>0.02434750211319137</v>
       </c>
       <c r="S3" t="n">
         <v>0.0411430796211817</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04588851431820352</v>
+        <v>0.04588851431820353</v>
       </c>
       <c r="U3" t="n">
         <v>0.3135107620590022</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03234811318405199</v>
+        <v>0.03234811318405203</v>
       </c>
       <c r="W3" t="n">
         <v>0.3351450198997017</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05124158501299376</v>
+        <v>0.05124158501299378</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04971491526662746</v>
+        <v>0.04971491526662742</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.265378735277465</v>
+        <v>0.2653787352774651</v>
       </c>
       <c r="AA3" t="n">
         <v>0.02873975878298242</v>
@@ -6782,22 +6782,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009056990099861894</v>
+        <v>0.009056990099861899</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01144687895761551</v>
+        <v>0.01144687895761552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01223101233187116</v>
+        <v>0.01223101233187117</v>
       </c>
       <c r="E4" t="n">
         <v>0.01077609940957413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06809671523802908</v>
+        <v>0.0680967152380291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02094894921219777</v>
+        <v>0.02094894921219781</v>
       </c>
       <c r="H4" t="n">
         <v>0.02115578989182918</v>
@@ -6806,31 +6806,31 @@
         <v>0.015647204924544</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0307043637300373</v>
+        <v>0.03070436373003731</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01904853458717232</v>
+        <v>0.01904853458717234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0152491338001331</v>
+        <v>0.01524913380013311</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05016242178123095</v>
+        <v>0.050162421781231</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02620364511155635</v>
+        <v>0.02620364511155633</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1202382873830452</v>
+        <v>0.1202382873830453</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09388187505668213</v>
+        <v>0.09388187505668209</v>
       </c>
       <c r="Q4" t="n">
         <v>0.02164774120956937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01265712210614295</v>
+        <v>0.01265712210614296</v>
       </c>
       <c r="S4" t="n">
         <v>0.03944041440274882</v>
@@ -6839,19 +6839,19 @@
         <v>0.04674166364452986</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04509706739106153</v>
+        <v>0.04509706739106163</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02608173547935115</v>
+        <v>0.02608173547935116</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0311668043191186</v>
+        <v>0.03116680431911862</v>
       </c>
       <c r="X4" t="n">
         <v>0.05536275478295694</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05277787592896264</v>
+        <v>0.05277787592896265</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01280272945567826</v>
@@ -6860,7 +6860,7 @@
         <v>0.01962118573991833</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04301332615267261</v>
+        <v>0.04301332615267259</v>
       </c>
     </row>
     <row r="5">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02400979412784411</v>
+        <v>0.02400979412784412</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06726070390320792</v>
+        <v>0.06726070390320797</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08164459352167168</v>
+        <v>0.08164459352167172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05255945973498036</v>
+        <v>0.05255945973498042</v>
       </c>
       <c r="F5" t="n">
         <v>1.104661334751726</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2081151819477786</v>
+        <v>0.2081151819477784</v>
       </c>
       <c r="H5" t="n">
-        <v>0.254682044756972</v>
+        <v>0.2546820447569715</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1467390291096329</v>
+        <v>0.1467390291096323</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3843850256968749</v>
+        <v>0.3843850256968753</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1948223443727149</v>
+        <v>0.1948223443727151</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1178967492827229</v>
+        <v>0.1178967492827227</v>
       </c>
       <c r="M5" t="n">
         <v>0.7379515587526437</v>
@@ -6909,46 +6909,46 @@
         <v>0.5615352627381168</v>
       </c>
       <c r="O5" t="n">
-        <v>1.754751608867386</v>
+        <v>1.754751608867384</v>
       </c>
       <c r="P5" t="n">
-        <v>1.35619757618211</v>
+        <v>1.356197576182107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2363296306869434</v>
+        <v>0.2363296306869435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09382473046575045</v>
+        <v>0.09382473046575064</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5014694177056069</v>
+        <v>0.5014694177056065</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6990779550151363</v>
+        <v>0.6990779550151369</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5804308027495143</v>
+        <v>0.5804308027495156</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2835260759388861</v>
+        <v>0.2835260759388866</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4009982345174439</v>
+        <v>0.4009982345174433</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8027518523718918</v>
+        <v>0.8027518523718926</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8116150950208622</v>
+        <v>0.8116150950208627</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.08041052616069799</v>
+        <v>0.08041052616069806</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2128523664283306</v>
+        <v>0.2128523664283303</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6618544686202965</v>
+        <v>0.6618544686202975</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739941542012325</v>
+        <v>6.739941542012326</v>
       </c>
       <c r="C6" t="n">
-        <v>6.742331430870073</v>
+        <v>6.742331430870077</v>
       </c>
       <c r="D6" t="n">
-        <v>6.743115564244329</v>
+        <v>6.743115564244327</v>
       </c>
       <c r="E6" t="n">
-        <v>6.741660651322032</v>
+        <v>6.74166065132203</v>
       </c>
       <c r="F6" t="n">
-        <v>1.837570170756251</v>
+        <v>6.798981267150487</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79042240473042</v>
+        <v>6.751833501124659</v>
       </c>
       <c r="H6" t="n">
-        <v>1.790629245410053</v>
+        <v>1.790629245410052</v>
       </c>
       <c r="I6" t="n">
-        <v>6.746531756837004</v>
+        <v>1.785120660442768</v>
       </c>
       <c r="J6" t="n">
-        <v>6.761588915642496</v>
+        <v>1.800177819248261</v>
       </c>
       <c r="K6" t="n">
-        <v>1.788521990105395</v>
+        <v>6.74993308649963</v>
       </c>
       <c r="L6" t="n">
-        <v>6.746133685712593</v>
+        <v>6.746133685712592</v>
       </c>
       <c r="M6" t="n">
-        <v>6.781046973693688</v>
+        <v>6.781046973693691</v>
       </c>
       <c r="N6" t="n">
         <v>1.795772166158843</v>
       </c>
       <c r="O6" t="n">
-        <v>1.889806808430331</v>
+        <v>6.851550274659979</v>
       </c>
       <c r="P6" t="n">
-        <v>6.825193373411648</v>
+        <v>6.825193373411643</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.752532293122033</v>
+        <v>6.752532293122024</v>
       </c>
       <c r="R6" t="n">
-        <v>6.743541674018602</v>
+        <v>1.782130577624366</v>
       </c>
       <c r="S6" t="n">
-        <v>1.808913869920972</v>
+        <v>1.808913869920971</v>
       </c>
       <c r="T6" t="n">
-        <v>6.777626215556991</v>
+        <v>6.77762621555699</v>
       </c>
       <c r="U6" t="n">
-        <v>6.775983737035414</v>
+        <v>6.775983737035412</v>
       </c>
       <c r="V6" t="n">
-        <v>1.795555190997574</v>
+        <v>1.795555190997576</v>
       </c>
       <c r="W6" t="n">
-        <v>6.762479321558683</v>
+        <v>6.762479321558673</v>
       </c>
       <c r="X6" t="n">
-        <v>6.786247306695413</v>
+        <v>1.82483621030118</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.899845101346358</v>
+        <v>1.899845101346357</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.743687281368131</v>
+        <v>1.782276184973902</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.750505737652379</v>
+        <v>1.789094641258141</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.81266420083514</v>
+        <v>1.812664200835141</v>
       </c>
     </row>
     <row r="7">
@@ -7049,82 +7049,82 @@
         <v>0.01129170540255398</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01368159426030761</v>
+        <v>0.0136815942603076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01446572763456325</v>
+        <v>0.01446572763456324</v>
       </c>
       <c r="E7" t="n">
         <v>0.01301081471226622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.070331430540721</v>
+        <v>0.07033143054072111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02318366451488985</v>
+        <v>0.0231836645148899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02339050519452127</v>
+        <v>0.02339050519452128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01788192022723608</v>
+        <v>0.01788192022723607</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03293907903272939</v>
+        <v>0.03293907903272938</v>
       </c>
       <c r="K7" t="n">
         <v>0.02128324988986443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0174838491028252</v>
+        <v>0.01748384910282519</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0523971370839231</v>
+        <v>0.05239713708392311</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02843836041424842</v>
+        <v>0.02843836041424841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1224729341088116</v>
+        <v>0.1224729341088117</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09611652178244856</v>
+        <v>0.09611652178244851</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02388245651226146</v>
+        <v>0.02388245651226147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01489183740883505</v>
+        <v>0.01489183740883504</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04167512970544091</v>
+        <v>0.04167512970544088</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04897637894722199</v>
+        <v>0.04897637894722202</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04729282536254698</v>
+        <v>0.047292825362547</v>
       </c>
       <c r="V7" t="n">
         <v>0.02831645078204326</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0334015196218107</v>
+        <v>0.03340151962181068</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05759747008564903</v>
+        <v>0.05759747008564904</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05501470896354853</v>
+        <v>0.05501470896354843</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01503744475837034</v>
+        <v>0.01503744475837035</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02185590104261043</v>
+        <v>0.02185590104261041</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04524804145536464</v>
+        <v>0.04524804145536473</v>
       </c>
     </row>
     <row r="8">
@@ -7137,82 +7137,82 @@
         <v>0.01331278020098866</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01896793028741375</v>
+        <v>0.01896793028741373</v>
       </c>
       <c r="D8" t="n">
         <v>0.01975206366166939</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01829715073937237</v>
+        <v>0.01655849545533731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07286119487605158</v>
+        <v>0.07286119487605168</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02847000054199602</v>
+        <v>0.02914707372855393</v>
       </c>
       <c r="H8" t="n">
         <v>0.02867684122162742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02316825625434224</v>
+        <v>0.02316825625434222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03822541505983557</v>
+        <v>0.03822541505983552</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02656958591697058</v>
+        <v>0.02656958591697055</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02277018512993135</v>
+        <v>0.02277018512993133</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05768347311102929</v>
+        <v>0.05768347311101827</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03119357272147065</v>
+        <v>0.03119357272147064</v>
       </c>
       <c r="O8" t="n">
         <v>0.1259237897658455</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09939687525549444</v>
+        <v>0.09939687525549448</v>
       </c>
       <c r="Q8" t="n">
         <v>0.02526183295472407</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02017817343594121</v>
+        <v>0.02017817343594118</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04696146573254703</v>
+        <v>0.04696146573254702</v>
       </c>
       <c r="T8" t="n">
         <v>0.05426271497432809</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05058112466776759</v>
+        <v>0.05099472700471318</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03360278680914941</v>
+        <v>0.03267529034889458</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03868849736105132</v>
+        <v>0.03868849736105128</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05927611420466298</v>
+        <v>0.05927611420466302</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.06349325524924138</v>
+        <v>0.06349325524924128</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02032378078547651</v>
+        <v>0.01699786565354007</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02714223706971657</v>
+        <v>0.02714223706971656</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05394521586763311</v>
+        <v>0.05394521586763306</v>
       </c>
     </row>
     <row r="9">
@@ -7222,79 +7222,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01900373953719471</v>
+        <v>0.0190037395371947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02438871493342765</v>
+        <v>0.02438871493342764</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0251728483076833</v>
+        <v>0.02517284830768331</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02371793538538627</v>
+        <v>0.0230266768000226</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08103855121384106</v>
+        <v>0.07413406750040212</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0338907851880099</v>
+        <v>0.03389077891006825</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03409762586764131</v>
+        <v>0.03409762586764133</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02858904090035611</v>
+        <v>0.02858904090035614</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04364619970584944</v>
+        <v>0.04364619970584942</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03199037056298446</v>
+        <v>0.03199037056298447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02819096977594524</v>
+        <v>0.02819096977594526</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06310425775704315</v>
+        <v>0.06310425775704316</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03914548108736848</v>
+        <v>0.03914548108736846</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1341726827575352</v>
+        <v>0.1341726827575353</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1080321364362779</v>
+        <v>0.1080321364362778</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03458957090743989</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02559895808195508</v>
+        <v>0.02559895808195507</v>
       </c>
       <c r="S9" t="n">
-        <v>0.05238225037856092</v>
+        <v>0.05238225037856094</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05968349962034201</v>
+        <v>0.05968349962034199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05804102109876744</v>
+        <v>0.05804102109876752</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03902357145516331</v>
+        <v>0.04247981998651613</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04410864029493076</v>
+        <v>0.04410864029493074</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06830459075876909</v>
+        <v>0.06830459075876912</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.06572182963666855</v>
+        <v>0.06572182963666851</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02574456543149039</v>
+        <v>0.023938792089373</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03256302171573047</v>
@@ -7466,61 +7466,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05293711758523426</v>
+        <v>0.05293711758523416</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0494224189052293</v>
+        <v>0.04942241890522936</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05317474395816574</v>
+        <v>0.05317474395816571</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0589676223075774</v>
+        <v>0.05896762230757736</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05411966652911734</v>
+        <v>0.05411966652911732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05387144806640332</v>
+        <v>0.05387144806640333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05483949582982674</v>
+        <v>0.05483949582982675</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0533185078784258</v>
+        <v>0.05331850787842581</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05538037007905926</v>
+        <v>0.05538037007905925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05375428359010119</v>
+        <v>0.05375428359010116</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05295723389922765</v>
+        <v>0.05295723389922754</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05454495547649951</v>
+        <v>0.05454495547649946</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05435698514780002</v>
+        <v>0.05435698514779996</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06655405525157583</v>
+        <v>0.06655405525157601</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05806507523938644</v>
+        <v>0.05806507523938646</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05461725072636996</v>
+        <v>0.05461725072636991</v>
       </c>
       <c r="R2" t="n">
         <v>0.05335526874423169</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05304224125755655</v>
+        <v>0.05304224125755654</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05574073819873392</v>
+        <v>0.05574073819873387</v>
       </c>
       <c r="U2" t="n">
         <v>0.2203516361734066</v>
@@ -7529,22 +7529,22 @@
         <v>0.05715321478661591</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2445508769927138</v>
+        <v>0.2445508769927137</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05312085889869816</v>
+        <v>0.05312085889869812</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05962599921507902</v>
+        <v>0.05962599921507911</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2062755598182431</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05329594216438863</v>
+        <v>0.05329594216438865</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05362483637000796</v>
+        <v>0.05362483637000793</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02459621208734333</v>
+        <v>0.02459621208734316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02084206362634595</v>
+        <v>0.02084206362634598</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02630114489226932</v>
+        <v>0.0263011448922693</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06762241985781885</v>
+        <v>0.06762241985781883</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03306052182111171</v>
+        <v>0.03306052182111174</v>
       </c>
       <c r="G3" t="n">
         <v>0.03122996048717118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0382491734456717</v>
+        <v>0.03824917344567184</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0273308475086928</v>
+        <v>0.02733084750869292</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04198008457364703</v>
+        <v>0.04198008457364715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03041323778239245</v>
+        <v>0.03041323778239248</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02474133570812174</v>
+        <v>0.02474133570812173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03627175709814751</v>
+        <v>0.03627175709814752</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03474498948755488</v>
+        <v>0.03474498948755481</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08589289766994909</v>
+        <v>0.08589289766994947</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06107382428118891</v>
+        <v>0.06107382428118924</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0365906251257969</v>
+        <v>0.03659062512579675</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02759896064282859</v>
+        <v>0.02759896064282864</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02534226744231459</v>
+        <v>0.0253422674423149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04466721695813759</v>
+        <v>0.0446672169581376</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3165074830511836</v>
+        <v>0.3165074830511844</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05451465793143487</v>
+        <v>0.05451465793143495</v>
       </c>
       <c r="W3" t="n">
         <v>0.3860782987159107</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02591357408401655</v>
+        <v>0.02591357408401665</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07231186853185065</v>
+        <v>0.0723118685318514</v>
       </c>
       <c r="Z3" t="n">
         <v>0.3013632653843837</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02715956505267149</v>
+        <v>0.02715956505267167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02979968603529748</v>
+        <v>0.0297996860352975</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01268558218091983</v>
+        <v>0.01268558218091993</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01683423116413359</v>
+        <v>0.01683423116413361</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0153696813767138</v>
+        <v>0.01536968137671394</v>
       </c>
       <c r="E4" t="n">
         <v>0.08080290718901741</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02604301650147051</v>
+        <v>0.02604301650147064</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02323927477898127</v>
+        <v>0.02323927477898142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03417381959082165</v>
+        <v>0.03417381959082177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01699356099072222</v>
+        <v>0.01699356099072243</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04039462766784997</v>
+        <v>0.04039462766784998</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02191584812082691</v>
+        <v>0.02191584812082686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01291280520143689</v>
+        <v>0.01291280520143681</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03123189083851466</v>
+        <v>0.03123189083851473</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02872363947144957</v>
+        <v>0.02872363947144931</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09325049560979622</v>
+        <v>0.09325049560979727</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0706082228616369</v>
+        <v>0.07060822286163733</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03166345890947827</v>
+        <v>0.03166345890947884</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0174087918808332</v>
+        <v>0.01740879188083348</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01387300241907937</v>
+        <v>0.01387300241907958</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04435376673960084</v>
+        <v>0.04435376673960077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04523298902517228</v>
+        <v>0.04523298902517353</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06105279388901241</v>
+        <v>0.06105279388901259</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1056875533056478</v>
+        <v>0.1056875533056479</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01476102484167497</v>
+        <v>0.01476102484167532</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08867356537267471</v>
+        <v>0.08867356537267454</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06165367814654452</v>
+        <v>0.06165367814654461</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01673867086993068</v>
+        <v>0.0167386708699311</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02093362147322419</v>
+        <v>0.02093362147322422</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03249327003959796</v>
+        <v>0.03249327003959667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.11374521717621</v>
+        <v>0.1137452171762101</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08823906233197662</v>
+        <v>0.08823906233197562</v>
       </c>
       <c r="E5" t="n">
-        <v>1.312771428370668</v>
+        <v>1.312771428370669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2986239041210483</v>
+        <v>0.2986239041210493</v>
       </c>
       <c r="G5" t="n">
-        <v>0.212790370410633</v>
+        <v>0.2127903704106317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4808320222762617</v>
+        <v>0.4808320222762635</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1209744860227735</v>
+        <v>0.1209744860227776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5245296547636059</v>
+        <v>0.5245296547636079</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1986043302436925</v>
+        <v>0.1986043302436953</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03765299922520471</v>
+        <v>0.03765299922520141</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3782297292337477</v>
+        <v>0.3782297292337474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.604244576243515</v>
+        <v>0.6042445762435351</v>
       </c>
       <c r="O5" t="n">
-        <v>1.382234217301998</v>
+        <v>1.382234217302011</v>
       </c>
       <c r="P5" t="n">
-        <v>1.060462889292549</v>
+        <v>1.060462889292552</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3931154341184138</v>
+        <v>0.3931154341184196</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1320229526039072</v>
+        <v>0.1320229526039123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05259930691700309</v>
+        <v>0.0525993069170016</v>
       </c>
       <c r="T5" t="n">
-        <v>0.665433812780335</v>
+        <v>0.665433812780338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.620319937652151</v>
+        <v>0.6203199376521716</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8379982434934057</v>
+        <v>0.8379982434934075</v>
       </c>
       <c r="W5" t="n">
         <v>1.799924172929131</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07506749576676268</v>
+        <v>0.07506749576676801</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.448144245357236</v>
+        <v>1.448144245357231</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8857310008618532</v>
+        <v>0.8857310008618535</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1104657049731574</v>
+        <v>0.1104657049731605</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2075947762690821</v>
+        <v>0.2075947762690819</v>
       </c>
     </row>
     <row r="6">
@@ -7818,82 +7818,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.239569768405498</v>
+        <v>7.239569768405494</v>
       </c>
       <c r="C6" t="n">
         <v>1.918434975765267</v>
       </c>
       <c r="D6" t="n">
-        <v>7.242253867601293</v>
+        <v>7.242253867601286</v>
       </c>
       <c r="E6" t="n">
-        <v>7.307687093413596</v>
+        <v>7.307687093413592</v>
       </c>
       <c r="F6" t="n">
-        <v>7.252927202726045</v>
+        <v>7.252927202726043</v>
       </c>
       <c r="G6" t="n">
         <v>1.924840019380115</v>
       </c>
       <c r="H6" t="n">
-        <v>7.261058005815399</v>
+        <v>7.261058005815396</v>
       </c>
       <c r="I6" t="n">
-        <v>1.918594305591856</v>
+        <v>1.918594305591855</v>
       </c>
       <c r="J6" t="n">
-        <v>7.267278813892424</v>
+        <v>1.941995372268984</v>
       </c>
       <c r="K6" t="n">
-        <v>1.92351659272196</v>
+        <v>1.923516592721961</v>
       </c>
       <c r="L6" t="n">
-        <v>1.914513549802571</v>
+        <v>7.239796991426012</v>
       </c>
       <c r="M6" t="n">
-        <v>7.258116077063101</v>
+        <v>7.258116077063091</v>
       </c>
       <c r="N6" t="n">
-        <v>1.930131052438348</v>
+        <v>1.930131052438351</v>
       </c>
       <c r="O6" t="n">
-        <v>1.994657908576693</v>
+        <v>1.9946579085767</v>
       </c>
       <c r="P6" t="n">
-        <v>7.297931391059561</v>
+        <v>7.297931391059551</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.933264203510612</v>
+        <v>7.258547645134049</v>
       </c>
       <c r="R6" t="n">
-        <v>7.244292978105408</v>
+        <v>7.244292978105405</v>
       </c>
       <c r="S6" t="n">
-        <v>7.240757188643654</v>
+        <v>7.240757188643652</v>
       </c>
       <c r="T6" t="n">
-        <v>7.27123795296418</v>
+        <v>1.945954511340734</v>
       </c>
       <c r="U6" t="n">
-        <v>7.271683187104665</v>
+        <v>7.271683187104659</v>
       </c>
       <c r="V6" t="n">
-        <v>1.962653538490146</v>
+        <v>7.28793698011359</v>
       </c>
       <c r="W6" t="n">
-        <v>2.104165998145424</v>
+        <v>2.104165998145423</v>
       </c>
       <c r="X6" t="n">
-        <v>7.241645211066253</v>
+        <v>1.91636176944281</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.072990399943078</v>
+        <v>2.072990399943097</v>
       </c>
       <c r="Z6" t="n">
         <v>1.963254422747677</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.243622857094511</v>
+        <v>7.243622857094507</v>
       </c>
       <c r="AB6" t="n">
         <v>1.922183165030324</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01619661831148962</v>
+        <v>0.01619661831148956</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02034526729470334</v>
+        <v>0.0203452672947034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01888071750728358</v>
+        <v>0.01888071750728366</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0843139433195871</v>
+        <v>0.08431394331958704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02955405263204031</v>
+        <v>0.02955405263204038</v>
       </c>
       <c r="G7" t="n">
         <v>0.02675031090955118</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03768485572139143</v>
+        <v>0.0376848557213916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02050459712129202</v>
+        <v>0.02050459712129227</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0439056637984196</v>
+        <v>0.04390566379841982</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02542688425139667</v>
+        <v>0.02542688425139664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01642384133200669</v>
+        <v>0.01642384133200653</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03474292696908443</v>
+        <v>0.0347429269690845</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03223467560201936</v>
+        <v>0.03223467560201921</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09676138250365403</v>
+        <v>0.09676138250365507</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0741191097554947</v>
+        <v>0.07411910975549527</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03517449504004803</v>
+        <v>0.03517449504004852</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02091982801140297</v>
+        <v>0.02091982801140302</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01738403854964914</v>
+        <v>0.01738403854964961</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0478648028701706</v>
+        <v>0.04786480287017061</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04831837109901718</v>
+        <v>0.04831837109901815</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0645638300195822</v>
+        <v>0.06456383001958244</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1091985894362175</v>
+        <v>0.1091985894362176</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01827206097224475</v>
+        <v>0.01827206097224514</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09175061335815883</v>
+        <v>0.0917506133581595</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0651647142771144</v>
+        <v>0.06516471427711443</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02024970700050049</v>
+        <v>0.02024970700050059</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02444465760379395</v>
+        <v>0.02444465760379397</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01898424608945291</v>
+        <v>0.01898424608945276</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02790528550023069</v>
+        <v>0.02790528550023078</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02644073571281089</v>
+        <v>0.02644073571281102</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09187396152511443</v>
+        <v>0.08933280440074838</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03308516306156914</v>
+        <v>0.03308516306156923</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03431032911507816</v>
+        <v>0.03529991535885827</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04524487392691876</v>
+        <v>0.04524487392691877</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02806461532681934</v>
+        <v>0.02806461532681965</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05146568200394704</v>
+        <v>0.05146568200394713</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03298690245692402</v>
+        <v>0.03298690245692398</v>
       </c>
       <c r="L8" t="n">
-        <v>0.023983859537534</v>
+        <v>0.02398385953753379</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04230294517461176</v>
+        <v>0.04230294517460879</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03609529282059123</v>
+        <v>0.03609529282059164</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1016387764673692</v>
+        <v>0.1016387764673696</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0787473037521712</v>
+        <v>0.07874730375217188</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03702423917664876</v>
+        <v>0.03702423917664942</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02847984621693029</v>
+        <v>0.02847984621693058</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02494405675517646</v>
+        <v>0.0249440567551766</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05542482107569797</v>
+        <v>0.05542482107569789</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05293954787069516</v>
+        <v>0.05354728950876826</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07212384822510952</v>
+        <v>0.07082673329384717</v>
       </c>
       <c r="W8" t="n">
-        <v>0.116759545545188</v>
+        <v>0.1167595455451881</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02055920416949705</v>
+        <v>0.02055920416949744</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1040669575690113</v>
+        <v>0.1040669575690116</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.07272473248264162</v>
+        <v>0.06786369245341607</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0278097252060278</v>
+        <v>0.02780972520602809</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03698983666425108</v>
+        <v>0.03698983666425117</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03250551973346073</v>
+        <v>0.03250551973346077</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04247073512163497</v>
+        <v>0.04247073512163513</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04100618533421528</v>
+        <v>0.04100618533421534</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1064394111465188</v>
+        <v>0.1050969793257405</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05167952045897201</v>
+        <v>0.03827073386233574</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04887577873648223</v>
+        <v>0.04887578911102954</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0598103235483231</v>
+        <v>0.05981032354832319</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04263006494822364</v>
+        <v>0.04263006494822395</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06603113162535136</v>
+        <v>0.06603113162535156</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04755235207832834</v>
+        <v>0.04755235207832835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03854930915893832</v>
+        <v>0.03854930915893807</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05686839479601614</v>
+        <v>0.05686839479601623</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05436014342895101</v>
+        <v>0.05436014342895076</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1208146158704168</v>
+        <v>0.1208146158704182</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09859156433957392</v>
+        <v>0.09859156433957449</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05729997324152646</v>
+        <v>0.057299973241527</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04304529583833461</v>
+        <v>0.043045295838335</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03950950637658084</v>
+        <v>0.03950950637658125</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06999027069710238</v>
+        <v>0.06999027069710234</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07043550483758815</v>
+        <v>0.07043550483758913</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08668929784651393</v>
+        <v>0.09340150273030444</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1313240572631492</v>
+        <v>0.1313240572631494</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04039752879917637</v>
+        <v>0.04039752879917696</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1138760811850906</v>
+        <v>0.1138760811850908</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08729018210404607</v>
+        <v>0.08378331391073858</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04237517482743216</v>
+        <v>0.04237517482743255</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04657012543072565</v>
+        <v>0.04657012543072571</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05167549862510432</v>
+        <v>0.05167549862510439</v>
       </c>
       <c r="C2" t="n">
         <v>0.04807375652941501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05174219273223169</v>
+        <v>0.05174219273223173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05540353163069636</v>
+        <v>0.0554035316306964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05558283482527463</v>
+        <v>0.05558283482527467</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05257225476450386</v>
+        <v>0.05257225476450388</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05312266505946614</v>
+        <v>0.05312266505946617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05174853260301662</v>
+        <v>0.05174853260301664</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05442117335354781</v>
+        <v>0.05442117335354783</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05184257607831111</v>
+        <v>0.05184257607831121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05176807380625902</v>
+        <v>0.05176807380625901</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05950634559251579</v>
+        <v>0.05950634559251596</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05351650888851814</v>
+        <v>0.05351650888851819</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07277371766278187</v>
+        <v>0.07277371766278193</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05795377254252705</v>
+        <v>0.05795377254252706</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05463323833367145</v>
+        <v>0.05463323833367149</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05196017698015815</v>
+        <v>0.05196017698015819</v>
       </c>
       <c r="S2" t="n">
         <v>0.05188154526059285</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05512271245370912</v>
+        <v>0.05512271245370915</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196707189047349</v>
+        <v>0.2196707189047347</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05451932778087901</v>
+        <v>0.05451932778087905</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2399473538187037</v>
+        <v>0.239947353818704</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05368193310176515</v>
+        <v>0.05368193310176517</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05680332447097497</v>
+        <v>0.056803324470975</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2011841632418243</v>
+        <v>0.2011841632418242</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05207989179850978</v>
+        <v>0.05207989179850984</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05377004335978348</v>
+        <v>0.05377004335978344</v>
       </c>
     </row>
     <row r="3">
@@ -8414,25 +8414,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02343894971547538</v>
+        <v>0.02343894971547536</v>
       </c>
       <c r="C3" t="n">
         <v>0.01933111664531523</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02391803546913854</v>
+        <v>0.02391803546913853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05003741248315507</v>
+        <v>0.05003741248315505</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05135618368104243</v>
+        <v>0.05135618368104242</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02979425778035704</v>
+        <v>0.02979425778035698</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03382832550399952</v>
+        <v>0.0338283255039995</v>
       </c>
       <c r="I3" t="n">
         <v>0.02396409437543209</v>
@@ -8441,58 +8441,58 @@
         <v>0.04296991269088402</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02463041256747419</v>
+        <v>0.02463041256747417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02409887948129118</v>
+        <v>0.02409887948129119</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07887068770367292</v>
+        <v>0.07887068770367267</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0365972484140174</v>
+        <v>0.03659724841401737</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1220357849744184</v>
+        <v>0.1220357849744185</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06803993295895765</v>
+        <v>0.06803993295895761</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04446902865742546</v>
+        <v>0.04446902865742548</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02548170667421962</v>
+        <v>0.0254817066742196</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02490087925128036</v>
+        <v>0.02490087925128033</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04809612194428132</v>
+        <v>0.04809612194428126</v>
       </c>
       <c r="U3" t="n">
         <v>0.323668338801755</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04360461040590938</v>
+        <v>0.04360461040590939</v>
       </c>
       <c r="W3" t="n">
-        <v>0.36653801391665</v>
+        <v>0.3665380139166501</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03776140214970357</v>
+        <v>0.03776140214970355</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06002354998933083</v>
+        <v>0.06002354998933081</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.281998843246933</v>
+        <v>0.2819988432469329</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02632675655488153</v>
+        <v>0.02632675655488152</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0384829882739832</v>
+        <v>0.03848298827398311</v>
       </c>
     </row>
     <row r="4">
@@ -8502,64 +8502,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01157814171468563</v>
+        <v>0.01157814171468564</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01532698221774824</v>
+        <v>0.01532698221774814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01233148233549469</v>
+        <v>0.01233148233549459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05368798949275991</v>
+        <v>0.05368798949275983</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0557133015590662</v>
+        <v>0.05571330155906608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02170741483740846</v>
+        <v>0.02170741483740824</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0279245523202533</v>
+        <v>0.02792455232025324</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01240309409249476</v>
+        <v>0.01240309409249472</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04269638383918613</v>
+        <v>0.04269638383918615</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01346535840808237</v>
+        <v>0.01346535840808235</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01262382097251488</v>
+        <v>0.01262382097251476</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09942803700929943</v>
+        <v>0.09942803700929924</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03237319954650777</v>
+        <v>0.0323731995465078</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1440117118007109</v>
+        <v>0.1440117118007108</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08249413376066791</v>
+        <v>0.08249413376066789</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04498717235043916</v>
+        <v>0.0449871723504392</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01479371469353184</v>
+        <v>0.014793714693532</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01390553324866353</v>
+        <v>0.01390553324866358</v>
       </c>
       <c r="T4" t="n">
         <v>0.0505160077054851</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05920955181889871</v>
+        <v>0.05920955181889873</v>
       </c>
       <c r="V4" t="n">
         <v>0.04439894780313879</v>
@@ -8568,19 +8568,19 @@
         <v>0.07809812070232046</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03424174213403032</v>
+        <v>0.03424174213403033</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06964197535443378</v>
+        <v>0.0696419753544337</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03601824689595147</v>
+        <v>0.03601824689595134</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01614594863835167</v>
+        <v>0.01614594863835159</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03529566271356384</v>
+        <v>0.03529566271356387</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02212471062355393</v>
+        <v>0.02212471062355382</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08832456398441149</v>
+        <v>0.08832456398441119</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03704832778508268</v>
+        <v>0.03704832778508242</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7624010767742339</v>
+        <v>0.7624010767742351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8184718783221417</v>
+        <v>0.8184718783221433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1780169984504694</v>
+        <v>0.1780169984504683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3427858172140039</v>
+        <v>0.3427858172140033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03873514508239681</v>
+        <v>0.0387351450823968</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5370442163613973</v>
+        <v>0.5370442163613968</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05499681140114229</v>
+        <v>0.0549968114011424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04021302859880219</v>
+        <v>0.04021302859880207</v>
       </c>
       <c r="M5" t="n">
-        <v>1.508671964599658</v>
+        <v>1.508671964599656</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7610861660389781</v>
+        <v>0.7610861660389802</v>
       </c>
       <c r="O5" t="n">
-        <v>2.077064825656134</v>
+        <v>2.077064825656139</v>
       </c>
       <c r="P5" t="n">
-        <v>1.16892644188153</v>
+        <v>1.168926441881531</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.571842068359165</v>
+        <v>0.5718420683591648</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08469444855319765</v>
+        <v>0.0846944485531971</v>
       </c>
       <c r="S5" t="n">
         <v>0.05881330310404034</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7389111856613062</v>
+        <v>0.7389111856613058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7877798365171619</v>
+        <v>0.7877798365171634</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5231297688284166</v>
+        <v>0.5231297688284171</v>
       </c>
       <c r="W5" t="n">
-        <v>1.204959193771086</v>
+        <v>1.204959193771084</v>
       </c>
       <c r="X5" t="n">
-        <v>0.424226934507131</v>
+        <v>0.4242269345071304</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.039845667550546</v>
+        <v>1.039845667550542</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.401302788361016</v>
+        <v>0.4013027883610154</v>
       </c>
       <c r="AA5" t="n">
         <v>0.1037599676843294</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4744062518852403</v>
+        <v>0.4744062518852394</v>
       </c>
     </row>
     <row r="6">
@@ -8678,82 +8678,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.744161799944763</v>
+        <v>1.782434546966791</v>
       </c>
       <c r="C6" t="n">
-        <v>6.747910640447823</v>
+        <v>6.74791064044781</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7831878875876</v>
+        <v>1.783187887587599</v>
       </c>
       <c r="E6" t="n">
-        <v>1.824544394744866</v>
+        <v>6.786271647722829</v>
       </c>
       <c r="F6" t="n">
-        <v>1.826569706811172</v>
+        <v>6.788296959789128</v>
       </c>
       <c r="G6" t="n">
-        <v>6.75429107306748</v>
+        <v>1.792563820089514</v>
       </c>
       <c r="H6" t="n">
-        <v>1.798780957572358</v>
+        <v>6.760508210550316</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7832594993446</v>
+        <v>6.74498675232256</v>
       </c>
       <c r="J6" t="n">
-        <v>6.775280042069259</v>
+        <v>1.813552789091292</v>
       </c>
       <c r="K6" t="n">
-        <v>1.784321763660188</v>
+        <v>6.746049016638148</v>
       </c>
       <c r="L6" t="n">
-        <v>6.745207479202596</v>
+        <v>1.78348022622462</v>
       </c>
       <c r="M6" t="n">
-        <v>1.870284442261406</v>
+        <v>6.832011695239366</v>
       </c>
       <c r="N6" t="n">
-        <v>1.803160874217471</v>
+        <v>1.80316087421747</v>
       </c>
       <c r="O6" t="n">
-        <v>6.877075288516711</v>
+        <v>1.914799386471673</v>
       </c>
       <c r="P6" t="n">
-        <v>1.750963115790141</v>
+        <v>1.75096311579014</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.815843577602546</v>
+        <v>6.777570830580507</v>
       </c>
       <c r="R6" t="n">
-        <v>6.747377372923602</v>
+        <v>6.747377372923595</v>
       </c>
       <c r="S6" t="n">
-        <v>1.784761938500772</v>
+        <v>1.784761938500771</v>
       </c>
       <c r="T6" t="n">
-        <v>1.821372412957592</v>
+        <v>1.821372412957591</v>
       </c>
       <c r="U6" t="n">
-        <v>6.791650528254768</v>
+        <v>1.829923275276798</v>
       </c>
       <c r="V6" t="n">
-        <v>6.776982606033215</v>
+        <v>6.77698260603321</v>
       </c>
       <c r="W6" t="n">
-        <v>1.939176426924567</v>
+        <v>1.939176426924572</v>
       </c>
       <c r="X6" t="n">
-        <v>6.766825400364101</v>
+        <v>1.805098147386136</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.917877268385205</v>
+        <v>1.917877268385204</v>
       </c>
       <c r="Z6" t="n">
         <v>1.806874652148057</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.748729606868435</v>
+        <v>6.748729606868421</v>
       </c>
       <c r="AB6" t="n">
         <v>1.806052222580036</v>
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01457839964131346</v>
+        <v>0.01457839964131342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01832724014437596</v>
+        <v>0.01832724014437591</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0153317402621224</v>
+        <v>0.01533174026212236</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05668824741938762</v>
+        <v>0.05668824741938761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.058713559485694</v>
+        <v>0.05871355948569379</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02470767276403611</v>
+        <v>0.02470767276403596</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03092481024688102</v>
+        <v>0.03092481024688099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01540335201912246</v>
+        <v>0.01540335201912248</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04569664176581394</v>
+        <v>0.04569664176581389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01646561633471017</v>
+        <v>0.01646561633471012</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01562407889914262</v>
+        <v>0.01562407889914254</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1024282949359272</v>
+        <v>0.1024282949359271</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03537345747313561</v>
+        <v>0.03537345747313556</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1470118751274197</v>
+        <v>0.1470118751274198</v>
       </c>
       <c r="P7" t="n">
         <v>0.08549429708737689</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04798743027706689</v>
+        <v>0.04798743027706694</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0177939726201598</v>
+        <v>0.01779397262015977</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01690579117529132</v>
+        <v>0.01690579117529135</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05351626563211287</v>
+        <v>0.05351626563211292</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06204931651988434</v>
+        <v>0.06204931651988449</v>
       </c>
       <c r="V7" t="n">
         <v>0.04739920572976657</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08109837862894836</v>
+        <v>0.08109837862894831</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03724200006065821</v>
+        <v>0.03724200006065811</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07249955148685482</v>
+        <v>0.07249955148685466</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03901850482257917</v>
+        <v>0.03901850482257908</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01914620656497923</v>
+        <v>0.01914620656497936</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03829592064019176</v>
+        <v>0.03829592064019167</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01724199204495871</v>
+        <v>0.01724199204495881</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02531180383000649</v>
+        <v>0.02531180383000629</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02231630394775292</v>
+        <v>0.02231630394775273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06367281110501821</v>
+        <v>0.06137202135945753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06205030871400367</v>
+        <v>0.06205030871400361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03169223644966641</v>
+        <v>0.03258821799295553</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03790937393251134</v>
+        <v>0.03790937393251136</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0223879157047529</v>
+        <v>0.02238791570475286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0526812054514444</v>
+        <v>0.05268120545144427</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0234501800203405</v>
+        <v>0.02345018002034049</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02260864258477294</v>
+        <v>0.02260864258477291</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1094128586215578</v>
+        <v>0.109412858621554</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03900854553067546</v>
+        <v>0.03900854553067544</v>
       </c>
       <c r="O8" t="n">
         <v>0.1515675227668512</v>
       </c>
       <c r="P8" t="n">
-        <v>0.089824316518559</v>
+        <v>0.08982431651855892</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04980185320435056</v>
+        <v>0.04980185320435038</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02477853630579023</v>
+        <v>0.02477853630579015</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02389035486092172</v>
+        <v>0.02389035486092173</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06050082931774341</v>
+        <v>0.06050082931774325</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06637989851880767</v>
+        <v>0.06692895311187522</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05438376941539694</v>
+        <v>0.05318763889856932</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08808379150221812</v>
+        <v>0.08808379150221811</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03945244858752151</v>
+        <v>0.03945244858752141</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08375687034189268</v>
+        <v>0.08375687034189278</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0460030685082097</v>
+        <v>0.04160183296688744</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02613077025060982</v>
+        <v>0.02613077025060974</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04979410013702565</v>
+        <v>0.04979410013702554</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02521224498049589</v>
+        <v>0.02521224498049583</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03304602958167503</v>
+        <v>0.03304602958167489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03005052969942147</v>
+        <v>0.03005052969942135</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07140703685668666</v>
+        <v>0.0704642391402906</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0734323489229928</v>
+        <v>0.06401545363841873</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03942646220133519</v>
+        <v>0.03942645013596143</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04564359968417998</v>
+        <v>0.04564359968417999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03012214145642159</v>
+        <v>0.03012214145642145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06041543120311291</v>
+        <v>0.06041543120311292</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03118440577200908</v>
+        <v>0.03118440577200909</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03034286833644166</v>
+        <v>0.03034286833644155</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1171470843732262</v>
+        <v>0.1171470843732261</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05009224691043469</v>
+        <v>0.05009224691043455</v>
       </c>
       <c r="O9" t="n">
         <v>0.1630844882261537</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1018613256549233</v>
+        <v>0.1018613256549231</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06270620764899258</v>
+        <v>0.06270620764899244</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03251276205745898</v>
+        <v>0.03251276205745877</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03162458061259053</v>
+        <v>0.03162458061259035</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0682350550694119</v>
+        <v>0.06823505506941188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07678591738861867</v>
+        <v>0.07678591738861865</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06211799516706557</v>
+        <v>0.0668319003735084</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09581716806624725</v>
+        <v>0.09581716806624721</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05196078949795717</v>
+        <v>0.05196078949795713</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.08721834092415368</v>
+        <v>0.08721834092415369</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05373729425987821</v>
+        <v>0.05127443142509007</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03386499600227844</v>
+        <v>0.03386499600227837</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05301471007749081</v>
+        <v>0.05301471007749063</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05249610417725028</v>
+        <v>0.05247843093836461</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04891039605956912</v>
+        <v>0.0488976658139286</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05293181507703493</v>
+        <v>0.05290832245525293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0586838031630005</v>
+        <v>0.05862799455872881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05335322395595251</v>
+        <v>0.05332448259533213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05342514870240177</v>
+        <v>0.05337695148040524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05463552461586196</v>
+        <v>0.05458490810743861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05312466403762532</v>
+        <v>0.05307834633656791</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05482069543842386</v>
+        <v>0.05478054349452838</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0539292435686051</v>
+        <v>0.0541162992201687</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05258899138530479</v>
+        <v>0.05258201969309177</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05424467999642074</v>
+        <v>0.05420646017273223</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05367799778186941</v>
+        <v>0.05364536673168174</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05780080299884615</v>
+        <v>0.05778875353578213</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05719838627152804</v>
+        <v>0.05711501058552006</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05362037075720044</v>
+        <v>0.05357620081717465</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05365944233472141</v>
+        <v>0.05370654195283431</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05259388023921946</v>
+        <v>0.05250278200967524</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05538908790472787</v>
+        <v>0.05550975131770131</v>
       </c>
       <c r="U2" t="n">
-        <v>0.21961834436818</v>
+        <v>0.2200282382281904</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05613237589934672</v>
+        <v>0.05608844293452288</v>
       </c>
       <c r="W2" t="n">
-        <v>0.242452720618676</v>
+        <v>0.242990759978907</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05254090302313216</v>
+        <v>0.05249044896808425</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05868017785546387</v>
+        <v>0.05866876346113612</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2053849525540615</v>
+        <v>0.2053151623172736</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05289112467221206</v>
+        <v>0.052952194292058</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05283770303347416</v>
+        <v>0.0528280742435159</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02446036012354033</v>
+        <v>0.02452438566753731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02009575958668366</v>
+        <v>0.02007835705706199</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02758511099094287</v>
+        <v>0.02760824177257914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06861813400343411</v>
+        <v>0.0684105262034549</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03061181454401471</v>
+        <v>0.03059734582848656</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03107490567841461</v>
+        <v>0.03092186511051215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03982173802832311</v>
+        <v>0.03965029200577638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02896942796695342</v>
+        <v>0.02882907959195157</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04102792478522283</v>
+        <v>0.04093223173918265</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03471998430200664</v>
+        <v>0.03624961902645649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02512557582085711</v>
+        <v>0.02526645307840131</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03717677535500812</v>
+        <v>0.03709387203301345</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03291062044102208</v>
+        <v>0.03286835170384867</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04539446859125845</v>
+        <v>0.04537271902658577</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0579170170606832</v>
+        <v>0.05751378473343281</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03250303239211665</v>
+        <v>0.0323782468737047</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03280764366975194</v>
+        <v>0.03333692677844047</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02515756965080526</v>
+        <v>0.02469900864892222</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04518098988299148</v>
+        <v>0.04623633765644799</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3146208561827423</v>
+        <v>0.315232230553875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05032002483738887</v>
+        <v>0.05019730875816087</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3747921884789957</v>
+        <v>0.375740059856874</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02478594433012628</v>
+        <v>0.02461615122682073</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06861120196268169</v>
+        <v>0.06872036372368777</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2989184813374877</v>
+        <v>0.2987547828442114</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02728472848669081</v>
+        <v>0.02791167296826054</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02719578020961433</v>
+        <v>0.02731552619950392</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01275906277122135</v>
+        <v>0.01022723357006142</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01588550403979021</v>
+        <v>0.01316857672051148</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01768061782120564</v>
+        <v>0.01508305601318307</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0826519692974348</v>
+        <v>0.07968938360110488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02244062496624134</v>
+        <v>0.01978377623850036</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02325304806440359</v>
+        <v>0.02037643643228056</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03692480080736532</v>
+        <v>0.03402086222212506</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01985893554597822</v>
+        <v>0.01700355396748525</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03912475679096034</v>
+        <v>0.03633907565058467</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02894703147326563</v>
+        <v>0.02872770926967225</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01380826651642402</v>
+        <v>0.0113973162078853</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03284608788626307</v>
+        <v>0.030081279507307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02610909473331412</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03800432417910653</v>
+        <v>0.03527582284415887</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06587350218272374</v>
+        <v>0.06259953361669816</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02545817097993661</v>
+        <v>0.02262704935031431</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02589950242185027</v>
+        <v>0.02409931243747504</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01386348837037362</v>
+        <v>0.01050229012256093</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04543664481134485</v>
+        <v>0.04446739173093834</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04261322872416945</v>
+        <v>0.03975136056013</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05455633226977899</v>
+        <v>0.05172824078367555</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08843794850039581</v>
+        <v>0.08583619672766134</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01326508634394386</v>
+        <v>0.01036298274431121</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08298964860389808</v>
+        <v>0.0805258450909023</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05838039806060288</v>
+        <v>0.05555539502715678</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01722100098021944</v>
+        <v>0.01557860859193813</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01712045745403578</v>
+        <v>0.01467414946144487</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04084186896405664</v>
+        <v>0.04059539232546062</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1093969912434256</v>
+        <v>0.1056533349325082</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1489025784742497</v>
+        <v>0.1477118591037779</v>
       </c>
       <c r="E5" t="n">
-        <v>1.445872725049494</v>
+        <v>1.437273080191894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2561034603328768</v>
+        <v>0.2536362233869187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2426041610984272</v>
+        <v>0.235881118341114</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5823032892039656</v>
+        <v>0.5743530433448122</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1974909224549836</v>
+        <v>0.1907662620145819</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5559517587580203</v>
+        <v>0.5510159903412808</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3853983801243484</v>
+        <v>0.4343650127587304</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06332275853671569</v>
+        <v>0.06579238806038107</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4775389607383546</v>
+        <v>0.4727196404175456</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6052756929387425</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4991512286225431</v>
+        <v>0.4952225281822397</v>
       </c>
       <c r="P5" t="n">
-        <v>1.048779860824713</v>
+        <v>1.034577154458527</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3077041721960157</v>
+        <v>0.3016072391868139</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3318994008526341</v>
+        <v>0.3481520535303924</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06271228486906963</v>
+        <v>0.04662666314633558</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7424405446754748</v>
+        <v>0.7760423406308405</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6214011981067808</v>
+        <v>0.6149056186984423</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8136653808468978</v>
+        <v>0.807847449741562</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57396820965843</v>
+        <v>1.572612511365519</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05451059247112628</v>
+        <v>0.04689059980322734</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.456306238216784</v>
+        <v>1.457760720389636</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9168542154809158</v>
+        <v>0.9111218783606441</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.133719400653602</v>
+        <v>0.1519353667698065</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1430471508626802</v>
+        <v>0.1452424131421431</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.735499563210245</v>
+        <v>2.041885041321475</v>
       </c>
       <c r="C6" t="n">
-        <v>7.738626004478817</v>
+        <v>7.735879673185191</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049356800820997</v>
+        <v>7.737794152477865</v>
       </c>
       <c r="E6" t="n">
-        <v>2.114328152297224</v>
+        <v>7.802400480065784</v>
       </c>
       <c r="F6" t="n">
-        <v>7.745181125405275</v>
+        <v>2.051441583989915</v>
       </c>
       <c r="G6" t="n">
-        <v>7.745993548503434</v>
+        <v>7.743087532896958</v>
       </c>
       <c r="H6" t="n">
-        <v>7.759665301246391</v>
+        <v>7.756731958686809</v>
       </c>
       <c r="I6" t="n">
-        <v>2.051535118545767</v>
+        <v>2.048661361718901</v>
       </c>
       <c r="J6" t="n">
-        <v>7.761865257229995</v>
+        <v>2.067996883401999</v>
       </c>
       <c r="K6" t="n">
-        <v>2.060623214473058</v>
+        <v>7.751438805734354</v>
       </c>
       <c r="L6" t="n">
-        <v>2.045484449516214</v>
+        <v>7.734108412672568</v>
       </c>
       <c r="M6" t="n">
-        <v>2.064522270886055</v>
+        <v>7.752792375971987</v>
       </c>
       <c r="N6" t="n">
-        <v>2.057548612566317</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O6" t="n">
-        <v>7.761205966900397</v>
+        <v>2.066698885112092</v>
       </c>
       <c r="P6" t="n">
-        <v>7.789075211881581</v>
+        <v>7.785786329330945</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.057134353979727</v>
+        <v>7.745338145814999</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05757568542164</v>
+        <v>7.74681040890215</v>
       </c>
       <c r="S6" t="n">
-        <v>7.736603988809405</v>
+        <v>2.042160097873976</v>
       </c>
       <c r="T6" t="n">
-        <v>2.077112827811136</v>
+        <v>2.076125199482353</v>
       </c>
       <c r="U6" t="n">
-        <v>2.073910782901148</v>
+        <v>2.071033210329058</v>
       </c>
       <c r="V6" t="n">
-        <v>7.777296832708805</v>
+        <v>7.774439337248353</v>
       </c>
       <c r="W6" t="n">
-        <v>7.811639640392536</v>
+        <v>7.80902298070398</v>
       </c>
       <c r="X6" t="n">
-        <v>7.736005586782984</v>
+        <v>7.733074079208995</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.203078679787432</v>
+        <v>2.200600537420836</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.090056581060394</v>
+        <v>2.087213202778572</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.048897183980009</v>
+        <v>7.738289705056625</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04838559209751</v>
+        <v>2.045924495257484</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0163979312864526</v>
+        <v>0.01389204371120112</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01952437255502142</v>
+        <v>0.01683338686165124</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02131948633643681</v>
+        <v>0.01874786615432276</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08629083781266594</v>
+        <v>0.08335419374224452</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02607949348147258</v>
+        <v>0.02344858637963993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02689191657963477</v>
+        <v>0.02404124657342032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04056366932259649</v>
+        <v>0.03768567236326481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02349780406120933</v>
+        <v>0.02066836410862501</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04276362530619154</v>
+        <v>0.04000388579172438</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03258589998849679</v>
+        <v>0.032392519410812</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01744713503165515</v>
+        <v>0.01506212634902522</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03648495640149423</v>
+        <v>0.03374608964844675</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02974796324854532</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04164304154710981</v>
+        <v>0.03894048100748203</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06951221955072684</v>
+        <v>0.06626419178002133</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02909703949516786</v>
+        <v>0.02629185949145393</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02953837093708136</v>
+        <v>0.02776412257861485</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01750235688560479</v>
+        <v>0.01416710026370059</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04907551332657608</v>
+        <v>0.04813220187207812</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04588791838705528</v>
+        <v>0.04305639294881779</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05819520078501027</v>
+        <v>0.05539305092481525</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09207681701562707</v>
+        <v>0.0895010068688009</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01690395485917507</v>
+        <v>0.01402779288545097</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08624988829631575</v>
+        <v>0.08381469724955706</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06201926657583402</v>
+        <v>0.05922020516829653</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0208598694954506</v>
+        <v>0.01924341873307786</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02075932596926694</v>
+        <v>0.0183389596025845</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01932663290072536</v>
+        <v>0.01681532400325894</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02745605649512765</v>
+        <v>0.02477262336377737</v>
       </c>
       <c r="D8" t="n">
-        <v>0.029251170276543</v>
+        <v>0.02668710265644905</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09155858124474309</v>
+        <v>0.08862258152565304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02978760127000929</v>
+        <v>0.02715329402551682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03586100149578629</v>
+        <v>0.03302057427102165</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04849535326270275</v>
+        <v>0.04562490886539099</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03142948800131563</v>
+        <v>0.02860760061075112</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05069530924629777</v>
+        <v>0.04794312229385063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04051758392860297</v>
+        <v>0.04033175591293815</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02537881897176143</v>
+        <v>0.02300136285115135</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04441664034160101</v>
+        <v>0.04168532615057435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03380149890321742</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04676247716680038</v>
+        <v>0.04406017682104639</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07437041438354926</v>
+        <v>0.07112196934921659</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03104254089721304</v>
+        <v>0.02822938990686247</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03747005487718781</v>
+        <v>0.03570335908074097</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02543404082571101</v>
+        <v>0.02210633676582681</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05700719726668237</v>
+        <v>0.05607143837420438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05137457896016862</v>
+        <v>0.04854388499713856</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06477197488849611</v>
+        <v>0.0619753113252559</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1000094841765275</v>
+        <v>0.09744122914165283</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01930798952719657</v>
+        <v>0.01642504564922341</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09917528122702178</v>
+        <v>0.09676283738592521</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.06485503522559523</v>
+        <v>0.062050311499263</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02879155343555691</v>
+        <v>0.02718265523520407</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0339170432833044</v>
+        <v>0.03151778178576914</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03521353430976212</v>
+        <v>0.03259074285704551</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0449111343746926</v>
+        <v>0.04207806066883356</v>
       </c>
       <c r="D9" t="n">
-        <v>0.046706248156108</v>
+        <v>0.04399253996150515</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1101610109044725</v>
+        <v>0.1070880912154246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03631792739816705</v>
+        <v>0.03360298859149359</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05227868869444979</v>
+        <v>0.04928593067343607</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06595043114226777</v>
+        <v>0.0629303461704471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04888456588088065</v>
+        <v>0.04591303791580731</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06815038712586284</v>
+        <v>0.06524855959890678</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05797266180816799</v>
+        <v>0.05763719321799432</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04283389685132647</v>
+        <v>0.04030680015620776</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0618717182211654</v>
+        <v>0.05899076345562908</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05513472506821639</v>
+        <v>0.3152386798576731</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06920764164186706</v>
+        <v>0.06635464792789182</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09755042699395736</v>
+        <v>0.0941501509392427</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05448381160998286</v>
+        <v>0.05153654359146975</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05492513275675273</v>
+        <v>0.05300879638579715</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04288911870527597</v>
+        <v>0.03941177407088294</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07446227514624719</v>
+        <v>0.07337687567926049</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07126023023625838</v>
+        <v>0.06828488652596715</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09116494946503242</v>
+        <v>0.08819164967917059</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1174635788352982</v>
+        <v>0.1147456806759833</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04229071667884626</v>
+        <v>0.03927246669263337</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1116366501159871</v>
+        <v>0.1090593710567394</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08344420805962628</v>
+        <v>0.08051824243264114</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0462466313151219</v>
+        <v>0.04448809254026019</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04614608778893822</v>
+        <v>0.04358363340976688</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05135595151607757</v>
+        <v>0.05101045840617227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04769212650795212</v>
+        <v>0.04730616822044485</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05158521577176855</v>
+        <v>0.05124038199343629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05256071130488514</v>
+        <v>0.05221474628063182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05800167515682826</v>
+        <v>0.05765638610096264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05423201848557894</v>
+        <v>0.05388539692852012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05298275238688754</v>
+        <v>0.05263977800293993</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0521311530435663</v>
+        <v>0.05201805757693787</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05418336254817883</v>
+        <v>0.0538556370254445</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05497714508468824</v>
+        <v>0.05494770179019159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05419970014624108</v>
+        <v>0.05385368593077275</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05609466934162922</v>
+        <v>0.05574749267010665</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05358130669221419</v>
+        <v>0.05323619484509458</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07002640695009268</v>
+        <v>0.06947642127626164</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05810058632481069</v>
+        <v>0.05775514385919943</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0530138780533836</v>
+        <v>0.05266887579768275</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05231545746726524</v>
+        <v>0.05205287724951074</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05491755157324389</v>
+        <v>0.05456968491197115</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05581672818970077</v>
+        <v>0.05576777123488171</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2183113284743774</v>
+        <v>0.2177373072734186</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05231119641916449</v>
+        <v>0.05196513983085305</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2371478299067226</v>
+        <v>0.2365188706359173</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05461928309826788</v>
+        <v>0.05426968084837701</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0540078858581779</v>
+        <v>0.05365970182823698</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1979646475575593</v>
+        <v>0.1975425573947261</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05209292221232725</v>
+        <v>0.05181705128104301</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05329412839015947</v>
+        <v>0.05303277834841408</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02300578572167108</v>
+        <v>0.02265986476813916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01842012141216409</v>
+        <v>0.01801218624955284</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02464356821074959</v>
+        <v>0.02430215525997259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03156774045971152</v>
+        <v>0.03121788696462069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07048801965666819</v>
+        <v>0.07014339700481791</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04339811887326307</v>
+        <v>0.04304406295662482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03466598659536714</v>
+        <v>0.03433792516121603</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02855014848564627</v>
+        <v>0.0298656460248317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04312425375391451</v>
+        <v>0.04290512726427953</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04872756429475762</v>
+        <v>0.05062587482147815</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04319777130449836</v>
+        <v>0.04284797137005235</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05668585053734738</v>
+        <v>0.05632687738244867</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03891265200073132</v>
+        <v>0.03856944790980165</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1106951633868654</v>
+        <v>0.1100136425895439</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07085629885281719</v>
+        <v>0.07051072446452146</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03481272726272187</v>
+        <v>0.03447020022864875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02988011928421846</v>
+        <v>0.03012795539652727</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04828009189685013</v>
+        <v>0.04791727308789623</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05492085221344342</v>
+        <v>0.05669635777535402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3172016314701546</v>
+        <v>0.3165871924982139</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02978371752513688</v>
+        <v>0.02943367579598971</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3499344684522135</v>
+        <v>0.3491019112183526</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04626557285339938</v>
+        <v>0.04589022946784971</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04195029452357563</v>
+        <v>0.04158515987116162</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2685341493860686</v>
+        <v>0.2680773931024877</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02826900436895122</v>
+        <v>0.02842032025066046</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03691282434531976</v>
+        <v>0.03716189042396633</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00789690340106252</v>
+        <v>0.006047053732583229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01088139709661391</v>
+        <v>0.009041670567652947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01048654863585996</v>
+        <v>0.00864414642080639</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02150521943252855</v>
+        <v>0.01965003927439718</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08296340910725787</v>
+        <v>0.08111586432302684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0403834028777534</v>
+        <v>0.03852080687956323</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02627236760223554</v>
+        <v>0.02445096810211971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01665316126436905</v>
+        <v>0.01742834988490003</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03991965869144302</v>
+        <v>0.03827049284345166</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04879995058986272</v>
+        <v>0.05052002897652205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04001835236776127</v>
+        <v>0.03816261657222729</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06114363763333309</v>
+        <v>0.05927332899300929</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O4" t="n">
-        <v>0.12597752491158</v>
+        <v>0.1241319393247082</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08408065625100528</v>
+        <v>0.08223137863312477</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0266239463238223</v>
+        <v>0.02477964107938627</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01873496451427276</v>
+        <v>0.01782165410445131</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04812681446372894</v>
+        <v>0.04625015444066691</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05828342798829031</v>
+        <v>0.05978309060487991</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04608176413705906</v>
+        <v>0.04452783599980171</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01925812855248244</v>
+        <v>0.01740174438618894</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04958598119983722</v>
+        <v>0.04769757453269167</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04475773482859759</v>
+        <v>0.04286147053368375</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03742329654051813</v>
+        <v>0.03561289695910957</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01522554955402966</v>
+        <v>0.01340831643182251</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01622132643847366</v>
+        <v>0.015157891305303</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02981802043760649</v>
+        <v>0.02890431244318604</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01625649536466141</v>
+        <v>0.01381885736551855</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06886012431678827</v>
+        <v>0.06648850274236802</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06284223499814325</v>
+        <v>0.06043387508031697</v>
       </c>
       <c r="E5" t="n">
-        <v>0.238039290569532</v>
+        <v>0.2352148542003212</v>
       </c>
       <c r="F5" t="n">
-        <v>1.370554279168798</v>
+        <v>1.368075505496998</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5212361742673212</v>
+        <v>0.5185310271654642</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3669825901604911</v>
+        <v>0.364987635871891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1771941990012251</v>
+        <v>0.2226279127864833</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5496365551586216</v>
+        <v>0.5507414007638546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6760250633090589</v>
+        <v>0.7308032487831158</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5304870592663199</v>
+        <v>0.5278624903803691</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9638837862354679</v>
+        <v>0.9609532539611996</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O5" t="n">
-        <v>1.854364798054281</v>
+        <v>1.85194113867274</v>
       </c>
       <c r="P5" t="n">
-        <v>1.215333619287988</v>
+        <v>1.21289838485442</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3341242293760337</v>
+        <v>0.3317279954001422</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2215705269826594</v>
+        <v>0.2367354571311508</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6526405858359837</v>
+        <v>0.6497506828681743</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9479924697708962</v>
+        <v>1.007404808842251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6217426584466327</v>
+        <v>0.6227326043481696</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1870926764782086</v>
+        <v>0.1844908886611977</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7516232757962934</v>
+        <v>0.7485058697349504</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6522537684379843</v>
+        <v>0.6489458269116732</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5551368044461478</v>
+        <v>0.5521571889830463</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1273454045945403</v>
+        <v>0.1253601688308275</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1652610432592668</v>
+        <v>0.1769085759380697</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4343767603006624</v>
+        <v>0.4496464945099778</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.777531555333758</v>
+        <v>1.775592795302925</v>
       </c>
       <c r="C6" t="n">
-        <v>1.780516049029311</v>
+        <v>6.740785450240699</v>
       </c>
       <c r="D6" t="n">
-        <v>6.742452459423792</v>
+        <v>1.778189887991149</v>
       </c>
       <c r="E6" t="n">
-        <v>1.791139871365224</v>
+        <v>6.751393818947439</v>
       </c>
       <c r="F6" t="n">
-        <v>1.852598061039954</v>
+        <v>6.812859643996082</v>
       </c>
       <c r="G6" t="n">
-        <v>6.772349313665681</v>
+        <v>1.808066548449905</v>
       </c>
       <c r="H6" t="n">
-        <v>6.758238278390166</v>
+        <v>1.793996709672462</v>
       </c>
       <c r="I6" t="n">
-        <v>6.748619072052306</v>
+        <v>1.786974091455242</v>
       </c>
       <c r="J6" t="n">
-        <v>6.771885569479376</v>
+        <v>6.7700142725165</v>
       </c>
       <c r="K6" t="n">
-        <v>1.818434602522559</v>
+        <v>1.820065770546863</v>
       </c>
       <c r="L6" t="n">
-        <v>6.771984263155688</v>
+        <v>6.769906396245281</v>
       </c>
       <c r="M6" t="n">
-        <v>6.793109548421269</v>
+        <v>1.828819070563351</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O6" t="n">
-        <v>6.85846358974074</v>
+        <v>6.856355765323301</v>
       </c>
       <c r="P6" t="n">
-        <v>6.816564344486061</v>
+        <v>1.74954755190182</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.758589857111757</v>
+        <v>1.794325382649728</v>
       </c>
       <c r="R6" t="n">
-        <v>6.750700875302212</v>
+        <v>1.787367395674792</v>
       </c>
       <c r="S6" t="n">
-        <v>6.780092725251661</v>
+        <v>6.777993934113711</v>
       </c>
       <c r="T6" t="n">
-        <v>1.827918079920986</v>
+        <v>1.829328832175221</v>
       </c>
       <c r="U6" t="n">
-        <v>6.778476100129628</v>
+        <v>6.776630195610732</v>
       </c>
       <c r="V6" t="n">
-        <v>6.751224039340417</v>
+        <v>1.786947485956528</v>
       </c>
       <c r="W6" t="n">
-        <v>1.909413558208042</v>
+        <v>1.907430367419001</v>
       </c>
       <c r="X6" t="n">
-        <v>1.814392386761293</v>
+        <v>6.77460525020673</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.884970654671127</v>
+        <v>1.882998676198374</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.784860201486724</v>
+        <v>1.782954058002163</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.785855978371169</v>
+        <v>6.746901670978353</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.799499526058622</v>
+        <v>1.798507194324151</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01062181928233875</v>
+        <v>0.008707387826441237</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01360631297789009</v>
+        <v>0.01170200466151099</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01321146451713614</v>
+        <v>0.01130448051466438</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02423013531380473</v>
+        <v>0.02231037336825518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08568832498853404</v>
+        <v>0.0837761984168848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04310831875902954</v>
+        <v>0.04118114097342124</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02899728348351165</v>
+        <v>0.02711130219597764</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01937807714564523</v>
+        <v>0.02008868397875798</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04264457457271922</v>
+        <v>0.04093082693730964</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05152486647113896</v>
+        <v>0.05318036307038008</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04274326824903741</v>
+        <v>0.04082295066608524</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06386855351460928</v>
+        <v>0.06193366308686731</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1287023873601207</v>
+        <v>0.1267922094939624</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08680551869954574</v>
+        <v>0.08489164880237894</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02934886220509851</v>
+        <v>0.02743997517324425</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02145988039554891</v>
+        <v>0.02048198819830923</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05085173034500513</v>
+        <v>0.04891048853452489</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06100834386956646</v>
+        <v>0.06244342469873795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04917522807669552</v>
+        <v>0.04750719449784221</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02198304443375859</v>
+        <v>0.02006207848004687</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05231089708111342</v>
+        <v>0.05035790862654968</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04748265070987371</v>
+        <v>0.04552180462754179</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04057663762643052</v>
+        <v>0.03863181099084768</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01795046543530581</v>
+        <v>0.01606865052568048</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01894624231974978</v>
+        <v>0.01781822539916102</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03254293631888269</v>
+        <v>0.03156464653704402</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01335716900768132</v>
+        <v>0.01134120235337643</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02058462131033353</v>
+        <v>0.01838995007369437</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02018977284957957</v>
+        <v>0.01799242592684776</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0289491933488455</v>
+        <v>0.0268396136744279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08908467807556487</v>
+        <v>0.08704159915354126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05096643219841858</v>
+        <v>0.04870973683449493</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03597559181595508</v>
+        <v>0.03379924760816106</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02635638547808866</v>
+        <v>0.02677662939094139</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0496228829051625</v>
+        <v>0.04761877234949298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0585031748035823</v>
+        <v>0.05986830848256341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0497215765814808</v>
+        <v>0.04751089607826864</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0708468618470576</v>
+        <v>0.06862160849906575</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1332955928825419</v>
+        <v>0.1312012110722149</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09117716960249768</v>
+        <v>0.08908895578024308</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03125037372527006</v>
+        <v>0.02927706045155104</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02843818872799231</v>
+        <v>0.02716993361049265</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05783003867744849</v>
+        <v>0.05559843394670826</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06798665220200988</v>
+        <v>0.06913137011092126</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05409612017582094</v>
+        <v>0.0522253232379551</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02775055236940015</v>
+        <v>0.0256082123397086</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05929003926946488</v>
+        <v>0.05704665078663612</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04977303781294948</v>
+        <v>0.04773045905410361</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.05169431138573988</v>
+        <v>0.04929833016509007</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02060700002681502</v>
+        <v>0.01862715749045719</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02592455065219318</v>
+        <v>0.02450617081134444</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04395336970027252</v>
+        <v>0.04248747065515863</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02361148620420005</v>
+        <v>0.0194071404360767</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03127862985126594</v>
+        <v>0.02639701206142929</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03088378139051185</v>
+        <v>0.02599948791458266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04082171287395146</v>
+        <v>0.03608328935439349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09256586046641016</v>
+        <v>0.08926105804545263</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06078063198629722</v>
+        <v>0.05587614459731879</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04666960035688739</v>
+        <v>0.04180630959589602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03705039401902097</v>
+        <v>0.03478369137867633</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06031689144609498</v>
+        <v>0.05562583433722799</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0691971833445147</v>
+        <v>0.0678753704702984</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06041558512241312</v>
+        <v>0.0555179580660036</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08154087038798503</v>
+        <v>0.07662867048678554</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4734777156772439</v>
+        <v>0.4711140543954614</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1479265768743341</v>
+        <v>0.1428112979972561</v>
       </c>
       <c r="P9" t="n">
-        <v>0.106367203059754</v>
+        <v>0.1011986891469659</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04702117543236651</v>
+        <v>0.04213497879714186</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03913219726892474</v>
+        <v>0.03517699559822763</v>
       </c>
       <c r="S9" t="n">
-        <v>0.068524047218381</v>
+        <v>0.06360549593444323</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07868066074294239</v>
+        <v>0.07713843209865624</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06690742209634762</v>
+        <v>0.06224175743145812</v>
       </c>
       <c r="V9" t="n">
-        <v>0.04505902109038108</v>
+        <v>0.03936750604870362</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0699832139544892</v>
+        <v>0.06505291602646805</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0651549675832494</v>
+        <v>0.06021681202746012</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05824895449980634</v>
+        <v>0.05332681839076599</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03279955933756983</v>
+        <v>0.0283548730595602</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03661855919312554</v>
+        <v>0.03251323279907933</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05021525319225836</v>
+        <v>0.04625965393696237</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05235143385993509</v>
+        <v>0.05230576440450131</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04900745160428304</v>
+        <v>0.04896556330623313</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05245354864310585</v>
+        <v>0.05240992019875998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05800278621248221</v>
+        <v>0.05792409886938533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05325222246388581</v>
+        <v>0.05319409355419891</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05312416637538398</v>
+        <v>0.05304782053717546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05453006510080555</v>
+        <v>0.05447462810846709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05269789651306735</v>
+        <v>0.05317159413674229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05443177591846973</v>
+        <v>0.05438515393324154</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05341361134424869</v>
+        <v>0.05362833238144542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05238768462327514</v>
+        <v>0.05235328494830086</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05350422140764217</v>
+        <v>0.05343898439644616</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05325754838989961</v>
+        <v>0.05319698488936448</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0641090164363254</v>
+        <v>0.06402786277469433</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05671509729809648</v>
+        <v>0.05658288924070592</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05458662117171032</v>
+        <v>0.05451781654421278</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05283776846497273</v>
+        <v>0.0539944941599227</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05248141590577368</v>
+        <v>0.05235774216839513</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05474201501073938</v>
+        <v>0.05505572169615713</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2193219891599754</v>
+        <v>0.2196072760032521</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05646877712404483</v>
+        <v>0.05640653389394107</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2418283004362837</v>
+        <v>0.242199576461823</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05247268270900605</v>
+        <v>0.05239050758248793</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05869395387384788</v>
+        <v>0.05865105178997598</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2051453525470996</v>
+        <v>0.20503970118087</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05275450808016543</v>
+        <v>0.05307085430650403</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05272918017255088</v>
+        <v>0.0526873755897745</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02400593747347993</v>
+        <v>0.02402287615947126</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02125070214473236</v>
+        <v>0.02121579978748401</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02473995303387399</v>
+        <v>0.02477210702630161</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06432731721445098</v>
+        <v>0.0641090764959847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03045863962048511</v>
+        <v>0.03038687808770953</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029504499273945</v>
+        <v>0.02930330679887432</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03964100276886808</v>
+        <v>0.03958853938346264</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02649128496071649</v>
+        <v>0.03022939673505448</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03882128591381363</v>
+        <v>0.03883252025496833</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03157996421032764</v>
+        <v>0.03345271967514964</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02426562805120924</v>
+        <v>0.02436340057662646</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03247925315175501</v>
+        <v>0.03235684977803393</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03048331674858776</v>
+        <v>0.03039430533192033</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07670513645603444</v>
+        <v>0.0765842531561908</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05504861795047633</v>
+        <v>0.05445012189013341</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03998402561979493</v>
+        <v>0.03983607833714253</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02749647137799268</v>
+        <v>0.03613427586607734</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0249313834789538</v>
+        <v>0.02439334344688585</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0411208449727172</v>
+        <v>0.04371074846772248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3130439823228524</v>
+        <v>0.3134828535687009</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05322986608679056</v>
+        <v>0.05312891016795351</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3709576448827557</v>
+        <v>0.3716340050375174</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02487577039566577</v>
+        <v>0.02463215023274534</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06925857660399704</v>
+        <v>0.06929554124463287</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2978321261596271</v>
+        <v>0.2976445036173785</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02688485390349976</v>
+        <v>0.02948634392950533</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02698248123121027</v>
+        <v>0.02702622587876874</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01159352420449188</v>
+        <v>0.009625875273664996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01722538605802366</v>
+        <v>0.01513766114301558</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01274695765552657</v>
+        <v>0.01080236288384843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07542814877703535</v>
+        <v>0.07308754761607472</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02176834586934522</v>
+        <v>0.01965996167109722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02032189344100612</v>
+        <v>0.01800774065490496</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03620216629000944</v>
+        <v>0.03412418853655473</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01550697925231565</v>
+        <v>0.01940582040068161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03520414474441786</v>
+        <v>0.03322601915881589</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02359130751559797</v>
+        <v>0.02456488898457641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01200299325259255</v>
+        <v>0.01016264167641062</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02500662059806242</v>
+        <v>0.02281842193186881</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02182850465371876</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08064910536258903</v>
+        <v>0.07851740622248728</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06088311012288215</v>
+        <v>0.05793796787322882</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03684099312795695</v>
+        <v>0.03461202178596499</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01708689729336351</v>
+        <v>0.02870085471521703</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01306173120693391</v>
+        <v>0.01021298802779795</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03859623802448783</v>
+        <v>0.04068790792577105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03972263662847166</v>
+        <v>0.03750219160128207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05885073624002669</v>
+        <v>0.05669771856173408</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0819483712167715</v>
+        <v>0.07992051220166642</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01296308573197451</v>
+        <v>0.01058308845281127</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08368067087590966</v>
+        <v>0.081748556823836</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05625791288910251</v>
+        <v>0.05407175884522053</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01614643294529561</v>
+        <v>0.01826791767552909</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01633617269458106</v>
+        <v>0.01440920476346754</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02779469454024236</v>
+        <v>0.0272583268206873</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1373151328460463</v>
+        <v>0.1346343757941823</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05250529625405482</v>
+        <v>0.05276550386669941</v>
       </c>
       <c r="E5" t="n">
-        <v>1.22776408729117</v>
+        <v>1.220437869739905</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2333761735731735</v>
+        <v>0.2303031121042425</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1836707705835703</v>
+        <v>0.1770319519488816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5409580820324513</v>
+        <v>0.538507660056965</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1088120518014586</v>
+        <v>0.2272208548482063</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4543288540163243</v>
+        <v>0.4541977130832598</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2508730746583471</v>
+        <v>0.304501463821937</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03607473580436792</v>
+        <v>0.03816823042406588</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2997189912110799</v>
+        <v>0.2950428495478357</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5206526782156532</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O5" t="n">
-        <v>1.194381353632407</v>
+        <v>1.190983803904122</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9035844221858976</v>
+        <v>0.8857867753098467</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5193226497958369</v>
+        <v>0.5139736427226996</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1425298517583375</v>
+        <v>0.4206564749386438</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05430833238131882</v>
+        <v>0.03808098628571575</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5679526521341388</v>
+        <v>0.6486628604952751</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5381013447794899</v>
+        <v>0.5329748304653932</v>
       </c>
       <c r="V5" t="n">
-        <v>0.817939250525617</v>
+        <v>0.8140837112994316</v>
       </c>
       <c r="W5" t="n">
-        <v>1.365339852442644</v>
+        <v>1.363899469095705</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05617837035050651</v>
+        <v>0.04783643068868865</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.374467822017672</v>
+        <v>1.374675481085584</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8265446744628944</v>
+        <v>0.822199935541634</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1150795146031898</v>
+        <v>0.1923202404714379</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1297155196030829</v>
+        <v>0.1304145591547364</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.912766758513746</v>
+        <v>1.910761728023527</v>
       </c>
       <c r="C6" t="n">
-        <v>7.243604509208565</v>
+        <v>7.241445020330259</v>
       </c>
       <c r="D6" t="n">
-        <v>7.239126080806066</v>
+        <v>1.91193821563371</v>
       </c>
       <c r="E6" t="n">
-        <v>1.976601383086291</v>
+        <v>7.299394906803315</v>
       </c>
       <c r="F6" t="n">
-        <v>1.922941580178599</v>
+        <v>1.92079581442096</v>
       </c>
       <c r="G6" t="n">
-        <v>1.921495127750262</v>
+        <v>7.244315099842148</v>
       </c>
       <c r="H6" t="n">
-        <v>7.262581289440543</v>
+        <v>7.260431547723798</v>
       </c>
       <c r="I6" t="n">
-        <v>1.916680213561573</v>
+        <v>7.245713179587927</v>
       </c>
       <c r="J6" t="n">
-        <v>7.26158326789495</v>
+        <v>7.25953337834606</v>
       </c>
       <c r="K6" t="n">
-        <v>7.249970430666129</v>
+        <v>1.925700741734439</v>
       </c>
       <c r="L6" t="n">
-        <v>1.913176227561848</v>
+        <v>7.236470000863651</v>
       </c>
       <c r="M6" t="n">
-        <v>1.926179854907317</v>
+        <v>7.249125781119106</v>
       </c>
       <c r="N6" t="n">
-        <v>1.922826163402173</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O6" t="n">
-        <v>7.307452908335804</v>
+        <v>1.979483024513158</v>
       </c>
       <c r="P6" t="n">
-        <v>7.287686672201578</v>
+        <v>7.284680011017526</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.263220116278496</v>
+        <v>1.935747874535828</v>
       </c>
       <c r="R6" t="n">
-        <v>7.243466020443903</v>
+        <v>7.255008213902457</v>
       </c>
       <c r="S6" t="n">
-        <v>7.239440854357469</v>
+        <v>1.911348840777658</v>
       </c>
       <c r="T6" t="n">
-        <v>1.939769472333744</v>
+        <v>1.941823760675634</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94045040552681</v>
+        <v>1.93818830279632</v>
       </c>
       <c r="V6" t="n">
-        <v>7.285229859390562</v>
+        <v>1.957833571311595</v>
       </c>
       <c r="W6" t="n">
-        <v>7.308752063907009</v>
+        <v>2.07780456825035</v>
       </c>
       <c r="X6" t="n">
-        <v>7.239342208882511</v>
+        <v>7.236890447640049</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.067560862034366</v>
+        <v>2.065591408603024</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.282637036039643</v>
+        <v>1.955207611595083</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91731966725455</v>
+        <v>7.244575276862768</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.917162532030277</v>
+        <v>1.915202232792207</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01488301905311738</v>
+        <v>0.01295194284101269</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02051488090664916</v>
+        <v>0.01846372871036337</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01603645250415207</v>
+        <v>0.0141284304511962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07871764362566078</v>
+        <v>0.0764136151834225</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02505784071797073</v>
+        <v>0.022986029238445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0236113882896316</v>
+        <v>0.02133380822225271</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03949166113863493</v>
+        <v>0.03745025610390251</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01879647410094115</v>
+        <v>0.02273188796802937</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03849363959304337</v>
+        <v>0.03655208672616365</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02688080236422345</v>
+        <v>0.02789095655192417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01529248810121804</v>
+        <v>0.01348870924375897</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02829611544668791</v>
+        <v>0.02614448949921656</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02511799950234427</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08393844849073047</v>
+        <v>0.08184331779949519</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06417245325102358</v>
+        <v>0.06126387945023672</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04013048797658245</v>
+        <v>0.03793808935331282</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02037639214198901</v>
+        <v>0.03202692228256479</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01635122605555942</v>
+        <v>0.01353905559514575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04188573287311329</v>
+        <v>0.04401397549311881</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04258192512133797</v>
+        <v>0.04040064197983832</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06214023108865217</v>
+        <v>0.06002378612908123</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08523786606539703</v>
+        <v>0.08324657976901405</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01625258058060001</v>
+        <v>0.0139091560201591</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08652470031361882</v>
+        <v>0.08462488283635937</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05954740773772802</v>
+        <v>0.05739782641256835</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01943592779392111</v>
+        <v>0.02159398524287682</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01962566754320655</v>
+        <v>0.01773527233081531</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01743776686051533</v>
+        <v>0.01547971820063692</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02752296117910178</v>
+        <v>0.02543864147703358</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0230445327766047</v>
+        <v>0.02110334321786643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0833544557271651</v>
+        <v>0.08102055846465189</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0283063656752881</v>
+        <v>0.02620661663043129</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03154289605887983</v>
+        <v>0.02923086390011672</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0464997414110876</v>
+        <v>0.04442516887057277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02580455437339377</v>
+        <v>0.02970680073469962</v>
       </c>
       <c r="J8" t="n">
-        <v>0.045501719865496</v>
+        <v>0.04352699949283394</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03388888263667614</v>
+        <v>0.03486586931859441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02230056837367065</v>
+        <v>0.02046362201042854</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03530419571913906</v>
+        <v>0.03311940226588865</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02867400208602896</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0884432637135342</v>
+        <v>0.08631845230522303</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06844472876024919</v>
+        <v>0.06550679772968576</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04181005431438375</v>
+        <v>0.03959190071343962</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02738447241444162</v>
+        <v>0.03900183504923505</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02335930632801204</v>
+        <v>0.02051396836181592</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04889381314556593</v>
+        <v>0.05098888825978903</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04741307716845119</v>
+        <v>0.0452001086922644</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06794432119507117</v>
+        <v>0.06580227388042852</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09224682153729515</v>
+        <v>0.09022236651831796</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01834030368283336</v>
+        <v>0.01597055635576396</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09798105864121162</v>
+        <v>0.09605102145154408</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0620194326089198</v>
+        <v>0.05984299391230406</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02644400806637372</v>
+        <v>0.02856889800954705</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03128562594958723</v>
+        <v>0.02935559197596449</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03011246318732042</v>
+        <v>0.02804180959485831</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04118789547342244</v>
+        <v>0.03896332799256506</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03670946707092533</v>
+        <v>0.03462802973339791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09813431201630603</v>
+        <v>0.09566467795321415</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03318192672119012</v>
+        <v>0.03101470553872764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04428441283527682</v>
+        <v>0.04183341750080901</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06016467570540819</v>
+        <v>0.0579498553861043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03946948866771442</v>
+        <v>0.04323148725023113</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05916665415981665</v>
+        <v>0.05705168600836543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04755381693099675</v>
+        <v>0.04839055583412587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03596550266799134</v>
+        <v>0.03398830852596044</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04896913001346123</v>
+        <v>0.04664408878141829</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04579101406911752</v>
+        <v>0.2235747660128168</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1064156201774524</v>
+        <v>0.104135864657628</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08704196299037541</v>
+        <v>0.08394632554507661</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06080351252222765</v>
+        <v>0.05843769863186906</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0410494067087623</v>
+        <v>0.05252652156476656</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03702424062233271</v>
+        <v>0.03403865487734738</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0625587474398866</v>
+        <v>0.06451357477532052</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06323968063295413</v>
+        <v>0.06087811689600707</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08909502212057183</v>
+        <v>0.08676611372605683</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1059108806321704</v>
+        <v>0.1037461790512159</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03692559514737331</v>
+        <v>0.03440875530236084</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1071977148803921</v>
+        <v>0.1051244821185611</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.07693843735733107</v>
+        <v>0.07463584200179947</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04010894236069441</v>
+        <v>0.04209358452507857</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04029868210997985</v>
+        <v>0.03823487161301703</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0511923437540899</v>
+        <v>0.05104623505724647</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04763770281157624</v>
+        <v>0.04743170785351847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05124014604808502</v>
+        <v>0.05108792843960027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05419623881684758</v>
+        <v>0.05402455334535597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05463800393394402</v>
+        <v>0.05449114739057592</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05168324542055212</v>
+        <v>0.05151388060432713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05312384100749787</v>
+        <v>0.05298408314552189</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0511656005625611</v>
+        <v>0.05147880574274793</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05267954093922524</v>
+        <v>0.05253953157436852</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05114136240850365</v>
+        <v>0.05106312771699079</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0510543673344801</v>
+        <v>0.05091687981853232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05203962381486723</v>
+        <v>0.05187939947752032</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05185021114771966</v>
+        <v>0.0516778831638605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06626255440187513</v>
+        <v>0.0659179306260565</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05503431493931527</v>
+        <v>0.05480682152970028</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05537944425289687</v>
+        <v>0.05521530985741261</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05158663436950717</v>
+        <v>0.05244454949954772</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05117266130353006</v>
+        <v>0.05095951986796586</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05466587167229957</v>
+        <v>0.05464844374482734</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2169750780984996</v>
+        <v>0.2171369908740653</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05415218083008105</v>
+        <v>0.0539917399907444</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2387280474613304</v>
+        <v>0.2389454631694079</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05130457081235405</v>
+        <v>0.05112010561143606</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05566113452388176</v>
+        <v>0.05551332622583104</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2011331829326759</v>
+        <v>0.2008988278507524</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05146738358843636</v>
+        <v>0.05167147323924701</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0513649833886518</v>
+        <v>0.05122274192705089</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02384769579505269</v>
+        <v>0.02373612736555836</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01950890583039064</v>
+        <v>0.01920872494745782</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02419794355680306</v>
+        <v>0.0240427811435723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04528733097422024</v>
+        <v>0.04499337062397001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04850220237206941</v>
+        <v>0.04838530962513489</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02733778243646543</v>
+        <v>0.02706079272905703</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03772329382316719</v>
+        <v>0.03765748961684962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02366565157106</v>
+        <v>0.02684374385667021</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0344381507541467</v>
+        <v>0.03437100093900426</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02348831780806577</v>
+        <v>0.0238588826759325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02286723212908742</v>
+        <v>0.02281725936869168</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03007840969820828</v>
+        <v>0.02986562109857736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02855587266316363</v>
+        <v>0.02825704867629183</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09354441514175306</v>
+        <v>0.09303717483575627</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05116122990141898</v>
+        <v>0.05047105803539109</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05374392899896975</v>
+        <v>0.05350371470603571</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02668524442730328</v>
+        <v>0.0337718764409946</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02370823867012749</v>
+        <v>0.02311980939362664</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04872338591126279</v>
+        <v>0.0495331860734593</v>
       </c>
       <c r="U3" t="n">
-        <v>0.307752539013325</v>
+        <v>0.3080614243802543</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04483893234557607</v>
+        <v>0.04462540896011095</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3607757812351871</v>
+        <v>0.3612040433712349</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02465719619321581</v>
+        <v>0.02427151036826592</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05574026394498482</v>
+        <v>0.05561660329711202</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2835547195632573</v>
+        <v>0.2832592588815851</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02581631066059349</v>
+        <v>0.02820504509450191</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02529180771422951</v>
+        <v>0.02520680279053188</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01106053369422393</v>
+        <v>0.009221551613885789</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01416739184638568</v>
+        <v>0.01214345672299522</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01160048259503995</v>
+        <v>0.00969249754747452</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0449909102880716</v>
+        <v>0.04286302677218489</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04998085050767079</v>
+        <v>0.04813342115681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01660549384283857</v>
+        <v>0.01450382319574177</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03287768370410153</v>
+        <v>0.03111043722511968</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01075845704343011</v>
+        <v>0.01410763649897158</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0279663611441567</v>
+        <v>0.02619663253143605</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01048467594324987</v>
+        <v>0.009412361976704703</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009502026562442225</v>
+        <v>0.007760424686259763</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02091042005058017</v>
+        <v>0.01891158563858823</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01849144853922466</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1040965608262808</v>
+        <v>0.1021168604812799</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05445736562540784</v>
+        <v>0.05169910577549756</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05835575998964062</v>
+        <v>0.05631316935092343</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01551422757800612</v>
+        <v>0.02501615649610213</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0108382113607757</v>
+        <v>0.00824206366000318</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05029562943218938</v>
+        <v>0.049910155837977</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03248089711176269</v>
+        <v>0.03042753389083903</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04520963537167657</v>
+        <v>0.04321108250039338</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06737178241382444</v>
+        <v>0.06540859029518734</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01232818994431493</v>
+        <v>0.01005595350559112</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0618027344771989</v>
+        <v>0.05991178576849796</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03638839971920828</v>
+        <v>0.0344705268256052</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01416723514774175</v>
+        <v>0.01628390450335533</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01336096587411163</v>
+        <v>0.01156317938794297</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04644613962209272</v>
+        <v>0.04496506333547014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1029146072681114</v>
+        <v>0.09814148354347681</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06070171763724296</v>
+        <v>0.05800312408667193</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6469165311502593</v>
+        <v>0.6404039019205615</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7672871400215714</v>
+        <v>0.7656634488128389</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1375203092173384</v>
+        <v>0.131682738944693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4791689768506999</v>
+        <v>0.479183644485053</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0456758503632048</v>
+        <v>0.1419231617850407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3313584339500591</v>
+        <v>0.3315560950233147</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03858197177177513</v>
+        <v>0.04947557768329432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02109984722173362</v>
+        <v>0.02137523664997185</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2371336233827217</v>
+        <v>0.2326938971281436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3938455694775696</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O5" t="n">
-        <v>1.50105182788685</v>
+        <v>1.497269763462617</v>
       </c>
       <c r="P5" t="n">
-        <v>0.758641335781282</v>
+        <v>0.7420638567696377</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8895156028646707</v>
+        <v>0.8844356774642368</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1373833501627663</v>
+        <v>0.3532922368657435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04304129897660995</v>
+        <v>0.02897441687411838</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7844058052889237</v>
+        <v>0.8101702701087099</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4075698647572503</v>
+        <v>0.4029869754383253</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5694124880700452</v>
+        <v>0.5652436917128051</v>
       </c>
       <c r="W5" t="n">
-        <v>1.050121901442328</v>
+        <v>1.046494534117903</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07328733826214799</v>
+        <v>0.063954232776724</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9384830660772878</v>
+        <v>0.9366820965829452</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4426466056066015</v>
+        <v>0.4398183893075694</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1043170305770769</v>
+        <v>0.1732748393626936</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09832744085693292</v>
+        <v>0.09773763619582901</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.78189447581417</v>
+        <v>6.741394469105411</v>
       </c>
       <c r="C6" t="n">
-        <v>1.78500133396633</v>
+        <v>1.782913245732806</v>
       </c>
       <c r="D6" t="n">
-        <v>6.74394444722816</v>
+        <v>6.741865415038991</v>
       </c>
       <c r="E6" t="n">
-        <v>1.815824852408018</v>
+        <v>6.775035944263706</v>
       </c>
       <c r="F6" t="n">
-        <v>6.782324815140783</v>
+        <v>1.81890321016662</v>
       </c>
       <c r="G6" t="n">
-        <v>1.787439435962785</v>
+        <v>1.78527361220555</v>
       </c>
       <c r="H6" t="n">
-        <v>1.803711625824047</v>
+        <v>1.801880226234929</v>
       </c>
       <c r="I6" t="n">
-        <v>1.781592399163375</v>
+        <v>1.784877425508779</v>
       </c>
       <c r="J6" t="n">
-        <v>6.760310325777272</v>
+        <v>6.758369550022956</v>
       </c>
       <c r="K6" t="n">
-        <v>6.742828640576363</v>
+        <v>6.74158527946822</v>
       </c>
       <c r="L6" t="n">
-        <v>1.780335968682388</v>
+        <v>6.739933342177783</v>
       </c>
       <c r="M6" t="n">
-        <v>6.753254384683694</v>
+        <v>1.789681374648397</v>
       </c>
       <c r="N6" t="n">
-        <v>1.789276663252452</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O6" t="n">
-        <v>1.874881775539508</v>
+        <v>6.834713478822298</v>
       </c>
       <c r="P6" t="n">
-        <v>6.787221135327251</v>
+        <v>6.784292849214089</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.790699724622761</v>
+        <v>6.788486086842441</v>
       </c>
       <c r="R6" t="n">
-        <v>6.747858192211122</v>
+        <v>1.795785945505911</v>
       </c>
       <c r="S6" t="n">
-        <v>1.781672153480722</v>
+        <v>6.740414981151522</v>
       </c>
       <c r="T6" t="n">
-        <v>1.821129571552135</v>
+        <v>1.820679944847785</v>
       </c>
       <c r="U6" t="n">
-        <v>1.803049685938852</v>
+        <v>1.800964938458662</v>
       </c>
       <c r="V6" t="n">
-        <v>6.777553600004792</v>
+        <v>6.775383999991909</v>
       </c>
       <c r="W6" t="n">
-        <v>1.928410239615256</v>
+        <v>6.798004922223556</v>
       </c>
       <c r="X6" t="n">
-        <v>1.783162132064261</v>
+        <v>1.780825742515401</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.90991962742436</v>
+        <v>1.907999009819319</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.807222341839154</v>
+        <v>6.766643444317128</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.746511199780857</v>
+        <v>6.748456821994873</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.784021501375306</v>
+        <v>1.782165243451031</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01361594668702948</v>
+        <v>0.0117643874088718</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01672280483919122</v>
+        <v>0.01468629251798114</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01415589558784549</v>
+        <v>0.01223533334246056</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04754632328087715</v>
+        <v>0.04540586256717092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05253626350047624</v>
+        <v>0.050676256951796</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01916090683564412</v>
+        <v>0.01704665899072779</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03543309669690708</v>
+        <v>0.03365327302010566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01331387003623566</v>
+        <v>0.0166504722939576</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03052177413696226</v>
+        <v>0.02873946832642215</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01304008893605543</v>
+        <v>0.01195519777169071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01205743955524776</v>
+        <v>0.01030326048124578</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0234658330433857</v>
+        <v>0.02145442143357423</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0210468615320302</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O7" t="n">
-        <v>0.106651861909958</v>
+        <v>0.1046595815298385</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05701266670908523</v>
+        <v>0.0542418268240563</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0609111729824461</v>
+        <v>0.05885600514590946</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01806964057081166</v>
+        <v>0.02755899229108812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01339362435358125</v>
+        <v>0.01078489945498919</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05285104242499492</v>
+        <v>0.05245299163296294</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03476390628292219</v>
+        <v>0.03274067699295388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04776504836448212</v>
+        <v>0.04575391829537941</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06992719540663005</v>
+        <v>0.06795142609017334</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01488360293712046</v>
+        <v>0.01259878930057714</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06409299417714714</v>
+        <v>0.06222223712149798</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03894381271201383</v>
+        <v>0.03701336262059121</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01672264814054729</v>
+        <v>0.01882674029834133</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01591637886691718</v>
+        <v>0.01410601518292899</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01571062711566834</v>
+        <v>0.01378778502828137</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02240839063535403</v>
+        <v>0.02019450751935053</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01984148138400831</v>
+        <v>0.01774354834382984</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05131985789537843</v>
+        <v>0.04905851510947781</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05519036501674002</v>
+        <v>0.05324254839072722</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02559109025178586</v>
+        <v>0.02327747357727973</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04111868249306991</v>
+        <v>0.03916148802147499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01899945583239849</v>
+        <v>0.02215868729532691</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03620735993312507</v>
+        <v>0.03424768332779145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01872567473221823</v>
+        <v>0.01746341277306003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01774302535141057</v>
+        <v>0.01581147548261509</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02915141883954702</v>
+        <v>0.02696263643494896</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02394889492112322</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1103189515750737</v>
+        <v>0.1082089400259783</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06049225002662238</v>
+        <v>0.0576092185699735</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06230015854991271</v>
+        <v>0.06019455661422085</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02375522636697446</v>
+        <v>0.03306720729245743</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01907921014974406</v>
+        <v>0.0162931144563585</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05853662822115774</v>
+        <v>0.05796120663433242</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03869853736594795</v>
+        <v>0.03654748235415439</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05246308365978315</v>
+        <v>0.05031207908111909</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07561348691134702</v>
+        <v>0.07346032595230245</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01660170211231181</v>
+        <v>0.0142567312028773</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07333947136522354</v>
+        <v>0.07119904745720865</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.04097179023051123</v>
+        <v>0.03897202796851167</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02240823393671012</v>
+        <v>0.02433495529971064</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02535296557931228</v>
+        <v>0.02325441333014062</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02436301013442429</v>
+        <v>0.02240619893313698</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03142567686865663</v>
+        <v>0.02922834313363022</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0288587676173109</v>
+        <v>0.02677738395810961</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06133621559552842</v>
+        <v>0.05904775866967479</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05811990901058482</v>
+        <v>0.05622718390764279</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03386378506694613</v>
+        <v>0.03158871579506002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05013596872637249</v>
+        <v>0.04819532363575473</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02801674206570105</v>
+        <v>0.03119252290960661</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04522464616642765</v>
+        <v>0.0432815189420711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02774296096552082</v>
+        <v>0.02649724838733975</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02676031158471317</v>
+        <v>0.02484531109689481</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03816870507285108</v>
+        <v>0.03599647204922325</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03574973356149558</v>
+        <v>0.1777972287123813</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1226658038900784</v>
+        <v>0.1204942892594776</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0733117182221925</v>
+        <v>0.07035763899641548</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07561405121374817</v>
+        <v>0.07339806195024159</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03277251260027704</v>
+        <v>0.04210104290673714</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02809649638304666</v>
+        <v>0.0253269500706382</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06755391445446039</v>
+        <v>0.06699504224861209</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04947402884117637</v>
+        <v>0.0472800358594881</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06703284590902729</v>
+        <v>0.06479676844763009</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08463006743609548</v>
+        <v>0.08249347670582241</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02958647496658585</v>
+        <v>0.02714083991622616</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.07879586620661259</v>
+        <v>0.076764287737147</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05126168639339556</v>
+        <v>0.04920391834438576</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03142552017001269</v>
+        <v>0.03336879091399034</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03061925089638258</v>
+        <v>0.02864806579857803</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04955865337624053</v>
+        <v>0.04934018498054465</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04578556933925401</v>
+        <v>0.04548133966150095</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05011900383672049</v>
+        <v>0.0499073702154239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05028776957611272</v>
+        <v>0.0500574133131026</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0545184771099451</v>
+        <v>0.05430311111966959</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05002427434038705</v>
+        <v>0.04979122983576249</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05131539801359263</v>
+        <v>0.05110246139033973</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05166079356014691</v>
+        <v>0.05173418337068874</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05085205103802781</v>
+        <v>0.0506532612765489</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05126754000349119</v>
+        <v>0.05115343002782555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05114072177551882</v>
+        <v>0.05091753770488406</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05159539842929734</v>
+        <v>0.05137169661301517</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04992119320560124</v>
+        <v>0.04969576800240504</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06012219036226973</v>
+        <v>0.05963831087621439</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05226908202012877</v>
+        <v>0.05199599145735102</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05448181858885654</v>
+        <v>0.05424912180568762</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05059823823543563</v>
+        <v>0.05123987606366976</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05107622163962333</v>
+        <v>0.05081304729419097</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05323295386527794</v>
+        <v>0.05329119132761091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2133048677904296</v>
+        <v>0.2133775794532431</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05022305843549665</v>
+        <v>0.04998314245609565</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2347456911701473</v>
+        <v>0.2348917361953771</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05007284683115331</v>
+        <v>0.04982363514680754</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05047689912230483</v>
+        <v>0.05023624151764027</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1962822959993168</v>
+        <v>0.1959733264791282</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04985911087389214</v>
+        <v>0.04993036868846022</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04955802614708894</v>
+        <v>0.04934835397608781</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02328674586334171</v>
+        <v>0.02307992597743077</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01721691445350653</v>
+        <v>0.01686228363160455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02729813334580149</v>
+        <v>0.02714000339791227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02847570548378379</v>
+        <v>0.02818431120270358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05876120867373574</v>
+        <v>0.05857646374301982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02659085405969775</v>
+        <v>0.02628057156450134</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03592177031448007</v>
+        <v>0.03575451418870666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.038342093783349</v>
+        <v>0.0402231435592713</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03251144986903596</v>
+        <v>0.03244607161211894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03544196037473013</v>
+        <v>0.035977063940297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03455418999924996</v>
+        <v>0.03431375913292541</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03783538810356521</v>
+        <v>0.037590150078574</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02589224339504851</v>
+        <v>0.02563561656470577</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07216750572588136</v>
+        <v>0.07150605015330597</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04252099354798192</v>
+        <v>0.04192653142013684</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05839173430281868</v>
+        <v>0.05808342360707681</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03076033273238979</v>
+        <v>0.03671963523318579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03407623782977367</v>
+        <v>0.03355162460687738</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0496104679194708</v>
+        <v>0.05138461544498536</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2973978355969519</v>
+        <v>0.2976237026947537</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02799459665788173</v>
+        <v>0.02763571268419879</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3487189098085832</v>
+        <v>0.3490769245878047</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02696743902516414</v>
+        <v>0.02654114532311953</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02985886101772348</v>
+        <v>0.0294934622280373</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2679050109895053</v>
+        <v>0.2675301884410979</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02544442445609799</v>
+        <v>0.02730667886697657</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02342132338821054</v>
+        <v>0.02327595247053295</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01073195766614992</v>
+        <v>0.007936021996639604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01102020873113885</v>
+        <v>0.008211458055526519</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01706137389121805</v>
+        <v>0.01434264014269914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01896766055372924</v>
+        <v>0.01603744595421525</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06675544836998511</v>
+        <v>0.06399455579687581</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01599136065241068</v>
+        <v>0.01303078112720918</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03057519648750191</v>
+        <v>0.02784174473247587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03447659807563357</v>
+        <v>0.03497733510698618</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02543596743526444</v>
+        <v>0.02286242745525159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03003461824763379</v>
+        <v>0.02841745893960956</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02860214802341869</v>
+        <v>0.02575294663615554</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03370640809542833</v>
+        <v>0.03084967715058726</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01482701181533999</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07599160233058228</v>
+        <v>0.07316136975328254</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04134749605764563</v>
+        <v>0.03793457788350567</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06634137351053736</v>
+        <v>0.06338472165913747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02247454688342073</v>
+        <v>0.02939390668161079</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02787358931695061</v>
+        <v>0.02457267937941357</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05223487195156059</v>
+        <v>0.05256445623946907</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01855278053540952</v>
+        <v>0.01554747712534938</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01886658244793683</v>
+        <v>0.01582904413135669</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05134433334579764</v>
+        <v>0.04847266483867737</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01654000928006549</v>
+        <v>0.01339681402264322</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0210298720373364</v>
+        <v>0.01787312302276768</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01579432548172714</v>
+        <v>0.01295959657383654</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01412576331940232</v>
+        <v>0.01460241847546428</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01093875513688091</v>
+        <v>0.008239439354703653</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06463364552467352</v>
+        <v>0.06157372873287911</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07418343467647111</v>
+        <v>0.07086072603703311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1828701883687112</v>
+        <v>0.1811289775066873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2026367747678278</v>
+        <v>0.1973417857229481</v>
       </c>
       <c r="F5" t="n">
-        <v>1.094862536988798</v>
+        <v>1.092387659433047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.147781734011061</v>
+        <v>0.1421040704365016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4658879788452158</v>
+        <v>0.4639763221475691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5116836877341518</v>
+        <v>0.5694510430293886</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3198363011762134</v>
+        <v>0.3212231131587298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3846850232998753</v>
+        <v>0.4009771850922144</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3683342163685783</v>
+        <v>0.3643555414158216</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4862197098629091</v>
+        <v>0.4820050187820996</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1918722442124238</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O5" t="n">
-        <v>1.087313915056429</v>
+        <v>1.0837160170822</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5490029648785968</v>
+        <v>0.5361702121842286</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.031653238987698</v>
+        <v>1.025780796979891</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3003141233497406</v>
+        <v>0.4833371366290499</v>
       </c>
       <c r="S5" t="n">
-        <v>0.346321747735778</v>
+        <v>0.3349913963330055</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8505328110367895</v>
+        <v>0.9059160681444335</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1956721066770122</v>
+        <v>0.1909695939662126</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1803565796906526</v>
+        <v>0.1735351176632622</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7938355710339994</v>
+        <v>0.7893963201739121</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1729911237589503</v>
+        <v>0.1637595852306504</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2576925268568279</v>
+        <v>0.2500890794448272</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1361190129573767</v>
+        <v>0.132491358664373</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1315502855703007</v>
+        <v>0.1870368815846619</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.08013136056753027</v>
+        <v>0.07886180222333097</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741345042744954</v>
+        <v>1.777426394473062</v>
       </c>
       <c r="C6" t="n">
-        <v>1.780579591928148</v>
+        <v>1.777701830531948</v>
       </c>
       <c r="D6" t="n">
-        <v>1.786620757088228</v>
+        <v>6.744731516537835</v>
       </c>
       <c r="E6" t="n">
-        <v>6.749580745632532</v>
+        <v>6.746426322349348</v>
       </c>
       <c r="F6" t="n">
-        <v>1.836314831566993</v>
+        <v>1.833484928273299</v>
       </c>
       <c r="G6" t="n">
-        <v>6.746604445731218</v>
+        <v>1.782521153603631</v>
       </c>
       <c r="H6" t="n">
-        <v>1.800134579684511</v>
+        <v>6.758230621127602</v>
       </c>
       <c r="I6" t="n">
-        <v>1.804035981272643</v>
+        <v>1.804467707583409</v>
       </c>
       <c r="J6" t="n">
-        <v>6.756049052514063</v>
+        <v>6.753251303850371</v>
       </c>
       <c r="K6" t="n">
-        <v>6.76064770332644</v>
+        <v>6.758806335334739</v>
       </c>
       <c r="L6" t="n">
-        <v>6.759215233102223</v>
+        <v>1.79524331911258</v>
       </c>
       <c r="M6" t="n">
-        <v>1.803265791292437</v>
+        <v>1.800340049627009</v>
       </c>
       <c r="N6" t="n">
-        <v>1.784390195185456</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O6" t="n">
-        <v>6.807047546331062</v>
+        <v>1.842661587363541</v>
       </c>
       <c r="P6" t="n">
-        <v>1.70866758196749</v>
+        <v>6.768750063339376</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.796954458589341</v>
+        <v>6.793773598054267</v>
       </c>
       <c r="R6" t="n">
-        <v>6.753087631962225</v>
+        <v>6.759782783076735</v>
       </c>
       <c r="S6" t="n">
-        <v>6.758486674395759</v>
+        <v>1.794063051855834</v>
       </c>
       <c r="T6" t="n">
-        <v>6.782847957030363</v>
+        <v>6.782953332634602</v>
       </c>
       <c r="U6" t="n">
-        <v>1.788186257476942</v>
+        <v>6.746120623287217</v>
       </c>
       <c r="V6" t="n">
-        <v>1.788425965644946</v>
+        <v>1.785319416607779</v>
       </c>
       <c r="W6" t="n">
-        <v>6.78240051021127</v>
+        <v>1.908157024383182</v>
       </c>
       <c r="X6" t="n">
-        <v>1.786099392477074</v>
+        <v>1.782887186499066</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.86815392715135</v>
+        <v>1.865037122994512</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.746407410560532</v>
+        <v>1.78244996905026</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.744738848398206</v>
+        <v>6.7449912948706</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.780453530904061</v>
+        <v>1.777691875251638</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01276086673439795</v>
+        <v>0.009903951358470104</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01304911779938688</v>
+        <v>0.010179387417357</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01909028295946606</v>
+        <v>0.01631056950452961</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02099656962197727</v>
+        <v>0.01800537531604576</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06878435743823318</v>
+        <v>0.0659624851587064</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01802026972065872</v>
+        <v>0.01499871048903968</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0326041055557499</v>
+        <v>0.02980967409430635</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03650550714388162</v>
+        <v>0.03694526446881664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02746487650351247</v>
+        <v>0.0248303568170821</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03206352731588182</v>
+        <v>0.03038538830144008</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03063105709166673</v>
+        <v>0.02772087599798602</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03573531716367632</v>
+        <v>0.03281760651241768</v>
       </c>
       <c r="N7" t="n">
-        <v>0.016855920883588</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07802046392497301</v>
+        <v>0.07512924438517483</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04337635765203646</v>
+        <v>0.03990245251539786</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0683702825787854</v>
+        <v>0.06535265102096799</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02450345595166877</v>
+        <v>0.03136183604344125</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02990249838519864</v>
+        <v>0.02654060874124405</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05426378101980855</v>
+        <v>0.05453238560129959</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02059340864005826</v>
+        <v>0.01765920620197692</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02089549151618484</v>
+        <v>0.0177969734931872</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05337324241404565</v>
+        <v>0.0504405942005079</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01856891834831349</v>
+        <v>0.01536474338447367</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02313287485010696</v>
+        <v>0.0200253221513364</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01782323454997516</v>
+        <v>0.01492752593566704</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01615467238765033</v>
+        <v>0.0165703478372948</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01296766420512894</v>
+        <v>0.01020736871653422</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01473456314113013</v>
+        <v>0.01177224130797982</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01817157317171366</v>
+        <v>0.01499712486342311</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02421273833179287</v>
+        <v>0.02112830695059578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02444240372910705</v>
+        <v>0.02125261897444058</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07124859369069068</v>
+        <v>0.06829026455668613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02379564077621449</v>
+        <v>0.02042803508700108</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03772656092807671</v>
+        <v>0.03462741154037255</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04162796251620839</v>
+        <v>0.04176300191488281</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03258733187583927</v>
+        <v>0.02964809426314827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0371859826882086</v>
+        <v>0.03520312574750614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0357535124639935</v>
+        <v>0.03253861344405216</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04085777253600108</v>
+        <v>0.03763534395849572</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01953756127991306</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08137290894021078</v>
+        <v>0.07828902059622025</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04656438388362585</v>
+        <v>0.04290821739183465</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06972517598374819</v>
+        <v>0.06664130722087076</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02962591132399556</v>
+        <v>0.03617957348950738</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03502495375752548</v>
+        <v>0.03135834618731016</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05938623639213541</v>
+        <v>0.05935012304736575</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02419306941475881</v>
+        <v>0.02104650685738221</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02510406780479257</v>
+        <v>0.02177403644657564</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05849631660080738</v>
+        <v>0.05525891129259757</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02021240176489814</v>
+        <v>0.01692372230505098</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03130343878994102</v>
+        <v>0.02772204719098523</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01973844114296455</v>
+        <v>0.01674102838409855</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02127712775997713</v>
+        <v>0.021388085283361</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02137926160546757</v>
+        <v>0.01810605069697805</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01985043105676794</v>
+        <v>0.01693293570529735</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02292400947731195</v>
+        <v>0.01991934511306216</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02896517463739113</v>
+        <v>0.02605052720023477</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03022861943693492</v>
+        <v>0.02711965172875652</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07223830881442479</v>
+        <v>0.06945290886765897</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02789516182701503</v>
+        <v>0.02473866858524623</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04247899723367498</v>
+        <v>0.03954963179001159</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04638039882180664</v>
+        <v>0.04668522216452182</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03733976818143753</v>
+        <v>0.0345703145127873</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04193841899380688</v>
+        <v>0.04012534599714516</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04050594876959179</v>
+        <v>0.03746083369369133</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04561020884160141</v>
+        <v>0.04255756420812297</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02673081256151308</v>
+        <v>0.1418759121484599</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08881845748572471</v>
+        <v>0.08576767036214732</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05437509961661584</v>
+        <v>0.05073626793850151</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07824517468514179</v>
+        <v>0.07509260911717454</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03437834762959383</v>
+        <v>0.04110179373914637</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0397773900631237</v>
+        <v>0.03628056643694916</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0641386726977337</v>
+        <v>0.06427234329700476</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03053067502610516</v>
+        <v>0.02743963394962325</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03398458486905414</v>
+        <v>0.03066532990217448</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06324813409197079</v>
+        <v>0.06018055189621304</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02844381002623858</v>
+        <v>0.02510470108017899</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03300776652803201</v>
+        <v>0.02976527984704146</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02601882168359834</v>
+        <v>0.02303300793018981</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02602956406557543</v>
+        <v>0.02631030553299976</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.022842555883054</v>
+        <v>0.01994732641223931</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05476462004480831</v>
+        <v>0.05461387539358902</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05112174510585895</v>
+        <v>0.05089850950633486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0550608133163203</v>
+        <v>0.05491160711280154</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06103762403830547</v>
+        <v>0.06088657307094907</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05609639009151215</v>
+        <v>0.05594101781737497</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05714239924180279</v>
+        <v>0.05698406665450173</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05566491574663518</v>
+        <v>0.05551178296908005</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05490277378320403</v>
+        <v>0.05515388668779539</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05849510050329138</v>
+        <v>0.05836096857683355</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05539092488481036</v>
+        <v>0.05529667593216653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05488043762908965</v>
+        <v>0.05472137999673726</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05981368510885095</v>
+        <v>0.05966166827010845</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05824158338655466</v>
+        <v>0.05808888194999558</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07871665156451688</v>
+        <v>0.07834697445995606</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06330685032992169</v>
+        <v>0.06314398363361412</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05962661072108821</v>
+        <v>0.05947442247755313</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05496075719334706</v>
+        <v>0.05527470314285395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05496677650625371</v>
+        <v>0.05479497547810925</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05988616879709657</v>
+        <v>0.05995054754569196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2229893791477367</v>
+        <v>0.2236383541501462</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05913268232325398</v>
+        <v>0.05898107277762749</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2472718602915501</v>
+        <v>0.2478375437361284</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05489241810879256</v>
+        <v>0.05473438767241053</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06258839687301876</v>
+        <v>0.06244052514519884</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2085488473118235</v>
+        <v>0.2083010079203375</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05499957003222154</v>
+        <v>0.05536859626170623</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05832310795411799</v>
+        <v>0.05817854141565639</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02614900832667227</v>
+        <v>0.02600750082240084</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0219053287465284</v>
+        <v>0.02164645696477861</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02827181386887816</v>
+        <v>0.02814127788512928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07090440007417202</v>
+        <v>0.070760794946284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03567637788371768</v>
+        <v>0.03550167277106973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04298687527070839</v>
+        <v>0.04279134097151735</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03261330025022226</v>
+        <v>0.03245457834285342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0271429177115502</v>
+        <v>0.02987793775951256</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05265839682639769</v>
+        <v>0.05263553983963459</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03061027602171933</v>
+        <v>0.03087036371904767</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02697381635605348</v>
+        <v>0.0267730512025974</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06213113416112789</v>
+        <v>0.06197968889535405</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05095452050228868</v>
+        <v>0.05079904998007811</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1364258114642596</v>
+        <v>0.1359906495695261</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08688431566729492</v>
+        <v>0.08665671467670534</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06080759680659629</v>
+        <v>0.06065573405124627</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02756056474932514</v>
+        <v>0.03075049937937514</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02757869413383936</v>
+        <v>0.02728810684082955</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06270089977204284</v>
+        <v>0.06409428326545867</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3235639677601991</v>
+        <v>0.3259306144146535</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05714478821671882</v>
+        <v>0.05699699679532646</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3935871446354022</v>
+        <v>0.3946657648562858</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02706616079584256</v>
+        <v>0.02687256489110494</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08196258620286374</v>
+        <v>0.08184155429116276</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3057985284199067</v>
+        <v>0.3055175107072607</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02782830974978217</v>
+        <v>0.03139683322925664</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05170831238500168</v>
+        <v>0.05161019692387919</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01605817351108133</v>
+        <v>0.01125139590429661</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01962240960958977</v>
+        <v>0.01482040841874202</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01940381276844579</v>
+        <v>0.01461441263615944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08691463934203897</v>
+        <v>0.08210440175357313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03110112883309078</v>
+        <v>0.02624208009663607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04291628337360556</v>
+        <v>0.03802379653815451</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02622742761970056</v>
+        <v>0.02139367502735946</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01761868354012102</v>
+        <v>0.01735107188982601</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0583014673412157</v>
+        <v>0.05368251869159309</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02313257479336596</v>
+        <v>0.0189639420912955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01736638640425983</v>
+        <v>0.01246570985141674</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07313846826079042</v>
+        <v>0.0683164713428185</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05533207393826711</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1629575783953481</v>
+        <v>0.1582915528457508</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1125465942015126</v>
+        <v>0.1076028925190393</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07097659482587491</v>
+        <v>0.0661535111797983</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0182736328313723</v>
+        <v>0.01871574932802738</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01834162373967345</v>
+        <v>0.01329700466910766</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0739084226970039</v>
+        <v>0.07153156285277915</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05711216673411313</v>
+        <v>0.05469094609203317</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06610428582627767</v>
+        <v>0.06128887872320661</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1182837729525474</v>
+        <v>0.1135540898463139</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01750171143379663</v>
+        <v>0.01261263753197254</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1047157303898059</v>
+        <v>0.09987153336755955</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06960923992011694</v>
+        <v>0.06484568153187756</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01871204170124803</v>
+        <v>0.01977631529843269</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05638851788698701</v>
+        <v>0.05165026309291419</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03885173956660027</v>
+        <v>0.03346326432199943</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1091205381967662</v>
+        <v>0.1037619962702292</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1070379410897504</v>
+        <v>0.1019733338655027</v>
       </c>
       <c r="E5" t="n">
-        <v>1.370061827608238</v>
+        <v>1.364657189723324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3357738722841847</v>
+        <v>0.3293024953227223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4730134311912921</v>
+        <v>0.466075941470079</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2527300977710524</v>
+        <v>0.246736910287972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07275090914764321</v>
+        <v>0.1578881164218011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7716001908149662</v>
+        <v>0.7698070245076436</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1677746678490454</v>
+        <v>0.1735526462219276</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06259299091051938</v>
+        <v>0.05546941083932515</v>
       </c>
       <c r="M5" t="n">
-        <v>1.073735346376788</v>
+        <v>1.06783852633711</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7676180373436583</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O5" t="n">
-        <v>2.476293629864085</v>
+        <v>2.47321522242051</v>
       </c>
       <c r="P5" t="n">
-        <v>1.734765486956942</v>
+        <v>1.727022846142503</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.054062825211271</v>
+        <v>1.048336971996211</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08725721012279741</v>
+        <v>0.1894133113454375</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07473309721084805</v>
+        <v>0.06551526750957244</v>
       </c>
       <c r="T5" t="n">
-        <v>1.132201927010032</v>
+        <v>1.172504815740472</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7691137316505728</v>
+        <v>0.8076111423314892</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8727436585485703</v>
+        <v>0.8671098035863558</v>
       </c>
       <c r="W5" t="n">
-        <v>1.981320338200792</v>
+        <v>1.977437439206566</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06895531726862497</v>
+        <v>0.06196107789316051</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.695839454924724</v>
+        <v>1.691048651218504</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9345867814481749</v>
+        <v>0.9298877105478726</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09039431667307275</v>
+        <v>0.1962377427843339</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8506510957620288</v>
+        <v>0.8465494075480418</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.917900814445127</v>
+        <v>1.913036386888185</v>
       </c>
       <c r="C6" t="n">
-        <v>7.247936091806275</v>
+        <v>1.916605399402631</v>
       </c>
       <c r="D6" t="n">
-        <v>1.92124645370249</v>
+        <v>7.242741186336795</v>
       </c>
       <c r="E6" t="n">
-        <v>1.988757280276084</v>
+        <v>7.310231175454217</v>
       </c>
       <c r="F6" t="n">
-        <v>7.259414811029768</v>
+        <v>1.928027071080523</v>
       </c>
       <c r="G6" t="n">
-        <v>7.271229965570282</v>
+        <v>1.939808787522041</v>
       </c>
       <c r="H6" t="n">
-        <v>1.928070068553745</v>
+        <v>7.249520448727999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.919461324474165</v>
+        <v>7.245477845590461</v>
       </c>
       <c r="J6" t="n">
-        <v>1.96014410827526</v>
+        <v>1.95546750967548</v>
       </c>
       <c r="K6" t="n">
-        <v>1.92497521572741</v>
+        <v>7.247090715791938</v>
       </c>
       <c r="L6" t="n">
-        <v>1.919209027338305</v>
+        <v>1.914250700835304</v>
       </c>
       <c r="M6" t="n">
-        <v>7.301452150457468</v>
+        <v>7.296443245043456</v>
       </c>
       <c r="N6" t="n">
-        <v>1.956976005255684</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O6" t="n">
-        <v>7.39177050188415</v>
+        <v>7.386962242938258</v>
       </c>
       <c r="P6" t="n">
-        <v>1.904298364396518</v>
+        <v>7.336272349400859</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.299290277022544</v>
+        <v>7.294280284880439</v>
       </c>
       <c r="R6" t="n">
-        <v>1.920116273765417</v>
+        <v>7.246842523028664</v>
       </c>
       <c r="S6" t="n">
-        <v>1.920184264673717</v>
+        <v>1.915081995652995</v>
       </c>
       <c r="T6" t="n">
-        <v>7.302222104893683</v>
+        <v>1.973316553836666</v>
       </c>
       <c r="U6" t="n">
-        <v>1.958670409179227</v>
+        <v>1.956261408993859</v>
       </c>
       <c r="V6" t="n">
-        <v>7.294417968022956</v>
+        <v>7.289415652423844</v>
       </c>
       <c r="W6" t="n">
-        <v>2.117067619261676</v>
+        <v>7.342223820945445</v>
       </c>
       <c r="X6" t="n">
-        <v>1.919344352367841</v>
+        <v>1.91439762851586</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.089414162466448</v>
+        <v>2.084584768315942</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.297922922116789</v>
+        <v>1.966630672515763</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.247025723897928</v>
+        <v>7.247903088999067</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.958054221754267</v>
+        <v>1.953262254397263</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02039515565203253</v>
+        <v>0.01555183012444365</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02395939175054095</v>
+        <v>0.01912084263888912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.023740794909397</v>
+        <v>0.01891484685630654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09125162148299014</v>
+        <v>0.0864048359737202</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0354381109740419</v>
+        <v>0.03054251431678322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04725326551455673</v>
+        <v>0.04232423075830166</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03056440976065171</v>
+        <v>0.02569410924750657</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02195566568107222</v>
+        <v>0.02165150610997311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06263844948216689</v>
+        <v>0.05798295291174018</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02746955693431716</v>
+        <v>0.02326437631144259</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02170336854521103</v>
+        <v>0.01676614407156385</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07747545040174161</v>
+        <v>0.07261690556296564</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05966905607921832</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1672944230047296</v>
+        <v>0.1625918508298181</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1168834388108942</v>
+        <v>0.1119031905031064</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07531357696682617</v>
+        <v>0.0704539453999454</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0226106149723235</v>
+        <v>0.02301618354817445</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02267860588062464</v>
+        <v>0.01759743888925476</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07824540483795506</v>
+        <v>0.07583199707292623</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06115153054131812</v>
+        <v>0.0587693819007928</v>
       </c>
       <c r="V7" t="n">
-        <v>0.07044126796722881</v>
+        <v>0.06558931294335388</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1226207550934987</v>
+        <v>0.1178545240664611</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02183869357474783</v>
+        <v>0.0169130717521196</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1087683140418261</v>
+        <v>0.1039574395056432</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.07394622206106816</v>
+        <v>0.06914611575202466</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02304902384219923</v>
+        <v>0.02407674951857978</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06072550002793818</v>
+        <v>0.0559506973130612</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02397661173278022</v>
+        <v>0.01906282020042739</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03351714729836543</v>
+        <v>0.0284899591686708</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03329855045722146</v>
+        <v>0.02828396338608823</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09762717385603543</v>
+        <v>0.09265467297214393</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0399506046643128</v>
+        <v>0.03496613202808026</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05805024568822502</v>
+        <v>0.05290806796989612</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0401221653084762</v>
+        <v>0.03506322577728825</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03151342122889669</v>
+        <v>0.0310206226397548</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07219620502999134</v>
+        <v>0.06735206944152182</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0370273124821416</v>
+        <v>0.03263349284122432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0312611240930355</v>
+        <v>0.02613526060134556</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08703320594956232</v>
+        <v>0.08198602209275252</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06459417972482535</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1734927716488824</v>
+        <v>0.1686679894817832</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1227697229552379</v>
+        <v>0.1176734352966952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07772055380210499</v>
+        <v>0.07281367992436306</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03216837052014797</v>
+        <v>0.03238530007795615</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03223636142844909</v>
+        <v>0.02696655541903643</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0878031603857795</v>
+        <v>0.08520111360270784</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06779541545235906</v>
+        <v>0.06528101167901554</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07835442831671377</v>
+        <v>0.07335104617807635</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1321796851472298</v>
+        <v>0.1272247918790811</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02479341012625939</v>
+        <v>0.01980971520209256</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1242508241429553</v>
+        <v>0.1191414345977346</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.07741666531167257</v>
+        <v>0.07254828812212713</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03260677939002367</v>
+        <v>0.03344586604836144</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07652600009154674</v>
+        <v>0.07143911676606039</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04048108618709816</v>
+        <v>0.03553677938442192</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05121092028814612</v>
+        <v>0.04621151549740334</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05099232344700207</v>
+        <v>0.04600551971482074</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1168493621509918</v>
+        <v>0.1118555397514797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04617097548111957</v>
+        <v>0.0412525499522695</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0745047978501656</v>
+        <v>0.06941490744163686</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05781593829825685</v>
+        <v>0.05278478210602073</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04920719421867729</v>
+        <v>0.04874217896848732</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08988997801977198</v>
+        <v>0.0850736257702544</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05472108547192224</v>
+        <v>0.0503550491699568</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04895489708281616</v>
+        <v>0.04385681693007808</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1047269789393467</v>
+        <v>0.0997075784214799</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08692058461682345</v>
+        <v>0.7702123175005279</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1969207639260548</v>
+        <v>0.1920374925131789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1470262299440021</v>
+        <v>0.141860967040568</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.102565109302435</v>
+        <v>0.09754462208328063</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04986214350992865</v>
+        <v>0.05010685640668869</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04993013441822975</v>
+        <v>0.04468811174776899</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1054969333755602</v>
+        <v>0.1029226699314405</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0884162789237385</v>
+        <v>0.08586752508863101</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1059617367865413</v>
+        <v>0.1008798324184935</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1498722836311039</v>
+        <v>0.1449451969249752</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0490902221123529</v>
+        <v>0.0440037446106338</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1360198425794311</v>
+        <v>0.1310481123641575</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.09687753370112354</v>
+        <v>0.09195267066501242</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05030055237980434</v>
+        <v>0.05116742237709399</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08797702856554335</v>
+        <v>0.08304137017157535</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05224644245779659</v>
+        <v>0.05201607054781601</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04870811129489727</v>
+        <v>0.04840047481821481</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05234287276893888</v>
+        <v>0.05210945655800222</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05431262343931862</v>
+        <v>0.05408004584823455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05570224205324359</v>
+        <v>0.05547992541265061</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05459022796173085</v>
+        <v>0.05436413987932377</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05284479479850879</v>
+        <v>0.05262224585738368</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05234159576193651</v>
+        <v>0.05238355452013731</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05505054985824696</v>
+        <v>0.05483351395095376</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05239197933740036</v>
+        <v>0.05223501236869</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05232976184277619</v>
+        <v>0.05209079911011587</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05651264803100286</v>
+        <v>0.05628853548812307</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05511926766556454</v>
+        <v>0.05489399039308927</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07587824528725078</v>
+        <v>0.07542410873002332</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06058299338989673</v>
+        <v>0.06037873132797719</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05478153086662514</v>
+        <v>0.05455580050608923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05240310259426175</v>
+        <v>0.05217518652540643</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05249609091374408</v>
+        <v>0.05225983761424491</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0561507725034958</v>
+        <v>0.05607853771391703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2193880449732573</v>
+        <v>0.2196967063557352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05525067020528171</v>
+        <v>0.05502748850177062</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2399932476259691</v>
+        <v>0.2403547298806271</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05611723061194435</v>
+        <v>0.05589618719471574</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05794229989510033</v>
+        <v>0.05772242130740747</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008282931579675</v>
+        <v>0.2004405355587046</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05286500760491832</v>
+        <v>0.05265529199044711</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05626068901134068</v>
+        <v>0.05603854726890283</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403593246573893</v>
+        <v>0.02378236498110595</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02020490796621777</v>
+        <v>0.01984555136863831</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02472733239631379</v>
+        <v>0.02445164468885918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03877255617658953</v>
+        <v>0.03850310900112749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04871118696844817</v>
+        <v>0.04851470740028552</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0406089668791926</v>
+        <v>0.04038551932208618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02832895286352425</v>
+        <v>0.02813085262844803</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02471983670923482</v>
+        <v>0.02641179990188377</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04393512534180776</v>
+        <v>0.04377628898200519</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02507464223645697</v>
+        <v>0.02534212826424304</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02462854878117084</v>
+        <v>0.02431407293862639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05420779045780989</v>
+        <v>0.05399628475527913</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04450794227879457</v>
+        <v>0.0442904704395698</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1349737565440345</v>
+        <v>0.1345140181565361</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08325672839772925</v>
+        <v>0.08318866633110422</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04202511003303586</v>
+        <v>0.04180431276981587</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02516114532529519</v>
+        <v>0.02492464903112021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02580254901523674</v>
+        <v>0.02550737817364382</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05185989781360947</v>
+        <v>0.05273265816007162</v>
       </c>
       <c r="U3" t="n">
-        <v>0.319243282132546</v>
+        <v>0.3200857276780248</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04532709388432289</v>
+        <v>0.0451243534929166</v>
       </c>
       <c r="W3" t="n">
-        <v>0.36437959315285</v>
+        <v>0.3652290547351938</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05161100474281009</v>
+        <v>0.05142358294517602</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06469665502596088</v>
+        <v>0.06451775587938732</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2781731162876744</v>
+        <v>0.2776559639665127</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02845251334599629</v>
+        <v>0.02834616442588825</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0525587360419205</v>
+        <v>0.0523620675766577</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01222246372387605</v>
+        <v>0.008329677902196509</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01633125882549741</v>
+        <v>0.012484152866916</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01331168844836341</v>
+        <v>0.009384515846937121</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03556092840037838</v>
+        <v>0.03164322839597131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05125730990080628</v>
+        <v>0.04745551205246644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03869659918541415</v>
+        <v>0.03485220116683537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01898112866789638</v>
+        <v>0.01517670687818297</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0132972640668186</v>
+        <v>0.01248057842054515</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04399732176835231</v>
+        <v>0.04025574770687682</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01386636972927299</v>
+        <v>0.01080272648718202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01316359450603162</v>
+        <v>0.00917377139021102</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06022555040735018</v>
+        <v>0.0564001942392007</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04467234601050281</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O4" t="n">
-        <v>0.161630686270354</v>
+        <v>0.158076801054362</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1063876415048458</v>
+        <v>0.1027897784281396</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0408574534998792</v>
+        <v>0.03701709611439581</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01399201203247352</v>
+        <v>0.01012696606604675</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0150423578777665</v>
+        <v>0.01108313905590194</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05632366767060581</v>
+        <v>0.05421711337053459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05252319489697694</v>
+        <v>0.04899463643584553</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04683185312058406</v>
+        <v>0.04302401858444906</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07512864965485364</v>
+        <v>0.07149694690115004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05594479657549992</v>
+        <v>0.05215738037077251</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07664706368015059</v>
+        <v>0.07280694273377741</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03065935934182988</v>
+        <v>0.02675866719744839</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0192094416146423</v>
+        <v>0.01554997815310662</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05728612783333682</v>
+        <v>0.05348378506281475</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02664651051511433</v>
+        <v>0.02106190890276051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09922410224405973</v>
+        <v>0.09422021239720174</v>
       </c>
       <c r="D5" t="n">
-        <v>0.047555052032412</v>
+        <v>0.04115865552352881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.434340453126736</v>
+        <v>0.4282438773126979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7227636433328365</v>
+        <v>0.7185794993098751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4147265113741319</v>
+        <v>0.4097624728573121</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1578705741764844</v>
+        <v>0.1536593375015488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04813861519537913</v>
+        <v>0.09794098382262362</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5279432323135089</v>
+        <v>0.5247909864320437</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05572470953080005</v>
+        <v>0.06333247604049401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04223566982834114</v>
+        <v>0.03514456629249632</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7847705338420018</v>
+        <v>0.7799466135381935</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6147783570476287</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O5" t="n">
-        <v>2.337250791553954</v>
+        <v>2.336926779494186</v>
       </c>
       <c r="P5" t="n">
-        <v>1.548262359655559</v>
+        <v>1.54745767603802</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4792730788506325</v>
+        <v>0.4744308848400539</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06163451011640832</v>
+        <v>0.0563040832025338</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06867666318657088</v>
+        <v>0.06211007807045625</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7851775617478369</v>
+        <v>0.8099910697189067</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6225419359560487</v>
+        <v>0.6231849737861639</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5496853874296005</v>
+        <v>0.5452871613139202</v>
       </c>
       <c r="W5" t="n">
-        <v>1.076412547423271</v>
+        <v>1.07505884354629</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7735519542782363</v>
+        <v>0.7696069955402067</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.169276315386139</v>
+        <v>1.165672479936287</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.311572910621469</v>
+        <v>0.3058740058109602</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1511817646032168</v>
+        <v>0.1496168683842615</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8364019575396221</v>
+        <v>0.8321730772903918</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.782916781074871</v>
+        <v>6.741223459442617</v>
       </c>
       <c r="C6" t="n">
-        <v>1.787025576176492</v>
+        <v>1.783064888550909</v>
       </c>
       <c r="D6" t="n">
-        <v>1.784006005799359</v>
+        <v>1.779965251530932</v>
       </c>
       <c r="E6" t="n">
-        <v>6.768730641920939</v>
+        <v>1.802223964079968</v>
       </c>
       <c r="F6" t="n">
-        <v>6.784427023421365</v>
+        <v>6.780349293592887</v>
       </c>
       <c r="G6" t="n">
-        <v>1.809390916536408</v>
+        <v>6.767745982707259</v>
       </c>
       <c r="H6" t="n">
-        <v>1.789675446018892</v>
+        <v>6.748070488418602</v>
       </c>
       <c r="I6" t="n">
-        <v>1.783991581417814</v>
+        <v>6.745374359960961</v>
       </c>
       <c r="J6" t="n">
-        <v>1.814691639119348</v>
+        <v>6.773149529247298</v>
       </c>
       <c r="K6" t="n">
-        <v>1.784560687080268</v>
+        <v>6.743696508027599</v>
       </c>
       <c r="L6" t="n">
-        <v>6.746333308026584</v>
+        <v>1.779754507074205</v>
       </c>
       <c r="M6" t="n">
-        <v>6.793395263927906</v>
+        <v>6.78929397577962</v>
       </c>
       <c r="N6" t="n">
-        <v>1.815392363154694</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O6" t="n">
-        <v>1.932350703414546</v>
+        <v>6.891481187800236</v>
       </c>
       <c r="P6" t="n">
-        <v>1.774789059626335</v>
+        <v>1.771094869953725</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.811551770850874</v>
+        <v>6.769910877654814</v>
       </c>
       <c r="R6" t="n">
-        <v>6.747161725553032</v>
+        <v>1.780707701750041</v>
       </c>
       <c r="S6" t="n">
-        <v>1.785736675228762</v>
+        <v>6.74397692059632</v>
       </c>
       <c r="T6" t="n">
-        <v>6.789493381191159</v>
+        <v>1.824797849054529</v>
       </c>
       <c r="U6" t="n">
-        <v>1.823130242269917</v>
+        <v>1.819553964168887</v>
       </c>
       <c r="V6" t="n">
-        <v>6.780001566641139</v>
+        <v>1.813604754268444</v>
       </c>
       <c r="W6" t="n">
-        <v>1.936127635747726</v>
+        <v>1.932379147242124</v>
       </c>
       <c r="X6" t="n">
-        <v>1.826639113926495</v>
+        <v>6.785051161911191</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.924855445912591</v>
+        <v>1.920966374289978</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.763829072862395</v>
+        <v>1.797339402881442</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.752379155135195</v>
+        <v>6.748443759693523</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.828101240879666</v>
+        <v>1.824192420256756</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01534032770184595</v>
+        <v>0.01137793921111227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01944912280346733</v>
+        <v>0.01553241417583168</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01642955242633331</v>
+        <v>0.01243277715585278</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03867879237834827</v>
+        <v>0.03469148970488711</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05437517387877614</v>
+        <v>0.05050377336138215</v>
       </c>
       <c r="G7" t="n">
-        <v>0.041814463163384</v>
+        <v>0.03790046247575102</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02209899264586629</v>
+        <v>0.01822496818709865</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0164151280447885</v>
+        <v>0.01552883972946081</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04711518574632223</v>
+        <v>0.04330400901579253</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01698423370724289</v>
+        <v>0.0138509877960977</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01628145848400151</v>
+        <v>0.0122220326991267</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06334341438532</v>
+        <v>0.05944845554811647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04779020998847266</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1647484521525142</v>
+        <v>0.1611249582584399</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1095054073870061</v>
+        <v>0.1058379356322177</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04397531747784909</v>
+        <v>0.04006535742331159</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01710987601044341</v>
+        <v>0.0131752273749624</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01816022185573642</v>
+        <v>0.0141314003648177</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05944153164857569</v>
+        <v>0.05726537467945025</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05552126071372831</v>
+        <v>0.05200595901524861</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04994971709855395</v>
+        <v>0.04607227989336479</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07824651363282357</v>
+        <v>0.07454520821006567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05906266055346985</v>
+        <v>0.05520564167968824</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0796776576800661</v>
+        <v>0.07583379609173901</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03377722331979981</v>
+        <v>0.02980692850636411</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0223273055926122</v>
+        <v>0.01859823946202227</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06040399181130678</v>
+        <v>0.05653204637173052</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01801523900975878</v>
+        <v>0.01395080040358909</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02656458156577202</v>
+        <v>0.02235879729959745</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02354501118863801</v>
+        <v>0.01925916027961856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04342979061049046</v>
+        <v>0.03925299787225577</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05774187058153254</v>
+        <v>0.05373928355822558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04985069836731893</v>
+        <v>0.04560884108072199</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02921445140817098</v>
+        <v>0.02505135131086445</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02353058680709319</v>
+        <v>0.02235522285322658</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05423064450862691</v>
+        <v>0.05013039213955824</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02409969246954759</v>
+        <v>0.02067737091986346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02339691724630621</v>
+        <v>0.01904841582289245</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07045887314761644</v>
+        <v>0.06627483867188323</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05146350158449648</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1693677792660186</v>
+        <v>0.1655603511302615</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1138928623817766</v>
+        <v>0.1100512222989804</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04577755986223514</v>
+        <v>0.04180230447568237</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02422533477274811</v>
+        <v>0.02000161049872816</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02527568061804111</v>
+        <v>0.02095778348858337</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06655699041088045</v>
+        <v>0.06409175780321598</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06047674318844913</v>
+        <v>0.05675983033772103</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05582378684648619</v>
+        <v>0.05172292499633892</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08536284508324767</v>
+        <v>0.08137242726793811</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06127188793144268</v>
+        <v>0.05733243246597646</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09116525726877557</v>
+        <v>0.0868689072253564</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03636964917954506</v>
+        <v>0.03230077834560998</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02944276435491689</v>
+        <v>0.02542462258578804</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07215797369601555</v>
+        <v>0.06780158882198785</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02834564512668131</v>
+        <v>0.02433229799659851</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03724413436279569</v>
+        <v>0.0332091932688464</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0342245639856617</v>
+        <v>0.0301095562488675</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05536835914283868</v>
+        <v>0.05127835045870568</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06112863819070161</v>
+        <v>0.05729408985637127</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05960947091955546</v>
+        <v>0.05557723767562413</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03989400420519464</v>
+        <v>0.03590174728011335</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03421013960411685</v>
+        <v>0.03320561882247551</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06491019730565056</v>
+        <v>0.0609807881088073</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03477924526657123</v>
+        <v>0.03152776688911241</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03407647004332993</v>
+        <v>0.02989881179214139</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08113842594464842</v>
+        <v>0.07712523464113123</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06558522154780101</v>
+        <v>0.5795547819009172</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1841308551087364</v>
+        <v>0.1803668401794024</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1292330202299685</v>
+        <v>0.1254201787712919</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0617703252340205</v>
+        <v>0.05774213262318464</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03490488756977177</v>
+        <v>0.0308520064679771</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03595523341506476</v>
+        <v>0.03180817945783239</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07723654320790407</v>
+        <v>0.07494215377246498</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0733488004562208</v>
+        <v>0.06969826888682183</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07327191962692094</v>
+        <v>0.06919861735326664</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09604152519215192</v>
+        <v>0.09222198730308045</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07685767211279818</v>
+        <v>0.07288242077270293</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09747266923939436</v>
+        <v>0.09351057518475378</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04868447372205814</v>
+        <v>0.04463650654201436</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04012231715194054</v>
+        <v>0.03627501855503698</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.07819900337063515</v>
+        <v>0.07420882546474523</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04976031167560874</v>
+        <v>0.0495725829173753</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04606111531670323</v>
+        <v>0.0458059456737777</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05004131149550297</v>
+        <v>0.04985954102733287</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04991250638979065</v>
+        <v>0.04971814823926575</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05498716609493946</v>
+        <v>0.05481944654007413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05081312042252192</v>
+        <v>0.05063189714887711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05083143226455541</v>
+        <v>0.05064934688268771</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05034375093451644</v>
+        <v>0.0502433504425474</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05166815168828642</v>
+        <v>0.05149135122217424</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05064487454132711</v>
+        <v>0.05048215686570202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05030850924240213</v>
+        <v>0.05012071949388721</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05342323354076023</v>
+        <v>0.05323903276581288</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05127832466287918</v>
+        <v>0.0510973576835307</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06698891578138882</v>
+        <v>0.06664931125795397</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05726995579688791</v>
+        <v>0.05711570067244049</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05087498527760224</v>
+        <v>0.05069292818852594</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05007903548137119</v>
+        <v>0.04988374671285794</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05245019099364915</v>
+        <v>0.05227240222220509</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05309657894306335</v>
+        <v>0.05297132783443435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2158128698926944</v>
+        <v>0.2158004262289118</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0512100071984122</v>
+        <v>0.05102716114239953</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23294035278532</v>
+        <v>0.2329087091914709</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05385981400574167</v>
+        <v>0.05368947919086826</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05363115920842452</v>
+        <v>0.05346032766584276</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1960739683458327</v>
+        <v>0.1957603394782084</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05069557200310317</v>
+        <v>0.05051125258849831</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05279251602218554</v>
+        <v>0.0526653029278655</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02206090500389546</v>
+        <v>0.02183994369791935</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01712403049123478</v>
+        <v>0.01681451204895624</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02406930339414918</v>
+        <v>0.02389040485545386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0231435455427015</v>
+        <v>0.0228752808311755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05943553595181652</v>
+        <v>0.05935717339001805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02952425088377405</v>
+        <v>0.02934923323514677</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02973774252703946</v>
+        <v>0.02955657201457623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02623684690635363</v>
+        <v>0.02663989276641874</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03563698546792728</v>
+        <v>0.03549360564852356</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02836268075731682</v>
+        <v>0.0283193582055876</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0259432551486331</v>
+        <v>0.02572151394179111</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04803200030149339</v>
+        <v>0.04783434923458572</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03289324790177357</v>
+        <v>0.03272029684623216</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1040474302755715</v>
+        <v>0.1037868208379645</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0753332708408508</v>
+        <v>0.07534974904887623</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02999637858357482</v>
+        <v>0.02981554649833821</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02434750211319137</v>
+        <v>0.02407190092640319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0411430796211817</v>
+        <v>0.04099258311989001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04588851431820353</v>
+        <v>0.04611324891084932</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3135107620590022</v>
+        <v>0.3137538760897829</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03234811318405203</v>
+        <v>0.03216165841421295</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3351450198997017</v>
+        <v>0.3352346563022569</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05124158501299378</v>
+        <v>0.05114410433675048</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04971491526662742</v>
+        <v>0.04961444636983085</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2653787352774651</v>
+        <v>0.2649567131401738</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02873975878298242</v>
+        <v>0.02854293220207094</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04361418762697929</v>
+        <v>0.04382032125602408</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009056990099861899</v>
+        <v>0.005899592318055181</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01144687895761552</v>
+        <v>0.008337286068400859</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01223101233187117</v>
+        <v>0.009140916177278914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01077609940957413</v>
+        <v>0.007543819592164892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0680967152380291</v>
+        <v>0.06516533061295433</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02094894921219781</v>
+        <v>0.01786503387149086</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02115578989182918</v>
+        <v>0.01806213664215574</v>
       </c>
       <c r="I4" t="n">
-        <v>0.015647204924544</v>
+        <v>0.01347622008318109</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03070436373003731</v>
+        <v>0.0276707395482473</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01904853458717234</v>
+        <v>0.01617364848909469</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01524913380013311</v>
+        <v>0.01209104710504126</v>
       </c>
       <c r="M4" t="n">
-        <v>0.050162421781231</v>
+        <v>0.04704258746410074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02620364511155633</v>
+        <v>0.3226250321204206</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1202382873830453</v>
+        <v>0.1175190851157763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09388187505668209</v>
+        <v>0.09110257736712198</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02164774120956937</v>
+        <v>0.0185544075399897</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01265712210614296</v>
+        <v>0.009414330530450491</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03944041440274882</v>
+        <v>0.03639529334434862</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04674166364452986</v>
+        <v>0.04428997965614461</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04509706739106163</v>
+        <v>0.04220931608786962</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02608173547935116</v>
+        <v>0.0229816287491993</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03116680431911862</v>
+        <v>0.02811921324725942</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05536275478295694</v>
+        <v>0.05240182959301219</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05277787592896265</v>
+        <v>0.04971740259012589</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01280272945567826</v>
+        <v>0.009659454042375226</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01962118573991833</v>
+        <v>0.01650229806277272</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.04301332615267259</v>
+        <v>0.04052925168363843</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02400979412784412</v>
+        <v>0.01906465408416125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06726070390320797</v>
+        <v>0.06292754748610259</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08164459352167172</v>
+        <v>0.07765045385143407</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05255945973498042</v>
+        <v>0.04629555479501017</v>
       </c>
       <c r="F5" t="n">
-        <v>1.104661334751726</v>
+        <v>1.103605851857839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2081151819477784</v>
+        <v>0.2042176820430197</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2546820447569715</v>
+        <v>0.2506123374572385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1467390291096323</v>
+        <v>0.159624221794503</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3843850256968753</v>
+        <v>0.381408771143069</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1948223443727151</v>
+        <v>0.19442480173765</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1178967492827227</v>
+        <v>0.1127608391675319</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7379515587526437</v>
+        <v>0.733346004883761</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5615352627381168</v>
+        <v>0.3226250321204205</v>
       </c>
       <c r="O5" t="n">
-        <v>1.754751608867384</v>
+        <v>1.756630499396842</v>
       </c>
       <c r="P5" t="n">
-        <v>1.356197576182107</v>
+        <v>1.357181349221783</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2363296306869435</v>
+        <v>0.2323363134421488</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09382473046575064</v>
+        <v>0.08701494457917129</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5014694177056065</v>
+        <v>0.4982626884727439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6990779550151369</v>
+        <v>0.7065055964589493</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5804308027495156</v>
+        <v>0.5809534666843355</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2835260759388866</v>
+        <v>0.2793815340061149</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4009982345174433</v>
+        <v>0.3977961457294576</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8027518523718926</v>
+        <v>0.8009392056750723</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8116150950208627</v>
+        <v>0.8099918377980853</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.08041052616069806</v>
+        <v>0.07566381315875174</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2128523664283303</v>
+        <v>0.2084857687271795</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6618544686202975</v>
+        <v>0.6692064258295775</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739941542012326</v>
+        <v>6.736556832020069</v>
       </c>
       <c r="C6" t="n">
-        <v>6.742331430870077</v>
+        <v>6.738994525770412</v>
       </c>
       <c r="D6" t="n">
-        <v>6.743115564244327</v>
+        <v>6.739798155879302</v>
       </c>
       <c r="E6" t="n">
-        <v>6.74166065132203</v>
+        <v>1.776906115653319</v>
       </c>
       <c r="F6" t="n">
-        <v>6.798981267150487</v>
+        <v>6.795822570314974</v>
       </c>
       <c r="G6" t="n">
-        <v>6.751833501124659</v>
+        <v>6.748522273573511</v>
       </c>
       <c r="H6" t="n">
-        <v>1.790629245410052</v>
+        <v>6.748719376344176</v>
       </c>
       <c r="I6" t="n">
-        <v>1.785120660442768</v>
+        <v>6.744133459785198</v>
       </c>
       <c r="J6" t="n">
-        <v>1.800177819248261</v>
+        <v>1.797033035609402</v>
       </c>
       <c r="K6" t="n">
-        <v>6.74993308649963</v>
+        <v>1.78553594455025</v>
       </c>
       <c r="L6" t="n">
-        <v>6.746133685712592</v>
+        <v>6.742748286807053</v>
       </c>
       <c r="M6" t="n">
-        <v>6.781046973693691</v>
+        <v>6.777699827166112</v>
       </c>
       <c r="N6" t="n">
-        <v>1.795772166158843</v>
+        <v>0.3226250321204205</v>
       </c>
       <c r="O6" t="n">
-        <v>6.851550274659979</v>
+        <v>1.886982536856932</v>
       </c>
       <c r="P6" t="n">
-        <v>6.825193373411643</v>
+        <v>6.822207921854284</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.752532293122024</v>
+        <v>6.749211647242013</v>
       </c>
       <c r="R6" t="n">
-        <v>1.782130577624366</v>
+        <v>6.740071570232469</v>
       </c>
       <c r="S6" t="n">
-        <v>1.808913869920971</v>
+        <v>6.767052533046372</v>
       </c>
       <c r="T6" t="n">
-        <v>6.77762621555699</v>
+        <v>1.8136522757173</v>
       </c>
       <c r="U6" t="n">
-        <v>6.775983737035412</v>
+        <v>6.772962610902705</v>
       </c>
       <c r="V6" t="n">
-        <v>1.795555190997576</v>
+        <v>1.792343924810355</v>
       </c>
       <c r="W6" t="n">
-        <v>6.762479321558673</v>
+        <v>6.759225549487955</v>
       </c>
       <c r="X6" t="n">
-        <v>1.82483621030118</v>
+        <v>1.821764125654168</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.899845101346357</v>
+        <v>1.896769495909433</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.782276184973902</v>
+        <v>1.77902175010353</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.789094641258141</v>
+        <v>6.747159537764788</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.812664200835141</v>
+        <v>1.810080768173681</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01129170540255398</v>
+        <v>0.008077644538977774</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0136815942603076</v>
+        <v>0.01051533828932346</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01446572763456324</v>
+        <v>0.01131896839820152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01301081471226622</v>
+        <v>0.009721871813087488</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07033143054072111</v>
+        <v>0.06734338283387692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0231836645148899</v>
+        <v>0.02004308609241346</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02339050519452128</v>
+        <v>0.02024018886307833</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01788192022723607</v>
+        <v>0.0156542723041037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03293907903272938</v>
+        <v>0.02984879176916989</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02128324988986443</v>
+        <v>0.01835170071001729</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01748384910282519</v>
+        <v>0.01426909932596386</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05239713708392311</v>
+        <v>0.04922063968502334</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02843836041424841</v>
+        <v>0.3226250321204205</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1224729341088117</v>
+        <v>0.1196970647063857</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09611652178244851</v>
+        <v>0.09328055695773137</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02388245651226147</v>
+        <v>0.02073245976091232</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01489183740883504</v>
+        <v>0.0115923827513731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04167512970544088</v>
+        <v>0.03857334556527123</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04897637894722202</v>
+        <v>0.04646803187706722</v>
       </c>
       <c r="U7" t="n">
-        <v>0.047292825362547</v>
+        <v>0.04445905881314499</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02831645078204326</v>
+        <v>0.02515968097012192</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03340151962181068</v>
+        <v>0.03029726546818199</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05759747008564904</v>
+        <v>0.05457988181393478</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05501470896354843</v>
+        <v>0.05199150992386178</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01503744475837035</v>
+        <v>0.01183750626329783</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02185590104261041</v>
+        <v>0.01868035028369533</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04524804145536473</v>
+        <v>0.04270730390456103</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01331278020098866</v>
+        <v>0.01003643786935889</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01896793028741373</v>
+        <v>0.01560759136385463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01975206366166939</v>
+        <v>0.01641122147273269</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01655849545533731</v>
+        <v>0.01314565000588897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07286119487605168</v>
+        <v>0.06979033257043354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02914707372855393</v>
+        <v>0.02578508245719797</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02867684122162742</v>
+        <v>0.02533244193760952</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02316825625434222</v>
+        <v>0.02074652537863485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03822541505983552</v>
+        <v>0.03494104484370109</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02656958591697055</v>
+        <v>0.02344395378454843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02277018512993133</v>
+        <v>0.01936135240049502</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05768347311101827</v>
+        <v>0.05431289275955593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03119357272147064</v>
+        <v>0.3226250321204205</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1259237897658455</v>
+        <v>0.1230279329571122</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09939687525549448</v>
+        <v>0.09644780530392652</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02526183295472407</v>
+        <v>0.02207545673484479</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02017817343594118</v>
+        <v>0.01668463582590428</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04696146573254702</v>
+        <v>0.04366559863980242</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05426271497432809</v>
+        <v>0.0515602849515984</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05099472700471318</v>
+        <v>0.04802745092784483</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03267529034889458</v>
+        <v>0.0293747480659693</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03868849736105128</v>
+        <v>0.03539013435355165</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05927611420466302</v>
+        <v>0.05621006659737875</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.06349325524924128</v>
+        <v>0.0601670854261112</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01699786565354007</v>
+        <v>0.01373809397052021</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02714223706971656</v>
+        <v>0.0237726033582265</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05394521586763306</v>
+        <v>0.05107271769402703</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0190037395371947</v>
+        <v>0.01575306537604177</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02438871493342764</v>
+        <v>0.02113557728956073</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02517284830768331</v>
+        <v>0.02193920739843879</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0230266768000226</v>
+        <v>0.01966245394341919</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07413406750040212</v>
+        <v>0.07117502048012017</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03389077891006825</v>
+        <v>0.03066331878803013</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03409762586764133</v>
+        <v>0.03086042786331561</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02858904090035614</v>
+        <v>0.02627451130434097</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04364619970584942</v>
+        <v>0.04046903076940717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03199037056298447</v>
+        <v>0.02897193971025452</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02819096977594526</v>
+        <v>0.02488933832620112</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06310425775704316</v>
+        <v>0.05984087868526058</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03914548108736846</v>
+        <v>0.3226250321204205</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1341726827575353</v>
+        <v>0.131293276826338</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1080321364362778</v>
+        <v>0.105089012061643</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03458957090743989</v>
+        <v>0.03135269245652897</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02559895808195507</v>
+        <v>0.02221262175161035</v>
       </c>
       <c r="S9" t="n">
-        <v>0.05238225037856094</v>
+        <v>0.04919358456550846</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05968349962034199</v>
+        <v>0.0570882708773045</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05804102109876752</v>
+        <v>0.05510366242184266</v>
       </c>
       <c r="V9" t="n">
-        <v>0.04247981998651613</v>
+        <v>0.03917815991731408</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04410864029493074</v>
+        <v>0.04091750446841924</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06830459075876912</v>
+        <v>0.06520012081417199</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.06572182963666851</v>
+        <v>0.06261174892409904</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.023938792089373</v>
+        <v>0.02068227927109499</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03256302171573047</v>
+        <v>0.02930058928393258</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05595516212848477</v>
+        <v>0.05332754290479823</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05293711758523416</v>
+        <v>0.05285523631409</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04942241890522936</v>
+        <v>0.04934554255016408</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05317474395816571</v>
+        <v>0.05308105280135945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05896762230757736</v>
+        <v>0.05886649918666764</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05411966652911732</v>
+        <v>0.05402583911912792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05387144806640333</v>
+        <v>0.05376611024714319</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05483949582982675</v>
+        <v>0.05475272756706617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05331850787842581</v>
+        <v>0.05366558709445874</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05538037007905925</v>
+        <v>0.05529998164979819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05375428359010116</v>
+        <v>0.05391991983607718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05295723389922754</v>
+        <v>0.05289080638599424</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05454495547649946</v>
+        <v>0.05444873848901606</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05435698514779996</v>
+        <v>0.0542288459520417</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06655405525157601</v>
+        <v>0.06641735925318507</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05806507523938646</v>
+        <v>0.05792468284676207</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05461725072636991</v>
+        <v>0.05452090987311228</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05335526874423169</v>
+        <v>0.0540718075083813</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05304224125755654</v>
+        <v>0.05291132033908907</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05574073819873387</v>
+        <v>0.05594904550600597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2203516361734066</v>
+        <v>0.2208799047181116</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05715321478661591</v>
+        <v>0.05706261650994376</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2445508769927137</v>
+        <v>0.2452061961098655</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05312085889869812</v>
+        <v>0.0530117844497769</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05962599921507911</v>
+        <v>0.05955495731133878</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2062755598182431</v>
+        <v>0.2061217388922285</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05329594216438865</v>
+        <v>0.05361177419819511</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05362483637000793</v>
+        <v>0.05355286702823783</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02459621208734316</v>
+        <v>0.02453923610725992</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02084206362634598</v>
+        <v>0.02075057386022074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0263011448922693</v>
+        <v>0.02615992932382668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06762241985781883</v>
+        <v>0.06742841933493565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03306052182111174</v>
+        <v>0.03291820567378946</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03122996048717118</v>
+        <v>0.03100627607230527</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03824917344567184</v>
+        <v>0.03815738287682453</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02733084750869292</v>
+        <v>0.03034475624844845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04198008457364715</v>
+        <v>0.04193447960232249</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03041323778239248</v>
+        <v>0.03211639321038855</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02474133570812173</v>
+        <v>0.02479443899183331</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03627175709814752</v>
+        <v>0.0361121873017581</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03474498948755481</v>
+        <v>0.03435772784340608</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08589289766994947</v>
+        <v>0.0856944734127907</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06107382428118924</v>
+        <v>0.06060082343105517</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03659062512579675</v>
+        <v>0.03643057477760499</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02759896064282864</v>
+        <v>0.03326631051565952</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0253422674423149</v>
+        <v>0.02493726889360492</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0446672169581376</v>
+        <v>0.04668752323560132</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3165074830511844</v>
+        <v>0.3174869538277572</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05451465793143495</v>
+        <v>0.05439559457331066</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3860782987159107</v>
+        <v>0.3872530838484449</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02591357408401665</v>
+        <v>0.0256623823900843</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0723118685318514</v>
+        <v>0.07233231870844276</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3013632653843837</v>
+        <v>0.3011259462851049</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02715956505267167</v>
+        <v>0.02994155941015168</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0297996860352975</v>
+        <v>0.02981210889117729</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01268558218091993</v>
+        <v>0.01006212669030981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01683423116413361</v>
+        <v>0.0141226655844483</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01536968137671394</v>
+        <v>0.0126128277947344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08080290718901741</v>
+        <v>0.07796210615361712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02604301650147064</v>
+        <v>0.0232846238771079</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02323927477898142</v>
+        <v>0.02035086678685691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03417381959082177</v>
+        <v>0.03149516328177768</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01699356099072243</v>
+        <v>0.01921541153435046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04039462766784998</v>
+        <v>0.03778832799899322</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02191584812082686</v>
+        <v>0.02208821684977286</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01291280520143681</v>
+        <v>0.01046390701550926</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03123189083851473</v>
+        <v>0.02844641180022403</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02872363947144931</v>
+        <v>0.3316841556672353</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09325049560979727</v>
+        <v>0.09052149500475647</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07060822286163733</v>
+        <v>0.06732385733746217</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03166345890947884</v>
+        <v>0.02887667578716028</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01740879188083348</v>
+        <v>0.02380385798022916</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01387300241907958</v>
+        <v>0.01069562155260007</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04435376673960077</v>
+        <v>0.04500812473554389</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04523298902517353</v>
+        <v>0.04264087689400769</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06105279388901259</v>
+        <v>0.05833279052412488</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1056875533056479</v>
+        <v>0.103094175511035</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01476102484167532</v>
+        <v>0.0118304098985938</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08867356537267454</v>
+        <v>0.08614370723471838</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06165367814654461</v>
+        <v>0.05890264832065117</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0167386708699311</v>
+        <v>0.01860757011589797</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02093362147322422</v>
+        <v>0.01841853902448305</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03249327003959667</v>
+        <v>0.02999125868930641</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1137452171762101</v>
+        <v>0.1095847391342089</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08823906233197562</v>
+        <v>0.08324155376287758</v>
       </c>
       <c r="E5" t="n">
-        <v>1.312771428370669</v>
+        <v>1.306329771737979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2986239041210493</v>
+        <v>0.2935260339628765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2127903704106317</v>
+        <v>0.2056691472340671</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4808320222762635</v>
+        <v>0.4773219362835541</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1209744860227776</v>
+        <v>0.2152995055445748</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5245296547636079</v>
+        <v>0.5227452635570833</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1986043302436953</v>
+        <v>0.2453986411281465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03765299922520141</v>
+        <v>0.03833194088334203</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3782297292337474</v>
+        <v>0.3725376904529245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6042445762435351</v>
+        <v>0.3316841556672352</v>
       </c>
       <c r="O5" t="n">
-        <v>1.382234217302011</v>
+        <v>1.377902435619591</v>
       </c>
       <c r="P5" t="n">
-        <v>1.060462889292552</v>
+        <v>1.046338681459238</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3931154341184196</v>
+        <v>0.3875944194353328</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1320229526039123</v>
+        <v>0.3144812546413333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0525993069170016</v>
+        <v>0.04072259478865129</v>
       </c>
       <c r="T5" t="n">
-        <v>0.665433812780338</v>
+        <v>0.7283520288023105</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6203199376521716</v>
+        <v>0.6189821729346446</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8379982434934075</v>
+        <v>0.8337066815747206</v>
       </c>
       <c r="W5" t="n">
-        <v>1.799924172929131</v>
+        <v>1.798139774508388</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07506749576676801</v>
+        <v>0.066681745493629</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.448144245357231</v>
+        <v>1.447993413762017</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8857310008618535</v>
+        <v>0.881023233049618</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1104657049731605</v>
+        <v>0.1931664629098238</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2075947762690819</v>
+        <v>0.2074787115324276</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.239569768405494</v>
+        <v>1.911612087209741</v>
       </c>
       <c r="C6" t="n">
-        <v>1.918434975765267</v>
+        <v>1.915672626103879</v>
       </c>
       <c r="D6" t="n">
-        <v>7.242253867601286</v>
+        <v>1.914162788314166</v>
       </c>
       <c r="E6" t="n">
-        <v>7.307687093413592</v>
+        <v>7.30474276573536</v>
       </c>
       <c r="F6" t="n">
-        <v>7.252927202726043</v>
+        <v>1.924834584396538</v>
       </c>
       <c r="G6" t="n">
-        <v>1.924840019380115</v>
+        <v>7.247131526368594</v>
       </c>
       <c r="H6" t="n">
-        <v>7.261058005815396</v>
+        <v>1.933045123801207</v>
       </c>
       <c r="I6" t="n">
-        <v>1.918594305591855</v>
+        <v>1.920765372053781</v>
       </c>
       <c r="J6" t="n">
-        <v>1.941995372268984</v>
+        <v>1.939338288518424</v>
       </c>
       <c r="K6" t="n">
-        <v>1.923516592721961</v>
+        <v>7.248868876431514</v>
       </c>
       <c r="L6" t="n">
-        <v>7.239796991426012</v>
+        <v>7.23724456659725</v>
       </c>
       <c r="M6" t="n">
-        <v>7.258116077063091</v>
+        <v>1.929996372319654</v>
       </c>
       <c r="N6" t="n">
-        <v>1.930131052438351</v>
+        <v>0.3316841556672352</v>
       </c>
       <c r="O6" t="n">
-        <v>1.9946579085767</v>
+        <v>7.317761562389645</v>
       </c>
       <c r="P6" t="n">
-        <v>7.297931391059551</v>
+        <v>7.294562641746086</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.258547645134049</v>
+        <v>1.930426636306591</v>
       </c>
       <c r="R6" t="n">
-        <v>7.244292978105405</v>
+        <v>7.250584517561972</v>
       </c>
       <c r="S6" t="n">
-        <v>7.240757188643652</v>
+        <v>1.912245582072032</v>
       </c>
       <c r="T6" t="n">
-        <v>1.945954511340734</v>
+        <v>1.946558085254973</v>
       </c>
       <c r="U6" t="n">
-        <v>7.271683187104659</v>
+        <v>7.269016386619187</v>
       </c>
       <c r="V6" t="n">
-        <v>7.28793698011359</v>
+        <v>1.959882751043557</v>
       </c>
       <c r="W6" t="n">
-        <v>2.104165998145423</v>
+        <v>2.101522069655668</v>
       </c>
       <c r="X6" t="n">
-        <v>1.91636176944281</v>
+        <v>7.238611069480338</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.072990399943097</v>
+        <v>2.070441319123577</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.963254422747677</v>
+        <v>7.285683307902394</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.243622857094507</v>
+        <v>7.245388229697635</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.922183165030324</v>
+        <v>1.919621304538864</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01619661831148956</v>
+        <v>0.01359384548966817</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0203452672947034</v>
+        <v>0.01765438438380661</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01888071750728366</v>
+        <v>0.01614454659409278</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08431394331958704</v>
+        <v>0.0814938249529755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02955405263204038</v>
+        <v>0.02681634267646623</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02675031090955118</v>
+        <v>0.02388258558621526</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0376848557213916</v>
+        <v>0.03502688208113598</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02050459712129227</v>
+        <v>0.02274713033370879</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04390566379841982</v>
+        <v>0.04132004679835156</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02542688425139664</v>
+        <v>0.02561993564913122</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01642384133200653</v>
+        <v>0.01399562581486764</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0347429269690845</v>
+        <v>0.03197813059958237</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03223467560201921</v>
+        <v>0.3316841556672352</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09676138250365507</v>
+        <v>0.0940530646899045</v>
       </c>
       <c r="P7" t="n">
-        <v>0.07411910975549527</v>
+        <v>0.0708554270226102</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03517449504004852</v>
+        <v>0.03240839458651862</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02091982801140302</v>
+        <v>0.02733557677958749</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01738403854964961</v>
+        <v>0.01422734035195842</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04786480287017061</v>
+        <v>0.0485398435349022</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04831837109901815</v>
+        <v>0.04578016576406359</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06456383001958244</v>
+        <v>0.0618645093234832</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1091985894362176</v>
+        <v>0.1066258943103933</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01827206097224514</v>
+        <v>0.01536212869795211</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0917506133581595</v>
+        <v>0.0892702761775207</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06516471427711443</v>
+        <v>0.06243436712000949</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02024970700050059</v>
+        <v>0.02213928891525632</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02444465760379397</v>
+        <v>0.02195025782384135</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01898424608945276</v>
+        <v>0.0163511913530621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02790528550023078</v>
+        <v>0.02516002090219721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02644073571281102</v>
+        <v>0.02365018311248323</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08933280440074838</v>
+        <v>0.08647113676482102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03308516306156923</v>
+        <v>0.03031341672861498</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03529991535885827</v>
+        <v>0.03237281110359921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04524487392691877</v>
+        <v>0.04253251859952648</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02806461532681965</v>
+        <v>0.03025276685209937</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05146568200394713</v>
+        <v>0.04882568331674202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03298690245692398</v>
+        <v>0.03312557216752172</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02398385953753379</v>
+        <v>0.02150126233325806</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04230294517460879</v>
+        <v>0.03948376711797296</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03609529282059164</v>
+        <v>0.3316841556672352</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1016387764673696</v>
+        <v>0.09888962440142479</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07874730375217188</v>
+        <v>0.07544404518505771</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03702423917664942</v>
+        <v>0.03423259296366615</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02847984621693058</v>
+        <v>0.03484121329797803</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0249440567551766</v>
+        <v>0.02173297687034895</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05542482107569789</v>
+        <v>0.05604548005329275</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05354728950876826</v>
+        <v>0.0509654782481728</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07082673329384717</v>
+        <v>0.06808336654413527</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1167595455451881</v>
+        <v>0.1141324639967959</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02055920416949744</v>
+        <v>0.0176215173442346</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1040669575690116</v>
+        <v>0.101514091242683</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.06786369245341607</v>
+        <v>0.0651035110473069</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02780972520602809</v>
+        <v>0.02964492543364679</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03698983666425117</v>
+        <v>0.03441588097035357</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03250551973346077</v>
+        <v>0.02975542878369398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04247073512163513</v>
+        <v>0.03958967758337489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04100618533421534</v>
+        <v>0.038079839793661</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1050969793257405</v>
+        <v>0.1020965774591772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03827073386233574</v>
+        <v>0.0354416451696108</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04887578911102954</v>
+        <v>0.04581788918913224</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05981032354832319</v>
+        <v>0.05696217528070419</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04263006494822395</v>
+        <v>0.04468242353327704</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06603113162535156</v>
+        <v>0.06325533999791973</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04755235207832835</v>
+        <v>0.04755522884869948</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03854930915893807</v>
+        <v>0.03593091901443593</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05686839479601623</v>
+        <v>0.05391342379915062</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05436014342895076</v>
+        <v>0.3316841556672352</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1208146158704182</v>
+        <v>0.117901920757358</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09859156433957449</v>
+        <v>0.09512041549028655</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.057299973241527</v>
+        <v>0.05434369818943559</v>
       </c>
       <c r="R9" t="n">
-        <v>0.043045295838335</v>
+        <v>0.04927086997915577</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03950950637658125</v>
+        <v>0.0361626335515267</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06999027069710234</v>
+        <v>0.07047513673447044</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07043550483758913</v>
+        <v>0.06770273903637816</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09340150273030444</v>
+        <v>0.09046255204882465</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1313240572631494</v>
+        <v>0.1285611875099616</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04039752879917696</v>
+        <v>0.03729742189752042</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1138760811850908</v>
+        <v>0.1112055693770889</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08378331391073858</v>
+        <v>0.08088863079590776</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04237517482743255</v>
+        <v>0.04407458211482453</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04657012543072571</v>
+        <v>0.04388555102340962</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05167549862510439</v>
+        <v>0.05144005559020474</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04807375652941501</v>
+        <v>0.04775679134635797</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05174219273223173</v>
+        <v>0.05150526485450799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0554035316306964</v>
+        <v>0.05517165637071825</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05558283482527467</v>
+        <v>0.05535646192174701</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05257225476450388</v>
+        <v>0.05232216010014567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05312266505946617</v>
+        <v>0.05289453754970482</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05174853260301664</v>
+        <v>0.05171951205279779</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05442117335354783</v>
+        <v>0.05419920037611536</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05184257607831121</v>
+        <v>0.05203253830393963</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05176807380625901</v>
+        <v>0.05152221026042199</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05950634559251596</v>
+        <v>0.0592795277127323</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05351650888851819</v>
+        <v>0.0532792423968277</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07277371766278193</v>
+        <v>0.07227810920974839</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05795377254252706</v>
+        <v>0.05769422280404934</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05463323833367149</v>
+        <v>0.05439499252099817</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05196017698015819</v>
+        <v>0.05187400636777565</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05188154526059285</v>
+        <v>0.05162870142709006</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05512271245370915</v>
+        <v>0.05520606080550635</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196707189047347</v>
+        <v>0.2198700303989288</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05451932778087905</v>
+        <v>0.05428732777596904</v>
       </c>
       <c r="W2" t="n">
-        <v>0.239947353818704</v>
+        <v>0.2402243948895542</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05368193310176517</v>
+        <v>0.05344177066018125</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.056803324470975</v>
+        <v>0.05657188251563847</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2011841632418242</v>
+        <v>0.2008175000182143</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05207989179850984</v>
+        <v>0.05210758870363116</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05377004335978344</v>
+        <v>0.05353875954540251</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02343894971547536</v>
+        <v>0.02318456117096505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01933111664531523</v>
+        <v>0.01894463160444192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02391803546913853</v>
+        <v>0.02365261335814777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05003741248315505</v>
+        <v>0.04980849273654286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05135618368104242</v>
+        <v>0.05116610667335149</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02979425778035698</v>
+        <v>0.0294354823392663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0338283255039995</v>
+        <v>0.03362604194973977</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02396409437543209</v>
+        <v>0.02518729520785467</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04296991269088402</v>
+        <v>0.04281150963723072</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02463041256747417</v>
+        <v>0.02739633055841284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02409887948129119</v>
+        <v>0.02376992021293426</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07887068770367267</v>
+        <v>0.07867465512085724</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03659724841401737</v>
+        <v>0.0363297274592937</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1220357849744185</v>
+        <v>0.1214920197876797</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06803993295895761</v>
+        <v>0.06761428206674873</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04446902865742548</v>
+        <v>0.04419430056876654</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0254817066742196</v>
+        <v>0.02629683018640452</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02490087925128033</v>
+        <v>0.02452283625247961</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04809612194428126</v>
+        <v>0.05012143126536841</v>
       </c>
       <c r="U3" t="n">
-        <v>0.323668338801755</v>
+        <v>0.3242160703804642</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04360461040590939</v>
+        <v>0.04337416084715378</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3665380139166501</v>
+        <v>0.3672277120650355</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03776140214970355</v>
+        <v>0.03747299444862069</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06002354998933081</v>
+        <v>0.0597975021589257</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2819988432469329</v>
+        <v>0.2815274427413089</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02632675655488152</v>
+        <v>0.02795083349428487</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03848298827398311</v>
+        <v>0.03825694107144886</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01157814171468564</v>
+        <v>0.00757195402664915</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01532698221774814</v>
+        <v>0.01132708118345837</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01233148233549459</v>
+        <v>0.008308522664698189</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05368798949275983</v>
+        <v>0.0497221014637194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05571330155906608</v>
+        <v>0.05180956517734202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02170741483740824</v>
+        <v>0.01753573025455489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02792455232025324</v>
+        <v>0.02400099685396082</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01240309409249472</v>
+        <v>0.01072854332796197</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04269638383918615</v>
+        <v>0.03884276757240334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01346535840808235</v>
+        <v>0.01426431883379918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01262382097251476</v>
+        <v>0.008499928819768859</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09942803700929924</v>
+        <v>0.09551556833470777</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0323731995465078</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1440117118007108</v>
+        <v>0.1402967739114681</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08249413376066789</v>
+        <v>0.07821564976608548</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0449871723504392</v>
+        <v>0.04094932599810805</v>
       </c>
       <c r="R4" t="n">
-        <v>0.014793714693532</v>
+        <v>0.01247362768653356</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01390553324866358</v>
+        <v>0.009702795535641641</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0505160077054851</v>
+        <v>0.05011071538147259</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05920955181889873</v>
+        <v>0.05536656606948934</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04439894780313879</v>
+        <v>0.04043437491002901</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07809812070232046</v>
+        <v>0.07429396413414426</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03424174213403033</v>
+        <v>0.0301822465764603</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0696419753544337</v>
+        <v>0.06566817327219747</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03601824689595134</v>
+        <v>0.0320116866161296</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01614594863835159</v>
+        <v>0.01511204762320492</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03529566271356387</v>
+        <v>0.03133476328700126</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02212471062355382</v>
+        <v>0.0165386349745628</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08832456398441119</v>
+        <v>0.08251928774976128</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03704832778508242</v>
+        <v>0.03093957829024527</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7624010767742351</v>
+        <v>0.7575305709088763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8184718783221433</v>
+        <v>0.8144789027238138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1780169984504683</v>
+        <v>0.1695984200096813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3427858172140033</v>
+        <v>0.3386061532128328</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0387351450823968</v>
+        <v>0.07663795067888518</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5370442163613968</v>
+        <v>0.5340713522473962</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0549968114011424</v>
+        <v>0.1261931677570885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04021302859880207</v>
+        <v>0.03244201932645036</v>
       </c>
       <c r="M5" t="n">
-        <v>1.508671964599656</v>
+        <v>1.504127496251207</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7610861660389802</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O5" t="n">
-        <v>2.077064825656139</v>
+        <v>2.075909551700037</v>
       </c>
       <c r="P5" t="n">
-        <v>1.168926441881531</v>
+        <v>1.158932923769636</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5718420683591648</v>
+        <v>0.5655219441467372</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0846944485531971</v>
+        <v>0.1110790974254618</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05881330310404034</v>
+        <v>0.0500286391702892</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7389111856613058</v>
+        <v>0.7993282347175844</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7877798365171634</v>
+        <v>0.784784741110283</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5231297688284171</v>
+        <v>0.5179056603710153</v>
       </c>
       <c r="W5" t="n">
-        <v>1.204959193771084</v>
+        <v>1.202950748848596</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4242269345071304</v>
+        <v>0.4175236304310018</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.039845667550542</v>
+        <v>1.034947406102086</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4013027883610154</v>
+        <v>0.3955919447845408</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1037599676843294</v>
+        <v>0.1509626954811442</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4744062518852394</v>
+        <v>0.4694014990419106</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.782434546966791</v>
+        <v>6.73994848687528</v>
       </c>
       <c r="C6" t="n">
-        <v>6.74791064044781</v>
+        <v>6.743703614032084</v>
       </c>
       <c r="D6" t="n">
-        <v>1.783187887587599</v>
+        <v>6.740685055513324</v>
       </c>
       <c r="E6" t="n">
-        <v>6.786271647722829</v>
+        <v>1.820535400555243</v>
       </c>
       <c r="F6" t="n">
-        <v>6.788296959789128</v>
+        <v>1.822622864268866</v>
       </c>
       <c r="G6" t="n">
-        <v>1.792563820089514</v>
+        <v>1.788349029346079</v>
       </c>
       <c r="H6" t="n">
-        <v>6.760508210550316</v>
+        <v>1.794814295945486</v>
       </c>
       <c r="I6" t="n">
-        <v>6.74498675232256</v>
+        <v>6.743105076176594</v>
       </c>
       <c r="J6" t="n">
-        <v>1.813552789091292</v>
+        <v>6.771219300421031</v>
       </c>
       <c r="K6" t="n">
-        <v>6.746049016638148</v>
+        <v>1.785077617925323</v>
       </c>
       <c r="L6" t="n">
-        <v>1.78348022622462</v>
+        <v>6.740876461668399</v>
       </c>
       <c r="M6" t="n">
-        <v>6.832011695239366</v>
+        <v>1.866328867426231</v>
       </c>
       <c r="N6" t="n">
-        <v>1.80316087421747</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O6" t="n">
-        <v>1.914799386471673</v>
+        <v>6.873150425815467</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75096311579014</v>
+        <v>1.746652239295573</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.777570830580507</v>
+        <v>1.811762625089631</v>
       </c>
       <c r="R6" t="n">
-        <v>6.747377372923595</v>
+        <v>6.744850160535169</v>
       </c>
       <c r="S6" t="n">
-        <v>1.784761938500771</v>
+        <v>1.780516094627166</v>
       </c>
       <c r="T6" t="n">
-        <v>1.821372412957591</v>
+        <v>1.820924014472996</v>
       </c>
       <c r="U6" t="n">
-        <v>1.829923275276798</v>
+        <v>6.787613225552366</v>
       </c>
       <c r="V6" t="n">
-        <v>6.77698260603321</v>
+        <v>1.811247674001552</v>
       </c>
       <c r="W6" t="n">
-        <v>1.939176426924572</v>
+        <v>1.935325443275913</v>
       </c>
       <c r="X6" t="n">
-        <v>1.805098147386136</v>
+        <v>6.762558779425084</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.917877268385204</v>
+        <v>1.913871272404536</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.806874652148057</v>
+        <v>6.764388219464758</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.748729606868421</v>
+        <v>1.785925346714729</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.806052222580036</v>
+        <v>1.80205313014905</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01457839964131342</v>
+        <v>0.01050536782937133</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01832724014437591</v>
+        <v>0.01426049498618055</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01533174026212236</v>
+        <v>0.01124193646742037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05668824741938761</v>
+        <v>0.0526555152664416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05871355948569379</v>
+        <v>0.05474297898006418</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02470767276403596</v>
+        <v>0.02046914405727707</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03092481024688099</v>
+        <v>0.02693441065668306</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01540335201912248</v>
+        <v>0.01366195713068415</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04569664176581389</v>
+        <v>0.04177618137512551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01646561633471012</v>
+        <v>0.01719773263652137</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01562407889914254</v>
+        <v>0.01143334262249101</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1024282949359271</v>
+        <v>0.09844898213742999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03537345747313556</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1470118751274198</v>
+        <v>0.1432300847193841</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08549429708737689</v>
+        <v>0.08114896057400132</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04798743027706694</v>
+        <v>0.04388273980083021</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01779397262015977</v>
+        <v>0.01540704148925574</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01690579117529135</v>
+        <v>0.01263620933836383</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05351626563211292</v>
+        <v>0.05304412918419481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06204931651988449</v>
+        <v>0.05816465586453253</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04739920572976657</v>
+        <v>0.04336778871275118</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08109837862894831</v>
+        <v>0.07722737793686633</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03724200006065811</v>
+        <v>0.03311566037918254</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07249955148685466</v>
+        <v>0.06847171370916559</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03901850482257908</v>
+        <v>0.03494510041885177</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01914620656497936</v>
+        <v>0.01804546142592712</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03829592064019167</v>
+        <v>0.03426817708972345</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01724199204495881</v>
+        <v>0.01305401176752504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02531180383000629</v>
+        <v>0.02091454504575507</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02231630394775273</v>
+        <v>0.01789598652699487</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06137202135945753</v>
+        <v>0.05712355766931909</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06205030871400361</v>
+        <v>0.05793119721042903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03258821799295553</v>
+        <v>0.02797447681995667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03790937393251136</v>
+        <v>0.03358846071625753</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02238791570475286</v>
+        <v>0.02031600719025867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05268120545144427</v>
+        <v>0.04843023143470005</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02345018002034049</v>
+        <v>0.02385178269609585</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02260864258477291</v>
+        <v>0.01808739268206553</v>
       </c>
       <c r="M8" t="n">
-        <v>0.109412858621554</v>
+        <v>0.1051030321970177</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03900854553067544</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1515675227668512</v>
+        <v>0.1475764059182934</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08982431651855892</v>
+        <v>0.08528090973293964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04980185320435038</v>
+        <v>0.04562457773620658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02477853630579015</v>
+        <v>0.02206109154883025</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02389035486092173</v>
+        <v>0.0192902593979383</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06050082931774325</v>
+        <v>0.05969817924376924</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06692895311187522</v>
+        <v>0.06281621833404498</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05318763889856932</v>
+        <v>0.04889519833785647</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08808379150221811</v>
+        <v>0.08388223482113569</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03945244858752141</v>
+        <v>0.03523376693993795</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08375687034189278</v>
+        <v>0.07920058594538187</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.04160183296688744</v>
+        <v>0.03741748433102702</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02613077025060974</v>
+        <v>0.02469951148550162</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04979410013702554</v>
+        <v>0.0452106671267408</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02521224498049583</v>
+        <v>0.02106167765553527</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03304602958167489</v>
+        <v>0.0288182702668806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03005052969942135</v>
+        <v>0.02579971174812044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0704642391402906</v>
+        <v>0.06628975927099176</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06401545363841873</v>
+        <v>0.06007630018616969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03942645013596143</v>
+        <v>0.03502690715535365</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04564359968417999</v>
+        <v>0.0414921859373831</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03012214145642145</v>
+        <v>0.02821973241138423</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06041543120311292</v>
+        <v>0.0563339566558256</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03118440577200909</v>
+        <v>0.03175550791722141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03034286833644155</v>
+        <v>0.02599111790319107</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1171470843732261</v>
+        <v>0.1130067574181301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05009224691043455</v>
+        <v>0.3937110344914039</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1630844882261537</v>
+        <v>0.1591140271871235</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1018613256549231</v>
+        <v>0.09732130190163316</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06270620764899244</v>
+        <v>0.05844050289890683</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03251276205745877</v>
+        <v>0.0299648167699558</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03162458061259035</v>
+        <v>0.02719398461906387</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06823505506941188</v>
+        <v>0.06760190446489484</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07678591738861865</v>
+        <v>0.07272788178715771</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0668319003735084</v>
+        <v>0.06254313652101691</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09581716806624721</v>
+        <v>0.09178515321756646</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05196078949795713</v>
+        <v>0.04767343565988257</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.08721834092415369</v>
+        <v>0.08302948898986569</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05127443142509007</v>
+        <v>0.04709034301707353</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03386499600227837</v>
+        <v>0.03260323670662718</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05301471007749063</v>
+        <v>0.0488259523704235</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -798,7 +798,7 @@
         <v>0.030081279507307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3152386798576731</v>
+        <v>0.02340831017256485</v>
       </c>
       <c r="O4" t="n">
         <v>0.03527582284415887</v>
@@ -974,7 +974,7 @@
         <v>7.752792375971987</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3152386798576731</v>
+        <v>2.054831340057707</v>
       </c>
       <c r="O6" t="n">
         <v>2.066698885112092</v>
@@ -1062,7 +1062,7 @@
         <v>0.03374608964844675</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3152386798576731</v>
+        <v>0.02707312031370452</v>
       </c>
       <c r="O7" t="n">
         <v>0.03894048100748203</v>
@@ -1150,7 +1150,7 @@
         <v>0.04168532615057435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3152386798576731</v>
+        <v>0.03112415159967812</v>
       </c>
       <c r="O8" t="n">
         <v>0.04406017682104639</v>
@@ -1238,7 +1238,7 @@
         <v>0.05899076345562908</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3152386798576731</v>
+        <v>0.05231779412088685</v>
       </c>
       <c r="O9" t="n">
         <v>0.06635464792789182</v>
@@ -1658,7 +1658,7 @@
         <v>0.05927332899300929</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4711140543954614</v>
+        <v>0.03118777069955849</v>
       </c>
       <c r="O4" t="n">
         <v>0.1241319393247082</v>
@@ -1834,7 +1834,7 @@
         <v>1.828819070563351</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4711140543954614</v>
+        <v>1.8007492995688</v>
       </c>
       <c r="O6" t="n">
         <v>6.856355765323301</v>
@@ -1922,7 +1922,7 @@
         <v>0.06193366308686731</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4711140543954614</v>
+        <v>0.03384810479341652</v>
       </c>
       <c r="O7" t="n">
         <v>0.1267922094939624</v>
@@ -2010,7 +2010,7 @@
         <v>0.06862160849906575</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4711140543954614</v>
+        <v>0.0373934205269287</v>
       </c>
       <c r="O8" t="n">
         <v>0.1312012110722149</v>
@@ -2098,7 +2098,7 @@
         <v>0.07662867048678554</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4711140543954614</v>
+        <v>0.04854311219333478</v>
       </c>
       <c r="O9" t="n">
         <v>0.1428112979972561</v>
@@ -2518,7 +2518,7 @@
         <v>0.02281842193186881</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2235747660128168</v>
+        <v>0.01969262063187264</v>
       </c>
       <c r="O4" t="n">
         <v>0.07851740622248728</v>
@@ -2694,7 +2694,7 @@
         <v>7.249125781119106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2235747660128168</v>
+        <v>1.920649084527631</v>
       </c>
       <c r="O6" t="n">
         <v>1.979483024513158</v>
@@ -2782,7 +2782,7 @@
         <v>0.02614448949921656</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2235747660128168</v>
+        <v>0.0230186881992204</v>
       </c>
       <c r="O7" t="n">
         <v>0.08184331779949519</v>
@@ -2870,7 +2870,7 @@
         <v>0.03311940226588865</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2235747660128168</v>
+        <v>0.02654632548365622</v>
       </c>
       <c r="O8" t="n">
         <v>0.08631845230522303</v>
@@ -2958,7 +2958,7 @@
         <v>0.04664408878141829</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2235747660128168</v>
+        <v>0.04351828748142212</v>
       </c>
       <c r="O9" t="n">
         <v>0.104135864657628</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05104623505724647</v>
+        <v>0.0510462350572466</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04743170785351847</v>
+        <v>0.04743170785351852</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05108792843960027</v>
+        <v>0.05108792843960033</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05402455334535597</v>
+        <v>0.05402455334535607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05449114739057592</v>
+        <v>0.05449114739057606</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05151388060432713</v>
+        <v>0.05151388060432724</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05298408314552189</v>
+        <v>0.05298408314552199</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05147880574274793</v>
+        <v>0.05147880574274805</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05253953157436852</v>
+        <v>0.05253953157436864</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05106312771699079</v>
+        <v>0.05106312771699087</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091687981853232</v>
+        <v>0.05091687981853244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05187939947752032</v>
+        <v>0.05187939947752039</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0516778831638605</v>
+        <v>0.05167788316386055</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0659179306260565</v>
+        <v>0.06591793062605655</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05480682152970028</v>
+        <v>0.05480682152970036</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05521530985741261</v>
+        <v>0.05521530985741269</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05244454949954772</v>
+        <v>0.05244454949954783</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05095951986796586</v>
+        <v>0.05095951986796598</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05464844374482734</v>
+        <v>0.05464844374482739</v>
       </c>
       <c r="U2" t="n">
         <v>0.2171369908740653</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0539917399907444</v>
+        <v>0.05399173999074452</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2389454631694079</v>
+        <v>0.238945463169408</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05112010561143606</v>
+        <v>0.05112010561143621</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05551332622583104</v>
+        <v>0.05551332622583112</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008988278507524</v>
+        <v>0.2008988278507526</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05167147323924701</v>
+        <v>0.05167147323924711</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05122274192705089</v>
+        <v>0.05122274192705092</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02373612736555836</v>
+        <v>0.02373612736555838</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01920872494745782</v>
+        <v>0.01920872494745783</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0240427811435723</v>
+        <v>0.02404278114357228</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04499337062397001</v>
+        <v>0.04499337062397005</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04838530962513489</v>
+        <v>0.04838530962513485</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02706079272905703</v>
+        <v>0.02706079272905706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03765748961684962</v>
+        <v>0.03765748961684964</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02684374385667021</v>
+        <v>0.02684374385667023</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03437100093900426</v>
+        <v>0.03437100093900425</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0238588826759325</v>
+        <v>0.02385888267593247</v>
       </c>
       <c r="L3" t="n">
         <v>0.02281725936869168</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02986562109857736</v>
+        <v>0.02986562109857735</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02825704867629183</v>
+        <v>0.0282570486762918</v>
       </c>
       <c r="O3" t="n">
         <v>0.09303717483575627</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05047105803539109</v>
+        <v>0.05047105803539115</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05350371470603571</v>
+        <v>0.05350371470603572</v>
       </c>
       <c r="R3" t="n">
         <v>0.0337718764409946</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02311980939362664</v>
+        <v>0.02311980939362665</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0495331860734593</v>
+        <v>0.04953318607345929</v>
       </c>
       <c r="U3" t="n">
         <v>0.3080614243802543</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04462540896011095</v>
+        <v>0.04462540896011097</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3612040433712349</v>
+        <v>0.3612040433712346</v>
       </c>
       <c r="X3" t="n">
         <v>0.02427151036826592</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05561660329711202</v>
+        <v>0.05561660329711206</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2832592588815851</v>
+        <v>0.2832592588815853</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02820504509450191</v>
+        <v>0.0282050450945019</v>
       </c>
       <c r="AB3" t="n">
         <v>0.02520680279053188</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009221551613885789</v>
+        <v>0.009221551613885713</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01214345672299522</v>
+        <v>0.01214345672299507</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00969249754747452</v>
+        <v>0.009692497547474367</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04286302677218489</v>
+        <v>0.04286302677218481</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04813342115681</v>
+        <v>0.04813342115680989</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01450382319574177</v>
+        <v>0.01450382319574163</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03111043722511968</v>
+        <v>0.03111043722511954</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01410763649897158</v>
+        <v>0.01410763649897145</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02619663253143605</v>
+        <v>0.026196632531436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009412361976704703</v>
+        <v>0.009412361976704593</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007760424686259763</v>
+        <v>0.00776042468625963</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01891158563858823</v>
+        <v>0.0189115856385881</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1777972287123813</v>
+        <v>0.01635630755057519</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1021168604812799</v>
+        <v>0.1021168604812797</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05169910577549756</v>
+        <v>0.0516991057754974</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05631316935092343</v>
+        <v>0.05631316935092335</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02501615649610213</v>
+        <v>0.02501615649610199</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00824206366000318</v>
+        <v>0.008242063660002996</v>
       </c>
       <c r="T4" t="n">
-        <v>0.049910155837977</v>
+        <v>0.0499101558379769</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03042753389083903</v>
+        <v>0.03042753389083899</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04321108250039338</v>
+        <v>0.04321108250039334</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06540859029518734</v>
+        <v>0.06540859029518725</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01005595350559112</v>
+        <v>0.01005595350559096</v>
       </c>
       <c r="Y4" t="n">
         <v>0.05991178576849796</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0344705268256052</v>
+        <v>0.03447052682560504</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01628390450335533</v>
+        <v>0.01628390450335518</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01156317938794297</v>
+        <v>0.01156317938794288</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04496506333547014</v>
+        <v>0.04496506333547071</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09814148354347681</v>
+        <v>0.09814148354347661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05800312408667193</v>
+        <v>0.0580031240866722</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6404039019205615</v>
+        <v>0.6404039019205608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7656634488128389</v>
+        <v>0.7656634488128381</v>
       </c>
       <c r="G5" t="n">
-        <v>0.131682738944693</v>
+        <v>0.1316827389446932</v>
       </c>
       <c r="H5" t="n">
-        <v>0.479183644485053</v>
+        <v>0.4791836444850557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1419231617850407</v>
+        <v>0.1419231617850406</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3315560950233147</v>
+        <v>0.3315560950233144</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04947557768329432</v>
+        <v>0.04947557768329419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02137523664997185</v>
+        <v>0.02137523664997204</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2326938971281436</v>
+        <v>0.2326938971281427</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1777972287123813</v>
+        <v>0.1777972287123827</v>
       </c>
       <c r="O5" t="n">
-        <v>1.497269763462617</v>
+        <v>1.497269763462618</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7420638567696377</v>
+        <v>0.7420638567696387</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8844356774642368</v>
+        <v>0.8844356774642355</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3532922368657435</v>
+        <v>0.3532922368657433</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02897441687411838</v>
+        <v>0.02897441687411878</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8101702701087099</v>
+        <v>0.8101702701087102</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4029869754383253</v>
+        <v>0.4029869754383288</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5652436917128051</v>
+        <v>0.5652436917128061</v>
       </c>
       <c r="W5" t="n">
-        <v>1.046494534117903</v>
+        <v>1.046494534117901</v>
       </c>
       <c r="X5" t="n">
-        <v>0.063954232776724</v>
+        <v>0.06395423277672474</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9366820965829452</v>
+        <v>0.9366820965829448</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4398183893075694</v>
+        <v>0.4398183893075691</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1732748393626936</v>
+        <v>0.1732748393626934</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09773763619582901</v>
+        <v>0.09773763619582886</v>
       </c>
     </row>
     <row r="6">
@@ -3518,19 +3518,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741394469105411</v>
+        <v>6.741394469105404</v>
       </c>
       <c r="C6" t="n">
-        <v>1.782913245732806</v>
+        <v>1.782913245732805</v>
       </c>
       <c r="D6" t="n">
-        <v>6.741865415038991</v>
+        <v>6.741865415038987</v>
       </c>
       <c r="E6" t="n">
-        <v>6.775035944263706</v>
+        <v>6.775035944263697</v>
       </c>
       <c r="F6" t="n">
-        <v>1.81890321016662</v>
+        <v>1.818903210166621</v>
       </c>
       <c r="G6" t="n">
         <v>1.78527361220555</v>
@@ -3539,61 +3539,61 @@
         <v>1.801880226234929</v>
       </c>
       <c r="I6" t="n">
-        <v>1.784877425508779</v>
+        <v>1.78487742550878</v>
       </c>
       <c r="J6" t="n">
-        <v>6.758369550022956</v>
+        <v>6.758369550022955</v>
       </c>
       <c r="K6" t="n">
-        <v>6.74158527946822</v>
+        <v>6.741585279468218</v>
       </c>
       <c r="L6" t="n">
-        <v>6.739933342177783</v>
+        <v>6.739933342177781</v>
       </c>
       <c r="M6" t="n">
-        <v>1.789681374648397</v>
+        <v>1.789681374648398</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1777972287123813</v>
+        <v>1.78707343396003</v>
       </c>
       <c r="O6" t="n">
-        <v>6.834713478822298</v>
+        <v>6.834713478822296</v>
       </c>
       <c r="P6" t="n">
-        <v>6.784292849214089</v>
+        <v>6.784292849214087</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.788486086842441</v>
+        <v>6.788486086842435</v>
       </c>
       <c r="R6" t="n">
         <v>1.795785945505911</v>
       </c>
       <c r="S6" t="n">
-        <v>6.740414981151522</v>
+        <v>6.740414981151516</v>
       </c>
       <c r="T6" t="n">
-        <v>1.820679944847785</v>
+        <v>1.820679944847787</v>
       </c>
       <c r="U6" t="n">
         <v>1.800964938458662</v>
       </c>
       <c r="V6" t="n">
-        <v>6.775383999991909</v>
+        <v>6.77538399999191</v>
       </c>
       <c r="W6" t="n">
-        <v>6.798004922223556</v>
+        <v>6.798004922223555</v>
       </c>
       <c r="X6" t="n">
-        <v>1.780825742515401</v>
+        <v>1.780825742515402</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.907999009819319</v>
+        <v>1.90799900981932</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.766643444317128</v>
+        <v>6.766643444317122</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.748456821994873</v>
+        <v>6.748456821994867</v>
       </c>
       <c r="AB6" t="n">
         <v>1.782165243451031</v>
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0117643874088718</v>
+        <v>0.01176438740887172</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01468629251798114</v>
+        <v>0.01468629251798109</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01223533334246056</v>
+        <v>0.01223533334246045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04540586256717092</v>
+        <v>0.04540586256717086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.050676256951796</v>
+        <v>0.05067625695179589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01704665899072779</v>
+        <v>0.01704665899072767</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03365327302010566</v>
+        <v>0.03365327302010562</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0166504722939576</v>
+        <v>0.0166504722939575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02873946832642215</v>
+        <v>0.02873946832642203</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01195519777169071</v>
+        <v>0.01195519777169064</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01030326048124578</v>
+        <v>0.0103032604812457</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02145442143357423</v>
+        <v>0.02145442143357415</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1777972287123813</v>
+        <v>0.01889914334556115</v>
       </c>
       <c r="O7" t="n">
         <v>0.1046595815298385</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0542418268240563</v>
+        <v>0.05424182682405623</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05885600514590946</v>
+        <v>0.0588560051459093</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02755899229108812</v>
+        <v>0.02755899229108803</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01078489945498919</v>
+        <v>0.0107848994549891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05245299163296294</v>
+        <v>0.05245299163296292</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03274067699295388</v>
+        <v>0.03274067699295403</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04575391829537941</v>
+        <v>0.04575391829537939</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06795142609017334</v>
+        <v>0.06795142609017327</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01259878930057714</v>
+        <v>0.01259878930057698</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06222223712149798</v>
+        <v>0.06222223712149787</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03701336262059121</v>
+        <v>0.03701336262059108</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01882674029834133</v>
+        <v>0.01882674029834122</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01410601518292899</v>
+        <v>0.01410601518292889</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01378778502828137</v>
+        <v>0.01378778502828138</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02019450751935053</v>
+        <v>0.0201945075193505</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01774354834382984</v>
+        <v>0.01774354834382976</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04905851510947781</v>
+        <v>0.04905851510947786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05324254839072722</v>
+        <v>0.05324254839072709</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02327747357727973</v>
+        <v>0.02327747357727961</v>
       </c>
       <c r="H8" t="n">
         <v>0.03916148802147499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02215868729532691</v>
+        <v>0.02215868729532689</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03424768332779145</v>
+        <v>0.03424768332779142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01746341277306003</v>
+        <v>0.01746341277306004</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01581147548261509</v>
+        <v>0.01581147548261507</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02696263643494896</v>
+        <v>0.02696263643494891</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1777972287123813</v>
+        <v>0.02170604187718768</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1082089400259783</v>
+        <v>0.1082089400259782</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0576092185699735</v>
+        <v>0.05760921856997336</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06019455661422085</v>
+        <v>0.06019455661422064</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03306720729245743</v>
+        <v>0.03306720729245739</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0162931144563585</v>
+        <v>0.01629311445635855</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05796120663433242</v>
+        <v>0.05796120663433231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03654748235415439</v>
+        <v>0.03654748235415418</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05031207908111909</v>
+        <v>0.05031207908111916</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07346032595230245</v>
+        <v>0.07346032595230231</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0142567312028773</v>
+        <v>0.01425673120287719</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07119904745720865</v>
+        <v>0.07119904745720855</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03897202796851167</v>
+        <v>0.0389720279685117</v>
       </c>
       <c r="AA8" t="n">
         <v>0.02433495529971064</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02325441333014062</v>
+        <v>0.02325441333014049</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02240619893313698</v>
+        <v>0.02240619893313696</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02922834313363022</v>
+        <v>0.02922834313363016</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02677738395810961</v>
+        <v>0.02677738395810949</v>
       </c>
       <c r="E9" t="n">
         <v>0.05904775866967479</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05622718390764279</v>
+        <v>0.05622718390764277</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03158871579506002</v>
+        <v>0.03158871579505996</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04819532363575473</v>
+        <v>0.04819532363575468</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03119252290960661</v>
+        <v>0.03119252290960656</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0432815189420711</v>
+        <v>0.04328151894207107</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02649724838733975</v>
+        <v>0.02649724838733969</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02484531109689481</v>
+        <v>0.02484531109689476</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03599647204922325</v>
+        <v>0.03599647204922318</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1777972287123813</v>
+        <v>0.0334411939612102</v>
       </c>
       <c r="O9" t="n">
         <v>0.1204942892594776</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07035763899641548</v>
+        <v>0.07035763899641541</v>
       </c>
       <c r="Q9" t="n">
         <v>0.07339806195024159</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04210104290673714</v>
+        <v>0.04210104290673707</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0253269500706382</v>
+        <v>0.02532695007063826</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06699504224861209</v>
+        <v>0.06699504224861208</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0472800358594881</v>
+        <v>0.0472800358594883</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06479676844763009</v>
+        <v>0.06479676844763012</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08249347670582241</v>
+        <v>0.0824934767058223</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02714083991622616</v>
+        <v>0.02714083991622615</v>
       </c>
       <c r="Y9" t="n">
         <v>0.076764287737147</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04920391834438576</v>
+        <v>0.04920391834438571</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03336879091399034</v>
+        <v>0.0333687909139903</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02864806579857803</v>
+        <v>0.02864806579857796</v>
       </c>
     </row>
   </sheetData>
@@ -4026,76 +4026,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04934018498054465</v>
+        <v>0.04934018498054471</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04548133966150095</v>
+        <v>0.04548133966150088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0499073702154239</v>
+        <v>0.04990737021542387</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0500574133131026</v>
+        <v>0.05005741331310263</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05430311111966959</v>
+        <v>0.05430311111966971</v>
       </c>
       <c r="G2" t="n">
         <v>0.04979122983576249</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05110246139033973</v>
+        <v>0.05110246139033976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05173418337068874</v>
+        <v>0.05173418337068873</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0506532612765489</v>
+        <v>0.05065326127654886</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05115343002782555</v>
+        <v>0.0511534300278256</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091753770488406</v>
+        <v>0.05091753770488408</v>
       </c>
       <c r="M2" t="n">
         <v>0.05137169661301517</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04969576800240504</v>
+        <v>0.04969576800240501</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05963831087621439</v>
+        <v>0.05963831087621432</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05199599145735102</v>
+        <v>0.05199599145735096</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05424912180568762</v>
+        <v>0.05424912180568763</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05123987606366976</v>
+        <v>0.05123987606366971</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05081304729419097</v>
+        <v>0.05081304729419099</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05329119132761091</v>
+        <v>0.0532911913276109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2133775794532431</v>
+        <v>0.213377579453243</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04998314245609565</v>
+        <v>0.04998314245609571</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2348917361953771</v>
+        <v>0.234891736195377</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04982363514680754</v>
+        <v>0.04982363514680756</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05023624151764027</v>
+        <v>0.0502362415176402</v>
       </c>
       <c r="Z2" t="n">
         <v>0.1959733264791282</v>
@@ -4104,7 +4104,7 @@
         <v>0.04993036868846022</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04934835397608781</v>
+        <v>0.04934835397608779</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02307992597743077</v>
+        <v>0.02307992597743075</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01686228363160455</v>
+        <v>0.01686228363160452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02714000339791227</v>
+        <v>0.02714000339791229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02818431120270358</v>
+        <v>0.02818431120270362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05857646374301982</v>
+        <v>0.05857646374301979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02628057156450134</v>
+        <v>0.02628057156450147</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03575451418870666</v>
+        <v>0.0357545141887066</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0402231435592713</v>
+        <v>0.04022314355927139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03244607161211894</v>
+        <v>0.03244607161211888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.035977063940297</v>
+        <v>0.03597706394029707</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03431375913292541</v>
+        <v>0.03431375913292542</v>
       </c>
       <c r="M3" t="n">
-        <v>0.037590150078574</v>
+        <v>0.03759015007857398</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02563561656470577</v>
+        <v>0.02563561656470582</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07150605015330597</v>
+        <v>0.07150605015330598</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04192653142013684</v>
+        <v>0.04192653142013688</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05808342360707681</v>
+        <v>0.0580834236070768</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03671963523318579</v>
+        <v>0.03671963523318578</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03355162460687738</v>
+        <v>0.03355162460687739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05138461544498536</v>
+        <v>0.0513846154449854</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2976237026947537</v>
+        <v>0.2976237026947539</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02763571268419879</v>
+        <v>0.02763571268419885</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3490769245878047</v>
+        <v>0.3490769245878046</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02654114532311953</v>
+        <v>0.02654114532311952</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0294934622280373</v>
+        <v>0.02949346222803728</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2675301884410979</v>
+        <v>0.2675301884410978</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02730667886697657</v>
+        <v>0.02730667886697661</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02327595247053295</v>
+        <v>0.02327595247053304</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007936021996639604</v>
+        <v>0.007936021996639737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008211458055526519</v>
+        <v>0.008211458055526609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01434264014269914</v>
+        <v>0.01434264014269922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01603744595421525</v>
+        <v>0.01603744595421537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06399455579687581</v>
+        <v>0.06399455579687616</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01303078112720918</v>
+        <v>0.01303078112720934</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02784174473247587</v>
+        <v>0.02784174473247589</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03497733510698618</v>
+        <v>0.03497733510698632</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02286242745525159</v>
+        <v>0.02286242745525165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02841745893960956</v>
+        <v>0.02841745893960966</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02575294663615554</v>
+        <v>0.02575294663615565</v>
       </c>
       <c r="M4" t="n">
         <v>0.03084967715058726</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1418759121484599</v>
+        <v>0.01195249580482323</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07316136975328254</v>
+        <v>0.07316136975328258</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03793457788350567</v>
+        <v>0.03793457788350579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06338472165913747</v>
+        <v>0.06338472165913746</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02939390668161079</v>
+        <v>0.02939390668161077</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02457267937941357</v>
+        <v>0.02457267937941364</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05256445623946907</v>
+        <v>0.05256445623946919</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01554747712534938</v>
+        <v>0.01554747712534956</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01582904413135669</v>
+        <v>0.01582904413135667</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04847266483867737</v>
+        <v>0.04847266483867734</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01339681402264322</v>
+        <v>0.01339681402264332</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01787312302276768</v>
+        <v>0.01787312302276776</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01295959657383654</v>
+        <v>0.01295959657383663</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01460241847546428</v>
+        <v>0.01460241847546437</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.008239439354703653</v>
+        <v>0.008239439354703811</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06157372873287911</v>
+        <v>0.06157372873287874</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07086072603703311</v>
+        <v>0.0708607260370334</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1811289775066873</v>
+        <v>0.1811289775066869</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1973417857229481</v>
+        <v>0.1973417857229483</v>
       </c>
       <c r="F5" t="n">
-        <v>1.092387659433047</v>
+        <v>1.092387659433046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1421040704365016</v>
+        <v>0.1421040704365013</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4639763221475691</v>
+        <v>0.4639763221475687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5694510430293886</v>
+        <v>0.5694510430293889</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3212231131587298</v>
+        <v>0.3212231131587296</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4009771850922144</v>
+        <v>0.4009771850922155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3643555414158216</v>
+        <v>0.3643555414158203</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4820050187820996</v>
+        <v>0.4820050187821001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1418759121484599</v>
+        <v>0.1418759121484589</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0837160170822</v>
+        <v>1.083716017082201</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5361702121842286</v>
+        <v>0.5361702121842261</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.025780796979891</v>
+        <v>1.02578079697989</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4833371366290499</v>
+        <v>0.4833371366290494</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3349913963330055</v>
+        <v>0.3349913963330047</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9059160681444335</v>
+        <v>0.9059160681444346</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1909695939662126</v>
+        <v>0.1909695939662135</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1735351176632622</v>
+        <v>0.1735351176632618</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7893963201739121</v>
+        <v>0.7893963201739116</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1637595852306504</v>
+        <v>0.1637595852306501</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2500890794448272</v>
+        <v>0.2500890794448277</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.132491358664373</v>
+        <v>0.1324913586643731</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1870368815846619</v>
+        <v>0.1870368815846622</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07886180222333097</v>
+        <v>0.07886180222333168</v>
       </c>
     </row>
     <row r="6">
@@ -4381,52 +4381,52 @@
         <v>1.777426394473062</v>
       </c>
       <c r="C6" t="n">
-        <v>1.777701830531948</v>
+        <v>1.777701830531949</v>
       </c>
       <c r="D6" t="n">
-        <v>6.744731516537835</v>
+        <v>6.744731516537828</v>
       </c>
       <c r="E6" t="n">
-        <v>6.746426322349348</v>
+        <v>6.746426322349346</v>
       </c>
       <c r="F6" t="n">
-        <v>1.833484928273299</v>
+        <v>1.833484928273297</v>
       </c>
       <c r="G6" t="n">
         <v>1.782521153603631</v>
       </c>
       <c r="H6" t="n">
-        <v>6.758230621127602</v>
+        <v>6.758230621127605</v>
       </c>
       <c r="I6" t="n">
-        <v>1.804467707583409</v>
+        <v>1.804467707583408</v>
       </c>
       <c r="J6" t="n">
-        <v>6.753251303850371</v>
+        <v>6.753251303850386</v>
       </c>
       <c r="K6" t="n">
-        <v>6.758806335334739</v>
+        <v>6.75880633533474</v>
       </c>
       <c r="L6" t="n">
-        <v>1.79524331911258</v>
+        <v>1.795243319112579</v>
       </c>
       <c r="M6" t="n">
         <v>1.800340049627009</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1418759121484599</v>
+        <v>1.781444455220243</v>
       </c>
       <c r="O6" t="n">
-        <v>1.842661587363541</v>
+        <v>1.842661587363542</v>
       </c>
       <c r="P6" t="n">
-        <v>6.768750063339376</v>
+        <v>6.768750063339377</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.793773598054267</v>
+        <v>6.793773598054265</v>
       </c>
       <c r="R6" t="n">
-        <v>6.759782783076735</v>
+        <v>6.759782783076734</v>
       </c>
       <c r="S6" t="n">
         <v>1.794063051855834</v>
@@ -4435,10 +4435,10 @@
         <v>6.782953332634602</v>
       </c>
       <c r="U6" t="n">
-        <v>6.746120623287217</v>
+        <v>6.74612062328722</v>
       </c>
       <c r="V6" t="n">
-        <v>1.785319416607779</v>
+        <v>1.785319416607778</v>
       </c>
       <c r="W6" t="n">
         <v>1.908157024383182</v>
@@ -4447,7 +4447,7 @@
         <v>1.782887186499066</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.865037122994512</v>
+        <v>1.865037122994513</v>
       </c>
       <c r="Z6" t="n">
         <v>1.78244996905026</v>
@@ -4456,7 +4456,7 @@
         <v>6.7449912948706</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.777691875251638</v>
+        <v>1.77769187525164</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009903951358470104</v>
+        <v>0.009903951358470157</v>
       </c>
       <c r="C7" t="n">
-        <v>0.010179387417357</v>
+        <v>0.0101793874173571</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01631056950452961</v>
+        <v>0.01631056950452968</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01800537531604576</v>
+        <v>0.01800537531604585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0659624851587064</v>
+        <v>0.06596248515870658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01499871048903968</v>
+        <v>0.01499871048903981</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02980967409430635</v>
+        <v>0.02980967409430633</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03694526446881664</v>
+        <v>0.0369452644688168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0248303568170821</v>
+        <v>0.02483035681708214</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03038538830144008</v>
+        <v>0.03038538830144017</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02772087599798602</v>
+        <v>0.02772087599798612</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03281760651241768</v>
+        <v>0.03281760651241775</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1418759121484599</v>
+        <v>0.01392042516665377</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07512924438517483</v>
+        <v>0.07512924438517485</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03990245251539786</v>
+        <v>0.03990245251539782</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06535265102096799</v>
+        <v>0.06535265102096802</v>
       </c>
       <c r="R7" t="n">
         <v>0.03136183604344125</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02654060874124405</v>
+        <v>0.02654060874124412</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05453238560129959</v>
+        <v>0.05453238560129967</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01765920620197692</v>
+        <v>0.01765920620197704</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0177969734931872</v>
+        <v>0.01779697349318716</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0504405942005079</v>
+        <v>0.05044059420050793</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01536474338447367</v>
+        <v>0.01536474338447371</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0200253221513364</v>
+        <v>0.02002532215133649</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01492752593566704</v>
+        <v>0.0149275259356671</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0165703478372948</v>
+        <v>0.01657034783729486</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01020736871653422</v>
+        <v>0.01020736871653447</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01177224130797982</v>
+        <v>0.01177224130797988</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01499712486342311</v>
+        <v>0.01499712486342318</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02112830695059578</v>
+        <v>0.02112830695059585</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02125261897444058</v>
+        <v>0.02125261897444056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06829026455668613</v>
+        <v>0.06829026455668631</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02042803508700108</v>
+        <v>0.02042803508700116</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03462741154037255</v>
+        <v>0.0346274115403724</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04176300191488281</v>
+        <v>0.04176300191488289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02964809426314827</v>
+        <v>0.02964809426314834</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03520312574750614</v>
+        <v>0.03520312574750624</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03253861344405216</v>
+        <v>0.03253861344405223</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03763534395849572</v>
+        <v>0.03763534395849578</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1418759121484599</v>
+        <v>0.01645184736979952</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07828902059622025</v>
+        <v>0.0782890205962203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04290821739183465</v>
+        <v>0.04290821739183463</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06664130722087076</v>
+        <v>0.066641307220871</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03617957348950738</v>
+        <v>0.03617957348950759</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03135834618731016</v>
+        <v>0.03135834618731027</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05935012304736575</v>
+        <v>0.05935012304736586</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02104650685738221</v>
+        <v>0.02104650685738213</v>
       </c>
       <c r="V8" t="n">
         <v>0.02177403644657564</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05525891129259757</v>
+        <v>0.05525891129259765</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01692372230505098</v>
+        <v>0.01692372230505114</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02772204719098523</v>
+        <v>0.02772204719098533</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01674102838409855</v>
+        <v>0.01674102838409864</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.021388085283361</v>
+        <v>0.02138808528336102</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01810605069697805</v>
+        <v>0.01810605069697818</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01693293570529735</v>
+        <v>0.01693293570529746</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01991934511306216</v>
+        <v>0.01991934511306228</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02605052720023477</v>
+        <v>0.02605052720023499</v>
       </c>
       <c r="E9" t="n">
         <v>0.02711965172875652</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06945290886765897</v>
+        <v>0.06945290886765915</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02473866858524623</v>
+        <v>0.02473866858524643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03954963179001159</v>
+        <v>0.03954963179001157</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04668522216452182</v>
+        <v>0.04668522216452192</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0345703145127873</v>
+        <v>0.03457031451278736</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04012534599714516</v>
+        <v>0.04012534599714535</v>
       </c>
       <c r="L9" t="n">
         <v>0.03746083369369133</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04255756420812297</v>
+        <v>0.04255756420812293</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1418759121484599</v>
+        <v>0.02366038286235898</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08576767036214732</v>
+        <v>0.08576767036214751</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05073626793850151</v>
+        <v>0.05073626793850167</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07509260911717454</v>
+        <v>0.07509260911717448</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04110179373914637</v>
+        <v>0.04110179373914638</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03628056643694916</v>
+        <v>0.03628056643694919</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06427234329700476</v>
+        <v>0.06427234329700496</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02743963394962325</v>
+        <v>0.0274396339496234</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03066532990217448</v>
+        <v>0.03066532990217446</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06018055189621304</v>
+        <v>0.06018055189621315</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02510470108017899</v>
+        <v>0.0251047010801789</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02976527984704146</v>
+        <v>0.02976527984704168</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02303300793018981</v>
+        <v>0.02303300793018987</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02631030553299976</v>
+        <v>0.02631030553300005</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01994732641223931</v>
+        <v>0.01994732641223951</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.0683164713428185</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7702123175005279</v>
+        <v>0.05050319354090302</v>
       </c>
       <c r="O4" t="n">
         <v>0.1582915528457508</v>
@@ -5274,7 +5274,7 @@
         <v>7.296443245043456</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7702123175005279</v>
+        <v>1.952086952892447</v>
       </c>
       <c r="O6" t="n">
         <v>7.386962242938258</v>
@@ -5362,7 +5362,7 @@
         <v>0.07261690556296564</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7702123175005279</v>
+        <v>0.05480362776105006</v>
       </c>
       <c r="O7" t="n">
         <v>0.1625918508298181</v>
@@ -5450,7 +5450,7 @@
         <v>0.08198602209275252</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7702123175005279</v>
+        <v>0.05963171624414409</v>
       </c>
       <c r="O8" t="n">
         <v>0.1686679894817832</v>
@@ -5538,7 +5538,7 @@
         <v>0.0997075784214799</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7702123175005279</v>
+        <v>0.08189430061956431</v>
       </c>
       <c r="O9" t="n">
         <v>0.1920374925131789</v>
@@ -5758,7 +5758,7 @@
         <v>0.05408004584823455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05547992541265061</v>
+        <v>0.05547992541265059</v>
       </c>
       <c r="G2" t="n">
         <v>0.05436413987932377</v>
@@ -5770,13 +5770,13 @@
         <v>0.05238355452013731</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05483351395095376</v>
+        <v>0.05483351395095377</v>
       </c>
       <c r="K2" t="n">
         <v>0.05223501236869</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05209079911011587</v>
+        <v>0.05209079911011588</v>
       </c>
       <c r="M2" t="n">
         <v>0.05628853548812307</v>
@@ -5797,7 +5797,7 @@
         <v>0.05217518652540643</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05225983761424491</v>
+        <v>0.05225983761424492</v>
       </c>
       <c r="T2" t="n">
         <v>0.05607853771391703</v>
@@ -5824,7 +5824,7 @@
         <v>0.05265529199044711</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05603854726890283</v>
+        <v>0.05603854726890285</v>
       </c>
     </row>
     <row r="3">
@@ -5849,7 +5849,7 @@
         <v>0.04851470740028552</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04038551932208618</v>
+        <v>0.04038551932208617</v>
       </c>
       <c r="H3" t="n">
         <v>0.02813085262844803</v>
@@ -5885,7 +5885,7 @@
         <v>0.02492464903112021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02550737817364382</v>
+        <v>0.02550737817364383</v>
       </c>
       <c r="T3" t="n">
         <v>0.05273265816007162</v>
@@ -5897,7 +5897,7 @@
         <v>0.0451243534929166</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3652290547351938</v>
+        <v>0.3652290547351937</v>
       </c>
       <c r="X3" t="n">
         <v>0.05142358294517602</v>
@@ -5955,10 +5955,10 @@
         <v>0.00917377139021102</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0564001942392007</v>
+        <v>0.05640019423920069</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5795547819009172</v>
+        <v>0.04083710646309543</v>
       </c>
       <c r="O4" t="n">
         <v>0.158076801054362</v>
@@ -5991,7 +5991,7 @@
         <v>0.05215738037077251</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07280694273377741</v>
+        <v>0.0728069427337774</v>
       </c>
       <c r="Z4" t="n">
         <v>0.02675866719744839</v>
@@ -6013,16 +6013,16 @@
         <v>0.02106190890276051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09422021239720174</v>
+        <v>0.09422021239720173</v>
       </c>
       <c r="D5" t="n">
         <v>0.04115865552352881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4282438773126979</v>
+        <v>0.4282438773126978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7185794993098751</v>
+        <v>0.7185794993098752</v>
       </c>
       <c r="G5" t="n">
         <v>0.4097624728573121</v>
@@ -6031,19 +6031,19 @@
         <v>0.1536593375015488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09794098382262362</v>
+        <v>0.09794098382262365</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5247909864320437</v>
+        <v>0.5247909864320436</v>
       </c>
       <c r="K5" t="n">
         <v>0.06333247604049401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03514456629249632</v>
+        <v>0.03514456629249633</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7799466135381935</v>
+        <v>0.7799466135381934</v>
       </c>
       <c r="N5" t="n">
         <v>0.5795547819009172</v>
@@ -6061,10 +6061,10 @@
         <v>0.0563040832025338</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06211007807045625</v>
+        <v>0.06211007807045624</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8099910697189067</v>
+        <v>0.8099910697189066</v>
       </c>
       <c r="U5" t="n">
         <v>0.6231849737861639</v>
@@ -6076,13 +6076,13 @@
         <v>1.07505884354629</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7696069955402067</v>
+        <v>0.7696069955402068</v>
       </c>
       <c r="Y5" t="n">
         <v>1.165672479936287</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3058740058109602</v>
+        <v>0.3058740058109601</v>
       </c>
       <c r="AA5" t="n">
         <v>0.1496168683842615</v>
@@ -6110,13 +6110,13 @@
         <v>1.802223964079968</v>
       </c>
       <c r="F6" t="n">
-        <v>6.780349293592887</v>
+        <v>6.780349293592886</v>
       </c>
       <c r="G6" t="n">
-        <v>6.767745982707259</v>
+        <v>6.76774598270726</v>
       </c>
       <c r="H6" t="n">
-        <v>6.748070488418602</v>
+        <v>6.748070488418601</v>
       </c>
       <c r="I6" t="n">
         <v>6.745374359960961</v>
@@ -6131,10 +6131,10 @@
         <v>1.779754507074205</v>
       </c>
       <c r="M6" t="n">
-        <v>6.78929397577962</v>
+        <v>6.789293975779618</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5795547819009172</v>
+        <v>1.811439731898776</v>
       </c>
       <c r="O6" t="n">
         <v>6.891481187800236</v>
@@ -6149,7 +6149,7 @@
         <v>1.780707701750041</v>
       </c>
       <c r="S6" t="n">
-        <v>6.74397692059632</v>
+        <v>6.743976920596321</v>
       </c>
       <c r="T6" t="n">
         <v>1.824797849054529</v>
@@ -6164,7 +6164,7 @@
         <v>1.932379147242124</v>
       </c>
       <c r="X6" t="n">
-        <v>6.785051161911191</v>
+        <v>6.785051161911192</v>
       </c>
       <c r="Y6" t="n">
         <v>1.920966374289978</v>
@@ -6222,7 +6222,7 @@
         <v>0.05944845554811647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5795547819009172</v>
+        <v>0.0438853677720111</v>
       </c>
       <c r="O7" t="n">
         <v>0.1611249582584399</v>
@@ -6249,13 +6249,13 @@
         <v>0.04607227989336479</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07454520821006567</v>
+        <v>0.07454520821006569</v>
       </c>
       <c r="X7" t="n">
         <v>0.05520564167968824</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07583379609173901</v>
+        <v>0.07583379609173903</v>
       </c>
       <c r="Z7" t="n">
         <v>0.02980692850636411</v>
@@ -6286,7 +6286,7 @@
         <v>0.03925299787225577</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05373928355822558</v>
+        <v>0.05373928355822559</v>
       </c>
       <c r="G8" t="n">
         <v>0.04560884108072199</v>
@@ -6310,7 +6310,7 @@
         <v>0.06627483867188323</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5795547819009172</v>
+        <v>0.04741455979906058</v>
       </c>
       <c r="O8" t="n">
         <v>0.1655603511302615</v>
@@ -6340,7 +6340,7 @@
         <v>0.08137242726793811</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05733243246597646</v>
+        <v>0.05733243246597647</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0868689072253564</v>
@@ -6395,10 +6395,10 @@
         <v>0.02989881179214139</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07712523464113123</v>
+        <v>0.07712523464113126</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5795547819009172</v>
+        <v>0.06156214686502587</v>
       </c>
       <c r="O9" t="n">
         <v>0.1803668401794024</v>
@@ -6818,7 +6818,7 @@
         <v>0.04704258746410074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3226250321204206</v>
+        <v>0.02312262473282826</v>
       </c>
       <c r="O4" t="n">
         <v>0.1175190851157763</v>
@@ -6906,7 +6906,7 @@
         <v>0.733346004883761</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3226250321204205</v>
+        <v>0.3226250321204206</v>
       </c>
       <c r="O5" t="n">
         <v>1.756630499396842</v>
@@ -6994,7 +6994,7 @@
         <v>6.777699827166112</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3226250321204205</v>
+        <v>1.792576127169616</v>
       </c>
       <c r="O6" t="n">
         <v>1.886982536856932</v>
@@ -7082,7 +7082,7 @@
         <v>0.04922063968502334</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3226250321204205</v>
+        <v>0.02530067695375085</v>
       </c>
       <c r="O7" t="n">
         <v>0.1196970647063857</v>
@@ -7170,7 +7170,7 @@
         <v>0.05431289275955593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3226250321204205</v>
+        <v>0.02796397450918524</v>
       </c>
       <c r="O8" t="n">
         <v>0.1230279329571122</v>
@@ -7258,7 +7258,7 @@
         <v>0.05984087868526058</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3226250321204205</v>
+        <v>0.03592091595398812</v>
       </c>
       <c r="O9" t="n">
         <v>0.131293276826338</v>
@@ -7678,7 +7678,7 @@
         <v>0.02844641180022403</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3316841556672353</v>
+        <v>0.02557767944262649</v>
       </c>
       <c r="O4" t="n">
         <v>0.09052149500475647</v>
@@ -7766,7 +7766,7 @@
         <v>0.3725376904529245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3316841556672352</v>
+        <v>0.3316841556672353</v>
       </c>
       <c r="O5" t="n">
         <v>1.377902435619591</v>
@@ -7854,7 +7854,7 @@
         <v>1.929996372319654</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3316841556672352</v>
+        <v>1.926930373488332</v>
       </c>
       <c r="O6" t="n">
         <v>7.317761562389645</v>
@@ -7942,7 +7942,7 @@
         <v>0.03197813059958237</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3316841556672352</v>
+        <v>0.02910939824198485</v>
       </c>
       <c r="O7" t="n">
         <v>0.0940530646899045</v>
@@ -8030,7 +8030,7 @@
         <v>0.03948376711797296</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3316841556672352</v>
+        <v>0.03293431512917285</v>
       </c>
       <c r="O8" t="n">
         <v>0.09888962440142479</v>
@@ -8118,7 +8118,7 @@
         <v>0.05391342379915062</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3316841556672352</v>
+        <v>0.05104469144155309</v>
       </c>
       <c r="O9" t="n">
         <v>0.117901920757358</v>
@@ -8538,7 +8538,7 @@
         <v>0.09551556833470777</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.02834641507518754</v>
       </c>
       <c r="O4" t="n">
         <v>0.1402967739114681</v>
@@ -8714,7 +8714,7 @@
         <v>1.866328867426231</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3937110344914039</v>
+        <v>1.799084939102211</v>
       </c>
       <c r="O6" t="n">
         <v>6.873150425815467</v>
@@ -8802,7 +8802,7 @@
         <v>0.09844898213742999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.03127982887790973</v>
       </c>
       <c r="O7" t="n">
         <v>0.1432300847193841</v>
@@ -8890,7 +8890,7 @@
         <v>0.1051030321970177</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.03475150237254433</v>
       </c>
       <c r="O8" t="n">
         <v>0.1475764059182934</v>
@@ -8978,7 +8978,7 @@
         <v>0.1130067574181301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.04583760415860978</v>
       </c>
       <c r="O9" t="n">
         <v>0.1591140271871235</v>

--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -586,67 +586,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05247843093836461</v>
+        <v>0.05247843093836465</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0488976658139286</v>
+        <v>0.04889766581392861</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05290832245525293</v>
+        <v>0.05290832245525295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05862799455872881</v>
+        <v>0.0586279945587288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05332448259533213</v>
+        <v>0.05332448259533216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05337695148040524</v>
+        <v>0.05337695148040527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05458490810743861</v>
+        <v>0.05458490810743865</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05307834633656791</v>
+        <v>0.0530783463365679</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05478054349452838</v>
+        <v>0.0547805434945284</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0541162992201687</v>
+        <v>0.05411629922016868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05258201969309177</v>
+        <v>0.05258201969309179</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05420646017273223</v>
+        <v>0.05420646017273222</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05364536673168174</v>
+        <v>0.05364536673168172</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05778875353578213</v>
+        <v>0.05778875353578215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05711501058552006</v>
+        <v>0.05711501058552008</v>
       </c>
       <c r="Q2" t="n">
         <v>0.05357620081717465</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05370654195283431</v>
+        <v>0.05370654195283434</v>
       </c>
       <c r="S2" t="n">
         <v>0.05250278200967524</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05550975131770131</v>
+        <v>0.05550975131770135</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2200282382281904</v>
+        <v>0.2200282382281905</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05608844293452288</v>
+        <v>0.05608844293452291</v>
       </c>
       <c r="W2" t="n">
         <v>0.242990759978907</v>
@@ -655,16 +655,16 @@
         <v>0.05249044896808425</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05866876346113612</v>
+        <v>0.0586687634611361</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2053151623172736</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.052952194292058</v>
+        <v>0.05295219429205802</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0528280742435159</v>
+        <v>0.05282807424351589</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02452438566753731</v>
+        <v>0.02457148022614095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02007835705706199</v>
+        <v>0.02019204316824067</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02760824177257914</v>
+        <v>0.02776508889842229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0684105262034549</v>
+        <v>0.07000518740654489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03059734582848656</v>
+        <v>0.03086111232818727</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03092186511051215</v>
+        <v>0.03119375980116681</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03965029200577638</v>
+        <v>0.04023677923783938</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02882907959195157</v>
+        <v>0.02902945945919036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04093223173918265</v>
+        <v>0.04155766893061002</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03624961902645649</v>
+        <v>0.03671257537229076</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02526645307840131</v>
+        <v>0.02533984791996072</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03709387203301345</v>
+        <v>0.03758974672020738</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03286835170384867</v>
+        <v>0.03321095403872274</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04537271902658577</v>
+        <v>0.04597362446504501</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05751378473343281</v>
+        <v>0.05871778619650897</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0323782468737047</v>
+        <v>0.03270388600889745</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03333692677844047</v>
+        <v>0.03369785697611308</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02469900864892222</v>
+        <v>0.02475232658794184</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04623633765644799</v>
+        <v>0.04705430127352001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.315232230553875</v>
+        <v>0.3159281508758647</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05019730875816087</v>
+        <v>0.05114856512943098</v>
       </c>
       <c r="W3" t="n">
-        <v>0.375740059856874</v>
+        <v>0.3774744553221466</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02461615122682073</v>
+        <v>0.02466684459281</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06872036372368777</v>
+        <v>0.0703304697419648</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2987547828442114</v>
+        <v>0.2998063781677814</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02791167296826054</v>
+        <v>0.02807859604830755</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02731552619950392</v>
+        <v>0.02746321199904527</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01022723357006142</v>
+        <v>0.01022723357006145</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01316857672051148</v>
+        <v>0.01316857672051138</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01508305601318307</v>
+        <v>0.01508305601318301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07968938360110488</v>
+        <v>0.07968938360110479</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01978377623850036</v>
+        <v>0.01978377623850029</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02037643643228056</v>
+        <v>0.02037643643228051</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03402086222212506</v>
+        <v>0.03402086222212499</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01700355396748525</v>
+        <v>0.01700355396748513</v>
       </c>
       <c r="J4" t="n">
         <v>0.03633907565058467</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02872770926967225</v>
+        <v>0.02872770926967227</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0113973162078853</v>
+        <v>0.01139731620788573</v>
       </c>
       <c r="M4" t="n">
-        <v>0.030081279507307</v>
+        <v>0.03008127950730691</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02340831017256485</v>
+        <v>0.02340831017256477</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03527582284415887</v>
+        <v>0.03527582284415875</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06259953361669816</v>
+        <v>0.062599533616698</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02262704935031431</v>
+        <v>0.02262704935031408</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02409931243747504</v>
+        <v>0.02409931243747496</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01050229012256093</v>
+        <v>0.01050229012256089</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04446739173093834</v>
+        <v>0.04446739173093825</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03975136056013</v>
+        <v>0.03975136056012968</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05172824078367555</v>
+        <v>0.05172824078367557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08583619672766134</v>
+        <v>0.08583619672766103</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01036298274431121</v>
+        <v>0.01036298274431125</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0805258450909023</v>
+        <v>0.08052584509090208</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05555539502715678</v>
+        <v>0.05555539502715665</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01557860859193813</v>
+        <v>0.01557860859193812</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01467414946144487</v>
+        <v>0.01467414946144477</v>
       </c>
     </row>
     <row r="5">
@@ -850,82 +850,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04059539232546062</v>
+        <v>0.04059539232545752</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1056533349325082</v>
+        <v>0.1056533349325081</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1477118591037779</v>
+        <v>0.1477118591037775</v>
       </c>
       <c r="E5" t="n">
-        <v>1.437273080191894</v>
+        <v>1.437273080191893</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2536362233869187</v>
+        <v>0.2536362233869188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.235881118341114</v>
+        <v>0.2358811183411142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5743530433448122</v>
+        <v>0.5743530433448121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1907662620145819</v>
+        <v>0.1907662620145822</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5510159903412808</v>
+        <v>0.5510159903412812</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4343650127587304</v>
+        <v>0.43436501275873</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06579238806038107</v>
+        <v>0.06579238806037047</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4727196404175456</v>
+        <v>0.4727196404175449</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3152386798576731</v>
+        <v>0.315238679857673</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4952225281822397</v>
+        <v>0.4952225281822368</v>
       </c>
       <c r="P5" t="n">
-        <v>1.034577154458527</v>
+        <v>1.034577154458529</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3016072391868139</v>
+        <v>0.3016072391868137</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3481520535303924</v>
+        <v>0.3481520535303921</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04662666314633558</v>
+        <v>0.04662666314633798</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7760423406308405</v>
+        <v>0.7760423406308399</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6149056186984423</v>
+        <v>0.6149056186984424</v>
       </c>
       <c r="V5" t="n">
         <v>0.807847449741562</v>
       </c>
       <c r="W5" t="n">
-        <v>1.572612511365519</v>
+        <v>1.572612511365518</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04689059980322734</v>
+        <v>0.0468905998032263</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.457760720389636</v>
+        <v>1.457760720389633</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9111218783606441</v>
+        <v>0.9111218783606424</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1519353667698065</v>
+        <v>0.1519353667698079</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1452424131421431</v>
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.041885041321475</v>
+        <v>2.041885041321478</v>
       </c>
       <c r="C6" t="n">
-        <v>7.735879673185191</v>
+        <v>7.735879673185193</v>
       </c>
       <c r="D6" t="n">
-        <v>7.737794152477865</v>
+        <v>7.737794152477867</v>
       </c>
       <c r="E6" t="n">
         <v>7.802400480065784</v>
       </c>
       <c r="F6" t="n">
-        <v>2.051441583989915</v>
+        <v>2.051441583989917</v>
       </c>
       <c r="G6" t="n">
-        <v>7.743087532896958</v>
+        <v>7.743087532896963</v>
       </c>
       <c r="H6" t="n">
-        <v>7.756731958686809</v>
+        <v>7.756731958686808</v>
       </c>
       <c r="I6" t="n">
         <v>2.048661361718901</v>
       </c>
       <c r="J6" t="n">
-        <v>2.067996883401999</v>
+        <v>2.067996883402002</v>
       </c>
       <c r="K6" t="n">
-        <v>7.751438805734354</v>
+        <v>7.751438805734361</v>
       </c>
       <c r="L6" t="n">
-        <v>7.734108412672568</v>
+        <v>7.734108412672575</v>
       </c>
       <c r="M6" t="n">
-        <v>7.752792375971987</v>
+        <v>7.752792375971985</v>
       </c>
       <c r="N6" t="n">
-        <v>2.054831340057707</v>
+        <v>2.054831340057708</v>
       </c>
       <c r="O6" t="n">
         <v>2.066698885112092</v>
       </c>
       <c r="P6" t="n">
-        <v>7.785786329330945</v>
+        <v>7.785786329330946</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.745338145814999</v>
+        <v>7.745338145814995</v>
       </c>
       <c r="R6" t="n">
-        <v>7.74681040890215</v>
+        <v>7.746810408902161</v>
       </c>
       <c r="S6" t="n">
         <v>2.042160097873976</v>
       </c>
       <c r="T6" t="n">
-        <v>2.076125199482353</v>
+        <v>2.076125199482354</v>
       </c>
       <c r="U6" t="n">
-        <v>2.071033210329058</v>
+        <v>2.07103321032906</v>
       </c>
       <c r="V6" t="n">
-        <v>7.774439337248353</v>
+        <v>7.77443933724836</v>
       </c>
       <c r="W6" t="n">
-        <v>7.80902298070398</v>
+        <v>7.809022980703981</v>
       </c>
       <c r="X6" t="n">
-        <v>7.733074079208995</v>
+        <v>7.733074079208993</v>
       </c>
       <c r="Y6" t="n">
         <v>2.200600537420836</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.087213202778572</v>
+        <v>2.087213202778574</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.738289705056625</v>
+        <v>7.738289705056616</v>
       </c>
       <c r="AB6" t="n">
         <v>2.045924495257484</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01389204371120112</v>
+        <v>0.0138920437112011</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01683338686165124</v>
+        <v>0.0168333868616511</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01874786615432276</v>
+        <v>0.01874786615432265</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08335419374224452</v>
+        <v>0.08335419374224444</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02344858637963993</v>
+        <v>0.02344858637963989</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02404124657342032</v>
+        <v>0.0240412465734202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03768567236326481</v>
+        <v>0.03768567236326469</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02066836410862501</v>
+        <v>0.02066836410862481</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04000388579172438</v>
+        <v>0.04000388579172436</v>
       </c>
       <c r="K7" t="n">
-        <v>0.032392519410812</v>
+        <v>0.03239251941081193</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01506212634902522</v>
+        <v>0.0150621263490254</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03374608964844675</v>
+        <v>0.03374608964844655</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02707312031370452</v>
+        <v>0.02707312031370443</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03894048100748203</v>
+        <v>0.03894048100748189</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06626419178002133</v>
+        <v>0.06626419178002119</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02629185949145393</v>
+        <v>0.02629185949145401</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02776412257861485</v>
+        <v>0.02776412257861467</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01416710026370059</v>
+        <v>0.01416710026370057</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04813220187207812</v>
+        <v>0.04813220187207798</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04305639294881779</v>
+        <v>0.04305639294881788</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05539305092481525</v>
+        <v>0.05539305092481524</v>
       </c>
       <c r="W7" t="n">
         <v>0.0895010068688009</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01402779288545097</v>
+        <v>0.01402779288545083</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08381469724955706</v>
+        <v>0.08381469724955692</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.05922020516829653</v>
+        <v>0.05922020516829633</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01924341873307786</v>
+        <v>0.0192434187330778</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0183389596025845</v>
+        <v>0.01833895960258441</v>
       </c>
     </row>
     <row r="8">
@@ -1114,37 +1114,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01681532400325894</v>
+        <v>0.01681532400325874</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02477262336377737</v>
+        <v>0.02477262336377736</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02668710265644905</v>
+        <v>0.02668710265644895</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08862258152565304</v>
+        <v>0.08862258152565296</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02715329402551682</v>
+        <v>0.0271532940255168</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03302057427102165</v>
+        <v>0.03302057427102169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04562490886539099</v>
+        <v>0.04562490886539097</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02860760061075112</v>
+        <v>0.02860760061075123</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04794312229385063</v>
+        <v>0.04794312229385064</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04033175591293815</v>
+        <v>0.04033175591293824</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02300136285115135</v>
+        <v>0.02300136285115197</v>
       </c>
       <c r="M8" t="n">
         <v>0.04168532615057435</v>
@@ -1153,46 +1153,46 @@
         <v>0.03112415159967812</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04406017682104639</v>
+        <v>0.04406017682104624</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07112196934921659</v>
+        <v>0.07112196934921627</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02822938990686247</v>
+        <v>0.02822938990686253</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03570335908074097</v>
+        <v>0.03570335908074095</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02210633676582681</v>
+        <v>0.02210633676582668</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05607143837420438</v>
+        <v>0.05607143837420425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04854388499713856</v>
+        <v>0.0485438849971386</v>
       </c>
       <c r="V8" t="n">
         <v>0.0619753113252559</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09744122914165283</v>
+        <v>0.09744122914165253</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01642504564922341</v>
+        <v>0.01642504564922335</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09676283738592521</v>
+        <v>0.0967628373859251</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.062050311499263</v>
+        <v>0.06205031149926291</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02718265523520407</v>
+        <v>0.02718265523520397</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03151778178576914</v>
+        <v>0.03151778178576934</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03259074285704551</v>
+        <v>0.03259074285704559</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04207806066883356</v>
+        <v>0.04207806066883347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04399253996150515</v>
+        <v>0.04399253996150503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1070880912154246</v>
+        <v>0.1070880912154247</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03360298859149359</v>
+        <v>0.03360298859149351</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04928593067343607</v>
+        <v>0.04928593067343595</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0629303461704471</v>
+        <v>0.06293034617044703</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04591303791580731</v>
+        <v>0.04591303791580719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06524855959890678</v>
+        <v>0.06524855959890681</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05763719321799432</v>
+        <v>0.05763719321799427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04030680015620776</v>
+        <v>0.04030680015620759</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05899076345562908</v>
+        <v>0.05899076345562892</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05231779412088685</v>
+        <v>0.05231779412088686</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06635464792789182</v>
+        <v>0.06635464792789179</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0941501509392427</v>
+        <v>0.09415015093924266</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05153654359146975</v>
+        <v>0.0515365435914697</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05300879638579715</v>
+        <v>0.05300879638579704</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03941177407088294</v>
+        <v>0.03941177407088289</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07337687567926049</v>
+        <v>0.07337687567926029</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06828488652596715</v>
+        <v>0.06828488652596713</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08819164967917059</v>
+        <v>0.08819164967917063</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1147456806759833</v>
+        <v>0.1147456806759832</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03927246669263337</v>
+        <v>0.0392724666926333</v>
       </c>
       <c r="Y9" t="n">
         <v>0.1090593710567394</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08051824243264114</v>
+        <v>0.08051824243264091</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04448809254026019</v>
+        <v>0.04448809254026031</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04358363340976688</v>
+        <v>0.04358363340976689</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05101045840617227</v>
+        <v>0.05101045840617229</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04730616822044485</v>
+        <v>0.04730616822044482</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05124038199343629</v>
+        <v>0.05124038199343624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05221474628063182</v>
+        <v>0.05221474628063186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05765638610096264</v>
+        <v>0.0576563861009626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05388539692852012</v>
+        <v>0.05388539692852019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05263977800293993</v>
+        <v>0.0526397780029399</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05201805757693787</v>
+        <v>0.05201805757693782</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0538556370254445</v>
+        <v>0.05385563702544447</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05494770179019159</v>
+        <v>0.05494770179019145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05385368593077275</v>
+        <v>0.05385368593077272</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05574749267010665</v>
+        <v>0.05574749267010662</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05323619484509458</v>
+        <v>0.05323619484509454</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06947642127626164</v>
+        <v>0.06947642127626155</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05775514385919943</v>
+        <v>0.05775514385919941</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05266887579768275</v>
+        <v>0.0526688757976827</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05205287724951074</v>
+        <v>0.05205287724951067</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05456968491197115</v>
+        <v>0.05456968491197114</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05576777123488171</v>
+        <v>0.05576777123488176</v>
       </c>
       <c r="U2" t="n">
         <v>0.2177373072734186</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05196513983085305</v>
+        <v>0.051965139830853</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2365188706359173</v>
+        <v>0.2365188706359171</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05426968084837701</v>
+        <v>0.05426968084837706</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05365970182823698</v>
+        <v>0.05365970182823694</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1975425573947261</v>
+        <v>0.1975425573947262</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05181705128104301</v>
+        <v>0.05181705128104302</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05303277834841408</v>
+        <v>0.05303277834841402</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02265986476813916</v>
+        <v>0.022674051156631</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01801218624955284</v>
+        <v>0.01809376530018506</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02430215525997259</v>
+        <v>0.02437488732711747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03121788696462069</v>
+        <v>0.03153491489085299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07014339700481791</v>
+        <v>0.07185372664562761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04304406295662482</v>
+        <v>0.04377746682857175</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03433792516121603</v>
+        <v>0.0347688971967183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0298656460248317</v>
+        <v>0.03013635919913523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04290512726427953</v>
+        <v>0.04363687139462371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05062587482147815</v>
+        <v>0.05163860844337692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04284797137005235</v>
+        <v>0.04357759477505582</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05632687738244867</v>
+        <v>0.05754242592329512</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03856944790980165</v>
+        <v>0.03914656928903808</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1100136425895439</v>
+        <v>0.1126388036762687</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07051072446452146</v>
+        <v>0.07220791423369864</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03447020022864875</v>
+        <v>0.03490458157786624</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03012795539652727</v>
+        <v>0.03040809943110143</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04791727308789623</v>
+        <v>0.04882414944352801</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05669635777535402</v>
+        <v>0.05791954288453983</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3165871924982139</v>
+        <v>0.3174657151860668</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02943367579598971</v>
+        <v>0.02968696464311581</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3491019112183526</v>
+        <v>0.3500454930688311</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04589022946784971</v>
+        <v>0.04673141201428583</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04158515987116162</v>
+        <v>0.04226820339550259</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2680773931024877</v>
+        <v>0.2682547142735648</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02842032025066046</v>
+        <v>0.0286380443970004</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03716189042396633</v>
+        <v>0.03769022070651217</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006047053732583229</v>
+        <v>0.006047053732583239</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009041670567652947</v>
+        <v>0.009041670567652905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00864414642080639</v>
+        <v>0.008644146420806327</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01965003927439718</v>
+        <v>0.01965003927439707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08111586432302684</v>
+        <v>0.08111586432302671</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03852080687956323</v>
+        <v>0.03852080687956289</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02445096810211971</v>
+        <v>0.02445096810211963</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01742834988490003</v>
+        <v>0.01742834988489995</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03827049284345166</v>
+        <v>0.03827049284345147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05052002897652205</v>
+        <v>0.05052002897652193</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03816261657222729</v>
+        <v>0.03816261657222714</v>
       </c>
       <c r="M4" t="n">
         <v>0.05927332899300929</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03118777069955849</v>
+        <v>0.03118777069955862</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1241319393247082</v>
+        <v>0.1241319393247083</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08223137863312477</v>
+        <v>0.08223137863312474</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02477964107938627</v>
+        <v>0.02477964107938618</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01782165410445131</v>
+        <v>0.01782165410445134</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04625015444066691</v>
+        <v>0.04625015444066693</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05978309060487991</v>
+        <v>0.05978309060487997</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04452783599980171</v>
+        <v>0.04452783599980156</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01740174438618894</v>
+        <v>0.01740174438618881</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04769757453269167</v>
+        <v>0.04769757453269172</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04286147053368375</v>
+        <v>0.04286147053368364</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03561289695910957</v>
+        <v>0.0356128969591096</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01340831643182251</v>
+        <v>0.01340831643182247</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.015157891305303</v>
+        <v>0.01515789130530301</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02890431244318604</v>
+        <v>0.02890431244318597</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01381885736551855</v>
+        <v>0.01381885736551835</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06648850274236802</v>
+        <v>0.06648850274236823</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06043387508031697</v>
+        <v>0.0604338750803167</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2352148542003212</v>
+        <v>0.2352148542003214</v>
       </c>
       <c r="F5" t="n">
-        <v>1.368075505496998</v>
+        <v>1.368075505496997</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5185310271654642</v>
+        <v>0.5185310271654646</v>
       </c>
       <c r="H5" t="n">
-        <v>0.364987635871891</v>
+        <v>0.3649876358718896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2226279127864833</v>
+        <v>0.2226279127864831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5507414007638546</v>
+        <v>0.5507414007638544</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7308032487831158</v>
+        <v>0.7308032487831154</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5278624903803691</v>
+        <v>0.5278624903803693</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9609532539611996</v>
+        <v>0.9609532539611987</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4711140543954614</v>
+        <v>0.4711140543954597</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85194113867274</v>
+        <v>1.851941138672739</v>
       </c>
       <c r="P5" t="n">
-        <v>1.21289838485442</v>
+        <v>1.212898384854418</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3317279954001422</v>
+        <v>0.3317279954001419</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2367354571311508</v>
+        <v>0.2367354571311507</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6497506828681743</v>
+        <v>0.6497506828681733</v>
       </c>
       <c r="T5" t="n">
         <v>1.007404808842251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6227326043481696</v>
+        <v>0.6227326043481697</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1844908886611977</v>
+        <v>0.1844908886611974</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7485058697349504</v>
+        <v>0.7485058697349467</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6489458269116732</v>
+        <v>0.6489458269116728</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5521571889830463</v>
+        <v>0.5521571889830468</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1253601688308275</v>
+        <v>0.1253601688308274</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1769085759380697</v>
+        <v>0.1769085759380702</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4496464945099778</v>
+        <v>0.4496464945099783</v>
       </c>
     </row>
     <row r="6">
@@ -1798,82 +1798,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.775592795302925</v>
+        <v>1.775592795302924</v>
       </c>
       <c r="C6" t="n">
-        <v>6.740785450240699</v>
+        <v>6.740785450240702</v>
       </c>
       <c r="D6" t="n">
-        <v>1.778189887991149</v>
+        <v>1.778189887991147</v>
       </c>
       <c r="E6" t="n">
-        <v>6.751393818947439</v>
+        <v>6.751393818947448</v>
       </c>
       <c r="F6" t="n">
-        <v>6.812859643996082</v>
+        <v>6.812859643996077</v>
       </c>
       <c r="G6" t="n">
-        <v>1.808066548449905</v>
+        <v>1.808066548449903</v>
       </c>
       <c r="H6" t="n">
-        <v>1.793996709672462</v>
+        <v>1.793996709672461</v>
       </c>
       <c r="I6" t="n">
-        <v>1.786974091455242</v>
+        <v>1.786974091455239</v>
       </c>
       <c r="J6" t="n">
-        <v>6.7700142725165</v>
+        <v>6.770014272516505</v>
       </c>
       <c r="K6" t="n">
         <v>1.820065770546863</v>
       </c>
       <c r="L6" t="n">
-        <v>6.769906396245281</v>
+        <v>6.769906396245278</v>
       </c>
       <c r="M6" t="n">
-        <v>1.828819070563351</v>
+        <v>1.828819070563349</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8007492995688</v>
+        <v>1.800749299568799</v>
       </c>
       <c r="O6" t="n">
-        <v>6.856355765323301</v>
+        <v>6.8563557653233</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74954755190182</v>
+        <v>1.749547551901819</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.794325382649728</v>
+        <v>1.794325382649727</v>
       </c>
       <c r="R6" t="n">
-        <v>1.787367395674792</v>
+        <v>1.787367395674791</v>
       </c>
       <c r="S6" t="n">
-        <v>6.777993934113711</v>
+        <v>6.777993934113708</v>
       </c>
       <c r="T6" t="n">
-        <v>1.829328832175221</v>
+        <v>1.829328832175224</v>
       </c>
       <c r="U6" t="n">
-        <v>6.776630195610732</v>
+        <v>6.776630195610729</v>
       </c>
       <c r="V6" t="n">
         <v>1.786947485956528</v>
       </c>
       <c r="W6" t="n">
-        <v>1.907430367419001</v>
+        <v>1.907430367418998</v>
       </c>
       <c r="X6" t="n">
-        <v>6.77460525020673</v>
+        <v>6.774605250206727</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.882998676198374</v>
+        <v>1.882998676198373</v>
       </c>
       <c r="Z6" t="n">
         <v>1.782954058002163</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.746901670978353</v>
+        <v>6.746901670978356</v>
       </c>
       <c r="AB6" t="n">
         <v>1.798507194324151</v>
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008707387826441237</v>
+        <v>0.008707387826441182</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01170200466151099</v>
+        <v>0.01170200466151087</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01130448051466438</v>
+        <v>0.01130448051466421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02231037336825518</v>
+        <v>0.02231037336825513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0837761984168848</v>
+        <v>0.08377619841688469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04118114097342124</v>
+        <v>0.04118114097342104</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02711130219597764</v>
+        <v>0.02711130219597766</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02008868397875798</v>
+        <v>0.02008868397875789</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04093082693730964</v>
+        <v>0.04093082693730956</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05318036307038008</v>
+        <v>0.05318036307038002</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04082295066608524</v>
+        <v>0.04082295066608514</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06193366308686731</v>
+        <v>0.06193366308686721</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03384810479341652</v>
+        <v>0.03384810479341654</v>
       </c>
       <c r="O7" t="n">
         <v>0.1267922094939624</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08489164880237894</v>
+        <v>0.08489164880237905</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02743997517324425</v>
+        <v>0.02743997517324414</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02048198819830923</v>
+        <v>0.02048198819830921</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04891048853452489</v>
+        <v>0.04891048853452482</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06244342469873795</v>
+        <v>0.06244342469873803</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04750719449784221</v>
+        <v>0.04750719449784202</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02006207848004687</v>
+        <v>0.02006207848004679</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05035790862654968</v>
+        <v>0.05035790862654938</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04552180462754179</v>
+        <v>0.04552180462754174</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03863181099084768</v>
+        <v>0.03863181099084751</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01606865052568048</v>
+        <v>0.01606865052568043</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01781822539916102</v>
+        <v>0.01781822539916092</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03156464653704402</v>
+        <v>0.0315646465370439</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01134120235337643</v>
+        <v>0.0113412023533764</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01838995007369437</v>
+        <v>0.01838995007369431</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01799242592684776</v>
+        <v>0.01799242592684772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0268396136744279</v>
+        <v>0.02683961367442788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08704159915354126</v>
+        <v>0.08704159915354132</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04870973683449493</v>
+        <v>0.04870973683449482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03379924760816106</v>
+        <v>0.03379924760816101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02677662939094139</v>
+        <v>0.02677662939094133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04761877234949298</v>
+        <v>0.04761877234949288</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05986830848256341</v>
+        <v>0.05986830848256337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04751089607826864</v>
+        <v>0.04751089607826857</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06862160849906575</v>
+        <v>0.06862160849906582</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0373934205269287</v>
+        <v>0.03739342052692871</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1312012110722149</v>
+        <v>0.1312012110722147</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08908895578024308</v>
+        <v>0.08908895578024317</v>
       </c>
       <c r="Q8" t="n">
         <v>0.02927706045155104</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02716993361049265</v>
+        <v>0.02716993361049276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05559843394670826</v>
+        <v>0.0555984339467083</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06913137011092126</v>
+        <v>0.06913137011092128</v>
       </c>
       <c r="U8" t="n">
         <v>0.0522253232379551</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0256082123397086</v>
+        <v>0.02560821233970859</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05704665078663612</v>
+        <v>0.05704665078663585</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04773045905410361</v>
+        <v>0.04773045905410345</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04929833016509007</v>
+        <v>0.04929833016509005</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01862715749045719</v>
+        <v>0.01862715749045721</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02450617081134444</v>
+        <v>0.02450617081134436</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04248747065515863</v>
+        <v>0.04248747065515861</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0194071404360767</v>
+        <v>0.01940714043607667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02639701206142929</v>
+        <v>0.02639701206142935</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02599948791458266</v>
+        <v>0.0259994879145827</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03608328935439349</v>
+        <v>0.03608328935439335</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08926105804545263</v>
+        <v>0.08926105804545267</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05587614459731879</v>
+        <v>0.05587614459731871</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04180630959589602</v>
+        <v>0.04180630959589587</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03478369137867633</v>
+        <v>0.03478369137867643</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05562583433722799</v>
+        <v>0.05562583433722788</v>
       </c>
       <c r="K9" t="n">
         <v>0.0678753704702984</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0555179580660036</v>
+        <v>0.05551795806600362</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07662867048678554</v>
+        <v>0.07662867048678566</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04854311219333478</v>
+        <v>0.04854311219333484</v>
       </c>
       <c r="O9" t="n">
         <v>0.1428112979972561</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1011986891469659</v>
+        <v>0.1011986891469658</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04213497879714186</v>
+        <v>0.04213497879714175</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03517699559822763</v>
+        <v>0.0351769955982275</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06360549593444323</v>
+        <v>0.06360549593444331</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07713843209865624</v>
+        <v>0.07713843209865637</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06224175743145812</v>
+        <v>0.06224175743145815</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03936750604870362</v>
+        <v>0.03936750604870341</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06505291602646805</v>
+        <v>0.06505291602646796</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06021681202746012</v>
+        <v>0.06021681202746015</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05332681839076599</v>
+        <v>0.05332681839076592</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0283548730595602</v>
+        <v>0.0283548730595601</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03251323279907933</v>
+        <v>0.03251323279907938</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04625965393696237</v>
+        <v>0.04625965393696245</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05230576440450131</v>
+        <v>0.05230576440450134</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04896556330623313</v>
+        <v>0.04896556330623316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05240992019875998</v>
+        <v>0.05240992019875994</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05792409886938533</v>
+        <v>0.05792409886938532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05319409355419891</v>
+        <v>0.0531940935541989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05304782053717546</v>
+        <v>0.05304782053717545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05447462810846709</v>
+        <v>0.05447462810846708</v>
       </c>
       <c r="I2" t="n">
         <v>0.05317159413674229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05438515393324154</v>
+        <v>0.05438515393324153</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05362833238144542</v>
+        <v>0.05362833238144545</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05235328494830086</v>
+        <v>0.05235328494830096</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05343898439644616</v>
+        <v>0.05343898439644622</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05319698488936448</v>
+        <v>0.05319698488936444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06402786277469433</v>
+        <v>0.06402786277469436</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05658288924070592</v>
+        <v>0.0565828892407059</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05451781654421278</v>
+        <v>0.05451781654421286</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0539944941599227</v>
+        <v>0.05399449415992267</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05235774216839513</v>
+        <v>0.05235774216839517</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05505572169615713</v>
+        <v>0.05505572169615711</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196072760032521</v>
+        <v>0.2196072760032522</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05640653389394107</v>
+        <v>0.05640653389394108</v>
       </c>
       <c r="W2" t="n">
         <v>0.242199576461823</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05239050758248793</v>
+        <v>0.05239050758248794</v>
       </c>
       <c r="Y2" t="n">
         <v>0.05865105178997598</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.20503970118087</v>
+        <v>0.2050397011808701</v>
       </c>
       <c r="AA2" t="n">
         <v>0.05307085430650403</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0526873755897745</v>
+        <v>0.0526873755897746</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02402287615947126</v>
+        <v>0.02405545649616561</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02121579978748401</v>
+        <v>0.02137248328634889</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02477210702630161</v>
+        <v>0.02483149727565186</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0641090764959847</v>
+        <v>0.06555545187736045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03038687808770953</v>
+        <v>0.03064662125078445</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02930330679887432</v>
+        <v>0.02952153716830595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03958853938346264</v>
+        <v>0.04017613701594721</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03022939673505448</v>
+        <v>0.03048266167547366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03883252025496833</v>
+        <v>0.03938748676327394</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03345271967514964</v>
+        <v>0.03382100320437183</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02436340057662646</v>
+        <v>0.02440808297039562</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03235684977803393</v>
+        <v>0.03268759780057766</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03039430533192033</v>
+        <v>0.03065250961465264</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0765842531561908</v>
+        <v>0.07814007538845177</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05445012189013341</v>
+        <v>0.0555499416856654</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03983607833714253</v>
+        <v>0.04042925247517273</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03613427586607734</v>
+        <v>0.0365978396846905</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02439334344688585</v>
+        <v>0.02443903127999677</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04371074846772248</v>
+        <v>0.04444246842915922</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3134828535687009</v>
+        <v>0.3141258728279669</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05312891016795351</v>
+        <v>0.05418853647135739</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3716340050375174</v>
+        <v>0.3732351966495946</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02463215023274534</v>
+        <v>0.02468656766239756</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06929554124463287</v>
+        <v>0.07093010998749931</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2976445036173785</v>
+        <v>0.2986620176878348</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02948634392950533</v>
+        <v>0.02971210724588897</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02702622587876874</v>
+        <v>0.02716673313589507</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009625875273664996</v>
+        <v>0.009625875273664567</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01513766114301558</v>
+        <v>0.01513766114301548</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01080236288384843</v>
+        <v>0.01080236288384835</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07308754761607472</v>
+        <v>0.07308754761607462</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01965996167109722</v>
+        <v>0.01965996167109711</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01800774065490496</v>
+        <v>0.01800774065490491</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03412418853655473</v>
+        <v>0.03412418853655465</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01940582040068161</v>
+        <v>0.01940582040068159</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03322601915881589</v>
+        <v>0.03322601915881585</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02456488898457641</v>
+        <v>0.02456488898457628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01016264167641062</v>
+        <v>0.01016264167641117</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02281842193186881</v>
+        <v>0.02281842193186877</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01969262063187264</v>
+        <v>0.01969262063187246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07851740622248728</v>
+        <v>0.07851740622248721</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05793796787322882</v>
+        <v>0.05793796787322868</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03461202178596499</v>
+        <v>0.03461202178596492</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02870085471521703</v>
+        <v>0.02870085471521699</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01021298802779795</v>
+        <v>0.01021298802779778</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04068790792577105</v>
+        <v>0.04068790792577096</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03750219160128207</v>
+        <v>0.03750219160128185</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05669771856173408</v>
+        <v>0.05669771856173395</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07992051220166642</v>
+        <v>0.0799205122016662</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01058308845281127</v>
+        <v>0.01058308845281124</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.081748556823836</v>
+        <v>0.08174855682383589</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05407175884522053</v>
+        <v>0.05407175884522052</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01826791767552909</v>
+        <v>0.01826791767552904</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01440920476346754</v>
+        <v>0.01440920476346742</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0272583268206873</v>
+        <v>0.0272583268206922</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1346343757941823</v>
+        <v>0.1346343757941821</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05276550386669941</v>
+        <v>0.05276550386669896</v>
       </c>
       <c r="E5" t="n">
-        <v>1.220437869739905</v>
+        <v>1.22043786973991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2303031121042425</v>
+        <v>0.2303031121042422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1770319519488816</v>
+        <v>0.1770319519488808</v>
       </c>
       <c r="H5" t="n">
-        <v>0.538507660056965</v>
+        <v>0.5385076600569638</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2272208548482063</v>
+        <v>0.2272208548482069</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4541977130832598</v>
+        <v>0.4541977130832602</v>
       </c>
       <c r="K5" t="n">
-        <v>0.304501463821937</v>
+        <v>0.3045014638219364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03816823042406588</v>
+        <v>0.03816823042407813</v>
       </c>
       <c r="M5" t="n">
         <v>0.2950428495478357</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2235747660128168</v>
+        <v>0.223574766012816</v>
       </c>
       <c r="O5" t="n">
         <v>1.190983803904122</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8857867753098467</v>
+        <v>0.8857867753098448</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5139736427226996</v>
+        <v>0.5139736427226979</v>
       </c>
       <c r="R5" t="n">
         <v>0.4206564749386438</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03808098628571575</v>
+        <v>0.03808098628571414</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6486628604952751</v>
+        <v>0.6486628604952744</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5329748304653932</v>
+        <v>0.532974830465391</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8140837112994316</v>
+        <v>0.8140837112994328</v>
       </c>
       <c r="W5" t="n">
-        <v>1.363899469095705</v>
+        <v>1.363899469095703</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04783643068868865</v>
+        <v>0.04783643068868814</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.374675481085584</v>
+        <v>1.374675481085581</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.822199935541634</v>
+        <v>0.8221999355416364</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1923202404714379</v>
+        <v>0.1923202404714384</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1304145591547364</v>
+        <v>0.130414559154736</v>
       </c>
     </row>
     <row r="6">
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.910761728023527</v>
+        <v>1.910761728023524</v>
       </c>
       <c r="C6" t="n">
         <v>7.241445020330259</v>
       </c>
       <c r="D6" t="n">
-        <v>1.91193821563371</v>
+        <v>1.911938215633709</v>
       </c>
       <c r="E6" t="n">
-        <v>7.299394906803315</v>
+        <v>7.299394906803316</v>
       </c>
       <c r="F6" t="n">
-        <v>1.92079581442096</v>
+        <v>1.920795814420957</v>
       </c>
       <c r="G6" t="n">
-        <v>7.244315099842148</v>
+        <v>7.244315099842154</v>
       </c>
       <c r="H6" t="n">
-        <v>7.260431547723798</v>
+        <v>7.260431547723799</v>
       </c>
       <c r="I6" t="n">
-        <v>7.245713179587927</v>
+        <v>7.245713179587931</v>
       </c>
       <c r="J6" t="n">
-        <v>7.25953337834606</v>
+        <v>7.259533378346061</v>
       </c>
       <c r="K6" t="n">
-        <v>1.925700741734439</v>
+        <v>1.925700741734437</v>
       </c>
       <c r="L6" t="n">
-        <v>7.236470000863651</v>
+        <v>7.236470000863656</v>
       </c>
       <c r="M6" t="n">
-        <v>7.249125781119106</v>
+        <v>7.249125781119113</v>
       </c>
       <c r="N6" t="n">
-        <v>1.920649084527631</v>
+        <v>1.920649084527629</v>
       </c>
       <c r="O6" t="n">
-        <v>1.979483024513158</v>
+        <v>1.979483024513156</v>
       </c>
       <c r="P6" t="n">
-        <v>7.284680011017526</v>
+        <v>7.284680011017528</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.935747874535828</v>
+        <v>1.935747874535826</v>
       </c>
       <c r="R6" t="n">
-        <v>7.255008213902457</v>
+        <v>7.255008213902465</v>
       </c>
       <c r="S6" t="n">
-        <v>1.911348840777658</v>
+        <v>1.911348840777659</v>
       </c>
       <c r="T6" t="n">
-        <v>1.941823760675634</v>
+        <v>1.941823760675633</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93818830279632</v>
+        <v>1.938188302796318</v>
       </c>
       <c r="V6" t="n">
-        <v>1.957833571311595</v>
+        <v>1.957833571311594</v>
       </c>
       <c r="W6" t="n">
-        <v>2.07780456825035</v>
+        <v>2.077804568250347</v>
       </c>
       <c r="X6" t="n">
-        <v>7.236890447640049</v>
+        <v>7.236890447640048</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.065591408603024</v>
+        <v>2.065591408603021</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.955207611595083</v>
+        <v>1.955207611595082</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.244575276862768</v>
+        <v>7.244575276862773</v>
       </c>
       <c r="AB6" t="n">
         <v>1.915202232792207</v>
@@ -2746,76 +2746,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01295194284101269</v>
+        <v>0.01295194284101231</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01846372871036337</v>
+        <v>0.01846372871036333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0141284304511962</v>
+        <v>0.01412843045119612</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0764136151834225</v>
+        <v>0.07641361518342246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.022986029238445</v>
+        <v>0.02298602923844491</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02133380822225271</v>
+        <v>0.02133380822225264</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03745025610390251</v>
+        <v>0.03745025610390246</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02273188796802937</v>
+        <v>0.02273188796802934</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03655208672616365</v>
+        <v>0.03655208672616356</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02789095655192417</v>
+        <v>0.02789095655192408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01348870924375897</v>
+        <v>0.0134887092437584</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02614448949921656</v>
+        <v>0.02614448949921653</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0230186881992204</v>
+        <v>0.02301868819922027</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08184331779949519</v>
+        <v>0.08184331779949509</v>
       </c>
       <c r="P7" t="n">
-        <v>0.06126387945023672</v>
+        <v>0.06126387945023657</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03793808935331282</v>
+        <v>0.03793808935331269</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03202692228256479</v>
+        <v>0.03202692228256471</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01353905559514575</v>
+        <v>0.01353905559514564</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04401397549311881</v>
+        <v>0.04401397549311864</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04040064197983832</v>
+        <v>0.04040064197983818</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06002378612908123</v>
+        <v>0.06002378612908173</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08324657976901405</v>
+        <v>0.08324657976901401</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0139091560201591</v>
+        <v>0.01390915602015902</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08462488283635937</v>
+        <v>0.08462488283635923</v>
       </c>
       <c r="Z7" t="n">
         <v>0.05739782641256835</v>
@@ -2824,7 +2824,7 @@
         <v>0.02159398524287682</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01773527233081531</v>
+        <v>0.01773527233081527</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01547971820063692</v>
+        <v>0.01547971820063661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02543864147703358</v>
+        <v>0.02543864147703347</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02110334321786643</v>
+        <v>0.02110334321786629</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08102055846465189</v>
+        <v>0.08102055846465178</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02620661663043129</v>
+        <v>0.02620661663043119</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02923086390011672</v>
+        <v>0.02923086390011665</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04442516887057277</v>
+        <v>0.04442516887057261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02970680073469962</v>
+        <v>0.02970680073469951</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04352699949283394</v>
+        <v>0.04352699949283381</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03486586931859441</v>
+        <v>0.03486586931859426</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02046362201042854</v>
+        <v>0.02046362201042885</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03311940226588865</v>
+        <v>0.03311940226588857</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02654632548365622</v>
+        <v>0.02654632548365616</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08631845230522303</v>
+        <v>0.08631845230522311</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06550679772968576</v>
+        <v>0.06550679772968562</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03959190071343962</v>
+        <v>0.03959190071343954</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03900183504923505</v>
+        <v>0.03900183504923489</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02051396836181592</v>
+        <v>0.02051396836181583</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05098888825978903</v>
+        <v>0.05098888825978887</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0452001086922644</v>
+        <v>0.04520010869226426</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06580227388042852</v>
+        <v>0.06580227388042885</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09022236651831796</v>
+        <v>0.09022236651831787</v>
       </c>
       <c r="X8" t="n">
         <v>0.01597055635576396</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09605102145154408</v>
+        <v>0.09605102145154394</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05984299391230406</v>
+        <v>0.05984299391230399</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02856889800954705</v>
+        <v>0.02856889800954699</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02935559197596449</v>
+        <v>0.0293555919759644</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02804180959485831</v>
+        <v>0.02804180959485822</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03896332799256506</v>
+        <v>0.03896332799256502</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03462802973339791</v>
+        <v>0.03462802973339785</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09566467795321415</v>
+        <v>0.09566467795321409</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03101470553872764</v>
+        <v>0.03101470553872756</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04183341750080901</v>
+        <v>0.04183341750080895</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0579498553861043</v>
+        <v>0.05794985538610418</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04323148725023113</v>
+        <v>0.04323148725023106</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05705168600836543</v>
+        <v>0.05705168600836531</v>
       </c>
       <c r="K9" t="n">
         <v>0.04839055583412587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03398830852596044</v>
+        <v>0.03398830852596019</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04664408878141829</v>
+        <v>0.04664408878141822</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04351828748142212</v>
+        <v>0.043518287481422</v>
       </c>
       <c r="O9" t="n">
-        <v>0.104135864657628</v>
+        <v>0.1041358646576279</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08394632554507661</v>
+        <v>0.08394632554507647</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05843769863186906</v>
+        <v>0.05843769863186905</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05252652156476656</v>
+        <v>0.05252652156476642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03403865487734738</v>
+        <v>0.0340386548773474</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06451357477532052</v>
+        <v>0.06451357477532042</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06087811689600707</v>
+        <v>0.06087811689600695</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08676611372605683</v>
+        <v>0.08676611372605678</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1037461790512159</v>
+        <v>0.1037461790512157</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03440875530236084</v>
+        <v>0.03440875530236074</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1051244821185611</v>
+        <v>0.1051244821185609</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.07463584200179947</v>
+        <v>0.07463584200179937</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04209358452507857</v>
+        <v>0.04209358452507853</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03823487161301703</v>
+        <v>0.03823487161301699</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0510462350572466</v>
+        <v>0.05104623505724652</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04743170785351852</v>
+        <v>0.04743170785351853</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05108792843960033</v>
+        <v>0.05108792843960026</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05402455334535607</v>
+        <v>0.05402455334535603</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05449114739057606</v>
+        <v>0.05449114739057598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05151388060432724</v>
+        <v>0.0515138806043272</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05298408314552199</v>
+        <v>0.05298408314552191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05147880574274805</v>
+        <v>0.05147880574274798</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05253953157436864</v>
+        <v>0.05253953157436854</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05106312771699087</v>
+        <v>0.05106312771699081</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091687981853244</v>
+        <v>0.05091687981853241</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05187939947752039</v>
+        <v>0.05187939947752036</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05167788316386055</v>
+        <v>0.05167788316386045</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06591793062605655</v>
+        <v>0.06591793062605658</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05480682152970036</v>
+        <v>0.05480682152970026</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05521530985741269</v>
+        <v>0.05521530985741264</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05244454949954783</v>
+        <v>0.05244454949954775</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05095951986796598</v>
+        <v>0.05095951986796587</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05464844374482739</v>
+        <v>0.05464844374482732</v>
       </c>
       <c r="U2" t="n">
         <v>0.2171369908740653</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05399173999074452</v>
+        <v>0.05399173999074442</v>
       </c>
       <c r="W2" t="n">
-        <v>0.238945463169408</v>
+        <v>0.2389454631694081</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05112010561143621</v>
+        <v>0.05112010561143612</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05551332622583112</v>
+        <v>0.05551332622583106</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008988278507526</v>
+        <v>0.2008988278507525</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05167147323924711</v>
+        <v>0.05167147323924702</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05122274192705092</v>
+        <v>0.05122274192705095</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02373612736555838</v>
+        <v>0.02379371485506129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01920872494745783</v>
+        <v>0.0193326562067273</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02404278114357228</v>
+        <v>0.02411174675522655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04499337062397005</v>
+        <v>0.04580057007922983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04838530962513485</v>
+        <v>0.0493230253132527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02706079272905706</v>
+        <v>0.02723539733858617</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03765748961684964</v>
+        <v>0.03821165159944219</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02684374385667023</v>
+        <v>0.02701227056865916</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03437100093900425</v>
+        <v>0.03480462864179556</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02385888267593247</v>
+        <v>0.02392147170241962</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02281725936869168</v>
+        <v>0.02284261942945365</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02986562109857735</v>
+        <v>0.03014287078447853</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0282570486762918</v>
+        <v>0.0284749346280222</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09303717483575627</v>
+        <v>0.09514872408062572</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05047105803539115</v>
+        <v>0.05146693723058433</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05350371470603572</v>
+        <v>0.05461795079747842</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0337718764409946</v>
+        <v>0.03418694822371205</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02311980939362665</v>
+        <v>0.02315580509959372</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04953318607345929</v>
+        <v>0.05050691777987724</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3080614243802543</v>
+        <v>0.3085860002978466</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04462540896011097</v>
+        <v>0.04542075965485053</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3612040433712346</v>
+        <v>0.3625156905116866</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02427151036826592</v>
+        <v>0.02434857963335274</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05561660329711206</v>
+        <v>0.05680232306260251</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2832592588815853</v>
+        <v>0.2838764125343235</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0282050450945019</v>
+        <v>0.02842078280336624</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02520680279053188</v>
+        <v>0.02531784780242134</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009221551613885713</v>
+        <v>0.009221551613885739</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01214345672299507</v>
+        <v>0.01214345672299515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009692497547474367</v>
+        <v>0.009692497547474433</v>
       </c>
       <c r="E4" t="n">
         <v>0.04286302677218481</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04813342115680989</v>
+        <v>0.04813342115680987</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01450382319574163</v>
+        <v>0.01450382319574181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03111043722511954</v>
+        <v>0.03111043722511962</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01410763649897145</v>
+        <v>0.01410763649897155</v>
       </c>
       <c r="J4" t="n">
         <v>0.026196632531436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009412361976704593</v>
+        <v>0.009412361976704633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00776042468625963</v>
+        <v>0.007760424686259677</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0189115856385881</v>
+        <v>0.01891158563858822</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01635630755057519</v>
+        <v>0.01635630755057509</v>
       </c>
       <c r="O4" t="n">
         <v>0.1021168604812797</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0516991057754974</v>
+        <v>0.05169910577549743</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05631316935092335</v>
+        <v>0.05631316935092333</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02501615649610199</v>
+        <v>0.02501615649610206</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008242063660002996</v>
+        <v>0.008242063660003159</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0499101558379769</v>
+        <v>0.04991015583797699</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03042753389083899</v>
+        <v>0.03042753389083901</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04321108250039334</v>
+        <v>0.04321108250039331</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06540859029518725</v>
+        <v>0.06540859029518728</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01005595350559096</v>
+        <v>0.010055953505591</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05991178576849796</v>
+        <v>0.05991178576849804</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03447052682560504</v>
+        <v>0.03447052682560523</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01628390450335518</v>
+        <v>0.01628390450335526</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01156317938794288</v>
+        <v>0.01156317938794285</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04496506333547071</v>
+        <v>0.04496506333546971</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09814148354347661</v>
+        <v>0.09814148354347671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0580031240866722</v>
+        <v>0.05800312408667204</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6404039019205608</v>
+        <v>0.6404039019205602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7656634488128381</v>
+        <v>0.7656634488128371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1316827389446932</v>
+        <v>0.1316827389446925</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4791836444850557</v>
+        <v>0.4791836444850541</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1419231617850406</v>
+        <v>0.1419231617850408</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3315560950233144</v>
+        <v>0.3315560950233142</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04947557768329419</v>
+        <v>0.04947557768329417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02137523664997204</v>
+        <v>0.02137523664997137</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2326938971281427</v>
+        <v>0.2326938971281432</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1777972287123827</v>
+        <v>0.1777972287123823</v>
       </c>
       <c r="O5" t="n">
-        <v>1.497269763462618</v>
+        <v>1.497269763462614</v>
       </c>
       <c r="P5" t="n">
         <v>0.7420638567696387</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8844356774642355</v>
+        <v>0.8844356774642345</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3532922368657433</v>
+        <v>0.3532922368657431</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02897441687411878</v>
+        <v>0.02897441687411826</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8101702701087102</v>
+        <v>0.8101702701087115</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4029869754383288</v>
+        <v>0.402986975438326</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5652436917128061</v>
+        <v>0.5652436917128051</v>
       </c>
       <c r="W5" t="n">
-        <v>1.046494534117901</v>
+        <v>1.046494534117903</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06395423277672474</v>
+        <v>0.06395423277672352</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9366820965829448</v>
+        <v>0.9366820965829458</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4398183893075691</v>
+        <v>0.4398183893075694</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1732748393626934</v>
+        <v>0.1732748393626937</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09773763619582886</v>
+        <v>0.09773763619582898</v>
       </c>
     </row>
     <row r="6">
@@ -3518,13 +3518,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741394469105404</v>
+        <v>6.741394469105402</v>
       </c>
       <c r="C6" t="n">
         <v>1.782913245732805</v>
       </c>
       <c r="D6" t="n">
-        <v>6.741865415038987</v>
+        <v>6.741865415038991</v>
       </c>
       <c r="E6" t="n">
         <v>6.775035944263697</v>
@@ -3533,31 +3533,31 @@
         <v>1.818903210166621</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78527361220555</v>
+        <v>1.785273612205549</v>
       </c>
       <c r="H6" t="n">
-        <v>1.801880226234929</v>
+        <v>1.801880226234928</v>
       </c>
       <c r="I6" t="n">
         <v>1.78487742550878</v>
       </c>
       <c r="J6" t="n">
-        <v>6.758369550022955</v>
+        <v>6.758369550022953</v>
       </c>
       <c r="K6" t="n">
-        <v>6.741585279468218</v>
+        <v>6.741585279468219</v>
       </c>
       <c r="L6" t="n">
-        <v>6.739933342177781</v>
+        <v>6.739933342177774</v>
       </c>
       <c r="M6" t="n">
-        <v>1.789681374648398</v>
+        <v>1.789681374648397</v>
       </c>
       <c r="N6" t="n">
-        <v>1.78707343396003</v>
+        <v>1.787073433960028</v>
       </c>
       <c r="O6" t="n">
-        <v>6.834713478822296</v>
+        <v>6.834713478822299</v>
       </c>
       <c r="P6" t="n">
         <v>6.784292849214087</v>
@@ -3572,28 +3572,28 @@
         <v>6.740414981151516</v>
       </c>
       <c r="T6" t="n">
-        <v>1.820679944847787</v>
+        <v>1.820679944847786</v>
       </c>
       <c r="U6" t="n">
-        <v>1.800964938458662</v>
+        <v>1.800964938458663</v>
       </c>
       <c r="V6" t="n">
         <v>6.77538399999191</v>
       </c>
       <c r="W6" t="n">
-        <v>6.798004922223555</v>
+        <v>6.79800492222355</v>
       </c>
       <c r="X6" t="n">
-        <v>1.780825742515402</v>
+        <v>1.780825742515401</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.90799900981932</v>
+        <v>1.907999009819319</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.766643444317122</v>
+        <v>6.76664344431712</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.748456821994867</v>
+        <v>6.748456821994873</v>
       </c>
       <c r="AB6" t="n">
         <v>1.782165243451031</v>
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01176438740887172</v>
+        <v>0.01176438740887177</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01468629251798109</v>
+        <v>0.01468629251798116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01223533334246045</v>
+        <v>0.01223533334246047</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04540586256717086</v>
+        <v>0.0454058625671709</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05067625695179589</v>
+        <v>0.05067625695179597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01704665899072767</v>
+        <v>0.01704665899072787</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03365327302010562</v>
+        <v>0.03365327302010569</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0166504722939575</v>
+        <v>0.01665047229395757</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02873946832642203</v>
+        <v>0.02873946832642204</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01195519777169064</v>
+        <v>0.01195519777169071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0103032604812457</v>
+        <v>0.01030326048124573</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02145442143357415</v>
+        <v>0.02145442143357427</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01889914334556115</v>
+        <v>0.01889914334556125</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1046595815298385</v>
+        <v>0.1046595815298384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05424182682405623</v>
+        <v>0.05424182682405627</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0588560051459093</v>
+        <v>0.05885600514590941</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02755899229108803</v>
+        <v>0.02755899229108813</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0107848994549891</v>
+        <v>0.01078489945498916</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05245299163296292</v>
+        <v>0.05245299163296302</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03274067699295403</v>
+        <v>0.03274067699295388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04575391829537939</v>
+        <v>0.04575391829537936</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06795142609017327</v>
+        <v>0.06795142609017336</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01259878930057698</v>
+        <v>0.01259878930057701</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06222223712149787</v>
+        <v>0.06222223712149806</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03701336262059108</v>
+        <v>0.03701336262059125</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01882674029834122</v>
+        <v>0.01882674029834127</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01410601518292889</v>
+        <v>0.01410601518292901</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01378778502828138</v>
+        <v>0.01378778502828145</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0201945075193505</v>
+        <v>0.02019450751935061</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01774354834382976</v>
+        <v>0.01774354834382991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04905851510947786</v>
+        <v>0.04905851510947785</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05324254839072709</v>
+        <v>0.05324254839072705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02327747357727961</v>
+        <v>0.02327747357727962</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03916148802147499</v>
+        <v>0.03916148802147508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02215868729532689</v>
+        <v>0.02215868729532696</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03424768332779142</v>
+        <v>0.03424768332779139</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01746341277306004</v>
+        <v>0.01746341277306014</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01581147548261507</v>
+        <v>0.01581147548261519</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02696263643494891</v>
+        <v>0.0269626364349491</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02170604187718768</v>
+        <v>0.02170604187718779</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1082089400259782</v>
+        <v>0.1082089400259784</v>
       </c>
       <c r="P8" t="n">
-        <v>0.05760921856997336</v>
+        <v>0.05760921856997352</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06019455661422064</v>
+        <v>0.06019455661422078</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03306720729245739</v>
+        <v>0.03306720729245757</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01629311445635855</v>
+        <v>0.01629311445635858</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05796120663433231</v>
+        <v>0.05796120663433246</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03654748235415418</v>
+        <v>0.03654748235415429</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05031207908111916</v>
+        <v>0.05031207908111904</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07346032595230231</v>
+        <v>0.07346032595230235</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01425673120287719</v>
+        <v>0.01425673120287717</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07119904745720855</v>
+        <v>0.07119904745720865</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0389720279685117</v>
+        <v>0.03897202796851181</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02433495529971064</v>
+        <v>0.0243349552997107</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02325441333014049</v>
+        <v>0.02325441333014069</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02240619893313696</v>
+        <v>0.0224061989331369</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02922834313363016</v>
+        <v>0.0292283431336302</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02677738395810949</v>
+        <v>0.02677738395810958</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05904775866967479</v>
+        <v>0.05904775866967486</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05622718390764277</v>
+        <v>0.0562271839076428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03158871579505996</v>
+        <v>0.03158871579506008</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04819532363575468</v>
+        <v>0.04819532363575474</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03119252290960656</v>
+        <v>0.03119252290960658</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04328151894207107</v>
+        <v>0.04328151894207108</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02649724838733969</v>
+        <v>0.02649724838733973</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02484531109689476</v>
+        <v>0.02484531109689482</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03599647204922318</v>
+        <v>0.03599647204922326</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0334411939612102</v>
+        <v>0.03344119396121027</v>
       </c>
       <c r="O9" t="n">
         <v>0.1204942892594776</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07035763899641541</v>
+        <v>0.07035763899641553</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07339806195024159</v>
+        <v>0.07339806195024162</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04210104290673707</v>
+        <v>0.04210104290673717</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02532695007063826</v>
+        <v>0.02532695007063817</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06699504224861208</v>
+        <v>0.06699504224861219</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0472800358594883</v>
+        <v>0.04728003585948808</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06479676844763012</v>
+        <v>0.0647967684476301</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0824934767058223</v>
+        <v>0.08249347670582244</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02714083991622615</v>
+        <v>0.02714083991622625</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.076764287737147</v>
+        <v>0.07676428773714701</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04920391834438571</v>
+        <v>0.04920391834438583</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0333687909139903</v>
+        <v>0.03336879091399023</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02864806579857796</v>
+        <v>0.028648065798578</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04934018498054471</v>
+        <v>0.04934018498054469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04548133966150088</v>
+        <v>0.04548133966150084</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04990737021542387</v>
+        <v>0.0499073702154239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05005741331310263</v>
+        <v>0.05005741331310266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05430311111966971</v>
+        <v>0.05430311111966962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04979122983576249</v>
+        <v>0.04979122983576247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05110246139033976</v>
+        <v>0.05110246139033973</v>
       </c>
       <c r="I2" t="n">
         <v>0.05173418337068873</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05065326127654886</v>
+        <v>0.05065326127654884</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0511534300278256</v>
+        <v>0.05115343002782557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091753770488408</v>
+        <v>0.05091753770488409</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05137169661301517</v>
+        <v>0.05137169661301519</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04969576800240501</v>
+        <v>0.04969576800240498</v>
       </c>
       <c r="O2" t="n">
         <v>0.05963831087621432</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05199599145735096</v>
+        <v>0.05199599145735094</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05424912180568763</v>
+        <v>0.05424912180568766</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05123987606366971</v>
+        <v>0.05123987606366975</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05081304729419099</v>
+        <v>0.05081304729419098</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0532911913276109</v>
+        <v>0.05329119132761089</v>
       </c>
       <c r="U2" t="n">
-        <v>0.213377579453243</v>
+        <v>0.2133775794532428</v>
       </c>
       <c r="V2" t="n">
         <v>0.04998314245609571</v>
       </c>
       <c r="W2" t="n">
-        <v>0.234891736195377</v>
+        <v>0.2348917361953769</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04982363514680756</v>
+        <v>0.04982363514680758</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0502362415176402</v>
+        <v>0.05023624151764018</v>
       </c>
       <c r="Z2" t="n">
         <v>0.1959733264791282</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04993036868846022</v>
+        <v>0.04993036868846018</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04934835397608779</v>
+        <v>0.0493483539760878</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02307992597743075</v>
+        <v>0.02316162588088693</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01686228363160452</v>
+        <v>0.01695130110669608</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02714000339791229</v>
+        <v>0.0273669581527888</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02818431120270362</v>
+        <v>0.02844679776335146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05857646374301979</v>
+        <v>0.05992623666654705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02628057156450147</v>
+        <v>0.02647515109047176</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0357545141887066</v>
+        <v>0.03628852681860885</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04022314355927139</v>
+        <v>0.0409152859418775</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03244607161211888</v>
+        <v>0.03286029341257475</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03597706394029707</v>
+        <v>0.03651967697397564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03431375913292542</v>
+        <v>0.0347928245695859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03759015007857398</v>
+        <v>0.03819047257895752</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02563561656470582</v>
+        <v>0.02580812202627331</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07150605015330598</v>
+        <v>0.07302986857832211</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04192653142013688</v>
+        <v>0.04267078888014667</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0580834236070768</v>
+        <v>0.05940953465979189</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03671963523318578</v>
+        <v>0.03728718749834378</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03355162460687739</v>
+        <v>0.03400296263503276</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0513846154449854</v>
+        <v>0.05247154098941955</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2976237026947539</v>
+        <v>0.2978792946009445</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02763571268419885</v>
+        <v>0.02787856164363029</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3490769245878046</v>
+        <v>0.3500637114938877</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02654114532311952</v>
+        <v>0.02674664207985936</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02949346222803728</v>
+        <v>0.02980211086393793</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2675301884410978</v>
+        <v>0.2677232961402053</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02730667886697661</v>
+        <v>0.027537931764791</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02327595247053304</v>
+        <v>0.02336571794084683</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007936021996639737</v>
+        <v>0.007936021996639755</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008211458055526609</v>
+        <v>0.008211458055526593</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01434264014269922</v>
+        <v>0.01434264014269919</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01603744595421537</v>
+        <v>0.01603744595421541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06399455579687616</v>
+        <v>0.06399455579687598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01303078112720934</v>
+        <v>0.01303078112720928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02784174473247589</v>
+        <v>0.02784174473247594</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03497733510698632</v>
+        <v>0.0349773351069863</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02286242745525165</v>
+        <v>0.02286242745525167</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02841745893960966</v>
+        <v>0.02841745893960969</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02575294663615565</v>
+        <v>0.02575294663615568</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03084967715058726</v>
+        <v>0.03084967715058734</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01195249580482323</v>
+        <v>0.01195249580482335</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07316136975328258</v>
+        <v>0.07316136975328257</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03793457788350579</v>
+        <v>0.03793457788350572</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06338472165913746</v>
+        <v>0.06338472165913754</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02939390668161077</v>
+        <v>0.02939390668161079</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02457267937941364</v>
+        <v>0.02457267937941358</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05256445623946919</v>
+        <v>0.05256445623946922</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01554747712534956</v>
+        <v>0.01554747712534945</v>
       </c>
       <c r="V4" t="n">
         <v>0.01582904413135667</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04847266483867734</v>
+        <v>0.04847266483867743</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01339681402264332</v>
+        <v>0.01339681402264329</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01787312302276776</v>
+        <v>0.01787312302276775</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01295959657383663</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01460241847546437</v>
+        <v>0.01460241847546433</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.008239439354703811</v>
+        <v>0.008239439354703778</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06157372873287874</v>
+        <v>0.06157372873287915</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0708607260370334</v>
+        <v>0.07086072603703329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1811289775066869</v>
+        <v>0.1811289775066866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1973417857229483</v>
+        <v>0.1973417857229488</v>
       </c>
       <c r="F5" t="n">
-        <v>1.092387659433046</v>
+        <v>1.092387659433048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1421040704365013</v>
+        <v>0.1421040704365011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4639763221475687</v>
+        <v>0.4639763221475696</v>
       </c>
       <c r="I5" t="n">
         <v>0.5694510430293889</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3212231131587296</v>
+        <v>0.3212231131587298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4009771850922155</v>
+        <v>0.4009771850922145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3643555414158203</v>
+        <v>0.364355541415821</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4820050187821001</v>
+        <v>0.4820050187821002</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1418759121484589</v>
+        <v>0.1418759121484594</v>
       </c>
       <c r="O5" t="n">
-        <v>1.083716017082201</v>
+        <v>1.083716017082199</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5361702121842261</v>
+        <v>0.536170212184229</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02578079697989</v>
+        <v>1.025780796979892</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4833371366290494</v>
+        <v>0.4833371366290495</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3349913963330047</v>
+        <v>0.3349913963330052</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9059160681444346</v>
+        <v>0.9059160681444338</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1909695939662135</v>
+        <v>0.1909695939662119</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1735351176632618</v>
+        <v>0.1735351176632622</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7893963201739116</v>
+        <v>0.7893963201739121</v>
       </c>
       <c r="X5" t="n">
         <v>0.1637595852306501</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2500890794448277</v>
+        <v>0.2500890794448258</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1324913586643731</v>
+        <v>0.132491358664373</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1870368815846622</v>
+        <v>0.1870368815846624</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07886180222333168</v>
+        <v>0.07886180222333153</v>
       </c>
     </row>
     <row r="6">
@@ -4384,40 +4384,40 @@
         <v>1.777701830531949</v>
       </c>
       <c r="D6" t="n">
-        <v>6.744731516537828</v>
+        <v>6.744731516537825</v>
       </c>
       <c r="E6" t="n">
-        <v>6.746426322349346</v>
+        <v>6.74642632234934</v>
       </c>
       <c r="F6" t="n">
-        <v>1.833484928273297</v>
+        <v>1.833484928273298</v>
       </c>
       <c r="G6" t="n">
-        <v>1.782521153603631</v>
+        <v>1.782521153603633</v>
       </c>
       <c r="H6" t="n">
-        <v>6.758230621127605</v>
+        <v>6.758230621127602</v>
       </c>
       <c r="I6" t="n">
-        <v>1.804467707583408</v>
+        <v>1.804467707583409</v>
       </c>
       <c r="J6" t="n">
-        <v>6.753251303850386</v>
+        <v>6.75325130385038</v>
       </c>
       <c r="K6" t="n">
-        <v>6.75880633533474</v>
+        <v>6.758806335334735</v>
       </c>
       <c r="L6" t="n">
-        <v>1.795243319112579</v>
+        <v>1.795243319112582</v>
       </c>
       <c r="M6" t="n">
-        <v>1.800340049627009</v>
+        <v>1.800340049627011</v>
       </c>
       <c r="N6" t="n">
-        <v>1.781444455220243</v>
+        <v>1.781444455220246</v>
       </c>
       <c r="O6" t="n">
-        <v>1.842661587363542</v>
+        <v>1.842661587363543</v>
       </c>
       <c r="P6" t="n">
         <v>6.768750063339377</v>
@@ -4426,37 +4426,37 @@
         <v>6.793773598054265</v>
       </c>
       <c r="R6" t="n">
-        <v>6.759782783076734</v>
+        <v>6.759782783076736</v>
       </c>
       <c r="S6" t="n">
-        <v>1.794063051855834</v>
+        <v>1.794063051855836</v>
       </c>
       <c r="T6" t="n">
         <v>6.782953332634602</v>
       </c>
       <c r="U6" t="n">
-        <v>6.74612062328722</v>
+        <v>6.746120623287218</v>
       </c>
       <c r="V6" t="n">
-        <v>1.785319416607778</v>
+        <v>1.78531941660778</v>
       </c>
       <c r="W6" t="n">
-        <v>1.908157024383182</v>
+        <v>1.908157024383181</v>
       </c>
       <c r="X6" t="n">
-        <v>1.782887186499066</v>
+        <v>1.782887186499067</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.865037122994513</v>
+        <v>1.865037122994512</v>
       </c>
       <c r="Z6" t="n">
         <v>1.78244996905026</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.7449912948706</v>
+        <v>6.744991294870592</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77769187525164</v>
+        <v>1.777691875251638</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009903951358470157</v>
+        <v>0.009903951358470128</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0101793874173571</v>
+        <v>0.01017938741735708</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01631056950452968</v>
+        <v>0.01631056950452969</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01800537531604585</v>
+        <v>0.01800537531604587</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06596248515870658</v>
+        <v>0.06596248515870651</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01499871048903981</v>
+        <v>0.01499871048903982</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02980967409430633</v>
+        <v>0.02980967409430637</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0369452644688168</v>
+        <v>0.03694526446881683</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02483035681708214</v>
+        <v>0.02483035681708218</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03038538830144017</v>
+        <v>0.03038538830144018</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02772087599798612</v>
+        <v>0.02772087599798623</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03281760651241775</v>
+        <v>0.03281760651241791</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01392042516665377</v>
+        <v>0.01392042516665376</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07512924438517485</v>
+        <v>0.07512924438517476</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03990245251539782</v>
+        <v>0.03990245251539785</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06535265102096802</v>
+        <v>0.06535265102096803</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03136183604344125</v>
+        <v>0.0313618360434413</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02654060874124412</v>
+        <v>0.02654060874124406</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05453238560129967</v>
+        <v>0.05453238560129972</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01765920620197704</v>
+        <v>0.01765920620197698</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01779697349318716</v>
+        <v>0.01779697349318717</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05044059420050793</v>
+        <v>0.05044059420050784</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01536474338447371</v>
+        <v>0.01536474338447373</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02002532215133649</v>
+        <v>0.02002532215133648</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0149275259356671</v>
+        <v>0.01492752593566709</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01657034783729486</v>
+        <v>0.01657034783729484</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01020736871653447</v>
+        <v>0.0102073687165343</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01177224130797988</v>
+        <v>0.01177224130797993</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01499712486342318</v>
+        <v>0.01499712486342316</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02112830695059585</v>
+        <v>0.02112830695059582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02125261897444056</v>
+        <v>0.02125261897444064</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06829026455668631</v>
+        <v>0.06829026455668617</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02042803508700116</v>
+        <v>0.02042803508700118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0346274115403724</v>
+        <v>0.03462741154037246</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04176300191488289</v>
+        <v>0.04176300191488287</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02964809426314834</v>
+        <v>0.02964809426314826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03520312574750624</v>
+        <v>0.03520312574750626</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03253861344405223</v>
+        <v>0.03253861344405234</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03763534395849578</v>
+        <v>0.03763534395849573</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01645184736979952</v>
+        <v>0.01645184736979945</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0782890205962203</v>
+        <v>0.07828902059622034</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04290821739183463</v>
+        <v>0.0429082173918347</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.066641307220871</v>
+        <v>0.06664130722087087</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03617957348950759</v>
+        <v>0.03617957348950738</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03135834618731027</v>
+        <v>0.03135834618731016</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05935012304736586</v>
+        <v>0.05935012304736587</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02104650685738213</v>
+        <v>0.02104650685738216</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02177403644657564</v>
+        <v>0.02177403644657561</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05525891129259765</v>
+        <v>0.05525891129259757</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01692372230505114</v>
+        <v>0.01692372230505104</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02772204719098533</v>
+        <v>0.02772204719098519</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01674102838409864</v>
+        <v>0.0167410283840986</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02138808528336102</v>
+        <v>0.02138808528336094</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01810605069697818</v>
+        <v>0.01810605069697809</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01693293570529746</v>
+        <v>0.01693293570529756</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01991934511306228</v>
+        <v>0.01991934511306219</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02605052720023499</v>
+        <v>0.02605052720023481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02711965172875652</v>
+        <v>0.02711965172875649</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06945290886765915</v>
+        <v>0.06945290886765899</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02473866858524643</v>
+        <v>0.02473866858524634</v>
       </c>
       <c r="H9" t="n">
         <v>0.03954963179001157</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04668522216452192</v>
+        <v>0.04668522216452198</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03457031451278736</v>
+        <v>0.0345703145127873</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04012534599714535</v>
+        <v>0.04012534599714527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03746083369369133</v>
+        <v>0.03746083369369131</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04255756420812293</v>
+        <v>0.04255756420812296</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02366038286235898</v>
+        <v>0.02366038286235891</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08576767036214751</v>
+        <v>0.08576767036214719</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05073626793850167</v>
+        <v>0.05073626793850157</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07509260911717448</v>
+        <v>0.07509260911717457</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04110179373914638</v>
+        <v>0.04110179373914644</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03628056643694919</v>
+        <v>0.0362805664369491</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06427234329700496</v>
+        <v>0.06427234329700485</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0274396339496234</v>
+        <v>0.02743963394962328</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03066532990217446</v>
+        <v>0.03066532990217444</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06018055189621315</v>
+        <v>0.06018055189621303</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0251047010801789</v>
+        <v>0.02510470108017887</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02976527984704168</v>
+        <v>0.0297652798470416</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02303300793018987</v>
+        <v>0.02303300793018983</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02631030553300005</v>
+        <v>0.02631030553299993</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01994732641223951</v>
+        <v>0.01994732641223939</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05461387539358902</v>
+        <v>0.05461387539358899</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05089850950633486</v>
+        <v>0.05089850950633479</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05491160711280154</v>
+        <v>0.05491160711280146</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06088657307094907</v>
+        <v>0.06088657307094901</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05594101781737497</v>
+        <v>0.05594101781737492</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05698406665450173</v>
+        <v>0.0569840666545017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05551178296908005</v>
+        <v>0.05551178296907998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05515388668779539</v>
+        <v>0.05515388668779536</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05836096857683355</v>
+        <v>0.05836096857683349</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05529667593216653</v>
+        <v>0.05529667593216647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05472137999673726</v>
+        <v>0.05472137999673724</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05966166827010845</v>
+        <v>0.05966166827010842</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05808888194999558</v>
+        <v>0.05808888194999559</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07834697445995606</v>
+        <v>0.07834697445995596</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06314398363361412</v>
+        <v>0.06314398363361408</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05947442247755313</v>
+        <v>0.05947442247755307</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05527470314285395</v>
+        <v>0.05527470314285388</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05479497547810925</v>
+        <v>0.05479497547810919</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05995054754569196</v>
+        <v>0.05995054754569192</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2236383541501462</v>
+        <v>0.2236383541501461</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05898107277762749</v>
+        <v>0.05898107277762742</v>
       </c>
       <c r="W2" t="n">
         <v>0.2478375437361284</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05473438767241053</v>
+        <v>0.05473438767241048</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06244052514519884</v>
+        <v>0.06244052514519879</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2083010079203375</v>
+        <v>0.2083010079203374</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05536859626170623</v>
+        <v>0.05536859626170618</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05817854141565639</v>
+        <v>0.05817854141565634</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02600750082240084</v>
+        <v>0.02604459038043283</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02164645696477861</v>
+        <v>0.02176410462054218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02814127788512928</v>
+        <v>0.02825442107616015</v>
       </c>
       <c r="E3" t="n">
-        <v>0.070760794946284</v>
+        <v>0.07237630210407338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03550167277106973</v>
+        <v>0.03587801833041784</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04279134097151735</v>
+        <v>0.04342138768985628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03245457834285342</v>
+        <v>0.03272187495244171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02987793775951256</v>
+        <v>0.03005291681693031</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05263553983963459</v>
+        <v>0.05361451602259961</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03087036371904767</v>
+        <v>0.03108100410983702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0267730512025974</v>
+        <v>0.02683737040483454</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06197968889535405</v>
+        <v>0.06330513154135298</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05079904998007811</v>
+        <v>0.05171518583009356</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1359906495695261</v>
+        <v>0.1392789264124742</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08665671467670534</v>
+        <v>0.08882229356468448</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06065573405124627</v>
+        <v>0.06192433008350849</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03075049937937514</v>
+        <v>0.03095662557314774</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02728810684082955</v>
+        <v>0.02737070521928559</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06409428326545867</v>
+        <v>0.06548788748386583</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3259306144146535</v>
+        <v>0.3269297312892179</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05699699679532646</v>
+        <v>0.05812786329224626</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3946657648562858</v>
+        <v>0.3969856799864364</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02687256489110494</v>
+        <v>0.02694064783227216</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08184155429116276</v>
+        <v>0.08385463224863658</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3055175107072607</v>
+        <v>0.3067422661818661</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03139683322925664</v>
+        <v>0.03162453958254639</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05161019692387919</v>
+        <v>0.05255617491986921</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01125139590429661</v>
+        <v>0.0112513959042966</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01482040841874202</v>
+        <v>0.01482040841874204</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01461441263615944</v>
+        <v>0.01461441263615948</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08210440175357313</v>
+        <v>0.08210440175357314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02624208009663607</v>
+        <v>0.02624208009663611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03802379653815451</v>
+        <v>0.0380237965381546</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02139367502735946</v>
+        <v>0.02139367502735947</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01735107188982601</v>
+        <v>0.01735107188982604</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05368251869159309</v>
+        <v>0.05368251869159314</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0189639420912955</v>
+        <v>0.01896394209129551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01246570985141674</v>
+        <v>0.01246570985141678</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0683164713428185</v>
+        <v>0.06831647134281849</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05050319354090302</v>
+        <v>0.05050319354090305</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1582915528457508</v>
+        <v>0.1582915528457509</v>
       </c>
       <c r="P4" t="n">
         <v>0.1076028925190393</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0661535111797983</v>
+        <v>0.06615351117979834</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01871574932802738</v>
+        <v>0.0187157493280274</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01329700466910766</v>
+        <v>0.01329700466910771</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07153156285277915</v>
+        <v>0.0715315628527792</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05469094609203317</v>
+        <v>0.05469094609203316</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06128887872320661</v>
+        <v>0.06128887872320677</v>
       </c>
       <c r="W4" t="n">
         <v>0.1135540898463139</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01261263753197254</v>
+        <v>0.01261263753197252</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09987153336755955</v>
+        <v>0.09987153336755966</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06484568153187756</v>
+        <v>0.06484568153187753</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01977631529843269</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05165026309291419</v>
+        <v>0.05165026309291417</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03346326432199943</v>
+        <v>0.0334632643219995</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1037619962702292</v>
+        <v>0.1037619962702293</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1019733338655027</v>
+        <v>0.1019733338655024</v>
       </c>
       <c r="E5" t="n">
-        <v>1.364657189723324</v>
+        <v>1.364657189723326</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3293024953227223</v>
+        <v>0.3293024953227214</v>
       </c>
       <c r="G5" t="n">
-        <v>0.466075941470079</v>
+        <v>0.4660759414700812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.246736910287972</v>
+        <v>0.2467369102879711</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1578881164218011</v>
+        <v>0.1578881164218008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7698070245076436</v>
+        <v>0.769807024507644</v>
       </c>
       <c r="K5" t="n">
         <v>0.1735526462219276</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05546941083932515</v>
+        <v>0.05546941083932522</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06783852633711</v>
+        <v>1.067838526337109</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7702123175005279</v>
+        <v>0.7702123175005299</v>
       </c>
       <c r="O5" t="n">
-        <v>2.47321522242051</v>
+        <v>2.473215222420508</v>
       </c>
       <c r="P5" t="n">
-        <v>1.727022846142503</v>
+        <v>1.727022846142505</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.048336971996211</v>
+        <v>1.04833697199621</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1894133113454375</v>
+        <v>0.1894133113454389</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06551526750957244</v>
+        <v>0.06551526750957262</v>
       </c>
       <c r="T5" t="n">
-        <v>1.172504815740472</v>
+        <v>1.172504815740473</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8076111423314892</v>
+        <v>0.8076111423314878</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8671098035863558</v>
+        <v>0.8671098035863549</v>
       </c>
       <c r="W5" t="n">
-        <v>1.977437439206566</v>
+        <v>1.97743743920657</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06196107789316051</v>
+        <v>0.06196107789316065</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.691048651218504</v>
+        <v>1.691048651218506</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9298877105478726</v>
+        <v>0.9298877105478711</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1962377427843339</v>
+        <v>0.1962377427843336</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8465494075480418</v>
+        <v>0.8465494075480421</v>
       </c>
     </row>
     <row r="6">
@@ -5238,16 +5238,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.913036386888185</v>
+        <v>1.913036386888184</v>
       </c>
       <c r="C6" t="n">
-        <v>1.916605399402631</v>
+        <v>1.916605399402629</v>
       </c>
       <c r="D6" t="n">
         <v>7.242741186336795</v>
       </c>
       <c r="E6" t="n">
-        <v>7.310231175454217</v>
+        <v>7.310231175454212</v>
       </c>
       <c r="F6" t="n">
         <v>1.928027071080523</v>
@@ -5256,16 +5256,16 @@
         <v>1.939808787522041</v>
       </c>
       <c r="H6" t="n">
-        <v>7.249520448727999</v>
+        <v>7.249520448727993</v>
       </c>
       <c r="I6" t="n">
-        <v>7.245477845590461</v>
+        <v>7.245477845590467</v>
       </c>
       <c r="J6" t="n">
-        <v>1.95546750967548</v>
+        <v>1.955467509675479</v>
       </c>
       <c r="K6" t="n">
-        <v>7.247090715791938</v>
+        <v>7.247090715791932</v>
       </c>
       <c r="L6" t="n">
         <v>1.914250700835304</v>
@@ -5274,34 +5274,34 @@
         <v>7.296443245043456</v>
       </c>
       <c r="N6" t="n">
-        <v>1.952086952892447</v>
+        <v>1.95208695289245</v>
       </c>
       <c r="O6" t="n">
-        <v>7.386962242938258</v>
+        <v>7.386962242938259</v>
       </c>
       <c r="P6" t="n">
-        <v>7.336272349400859</v>
+        <v>7.33627234940086</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.294280284880439</v>
+        <v>7.294280284880435</v>
       </c>
       <c r="R6" t="n">
         <v>7.246842523028664</v>
       </c>
       <c r="S6" t="n">
-        <v>1.915081995652995</v>
+        <v>1.915081995652994</v>
       </c>
       <c r="T6" t="n">
-        <v>1.973316553836666</v>
+        <v>1.973316553836667</v>
       </c>
       <c r="U6" t="n">
-        <v>1.956261408993859</v>
+        <v>1.956261408993857</v>
       </c>
       <c r="V6" t="n">
         <v>7.289415652423844</v>
       </c>
       <c r="W6" t="n">
-        <v>7.342223820945445</v>
+        <v>7.342223820945443</v>
       </c>
       <c r="X6" t="n">
         <v>1.91439762851586</v>
@@ -5310,7 +5310,7 @@
         <v>2.084584768315942</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.966630672515763</v>
+        <v>1.966630672515762</v>
       </c>
       <c r="AA6" t="n">
         <v>7.247903088999067</v>
@@ -5326,43 +5326,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01555183012444365</v>
+        <v>0.0155518301244437</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01912084263888912</v>
+        <v>0.01912084263888914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01891484685630654</v>
+        <v>0.01891484685630657</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0864048359737202</v>
+        <v>0.08640483597372021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03054251431678322</v>
+        <v>0.0305425143167832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04232423075830166</v>
+        <v>0.04232423075830172</v>
       </c>
       <c r="H7" t="n">
         <v>0.02569410924750657</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02165150610997311</v>
+        <v>0.02165150610997313</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05798295291174018</v>
+        <v>0.0579829529117402</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02326437631144259</v>
+        <v>0.02326437631144262</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01676614407156385</v>
+        <v>0.01676614407156387</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07261690556296564</v>
+        <v>0.07261690556296566</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05480362776105006</v>
+        <v>0.05480362776105011</v>
       </c>
       <c r="O7" t="n">
         <v>0.1625918508298181</v>
@@ -5371,40 +5371,40 @@
         <v>0.1119031905031064</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0704539453999454</v>
+        <v>0.07045394539994548</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02301618354817445</v>
+        <v>0.02301618354817449</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01759743888925476</v>
+        <v>0.0175974388892548</v>
       </c>
       <c r="T7" t="n">
         <v>0.07583199707292623</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0587693819007928</v>
+        <v>0.05876938190079279</v>
       </c>
       <c r="V7" t="n">
         <v>0.06558931294335388</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1178545240664611</v>
+        <v>0.117854524066461</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0169130717521196</v>
+        <v>0.01691307175211964</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1039574395056432</v>
+        <v>0.1039574395056433</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06914611575202466</v>
+        <v>0.06914611575202458</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02407674951857978</v>
+        <v>0.0240767495185798</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0559506973130612</v>
+        <v>0.05595069731306124</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01906282020042739</v>
+        <v>0.01906282020042745</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0284899591686708</v>
+        <v>0.02848995916867082</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02828396338608823</v>
+        <v>0.02828396338608827</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09265467297214393</v>
+        <v>0.09265467297214391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03496613202808026</v>
+        <v>0.03496613202808033</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05290806796989612</v>
+        <v>0.05290806796989617</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03506322577728825</v>
+        <v>0.03506322577728829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0310206226397548</v>
+        <v>0.03102062263975482</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06735206944152182</v>
+        <v>0.06735206944152196</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03263349284122432</v>
+        <v>0.03263349284122433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02613526060134556</v>
+        <v>0.02613526060134557</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08198602209275252</v>
+        <v>0.08198602209275251</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05963171624414409</v>
+        <v>0.05963171624414422</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1686679894817832</v>
+        <v>0.1686679894817834</v>
       </c>
       <c r="P8" t="n">
         <v>0.1176734352966952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07281367992436306</v>
+        <v>0.07281367992436311</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03238530007795615</v>
+        <v>0.03238530007795618</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02696655541903643</v>
+        <v>0.02696655541903648</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08520111360270784</v>
+        <v>0.08520111360270791</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06528101167901554</v>
+        <v>0.06528101167901557</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07335104617807635</v>
+        <v>0.07335104617807651</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1272247918790811</v>
+        <v>0.127224791879081</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01980971520209256</v>
+        <v>0.01980971520209257</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1191414345977346</v>
+        <v>0.1191414345977347</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.07254828812212713</v>
+        <v>0.07254828812212705</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03344586604836144</v>
+        <v>0.03344586604836149</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07143911676606039</v>
+        <v>0.07143911676606048</v>
       </c>
     </row>
     <row r="9">
@@ -5502,43 +5502,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03553677938442192</v>
+        <v>0.03553677938442198</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04621151549740334</v>
+        <v>0.04621151549740338</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04600551971482074</v>
+        <v>0.04600551971482079</v>
       </c>
       <c r="E9" t="n">
         <v>0.1118555397514797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0412525499522695</v>
+        <v>0.04125254995226951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06941490744163686</v>
+        <v>0.06941490744163689</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05278478210602073</v>
+        <v>0.05278478210602077</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04874217896848732</v>
+        <v>0.04874217896848736</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0850736257702544</v>
+        <v>0.0850736257702545</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0503550491699568</v>
+        <v>0.05035504916995685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04385681693007808</v>
+        <v>0.04385681693007813</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0997075784214799</v>
+        <v>0.09970757842147988</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08189430061956431</v>
+        <v>0.0818943006195644</v>
       </c>
       <c r="O9" t="n">
         <v>0.1920374925131789</v>
@@ -5547,13 +5547,13 @@
         <v>0.141860967040568</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09754462208328063</v>
+        <v>0.09754462208328064</v>
       </c>
       <c r="R9" t="n">
         <v>0.05010685640668869</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04468811174776899</v>
+        <v>0.04468811174776902</v>
       </c>
       <c r="T9" t="n">
         <v>0.1029226699314405</v>
@@ -5562,25 +5562,25 @@
         <v>0.08586752508863101</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1008798324184935</v>
+        <v>0.1008798324184936</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1449451969249752</v>
+        <v>0.1449451969249751</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0440037446106338</v>
+        <v>0.04400374461063384</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1310481123641575</v>
+        <v>0.1310481123641576</v>
       </c>
       <c r="Z9" t="n">
         <v>0.09195267066501242</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05116742237709399</v>
+        <v>0.05116742237709401</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08304137017157535</v>
+        <v>0.08304137017157547</v>
       </c>
     </row>
   </sheetData>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05201607054781601</v>
+        <v>0.05201607054781598</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04840047481821481</v>
+        <v>0.04840047481821482</v>
       </c>
       <c r="D2" t="n">
         <v>0.05210945655800222</v>
@@ -5758,37 +5758,37 @@
         <v>0.05408004584823455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05547992541265059</v>
+        <v>0.05547992541265061</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05436413987932377</v>
+        <v>0.05436413987932378</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05262224585738368</v>
+        <v>0.05262224585738366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05238355452013731</v>
+        <v>0.05238355452013729</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05483351395095377</v>
+        <v>0.05483351395095378</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05223501236869</v>
+        <v>0.05223501236868999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05209079911011588</v>
+        <v>0.05209079911011587</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05628853548812307</v>
+        <v>0.05628853548812308</v>
       </c>
       <c r="N2" t="n">
         <v>0.05489399039308927</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07542410873002332</v>
+        <v>0.07542410873002331</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06037873132797719</v>
+        <v>0.06037873132797721</v>
       </c>
       <c r="Q2" t="n">
         <v>0.05455580050608923</v>
@@ -5797,34 +5797,34 @@
         <v>0.05217518652540643</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05225983761424492</v>
+        <v>0.05225983761424493</v>
       </c>
       <c r="T2" t="n">
         <v>0.05607853771391703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196967063557352</v>
+        <v>0.2196967063557353</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05502748850177062</v>
+        <v>0.05502748850177064</v>
       </c>
       <c r="W2" t="n">
         <v>0.2403547298806271</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05589618719471574</v>
+        <v>0.05589618719471576</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05772242130740747</v>
+        <v>0.05772242130740746</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2004405355587046</v>
+        <v>0.2004405355587047</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05265529199044711</v>
+        <v>0.05265529199044712</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05603854726890285</v>
+        <v>0.05603854726890284</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02378236498110595</v>
+        <v>0.0238057264861832</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01984555136863831</v>
+        <v>0.01996245638770083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02445164468885918</v>
+        <v>0.02449899404107855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03850310900112749</v>
+        <v>0.03904571474508301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04851470740028552</v>
+        <v>0.04942234931774123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04038551932208617</v>
+        <v>0.04099629762732618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02813085262844803</v>
+        <v>0.0283095846834903</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02641179990188377</v>
+        <v>0.02652896162542163</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04377628898200519</v>
+        <v>0.04450888021669013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02534212826424304</v>
+        <v>0.02542125724237604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02431407293862639</v>
+        <v>0.02435634699895418</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05399628475527913</v>
+        <v>0.05510480040371266</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0442904704395698</v>
+        <v>0.04504176683995526</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1345140181565361</v>
+        <v>0.1378484330600574</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08318866633110422</v>
+        <v>0.08529875547574528</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04180431276981587</v>
+        <v>0.04247119313973814</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02492464903112021</v>
+        <v>0.02498891984885015</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02550737817364383</v>
+        <v>0.02559193090990541</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05273265816007162</v>
+        <v>0.05378857718538659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3200857276780248</v>
+        <v>0.3210136124341145</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0451243534929166</v>
+        <v>0.04590192826320238</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3652290547351937</v>
+        <v>0.3666619557947052</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05142358294517602</v>
+        <v>0.05243156526986533</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06451775587938732</v>
+        <v>0.06598176278520712</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2776559639665127</v>
+        <v>0.2780877260364092</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02834616442588825</v>
+        <v>0.02853091179465875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0523620675766577</v>
+        <v>0.05340106967844453</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008329677902196509</v>
+        <v>0.008329677902196644</v>
       </c>
       <c r="C4" t="n">
-        <v>0.012484152866916</v>
+        <v>0.01248415286691607</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009384515846937121</v>
+        <v>0.009384515846937124</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03164322839597131</v>
+        <v>0.03164322839597141</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04745551205246644</v>
+        <v>0.04745551205246654</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03485220116683537</v>
+        <v>0.03485220116683541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01517670687818297</v>
+        <v>0.01517670687818305</v>
       </c>
       <c r="I4" t="n">
         <v>0.01248057842054515</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04025574770687682</v>
+        <v>0.04025574770687679</v>
       </c>
       <c r="K4" t="n">
         <v>0.01080272648718202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00917377139021102</v>
+        <v>0.009173771390211038</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05640019423920069</v>
+        <v>0.05640019423920078</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04083710646309543</v>
+        <v>0.04083710646309535</v>
       </c>
       <c r="O4" t="n">
-        <v>0.158076801054362</v>
+        <v>0.1580768010543622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1027897784281396</v>
+        <v>0.1027897784281397</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03701709611439581</v>
+        <v>0.03701709611439593</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01012696606604675</v>
+        <v>0.01012696606604677</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01108313905590194</v>
+        <v>0.01108313905590206</v>
       </c>
       <c r="T4" t="n">
         <v>0.05421711337053459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04899463643584553</v>
+        <v>0.0489946364358456</v>
       </c>
       <c r="V4" t="n">
         <v>0.04302401858444906</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07149694690115004</v>
+        <v>0.07149694690115005</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05215738037077251</v>
+        <v>0.05215738037077253</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0728069427337774</v>
+        <v>0.07280694273377745</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02675866719744839</v>
+        <v>0.0267586671974485</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01554997815310662</v>
+        <v>0.01554997815310665</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05348378506281475</v>
+        <v>0.05348378506281477</v>
       </c>
     </row>
     <row r="5">
@@ -6010,73 +6010,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02106190890276051</v>
+        <v>0.02106190890276066</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09422021239720173</v>
+        <v>0.09422021239720221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04115865552352881</v>
+        <v>0.04115865552352879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4282438773126978</v>
+        <v>0.4282438773126975</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7185794993098752</v>
+        <v>0.7185794993098756</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4097624728573121</v>
+        <v>0.4097624728573124</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536593375015488</v>
+        <v>0.1536593375015492</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09794098382262365</v>
+        <v>0.09794098382262385</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5247909864320436</v>
+        <v>0.5247909864320438</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06333247604049401</v>
+        <v>0.06333247604049409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03514456629249633</v>
+        <v>0.03514456629249634</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7799466135381934</v>
+        <v>0.7799466135381929</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5795547819009172</v>
+        <v>0.5795547819009189</v>
       </c>
       <c r="O5" t="n">
-        <v>2.336926779494186</v>
+        <v>2.33692677949419</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54745767603802</v>
+        <v>1.547457676038023</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4744308848400539</v>
+        <v>0.4744308848400536</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0563040832025338</v>
+        <v>0.05630408320253386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06211007807045624</v>
+        <v>0.06211007807045601</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8099910697189066</v>
+        <v>0.8099910697189073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6231849737861639</v>
+        <v>0.6231849737861641</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5452871613139202</v>
+        <v>0.5452871613139215</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07505884354629</v>
+        <v>1.075058843546289</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7696069955402068</v>
+        <v>0.7696069955402067</v>
       </c>
       <c r="Y5" t="n">
         <v>1.165672479936287</v>
@@ -6085,10 +6085,10 @@
         <v>0.3058740058109601</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1496168683842615</v>
+        <v>0.1496168683842613</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8321730772903918</v>
+        <v>0.8321730772903911</v>
       </c>
     </row>
     <row r="6">
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741223459442617</v>
+        <v>6.741223459442622</v>
       </c>
       <c r="C6" t="n">
-        <v>1.783064888550909</v>
+        <v>1.783064888550911</v>
       </c>
       <c r="D6" t="n">
         <v>1.779965251530932</v>
@@ -6110,28 +6110,28 @@
         <v>1.802223964079968</v>
       </c>
       <c r="F6" t="n">
-        <v>6.780349293592886</v>
+        <v>6.780349293592893</v>
       </c>
       <c r="G6" t="n">
-        <v>6.76774598270726</v>
+        <v>6.767745982707264</v>
       </c>
       <c r="H6" t="n">
-        <v>6.748070488418601</v>
+        <v>6.748070488418604</v>
       </c>
       <c r="I6" t="n">
-        <v>6.745374359960961</v>
+        <v>6.74537435996097</v>
       </c>
       <c r="J6" t="n">
-        <v>6.773149529247298</v>
+        <v>6.773149529247299</v>
       </c>
       <c r="K6" t="n">
-        <v>6.743696508027599</v>
+        <v>6.743696508027607</v>
       </c>
       <c r="L6" t="n">
-        <v>1.779754507074205</v>
+        <v>1.779754507074207</v>
       </c>
       <c r="M6" t="n">
-        <v>6.789293975779618</v>
+        <v>6.789293975779627</v>
       </c>
       <c r="N6" t="n">
         <v>1.811439731898776</v>
@@ -6143,40 +6143,40 @@
         <v>1.771094869953725</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.769910877654814</v>
+        <v>6.769910877654817</v>
       </c>
       <c r="R6" t="n">
-        <v>1.780707701750041</v>
+        <v>1.780707701750042</v>
       </c>
       <c r="S6" t="n">
-        <v>6.743976920596321</v>
+        <v>6.743976920596326</v>
       </c>
       <c r="T6" t="n">
-        <v>1.824797849054529</v>
+        <v>1.82479784905453</v>
       </c>
       <c r="U6" t="n">
-        <v>1.819553964168887</v>
+        <v>1.819553964168888</v>
       </c>
       <c r="V6" t="n">
-        <v>1.813604754268444</v>
+        <v>1.813604754268445</v>
       </c>
       <c r="W6" t="n">
         <v>1.932379147242124</v>
       </c>
       <c r="X6" t="n">
-        <v>6.785051161911192</v>
+        <v>6.785051161911195</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.920966374289978</v>
+        <v>1.920966374289977</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.797339402881442</v>
+        <v>1.797339402881444</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.748443759693523</v>
+        <v>6.748443759693531</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.824192420256756</v>
+        <v>1.824192420256755</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01137793921111227</v>
+        <v>0.01137793921111237</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01553241417583168</v>
+        <v>0.0155324141758318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01243277715585278</v>
+        <v>0.01243277715585289</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03469148970488711</v>
+        <v>0.03469148970488712</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05050377336138215</v>
+        <v>0.0505037733613823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03790046247575102</v>
+        <v>0.03790046247575111</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01822496818709865</v>
+        <v>0.01822496818709879</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01552883972946081</v>
+        <v>0.01552883972946095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04330400901579253</v>
+        <v>0.04330400901579261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0138509877960977</v>
+        <v>0.01385098779609778</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0122220326991267</v>
+        <v>0.01222203269912675</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05944845554811647</v>
+        <v>0.05944845554811646</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0438853677720111</v>
+        <v>0.0438853677720112</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1611249582584399</v>
+        <v>0.1611249582584401</v>
       </c>
       <c r="P7" t="n">
         <v>0.1058379356322177</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04006535742331159</v>
+        <v>0.04006535742331169</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0131752273749624</v>
+        <v>0.01317522737496251</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0141314003648177</v>
+        <v>0.01413140036481778</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05726537467945025</v>
+        <v>0.05726537467945036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05200595901524861</v>
+        <v>0.05200595901524863</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04607227989336479</v>
+        <v>0.04607227989336481</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07454520821006569</v>
+        <v>0.07454520821006584</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05520564167968824</v>
+        <v>0.05520564167968826</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07583379609173903</v>
+        <v>0.07583379609173906</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02980692850636411</v>
+        <v>0.02980692850636423</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01859823946202227</v>
+        <v>0.01859823946202237</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05653204637173052</v>
+        <v>0.05653204637173055</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01395080040358909</v>
+        <v>0.01395080040358921</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02235879729959745</v>
+        <v>0.02235879729959751</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01925916027961856</v>
+        <v>0.01925916027961855</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03925299787225577</v>
+        <v>0.03925299787225579</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05373928355822559</v>
+        <v>0.05373928355822573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04560884108072199</v>
+        <v>0.04560884108072202</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02505135131086445</v>
+        <v>0.02505135131086447</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02235522285322658</v>
+        <v>0.02235522285322659</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05013039213955824</v>
+        <v>0.05013039213955822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02067737091986346</v>
+        <v>0.02067737091986345</v>
       </c>
       <c r="L8" t="n">
         <v>0.01904841582289245</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06627483867188323</v>
+        <v>0.06627483867188334</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04741455979906058</v>
+        <v>0.04741455979906069</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1655603511302615</v>
+        <v>0.1655603511302617</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1100512222989804</v>
+        <v>0.1100512222989805</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04180230447568237</v>
+        <v>0.0418023044756825</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02000161049872816</v>
+        <v>0.02000161049872817</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02095778348858337</v>
+        <v>0.02095778348858347</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06409175780321598</v>
+        <v>0.06409175780321603</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05675983033772103</v>
+        <v>0.05675983033772113</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05172292499633892</v>
+        <v>0.05172292499633887</v>
       </c>
       <c r="W8" t="n">
         <v>0.08137242726793811</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05733243246597647</v>
+        <v>0.05733243246597641</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0868689072253564</v>
+        <v>0.08686890722535641</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03230077834560998</v>
+        <v>0.03230077834561001</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02542462258578804</v>
+        <v>0.02542462258578808</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.06780158882198785</v>
+        <v>0.06780158882198775</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02433229799659851</v>
+        <v>0.02433229799659859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0332091932688464</v>
+        <v>0.03320919326884658</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0301095562488675</v>
+        <v>0.0301095562488676</v>
       </c>
       <c r="E9" t="n">
         <v>0.05127835045870568</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05729408985637127</v>
+        <v>0.05729408985637133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05557723767562413</v>
+        <v>0.05557723767562412</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03590174728011335</v>
+        <v>0.03590174728011355</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03320561882247551</v>
+        <v>0.03320561882247565</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0609807881088073</v>
+        <v>0.06098078810880734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03152776688911241</v>
+        <v>0.03152776688911255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02989881179214139</v>
+        <v>0.02989881179214151</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07712523464113126</v>
+        <v>0.07712523464113127</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06156214686502587</v>
+        <v>0.06156214686502599</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1803668401794024</v>
+        <v>0.1803668401794025</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1254201787712919</v>
+        <v>0.125420178771292</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05774213262318464</v>
+        <v>0.05774213262318466</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0308520064679771</v>
+        <v>0.03085200646797724</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03180817945783239</v>
+        <v>0.03180817945783253</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07494215377246498</v>
+        <v>0.07494215377246514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06969826888682183</v>
+        <v>0.06969826888682196</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06919861735326664</v>
+        <v>0.06919861735326666</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09222198730308045</v>
+        <v>0.09222198730308052</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07288242077270293</v>
+        <v>0.072882420772703</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09351057518475378</v>
+        <v>0.09351057518475379</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04463650654201436</v>
+        <v>0.04463650654201445</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03627501855503698</v>
+        <v>0.03627501855503715</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.07420882546474523</v>
+        <v>0.07420882546474533</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0495725829173753</v>
+        <v>0.04957258291737518</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0458059456737777</v>
+        <v>0.04580594567377769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04985954102733287</v>
+        <v>0.04985954102733281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04971814823926575</v>
+        <v>0.04971814823926564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05481944654007413</v>
+        <v>0.05481944654007399</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05063189714887711</v>
+        <v>0.05063189714887704</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05064934688268771</v>
+        <v>0.05064934688268763</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0502433504425474</v>
+        <v>0.0502433504425473</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05149135122217424</v>
+        <v>0.05149135122217428</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05048215686570202</v>
+        <v>0.0504821568657019</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05012071949388721</v>
+        <v>0.05012071949388715</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05323903276581288</v>
+        <v>0.05323903276581285</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0510973576835307</v>
+        <v>0.05109735768353061</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06664931125795397</v>
+        <v>0.0666493112579539</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05711570067244049</v>
+        <v>0.05711570067244045</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05069292818852594</v>
+        <v>0.0506929281885259</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04988374671285794</v>
+        <v>0.04988374671285786</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05227240222220509</v>
+        <v>0.05227240222220501</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05297132783443435</v>
+        <v>0.05297132783443427</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2158004262289118</v>
+        <v>0.2158004262289117</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05102716114239953</v>
+        <v>0.05102716114239944</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2329087091914709</v>
+        <v>0.2329087091914708</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05368947919086826</v>
+        <v>0.05368947919086822</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05346032766584276</v>
+        <v>0.05346032766584267</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1957603394782084</v>
+        <v>0.1957603394782083</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05051125258849831</v>
+        <v>0.05051125258849824</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0526653029278655</v>
+        <v>0.05266530292786541</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02183994369791935</v>
+        <v>0.02186197542183858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01681451204895624</v>
+        <v>0.01689154880738384</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02389040485545386</v>
+        <v>0.02398559347175754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0228752808311755</v>
+        <v>0.02293383327820575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05935717339001805</v>
+        <v>0.06071849849453406</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02934923323514677</v>
+        <v>0.02963627955848181</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02955657201457623</v>
+        <v>0.0298543058549884</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02663989276641874</v>
+        <v>0.02683289982299945</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03549360564852356</v>
+        <v>0.03600017881079354</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0283193582055876</v>
+        <v>0.0285722996407648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02572151394179111</v>
+        <v>0.02588157595552317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04783434923458572</v>
+        <v>0.0487852179010483</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03272029684623216</v>
+        <v>0.03312810517018458</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1037868208379645</v>
+        <v>0.1062768614710502</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07534974904887623</v>
+        <v>0.07725400343670534</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02981554649833821</v>
+        <v>0.03012159114469378</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02407190092640319</v>
+        <v>0.02417362262368459</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04099258311989001</v>
+        <v>0.04169178973892817</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04611324891084932</v>
+        <v>0.04699920053959705</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3137538760897829</v>
+        <v>0.3145861336523694</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03216165841421295</v>
+        <v>0.03254800532959037</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3352346563022569</v>
+        <v>0.3357526030708106</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05114410433675048</v>
+        <v>0.05221083934308632</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04961444636983085</v>
+        <v>0.0506180538387823</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2649567131401738</v>
+        <v>0.265062082691605</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02854293220207094</v>
+        <v>0.02880188769800917</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04382032125602408</v>
+        <v>0.04462134818705247</v>
       </c>
     </row>
     <row r="4">
@@ -6782,82 +6782,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005899592318055181</v>
+        <v>0.005899592318055185</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008337286068400859</v>
+        <v>0.008337286068400883</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009140916177278914</v>
+        <v>0.009140916177278942</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007543819592164892</v>
+        <v>0.00754381959216483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06516533061295433</v>
+        <v>0.06516533061295436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01786503387149086</v>
+        <v>0.01786503387149085</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01806213664215574</v>
+        <v>0.01806213664215571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01347622008318109</v>
+        <v>0.01347622008318111</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0276707395482473</v>
+        <v>0.02767073954824732</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01617364848909469</v>
+        <v>0.01617364848909468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01209104710504126</v>
+        <v>0.0120910471050413</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04704258746410074</v>
+        <v>0.04704258746410071</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02312262473282826</v>
+        <v>0.0231226247328283</v>
       </c>
       <c r="O4" t="n">
         <v>0.1175190851157763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09110257736712198</v>
+        <v>0.09110257736712199</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0185544075399897</v>
+        <v>0.01855440753998974</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009414330530450491</v>
+        <v>0.009414330530450501</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03639529334434862</v>
+        <v>0.03639529334434866</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04428997965614461</v>
+        <v>0.04428997965614466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04220931608786962</v>
+        <v>0.04220931608786964</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0229816287491993</v>
+        <v>0.02298162874919943</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02811921324725942</v>
+        <v>0.02811921324725938</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05240182959301219</v>
+        <v>0.05240182959301216</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04971740259012589</v>
+        <v>0.04971740259012596</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009659454042375226</v>
+        <v>0.009659454042375245</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01650229806277272</v>
+        <v>0.01650229806277275</v>
       </c>
       <c r="AB4" t="n">
         <v>0.04052925168363843</v>
@@ -6870,16 +6870,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01906465408416125</v>
+        <v>0.01906465408416127</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06292754748610259</v>
+        <v>0.06292754748610258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07765045385143407</v>
+        <v>0.07765045385143403</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04629555479501017</v>
+        <v>0.04629555479501004</v>
       </c>
       <c r="F5" t="n">
         <v>1.103605851857839</v>
@@ -6888,67 +6888,67 @@
         <v>0.2042176820430197</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2506123374572385</v>
+        <v>0.2506123374572383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.159624221794503</v>
+        <v>0.1596242217945031</v>
       </c>
       <c r="J5" t="n">
-        <v>0.381408771143069</v>
+        <v>0.3814087711430692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.19442480173765</v>
+        <v>0.1944248017376504</v>
       </c>
       <c r="L5" t="n">
         <v>0.1127608391675319</v>
       </c>
       <c r="M5" t="n">
-        <v>0.733346004883761</v>
+        <v>0.733346004883762</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3226250321204206</v>
+        <v>0.3226250321204211</v>
       </c>
       <c r="O5" t="n">
-        <v>1.756630499396842</v>
+        <v>1.756630499396844</v>
       </c>
       <c r="P5" t="n">
-        <v>1.357181349221783</v>
+        <v>1.357181349221785</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2323363134421488</v>
+        <v>0.2323363134421489</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08701494457917129</v>
+        <v>0.08701494457917137</v>
       </c>
       <c r="S5" t="n">
         <v>0.4982626884727439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7065055964589493</v>
+        <v>0.7065055964589504</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5809534666843355</v>
+        <v>0.5809534666843366</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2793815340061149</v>
+        <v>0.2793815340061148</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3977961457294576</v>
+        <v>0.3977961457294573</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8009392056750723</v>
+        <v>0.8009392056750712</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8099918377980853</v>
+        <v>0.8099918377980837</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07566381315875174</v>
+        <v>0.07566381315875197</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2084857687271795</v>
+        <v>0.2084857687271799</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6692064258295775</v>
+        <v>0.6692064258295758</v>
       </c>
     </row>
     <row r="6">
@@ -6958,82 +6958,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.736556832020069</v>
+        <v>6.736556832020078</v>
       </c>
       <c r="C6" t="n">
-        <v>6.738994525770412</v>
+        <v>6.738994525770416</v>
       </c>
       <c r="D6" t="n">
-        <v>6.739798155879302</v>
+        <v>6.739798155879297</v>
       </c>
       <c r="E6" t="n">
         <v>1.776906115653319</v>
       </c>
       <c r="F6" t="n">
-        <v>6.795822570314974</v>
+        <v>6.795822570314971</v>
       </c>
       <c r="G6" t="n">
-        <v>6.748522273573511</v>
+        <v>6.748522273573514</v>
       </c>
       <c r="H6" t="n">
-        <v>6.748719376344176</v>
+        <v>6.748719376344179</v>
       </c>
       <c r="I6" t="n">
-        <v>6.744133459785198</v>
+        <v>6.744133459785199</v>
       </c>
       <c r="J6" t="n">
-        <v>1.797033035609402</v>
+        <v>1.797033035609401</v>
       </c>
       <c r="K6" t="n">
-        <v>1.78553594455025</v>
+        <v>1.785535944550249</v>
       </c>
       <c r="L6" t="n">
-        <v>6.742748286807053</v>
+        <v>6.74274828680706</v>
       </c>
       <c r="M6" t="n">
-        <v>6.777699827166112</v>
+        <v>6.777699827166116</v>
       </c>
       <c r="N6" t="n">
-        <v>1.792576127169616</v>
+        <v>1.792576127169617</v>
       </c>
       <c r="O6" t="n">
         <v>1.886982536856932</v>
       </c>
       <c r="P6" t="n">
-        <v>6.822207921854284</v>
+        <v>6.822207921854293</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.749211647242013</v>
+        <v>6.749211647242016</v>
       </c>
       <c r="R6" t="n">
-        <v>6.740071570232469</v>
+        <v>6.740071570232472</v>
       </c>
       <c r="S6" t="n">
-        <v>6.767052533046372</v>
+        <v>6.767052533046375</v>
       </c>
       <c r="T6" t="n">
         <v>1.8136522757173</v>
       </c>
       <c r="U6" t="n">
-        <v>6.772962610902705</v>
+        <v>6.772962610902704</v>
       </c>
       <c r="V6" t="n">
-        <v>1.792343924810355</v>
+        <v>1.792343924810353</v>
       </c>
       <c r="W6" t="n">
-        <v>6.759225549487955</v>
+        <v>6.759225549487953</v>
       </c>
       <c r="X6" t="n">
-        <v>1.821764125654168</v>
+        <v>1.821764125654167</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.896769495909433</v>
+        <v>1.896769495909431</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.77902175010353</v>
+        <v>1.779021750103531</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.747159537764788</v>
+        <v>6.747159537764797</v>
       </c>
       <c r="AB6" t="n">
         <v>1.810080768173681</v>
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008077644538977774</v>
+        <v>0.008077644538977732</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01051533828932346</v>
+        <v>0.01051533828932342</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01131896839820152</v>
+        <v>0.01131896839820147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009721871813087488</v>
+        <v>0.00972187181308758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06734338283387692</v>
+        <v>0.067343382833877</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02004308609241346</v>
+        <v>0.02004308609241351</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02024018886307833</v>
+        <v>0.02024018886307836</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0156542723041037</v>
+        <v>0.01565427230410363</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02984879176916989</v>
+        <v>0.02984879176916993</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01835170071001729</v>
+        <v>0.01835170071001732</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01426909932596386</v>
+        <v>0.01426909932596382</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04922063968502334</v>
+        <v>0.04922063968502331</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02530067695375085</v>
+        <v>0.02530067695375088</v>
       </c>
       <c r="O7" t="n">
         <v>0.1196970647063857</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09328055695773137</v>
+        <v>0.09328055695773134</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02073245976091232</v>
+        <v>0.0207324597609123</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0115923827513731</v>
+        <v>0.01159238275137306</v>
       </c>
       <c r="S7" t="n">
         <v>0.03857334556527123</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04646803187706722</v>
+        <v>0.04646803187706731</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04445905881314499</v>
+        <v>0.04445905881314506</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02515968097012192</v>
+        <v>0.0251596809701221</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03029726546818199</v>
+        <v>0.03029726546818198</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05457988181393478</v>
+        <v>0.05457988181393473</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05199150992386178</v>
+        <v>0.0519915099238617</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01183750626329783</v>
+        <v>0.01183750626329778</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01868035028369533</v>
+        <v>0.0186803502836953</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04270730390456103</v>
+        <v>0.04270730390456099</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01003643786935889</v>
+        <v>0.01003643786935891</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01560759136385463</v>
+        <v>0.01560759136385468</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01641122147273269</v>
+        <v>0.01641122147273273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01314565000588897</v>
+        <v>0.013145650005889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06979033257043354</v>
+        <v>0.06979033257043353</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02578508245719797</v>
+        <v>0.025785082457198</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02533244193760952</v>
+        <v>0.02533244193760955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02074652537863485</v>
+        <v>0.0207465253786349</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03494104484370109</v>
+        <v>0.03494104484370111</v>
       </c>
       <c r="K8" t="n">
         <v>0.02344395378454843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01936135240049502</v>
+        <v>0.01936135240049501</v>
       </c>
       <c r="M8" t="n">
         <v>0.05431289275955593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02796397450918524</v>
+        <v>0.02796397450918523</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1230279329571122</v>
+        <v>0.1230279329571121</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09644780530392652</v>
+        <v>0.09644780530392649</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02207545673484479</v>
+        <v>0.0220754567348448</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01668463582590428</v>
+        <v>0.0166846358259043</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04366559863980242</v>
+        <v>0.04366559863980245</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0515602849515984</v>
+        <v>0.05156028495159844</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04802745092784483</v>
+        <v>0.04802745092784487</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0293747480659693</v>
+        <v>0.02937474806596927</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03539013435355165</v>
+        <v>0.03539013435355169</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05621006659737875</v>
+        <v>0.05621006659737877</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0601670854261112</v>
+        <v>0.0601670854261113</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01373809397052021</v>
+        <v>0.01373809397052024</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0237726033582265</v>
+        <v>0.02377260335822655</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05107271769402703</v>
+        <v>0.05107271769402708</v>
       </c>
     </row>
     <row r="9">
@@ -7222,43 +7222,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01575306537604177</v>
+        <v>0.0157530653760418</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02113557728956073</v>
+        <v>0.0211355772895607</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02193920739843879</v>
+        <v>0.02193920739843876</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01966245394341919</v>
+        <v>0.01966245394341922</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07117502048012017</v>
+        <v>0.07117502048012019</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03066331878803013</v>
+        <v>0.03066331878803011</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03086042786331561</v>
+        <v>0.03086042786331564</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02627451130434097</v>
+        <v>0.02627451130434091</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04046903076940717</v>
+        <v>0.04046903076940719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02897193971025452</v>
+        <v>0.02897193971025457</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02488933832620112</v>
+        <v>0.02488933832620113</v>
       </c>
       <c r="M9" t="n">
         <v>0.05984087868526058</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03592091595398812</v>
+        <v>0.03592091595398814</v>
       </c>
       <c r="O9" t="n">
         <v>0.131293276826338</v>
@@ -7267,40 +7267,40 @@
         <v>0.105089012061643</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03135269245652897</v>
+        <v>0.03135269245652902</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02221262175161035</v>
+        <v>0.02221262175161032</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04919358456550846</v>
+        <v>0.04919358456550851</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0570882708773045</v>
+        <v>0.05708827087730457</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05510366242184266</v>
+        <v>0.05510366242184269</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03917815991731408</v>
+        <v>0.03917815991731429</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04091750446841924</v>
+        <v>0.04091750446841922</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06520012081417199</v>
+        <v>0.06520012081417198</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.06261174892409904</v>
+        <v>0.062611748924099</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02068227927109499</v>
+        <v>0.02068227927109502</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02930058928393258</v>
+        <v>0.02930058928393256</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05332754290479823</v>
+        <v>0.05332754290479826</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05285523631409</v>
+        <v>0.05285523631408994</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04934554255016408</v>
+        <v>0.04934554255016409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05308105280135945</v>
+        <v>0.05308105280135943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05886649918666764</v>
+        <v>0.05886649918666758</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05402583911912792</v>
+        <v>0.05402583911912786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05376611024714319</v>
+        <v>0.05376611024714322</v>
       </c>
       <c r="H2" t="n">
         <v>0.05475272756706617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05366558709445874</v>
+        <v>0.0536655870944587</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05529998164979819</v>
+        <v>0.05529998164979813</v>
       </c>
       <c r="K2" t="n">
         <v>0.05391991983607718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05289080638599424</v>
+        <v>0.0528908063859941</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05444873848901606</v>
+        <v>0.05444873848901609</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0542288459520417</v>
+        <v>0.05422884595204169</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06641735925318507</v>
+        <v>0.06641735925318502</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05792468284676207</v>
+        <v>0.05792468284676209</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05452090987311228</v>
+        <v>0.05452090987311229</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0540718075083813</v>
+        <v>0.05407180750838129</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05291132033908907</v>
+        <v>0.05291132033908905</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05594904550600597</v>
+        <v>0.05594904550600596</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2208799047181116</v>
+        <v>0.2208799047181118</v>
       </c>
       <c r="V2" t="n">
         <v>0.05706261650994376</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2452061961098655</v>
+        <v>0.2452061961098656</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0530117844497769</v>
+        <v>0.05301178444977686</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05955495731133878</v>
+        <v>0.05955495731133884</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2061217388922285</v>
+        <v>0.2061217388922287</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05361177419819511</v>
+        <v>0.05361177419819516</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05355286702823783</v>
+        <v>0.05355286702823784</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02453923610725992</v>
+        <v>0.02457432323501766</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02075057386022074</v>
+        <v>0.02087721877732108</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02615992932382668</v>
+        <v>0.02625276721684229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06742841933493565</v>
+        <v>0.06897618356227644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03291820567378946</v>
+        <v>0.03325254861282548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03100627607230527</v>
+        <v>0.03126924735724781</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03815738287682453</v>
+        <v>0.03867817449422243</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03034475624844845</v>
+        <v>0.03058646547631715</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04193447960232249</v>
+        <v>0.04258370249600379</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03211639321038855</v>
+        <v>0.03242183165215932</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02479443899183331</v>
+        <v>0.02483864013910905</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0361121873017581</v>
+        <v>0.03656266268930287</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03435772784340608</v>
+        <v>0.03474045387425019</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0856944734127907</v>
+        <v>0.08750857671916161</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06060082343105517</v>
+        <v>0.06190085477922419</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03643057477760499</v>
+        <v>0.03688790175832167</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03326631051565952</v>
+        <v>0.03361206597561055</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02493726889360492</v>
+        <v>0.02498650257887644</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04668752323560132</v>
+        <v>0.04750917116127255</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3174869538277572</v>
+        <v>0.3182381299948341</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05439559457331066</v>
+        <v>0.05548443184491438</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3872530838484449</v>
+        <v>0.3893641273462554</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0256623823900843</v>
+        <v>0.02573756673742655</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07233231870844276</v>
+        <v>0.07405889396186986</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3011259462851049</v>
+        <v>0.3022433543747906</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02994155941015168</v>
+        <v>0.03016769863883635</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02981210889117729</v>
+        <v>0.03003551667167835</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01006212669030981</v>
+        <v>0.01006212669030959</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0141226655844483</v>
+        <v>0.01412266558444833</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0126128277947344</v>
+        <v>0.01261282779473431</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07796210615361712</v>
+        <v>0.07796210615361704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0232846238771079</v>
+        <v>0.02328462387710789</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02035086678685691</v>
+        <v>0.02035086678685692</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03149516328177768</v>
+        <v>0.03149516328177757</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01921541153435046</v>
+        <v>0.01921541153435048</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03778832799899322</v>
+        <v>0.03778832799899313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02208821684977286</v>
+        <v>0.02208821684977287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01046390701550926</v>
+        <v>0.01046390701550853</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02844641180022403</v>
+        <v>0.02844641180022407</v>
       </c>
       <c r="N4" t="n">
         <v>0.02557767944262649</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09052149500475647</v>
+        <v>0.09052149500475652</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06732385733746217</v>
+        <v>0.06732385733746206</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02887667578716028</v>
+        <v>0.02887667578716018</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02380385798022916</v>
+        <v>0.02380385798022918</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01069562155260007</v>
+        <v>0.01069562155260012</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04500812473554389</v>
+        <v>0.04500812473554387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04264087689400769</v>
+        <v>0.04264087689400763</v>
       </c>
       <c r="V4" t="n">
         <v>0.05833279052412488</v>
       </c>
       <c r="W4" t="n">
-        <v>0.103094175511035</v>
+        <v>0.1030941755110349</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0118304098985938</v>
+        <v>0.01183040989859361</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08614370723471838</v>
+        <v>0.0861437072347183</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05890264832065117</v>
+        <v>0.05890264832065112</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01860757011589797</v>
+        <v>0.01860757011589789</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01841853902448305</v>
+        <v>0.01841853902448302</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02999125868930641</v>
+        <v>0.02999125868930285</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1095847391342089</v>
+        <v>0.1095847391342091</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08324155376287758</v>
+        <v>0.08324155376287616</v>
       </c>
       <c r="E5" t="n">
-        <v>1.306329771737979</v>
+        <v>1.30632977173798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2935260339628765</v>
+        <v>0.2935260339628759</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2056691472340671</v>
+        <v>0.2056691472340663</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4773219362835541</v>
+        <v>0.4773219362835566</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2152995055445748</v>
+        <v>0.215299505544575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5227452635570833</v>
+        <v>0.5227452635570823</v>
       </c>
       <c r="K5" t="n">
         <v>0.2453986411281465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03833194088334203</v>
+        <v>0.03833194088333417</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3725376904529245</v>
+        <v>0.3725376904529246</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3316841556672353</v>
+        <v>0.3316841556672351</v>
       </c>
       <c r="O5" t="n">
         <v>1.377902435619591</v>
       </c>
       <c r="P5" t="n">
-        <v>1.046338681459238</v>
+        <v>1.046338681459237</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3875944194353328</v>
+        <v>0.3875944194353319</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3144812546413333</v>
+        <v>0.3144812546413353</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04072259478865129</v>
+        <v>0.04072259478865154</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7283520288023105</v>
+        <v>0.7283520288023088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6189821729346446</v>
+        <v>0.6189821729346435</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8337066815747206</v>
+        <v>0.8337066815747225</v>
       </c>
       <c r="W5" t="n">
-        <v>1.798139774508388</v>
+        <v>1.798139774508385</v>
       </c>
       <c r="X5" t="n">
-        <v>0.066681745493629</v>
+        <v>0.06668174549362778</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.447993413762017</v>
+        <v>1.447993413762016</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.881023233049618</v>
+        <v>0.8810232330496141</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1931664629098238</v>
+        <v>0.1931664629098232</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2074787115324276</v>
+        <v>0.2074787115324272</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.911612087209741</v>
+        <v>1.911612087209742</v>
       </c>
       <c r="C6" t="n">
-        <v>1.915672626103879</v>
+        <v>1.91567262610388</v>
       </c>
       <c r="D6" t="n">
-        <v>1.914162788314166</v>
+        <v>1.914162788314167</v>
       </c>
       <c r="E6" t="n">
-        <v>7.30474276573536</v>
+        <v>7.304742765735352</v>
       </c>
       <c r="F6" t="n">
-        <v>1.924834584396538</v>
+        <v>1.92483458439654</v>
       </c>
       <c r="G6" t="n">
-        <v>7.247131526368594</v>
+        <v>7.247131526368599</v>
       </c>
       <c r="H6" t="n">
-        <v>1.933045123801207</v>
+        <v>1.933045123801209</v>
       </c>
       <c r="I6" t="n">
-        <v>1.920765372053781</v>
+        <v>1.920765372053782</v>
       </c>
       <c r="J6" t="n">
-        <v>1.939338288518424</v>
+        <v>1.939338288518425</v>
       </c>
       <c r="K6" t="n">
-        <v>7.248868876431514</v>
+        <v>7.248868876431509</v>
       </c>
       <c r="L6" t="n">
-        <v>7.23724456659725</v>
+        <v>7.237244566597246</v>
       </c>
       <c r="M6" t="n">
-        <v>1.929996372319654</v>
+        <v>1.929996372319656</v>
       </c>
       <c r="N6" t="n">
-        <v>1.926930373488332</v>
+        <v>1.92693037348833</v>
       </c>
       <c r="O6" t="n">
-        <v>7.317761562389645</v>
+        <v>7.317761562389647</v>
       </c>
       <c r="P6" t="n">
-        <v>7.294562641746086</v>
+        <v>7.294562641746085</v>
       </c>
       <c r="Q6" t="n">
         <v>1.930426636306591</v>
       </c>
       <c r="R6" t="n">
-        <v>7.250584517561972</v>
+        <v>7.250584517561971</v>
       </c>
       <c r="S6" t="n">
         <v>1.912245582072032</v>
       </c>
       <c r="T6" t="n">
-        <v>1.946558085254973</v>
+        <v>1.946558085254975</v>
       </c>
       <c r="U6" t="n">
-        <v>7.269016386619187</v>
+        <v>7.269016386619188</v>
       </c>
       <c r="V6" t="n">
-        <v>1.959882751043557</v>
+        <v>1.959882751043558</v>
       </c>
       <c r="W6" t="n">
-        <v>2.101522069655668</v>
+        <v>2.101522069655669</v>
       </c>
       <c r="X6" t="n">
-        <v>7.238611069480338</v>
+        <v>7.238611069480331</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.070441319123577</v>
+        <v>2.070441319123579</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.285683307902394</v>
+        <v>7.28568330790239</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.245388229697635</v>
+        <v>7.245388229697631</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.919621304538864</v>
+        <v>1.919621304538865</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01359384548966817</v>
+        <v>0.01359384548966797</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01765438438380661</v>
+        <v>0.01765438438380666</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01614454659409278</v>
+        <v>0.01614454659409277</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0814938249529755</v>
+        <v>0.08149382495297547</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02681634267646623</v>
+        <v>0.02681634267646622</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02388258558621526</v>
+        <v>0.02388258558621525</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03502688208113598</v>
+        <v>0.03502688208113589</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02274713033370879</v>
+        <v>0.0227471303337088</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04132004679835156</v>
+        <v>0.04132004679835145</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02561993564913122</v>
+        <v>0.02561993564913118</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01399562581486764</v>
+        <v>0.0139956258148666</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03197813059958237</v>
+        <v>0.0319781305995824</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02910939824198485</v>
+        <v>0.02910939824198475</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0940530646899045</v>
+        <v>0.09405306468990449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0708554270226102</v>
+        <v>0.07085542702260994</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03240839458651862</v>
+        <v>0.03240839458651852</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02733557677958749</v>
+        <v>0.02733557677958751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01422734035195842</v>
+        <v>0.0142273403519584</v>
       </c>
       <c r="T7" t="n">
         <v>0.0485398435349022</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04578016576406359</v>
+        <v>0.04578016576406346</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0618645093234832</v>
+        <v>0.06186450932348316</v>
       </c>
       <c r="W7" t="n">
         <v>0.1066258943103933</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01536212869795211</v>
+        <v>0.01536212869795191</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0892702761775207</v>
+        <v>0.08927027617752065</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06243436712000949</v>
+        <v>0.0624343671200095</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02213928891525632</v>
+        <v>0.02213928891525625</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02195025782384135</v>
+        <v>0.02195025782384139</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0163511913530621</v>
+        <v>0.01635119135306181</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02516002090219721</v>
+        <v>0.02516002090219717</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02365018311248323</v>
+        <v>0.02365018311248318</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08647113676482102</v>
+        <v>0.08647113676482095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03031341672861498</v>
+        <v>0.03031341672861494</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03237281110359921</v>
+        <v>0.03237281110359935</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04253251859952648</v>
+        <v>0.04253251859952639</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03025276685209937</v>
+        <v>0.03025276685209932</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04882568331674202</v>
+        <v>0.04882568331674197</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03312557216752172</v>
+        <v>0.03312557216752168</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02150126233325806</v>
+        <v>0.02150126233325764</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03948376711797296</v>
+        <v>0.03948376711797295</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03293431512917285</v>
+        <v>0.03293431512917276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09888962440142479</v>
+        <v>0.09888962440142481</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07544404518505771</v>
+        <v>0.07544404518505768</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03423259296366615</v>
+        <v>0.03423259296366613</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03484121329797803</v>
+        <v>0.03484121329797801</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02173297687034895</v>
+        <v>0.02173297687034894</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05604548005329275</v>
+        <v>0.05604548005329272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0509654782481728</v>
+        <v>0.05096547824817274</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06808336654413527</v>
+        <v>0.06808336654413519</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1141324639967959</v>
+        <v>0.114132463996796</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0176215173442346</v>
+        <v>0.01762151734423445</v>
       </c>
       <c r="Y8" t="n">
         <v>0.101514091242683</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0651035110473069</v>
+        <v>0.06510351104730677</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02964492543364679</v>
+        <v>0.0296449254336467</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03441588097035357</v>
+        <v>0.03441588097035346</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02975542878369398</v>
+        <v>0.02975542878369373</v>
       </c>
       <c r="C9" t="n">
         <v>0.03958967758337489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.038079839793661</v>
+        <v>0.03807983979366104</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1020965774591772</v>
+        <v>0.1020965774591771</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0354416451696108</v>
+        <v>0.03544164516961074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04581788918913224</v>
+        <v>0.0458178891891322</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05696217528070419</v>
+        <v>0.0569621752807041</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04468242353327704</v>
+        <v>0.04468242353327701</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06325533999791973</v>
+        <v>0.06325533999791967</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04755522884869948</v>
+        <v>0.04755522884869946</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03593091901443593</v>
+        <v>0.03593091901443481</v>
       </c>
       <c r="M9" t="n">
         <v>0.05391342379915062</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05104469144155309</v>
+        <v>0.05104469144155308</v>
       </c>
       <c r="O9" t="n">
-        <v>0.117901920757358</v>
+        <v>0.1179019207573579</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09512041549028655</v>
+        <v>0.09512041549028635</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05434369818943559</v>
+        <v>0.05434369818943548</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04927086997915577</v>
+        <v>0.04927086997915572</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0361626335515267</v>
+        <v>0.03616263355152662</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07047513673447044</v>
+        <v>0.07047513673447039</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06770273903637816</v>
+        <v>0.06770273903637805</v>
       </c>
       <c r="V9" t="n">
         <v>0.09046255204882465</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1285611875099616</v>
+        <v>0.1285611875099615</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03729742189752042</v>
+        <v>0.03729742189752016</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1112055693770889</v>
+        <v>0.111205569377089</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.08088863079590776</v>
+        <v>0.0808886307959077</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04407458211482453</v>
+        <v>0.04407458211482446</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04388555102340962</v>
+        <v>0.04388555102340964</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05144005559020474</v>
+        <v>0.05144005559020459</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04775679134635797</v>
+        <v>0.04775679134635785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05150526485450799</v>
+        <v>0.05150526485450786</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05517165637071825</v>
+        <v>0.05517165637071818</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05535646192174701</v>
+        <v>0.05535646192174691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05232216010014567</v>
+        <v>0.05232216010014552</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05289453754970482</v>
+        <v>0.05289453754970467</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05171951205279779</v>
+        <v>0.05171951205279763</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05419920037611536</v>
+        <v>0.0541992003761153</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05203253830393963</v>
+        <v>0.0520325383039395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05152221026042199</v>
+        <v>0.05152221026042182</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0592795277127323</v>
+        <v>0.05927952771273224</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0532792423968277</v>
+        <v>0.05327924239682762</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07227810920974839</v>
+        <v>0.07227810920974838</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05769422280404934</v>
+        <v>0.05769422280404927</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05439499252099817</v>
+        <v>0.05439499252099805</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05187400636777565</v>
+        <v>0.05187400636777562</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05162870142709006</v>
+        <v>0.05162870142708995</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05520606080550635</v>
+        <v>0.05520606080550624</v>
       </c>
       <c r="U2" t="n">
         <v>0.2198700303989288</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05428732777596904</v>
+        <v>0.05428732777596887</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2402243948895542</v>
+        <v>0.2402243948895544</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05344177066018125</v>
+        <v>0.0534417706601811</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05657188251563847</v>
+        <v>0.05657188251563831</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008175000182143</v>
+        <v>0.2008175000182139</v>
       </c>
       <c r="AA2" t="n">
         <v>0.05210758870363116</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05353875954540251</v>
+        <v>0.05353875954540248</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02318456117096505</v>
+        <v>0.02320313306548036</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01894463160444192</v>
+        <v>0.01904770183164669</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02365261335814777</v>
+        <v>0.0236879339690591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04980849273654286</v>
+        <v>0.05076595053188798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05116610667335149</v>
+        <v>0.05218433210509488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0294354823392663</v>
+        <v>0.02967473352165524</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03362604194973977</v>
+        <v>0.03401674377669726</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02518729520785467</v>
+        <v>0.02527717762452939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04281150963723072</v>
+        <v>0.04352657355157075</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02739633055841284</v>
+        <v>0.02756531584148911</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02376992021293426</v>
+        <v>0.02380923922184464</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07867465512085724</v>
+        <v>0.08067809729568594</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0363297274592937</v>
+        <v>0.0368135100596636</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1214920197876797</v>
+        <v>0.1244452692042993</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06761428206674873</v>
+        <v>0.06919345288584172</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04419430056876654</v>
+        <v>0.04496148943456524</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02629683018640452</v>
+        <v>0.02642627311667881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02452283625247961</v>
+        <v>0.02458875828345012</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05012143126536841</v>
+        <v>0.05109714228332746</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3242160703804642</v>
+        <v>0.3252953776960188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04337416084715378</v>
+        <v>0.0441058286735715</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3672277120650355</v>
+        <v>0.3687350946332336</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03747299444862069</v>
+        <v>0.03799956823055874</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0597975021589257</v>
+        <v>0.06111163842077148</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2815274427413089</v>
+        <v>0.2820876056130632</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02795083349428487</v>
+        <v>0.02813788502388846</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03825694107144886</v>
+        <v>0.03881005044743736</v>
       </c>
     </row>
     <row r="4">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00757195402664915</v>
+        <v>0.007571954026649148</v>
       </c>
       <c r="C4" t="n">
         <v>0.01132708118345837</v>
@@ -8511,16 +8511,16 @@
         <v>0.008308522664698189</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0497221014637194</v>
+        <v>0.04972210146371943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05180956517734202</v>
+        <v>0.05180956517734201</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01753573025455489</v>
+        <v>0.01753573025455485</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02400099685396082</v>
+        <v>0.02400099685396087</v>
       </c>
       <c r="I4" t="n">
         <v>0.01072854332796197</v>
@@ -8529,13 +8529,13 @@
         <v>0.03884276757240334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01426431883379918</v>
+        <v>0.01426431883379917</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008499928819768859</v>
+        <v>0.008499928819768849</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09551556833470777</v>
+        <v>0.09551556833470766</v>
       </c>
       <c r="N4" t="n">
         <v>0.02834641507518754</v>
@@ -8544,43 +8544,43 @@
         <v>0.1402967739114681</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07821564976608548</v>
+        <v>0.0782156497660855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04094932599810805</v>
+        <v>0.04094932599810804</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01247362768653356</v>
+        <v>0.01247362768653355</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009702795535641641</v>
+        <v>0.009702795535641642</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05011071538147259</v>
+        <v>0.05011071538147264</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05536656606948934</v>
+        <v>0.05536656606948941</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04043437491002901</v>
+        <v>0.04043437491002898</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07429396413414426</v>
+        <v>0.07429396413414409</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0301822465764603</v>
+        <v>0.03018224657646038</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06566817327219747</v>
+        <v>0.06566817327219746</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0320116866161296</v>
+        <v>0.03201168661612955</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01511204762320492</v>
+        <v>0.01511204762320491</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03133476328700126</v>
+        <v>0.03133476328700129</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0165386349745628</v>
+        <v>0.01653863497456278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08251928774976128</v>
+        <v>0.08251928774976125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03093957829024527</v>
+        <v>0.03093957829024529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7575305709088763</v>
+        <v>0.7575305709088765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8144789027238138</v>
+        <v>0.8144789027238142</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1695984200096813</v>
+        <v>0.1695984200096809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3386061532128328</v>
+        <v>0.3386061532128333</v>
       </c>
       <c r="I5" t="n">
         <v>0.07663795067888518</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5340713522473962</v>
+        <v>0.5340713522473963</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1261931677570885</v>
+        <v>0.1261931677570882</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03244201932645036</v>
+        <v>0.03244201932645056</v>
       </c>
       <c r="M5" t="n">
-        <v>1.504127496251207</v>
+        <v>1.504127496251209</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.3937110344914032</v>
       </c>
       <c r="O5" t="n">
         <v>2.075909551700037</v>
       </c>
       <c r="P5" t="n">
-        <v>1.158932923769636</v>
+        <v>1.158932923769635</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5655219441467372</v>
+        <v>0.5655219441467377</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1110790974254618</v>
+        <v>0.1110790974254619</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0500286391702892</v>
+        <v>0.05002863917028941</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7993282347175844</v>
+        <v>0.7993282347175868</v>
       </c>
       <c r="U5" t="n">
-        <v>0.784784741110283</v>
+        <v>0.7847847411102847</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5179056603710153</v>
+        <v>0.5179056603710154</v>
       </c>
       <c r="W5" t="n">
-        <v>1.202950748848596</v>
+        <v>1.202950748848593</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4175236304310018</v>
+        <v>0.4175236304310023</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.034947406102086</v>
+        <v>1.034947406102085</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3955919447845408</v>
+        <v>0.3955919447845409</v>
       </c>
       <c r="AA5" t="n">
         <v>0.1509626954811442</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4694014990419106</v>
+        <v>0.4694014990419114</v>
       </c>
     </row>
     <row r="6">
@@ -8678,46 +8678,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.73994848687528</v>
+        <v>6.739948486875284</v>
       </c>
       <c r="C6" t="n">
-        <v>6.743703614032084</v>
+        <v>6.743703614032087</v>
       </c>
       <c r="D6" t="n">
-        <v>6.740685055513324</v>
+        <v>6.740685055513326</v>
       </c>
       <c r="E6" t="n">
         <v>1.820535400555243</v>
       </c>
       <c r="F6" t="n">
-        <v>1.822622864268866</v>
+        <v>1.822622864268865</v>
       </c>
       <c r="G6" t="n">
-        <v>1.788349029346079</v>
+        <v>1.788349029346078</v>
       </c>
       <c r="H6" t="n">
-        <v>1.794814295945486</v>
+        <v>1.794814295945485</v>
       </c>
       <c r="I6" t="n">
-        <v>6.743105076176594</v>
+        <v>6.743105076176589</v>
       </c>
       <c r="J6" t="n">
-        <v>6.771219300421031</v>
+        <v>6.771219300421037</v>
       </c>
       <c r="K6" t="n">
         <v>1.785077617925323</v>
       </c>
       <c r="L6" t="n">
-        <v>6.740876461668399</v>
+        <v>6.7408764616684</v>
       </c>
       <c r="M6" t="n">
-        <v>1.866328867426231</v>
+        <v>1.866328867426232</v>
       </c>
       <c r="N6" t="n">
-        <v>1.799084939102211</v>
+        <v>1.799084939102212</v>
       </c>
       <c r="O6" t="n">
-        <v>6.873150425815467</v>
+        <v>6.873150425815473</v>
       </c>
       <c r="P6" t="n">
         <v>1.746652239295573</v>
@@ -8726,7 +8726,7 @@
         <v>1.811762625089631</v>
       </c>
       <c r="R6" t="n">
-        <v>6.744850160535169</v>
+        <v>6.744850160535168</v>
       </c>
       <c r="S6" t="n">
         <v>1.780516094627166</v>
@@ -8735,28 +8735,28 @@
         <v>1.820924014472996</v>
       </c>
       <c r="U6" t="n">
-        <v>6.787613225552366</v>
+        <v>6.787613225552368</v>
       </c>
       <c r="V6" t="n">
-        <v>1.811247674001552</v>
+        <v>1.811247674001553</v>
       </c>
       <c r="W6" t="n">
-        <v>1.935325443275913</v>
+        <v>1.935325443275912</v>
       </c>
       <c r="X6" t="n">
-        <v>6.762558779425084</v>
+        <v>6.762558779425086</v>
       </c>
       <c r="Y6" t="n">
         <v>1.913871272404536</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.764388219464758</v>
+        <v>6.764388219464762</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.785925346714729</v>
+        <v>1.78592534671473</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.80205313014905</v>
+        <v>1.802053130149051</v>
       </c>
     </row>
     <row r="7">
@@ -8766,64 +8766,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01050536782937133</v>
+        <v>0.01050536782937134</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01426049498618055</v>
+        <v>0.01426049498618056</v>
       </c>
       <c r="D7" t="n">
         <v>0.01124193646742037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0526555152664416</v>
+        <v>0.05265551526644163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05474297898006418</v>
+        <v>0.0547429789800642</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02046914405727707</v>
+        <v>0.02046914405727703</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02693441065668306</v>
+        <v>0.02693441065668305</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01366195713068415</v>
+        <v>0.01366195713068416</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04177618137512551</v>
+        <v>0.04177618137512552</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01719773263652137</v>
+        <v>0.01719773263652135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01143334262249101</v>
+        <v>0.01143334262249103</v>
       </c>
       <c r="M7" t="n">
         <v>0.09844898213742999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03127982887790973</v>
+        <v>0.03127982887790971</v>
       </c>
       <c r="O7" t="n">
         <v>0.1432300847193841</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08114896057400132</v>
+        <v>0.0811489605740013</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04388273980083021</v>
+        <v>0.04388273980083019</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01540704148925574</v>
+        <v>0.01540704148925575</v>
       </c>
       <c r="S7" t="n">
         <v>0.01263620933836383</v>
       </c>
       <c r="T7" t="n">
-        <v>0.05304412918419481</v>
+        <v>0.05304412918419479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05816465586453253</v>
+        <v>0.05816465586453254</v>
       </c>
       <c r="V7" t="n">
         <v>0.04336778871275118</v>
@@ -8832,19 +8832,19 @@
         <v>0.07722737793686633</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03311566037918254</v>
+        <v>0.03311566037918258</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06847171370916559</v>
+        <v>0.06847171370916563</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03494510041885177</v>
+        <v>0.03494510041885174</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01804546142592712</v>
+        <v>0.01804546142592709</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03426817708972345</v>
+        <v>0.03426817708972348</v>
       </c>
     </row>
     <row r="8">
@@ -8857,79 +8857,79 @@
         <v>0.01305401176752504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02091454504575507</v>
+        <v>0.02091454504575505</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01789598652699487</v>
+        <v>0.01789598652699486</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05712355766931909</v>
+        <v>0.05712355766931915</v>
       </c>
       <c r="F8" t="n">
         <v>0.05793119721042903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02797447681995667</v>
+        <v>0.02797447681995662</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03358846071625753</v>
+        <v>0.03358846071625754</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02031600719025867</v>
+        <v>0.02031600719025865</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04843023143470005</v>
+        <v>0.04843023143470004</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02385178269609585</v>
+        <v>0.02385178269609584</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01808739268206553</v>
+        <v>0.01808739268206552</v>
       </c>
       <c r="M8" t="n">
         <v>0.1051030321970177</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03475150237254433</v>
+        <v>0.03475150237254436</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1475764059182934</v>
+        <v>0.1475764059182935</v>
       </c>
       <c r="P8" t="n">
         <v>0.08528090973293964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04562457773620658</v>
+        <v>0.04562457773620656</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02206109154883025</v>
+        <v>0.02206109154883024</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0192902593979383</v>
+        <v>0.01929025939793831</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05969817924376924</v>
+        <v>0.05969817924376928</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06281621833404498</v>
+        <v>0.06281621833404499</v>
       </c>
       <c r="V8" t="n">
-        <v>0.04889519833785647</v>
+        <v>0.04889519833785643</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08388223482113569</v>
+        <v>0.08388223482113559</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03523376693993795</v>
+        <v>0.03523376693993801</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07920058594538187</v>
+        <v>0.07920058594538192</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03741748433102702</v>
+        <v>0.03741748433102697</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02469951148550162</v>
+        <v>0.0246995114855016</v>
       </c>
       <c r="AB8" t="n">
         <v>0.0452106671267408</v>
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02106167765553527</v>
+        <v>0.02106167765553528</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0288182702668806</v>
+        <v>0.02881827026688061</v>
       </c>
       <c r="D9" t="n">
         <v>0.02579971174812044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06628975927099176</v>
+        <v>0.0662897592709918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06007630018616969</v>
+        <v>0.06007630018616972</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03502690715535365</v>
+        <v>0.03502690715535362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0414921859373831</v>
+        <v>0.04149218593738314</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02821973241138423</v>
+        <v>0.02821973241138424</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0563339566558256</v>
+        <v>0.05633395665582557</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03175550791722141</v>
+        <v>0.03175550791722143</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02599111790319107</v>
+        <v>0.0259911179031911</v>
       </c>
       <c r="M9" t="n">
         <v>0.1130067574181301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04583760415860978</v>
+        <v>0.0458376041586098</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1591140271871235</v>
+        <v>0.1591140271871236</v>
       </c>
       <c r="P9" t="n">
         <v>0.09732130190163316</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05844050289890683</v>
+        <v>0.05844050289890682</v>
       </c>
       <c r="R9" t="n">
         <v>0.0299648167699558</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02719398461906387</v>
+        <v>0.02719398461906391</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06760190446489484</v>
+        <v>0.06760190446489486</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07272788178715771</v>
+        <v>0.07272788178715774</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06254313652101691</v>
+        <v>0.06254313652101695</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09178515321756646</v>
+        <v>0.09178515321756645</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04767343565988257</v>
+        <v>0.04767343565988263</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08302948898986569</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04709034301707353</v>
+        <v>0.04709034301707354</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03260323670662718</v>
+        <v>0.03260323670662717</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0488259523704235</v>
+        <v>0.04882595237042354</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -586,64 +586,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05247843093836465</v>
+        <v>0.05247843093836468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0488976658139286</v>
+        <v>0.04889766581392863</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05290832245525297</v>
+        <v>0.05290832245525294</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05862799455872878</v>
+        <v>0.05862799455872879</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05332448259533213</v>
+        <v>0.05332448259533218</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05337695148040525</v>
+        <v>0.05337695148040527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05458490810743863</v>
+        <v>0.05458490810743864</v>
       </c>
       <c r="I2" t="n">
         <v>0.0530783463365679</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05478054349452838</v>
+        <v>0.05478054349452841</v>
       </c>
       <c r="K2" t="n">
         <v>0.05411629922016867</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05258201969309176</v>
+        <v>0.05258201969309177</v>
       </c>
       <c r="M2" t="n">
         <v>0.05420646017273223</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05364536673168173</v>
+        <v>0.0536453667316817</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05778875353578212</v>
+        <v>0.05778875353578211</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05711501058552008</v>
+        <v>0.05711501058552009</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05357620081717463</v>
+        <v>0.05357620081717465</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05370654195283429</v>
+        <v>0.05370654195283439</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05250278200967524</v>
+        <v>0.05250278200967518</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05550975131770131</v>
+        <v>0.05550975131770126</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2200282382281906</v>
+        <v>0.2200282382281903</v>
       </c>
       <c r="V2" t="n">
         <v>0.05608844293452292</v>
@@ -652,16 +652,16 @@
         <v>0.2429907599789073</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05249044896808426</v>
+        <v>0.0524904489680843</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05866876346113613</v>
+        <v>0.05866876346113614</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2053151623172736</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05295219429205801</v>
+        <v>0.05295219429205806</v>
       </c>
       <c r="AB2" t="n">
         <v>0.05282807424351593</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07721922148640405</v>
+        <v>0.07479581901467773</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07949448762471237</v>
+        <v>0.07311291485936069</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08730352022645205</v>
+        <v>0.07835489420330448</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1652703633730411</v>
+        <v>0.06952250322906517</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09711640951083797</v>
+        <v>0.08182996241107299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0979275892093146</v>
+        <v>0.08186033605563112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1267593402182689</v>
+        <v>0.09235192991918161</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09130179898381377</v>
+        <v>0.07977156944962593</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1304593569582727</v>
+        <v>0.09302761449309484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1154559135648951</v>
+        <v>0.08816807196144469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07963794083408908</v>
+        <v>0.07564531549593859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1184137906420773</v>
+        <v>0.08924321133771509</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1043972575631947</v>
+        <v>0.0842461285386094</v>
       </c>
       <c r="O3" t="n">
-        <v>0.131304929855114</v>
+        <v>0.09497145453103038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.183838868170516</v>
+        <v>0.1110691456543142</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1028293651801862</v>
+        <v>0.0837208424950688</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1060511922128048</v>
+        <v>0.08498368338122252</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07779083478030967</v>
+        <v>0.07499696587041743</v>
       </c>
       <c r="T3" t="n">
-        <v>0.148081874292026</v>
+        <v>0.09963231015286902</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3019088802073325</v>
+        <v>0.260231936480928</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1604583500993255</v>
+        <v>0.102948627436956</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4163193928433983</v>
+        <v>0.3122538804860946</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0775437319210423</v>
+        <v>0.07493851956032214</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2210052031102983</v>
+        <v>0.1244100523573837</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3185628086679121</v>
+        <v>0.255150550609981</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08824285364691598</v>
+        <v>0.0786302328300834</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08642674245463042</v>
+        <v>0.07809535292242918</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0405953923254596</v>
+        <v>0.04059539232545958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1056533349325082</v>
+        <v>0.1056533349325081</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1477118591037776</v>
+        <v>0.1477118591037777</v>
       </c>
       <c r="E4" t="n">
-        <v>1.437273080191894</v>
+        <v>1.437273080191895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2536362233869188</v>
+        <v>0.2536362233869182</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2358811183411141</v>
+        <v>0.235881118341114</v>
       </c>
       <c r="H4" t="n">
-        <v>0.574353043344811</v>
+        <v>0.5743530433448109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1907662620145822</v>
+        <v>0.1907662620145817</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5510159903412805</v>
+        <v>0.5510159903412806</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4343650127587314</v>
+        <v>0.4343650127587307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06579238806038261</v>
+        <v>0.0657923880603811</v>
       </c>
       <c r="M4" t="n">
-        <v>0.472719640417545</v>
+        <v>0.4727196404175451</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3152386798576733</v>
+        <v>0.3152386798576736</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4952225281822364</v>
+        <v>0.4952225281822359</v>
       </c>
       <c r="P4" t="n">
-        <v>1.034577154458529</v>
+        <v>1.034577154458528</v>
       </c>
       <c r="Q4" t="n">
         <v>0.3016072391868144</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3481520535303922</v>
+        <v>0.3481520535303924</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04662666314633756</v>
+        <v>0.04662666314633749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7760423406308412</v>
+        <v>0.7760423406308401</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6149056186984428</v>
+        <v>0.6149056186984416</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8078474497415614</v>
+        <v>0.8078474497415602</v>
       </c>
       <c r="W4" t="n">
-        <v>1.572612511365518</v>
+        <v>1.572612511365519</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04689059980322718</v>
+        <v>0.04689059980322625</v>
       </c>
       <c r="Y4" t="n">
         <v>1.457760720389631</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9111218783606418</v>
+        <v>0.9111218783606443</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1519353667698075</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1452424131421432</v>
+        <v>0.1452424131421431</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01681532400325891</v>
+        <v>0.01681532400325875</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0247726233637774</v>
+        <v>0.02477262336377728</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02668710265644897</v>
+        <v>0.02668710265644894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08862258152565296</v>
+        <v>0.08862258152565286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02715329402551675</v>
+        <v>0.02715329402551665</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03302057427102158</v>
+        <v>0.03302057427102147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04562490886539103</v>
+        <v>0.04562490886539095</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02860760061075115</v>
+        <v>0.02860760061075108</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04794312229385061</v>
+        <v>0.04794312229385054</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04033175591293819</v>
+        <v>0.0403317559129382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02300136285115145</v>
+        <v>0.02300136285115137</v>
       </c>
       <c r="M5" t="n">
         <v>0.04168532615057435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3152386798576733</v>
+        <v>0.03112415159967799</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04406017682104642</v>
+        <v>0.04406017682104629</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07112196934921643</v>
+        <v>0.07112196934921633</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02822938990686255</v>
+        <v>0.02822938990686249</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03570335908074099</v>
+        <v>0.03570335908074088</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0221063367658268</v>
+        <v>0.02210633676582675</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05607143837420428</v>
+        <v>0.0560714383742043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0485438849971386</v>
+        <v>0.04854388499713851</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06197531132525589</v>
+        <v>0.06197531132525588</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09744122914165275</v>
+        <v>0.09744122914165262</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01642504564922337</v>
+        <v>0.01642504564922324</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09676283738592506</v>
+        <v>0.09676283738592507</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.062050311499263</v>
+        <v>0.06205031149926295</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02718265523520408</v>
+        <v>0.02718265523520414</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03151778178576917</v>
+        <v>0.03151778178576909</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03259074285704551</v>
+        <v>0.03259074285704548</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04207806066883355</v>
+        <v>0.04207806066883343</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04399253996150513</v>
+        <v>0.043992539961505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1070880912154247</v>
+        <v>0.1070880912154246</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03360298859149354</v>
+        <v>0.0336029885914935</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04928593067343609</v>
+        <v>0.04928593067343594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06293034617044713</v>
+        <v>0.06293034617044711</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04591303791580734</v>
+        <v>0.04591303791580728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06524855959890678</v>
+        <v>0.06524855959890667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05763719321799435</v>
+        <v>0.05763719321799427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04030680015620765</v>
+        <v>0.04030680015620743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05899076345562911</v>
+        <v>0.05899076345562897</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3152386798576733</v>
+        <v>0.05231779412088673</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06635464792789189</v>
+        <v>0.06635464792789177</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09415015093924271</v>
+        <v>0.09415015093924253</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05153654359146981</v>
+        <v>0.05153654359146954</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05300879638579716</v>
+        <v>0.05300879638579703</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03941177407088297</v>
+        <v>0.03941177407088289</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07337687567926036</v>
+        <v>0.07337687567926025</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06828488652596712</v>
+        <v>0.06828488652596715</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08819164967917067</v>
+        <v>0.08819164967917056</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1147456806759832</v>
+        <v>0.1147456806759833</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03927246669263333</v>
+        <v>0.03927246669263322</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1090593710567394</v>
+        <v>0.1090593710567391</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.08051824243264098</v>
+        <v>0.08051824243264084</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04448809254026026</v>
+        <v>0.04448809254026017</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04358363340976687</v>
+        <v>0.04358363340976679</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05101045840617222</v>
+        <v>0.05101045840617231</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0473061682204448</v>
+        <v>0.04730616822044493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05124038199343624</v>
+        <v>0.05124038199343635</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05221474628063181</v>
+        <v>0.05221474628063189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0576563861009626</v>
+        <v>0.05765638610096264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05388539692852007</v>
+        <v>0.05388539692852016</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05263977800293992</v>
+        <v>0.05263977800294001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05201805757693784</v>
+        <v>0.05201805757693799</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05385563702544452</v>
+        <v>0.05385563702544451</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05494770179019148</v>
+        <v>0.05494770179019164</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05385368593077272</v>
+        <v>0.05385368593077283</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0557474926701066</v>
+        <v>0.05574749267010672</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05323619484509458</v>
+        <v>0.05323619484509465</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06947642127626157</v>
+        <v>0.0694764212762617</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05775514385919956</v>
+        <v>0.05775514385919954</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05266887579768268</v>
+        <v>0.05266887579768278</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05205287724951076</v>
+        <v>0.05205287724951079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0545696849119711</v>
+        <v>0.05456968491197121</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05576777123488166</v>
+        <v>0.05576777123488179</v>
       </c>
       <c r="U2" t="n">
         <v>0.2177373072734186</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05196513983085302</v>
+        <v>0.05196513983085309</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2365188706359171</v>
+        <v>0.2365188706359172</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05426968084837695</v>
+        <v>0.05426968084837702</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05365970182823694</v>
+        <v>0.05365970182823702</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1975425573947261</v>
+        <v>0.1975425573947265</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.051817051281043</v>
+        <v>0.05181705128104305</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05303277834841402</v>
+        <v>0.05303277834841411</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07294288862181696</v>
+        <v>0.07219364259750741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07516161851784353</v>
+        <v>0.07034047270947977</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07831851713670347</v>
+        <v>0.07404290858177554</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04597687827726978</v>
+        <v>0.02672597655324678</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2286094816830819</v>
+        <v>0.1257535599072874</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1391125263048522</v>
+        <v>0.0941458511611097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1112100647519299</v>
+        <v>0.08560797697802107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0965066205081859</v>
+        <v>0.08036430541311602</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1389035470978132</v>
+        <v>0.094477564244701</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1645600468500329</v>
+        <v>0.1026581852714896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1387013397313493</v>
+        <v>0.09412958526742939</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1832273572839931</v>
+        <v>0.1099997300754911</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1247266711717177</v>
+        <v>0.09017816883034871</v>
       </c>
       <c r="O3" t="n">
-        <v>0.321271819205117</v>
+        <v>0.1600654451759067</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2279074497177201</v>
+        <v>0.1239083445629329</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1115355640043757</v>
+        <v>0.08525922448570725</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0973737302880959</v>
+        <v>0.08074900864004936</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1550430938154919</v>
+        <v>0.0995377252292053</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1840604825460889</v>
+        <v>0.1108809330015805</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3156705630631305</v>
+        <v>0.2618213895158682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09493887936866048</v>
+        <v>0.07952056437228625</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3402851357884758</v>
+        <v>0.2834672071208117</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1488915549407362</v>
+        <v>0.09802522028244468</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1344852392523907</v>
+        <v>0.09351045393381917</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2338242617493594</v>
+        <v>0.2230081702242256</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09167137146165039</v>
+        <v>0.0786716519125886</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1202240788041491</v>
+        <v>0.08884253354150776</v>
       </c>
     </row>
     <row r="4">
@@ -1358,64 +1358,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01381885736551856</v>
+        <v>0.01381885736551852</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06648850274236807</v>
+        <v>0.06648850274236814</v>
       </c>
       <c r="D4" t="n">
         <v>0.06043387508031667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2352148542003215</v>
+        <v>0.2352148542003213</v>
       </c>
       <c r="F4" t="n">
         <v>1.368075505496996</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5185310271654648</v>
+        <v>0.5185310271654641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3649876358718899</v>
+        <v>0.3649876358718906</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2226279127864834</v>
+        <v>0.2226279127864829</v>
       </c>
       <c r="J4" t="n">
         <v>0.5507414007638544</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7308032487831158</v>
+        <v>0.7308032487831162</v>
       </c>
       <c r="L4" t="n">
-        <v>0.527862490380369</v>
+        <v>0.5278624903803691</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9609532539612012</v>
+        <v>0.9609532539611995</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4711140543954598</v>
+        <v>0.4711140543954594</v>
       </c>
       <c r="O4" t="n">
-        <v>1.851941138672742</v>
+        <v>1.851941138672741</v>
       </c>
       <c r="P4" t="n">
         <v>1.212898384854419</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3317279954001424</v>
+        <v>0.3317279954001422</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2367354571311504</v>
+        <v>0.2367354571311503</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6497506828681743</v>
+        <v>0.6497506828681736</v>
       </c>
       <c r="T4" t="n">
         <v>1.007404808842252</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6227326043481701</v>
+        <v>0.6227326043481691</v>
       </c>
       <c r="V4" t="n">
         <v>0.1844908886611975</v>
@@ -1424,19 +1424,19 @@
         <v>0.7485058697349485</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6489458269116721</v>
+        <v>0.6489458269116727</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5521571889830461</v>
+        <v>0.5521571889830459</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1253601688308272</v>
+        <v>0.1253601688308276</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1769085759380697</v>
+        <v>0.17690857593807</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4496464945099781</v>
+        <v>0.449646494509978</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01134120235337647</v>
+        <v>0.01134120235337643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0183899500736943</v>
+        <v>0.01838995007369432</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01799242592684771</v>
+        <v>0.01799242592684772</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0268396136744279</v>
+        <v>0.02683961367442794</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08704159915354132</v>
+        <v>0.08704159915354118</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04870973683449482</v>
+        <v>0.04870973683449478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.033799247608161</v>
+        <v>0.03379924760816102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02677662939094137</v>
+        <v>0.02677662939094135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04761877234949294</v>
+        <v>0.0476187723494929</v>
       </c>
       <c r="K5" t="n">
         <v>0.05986830848256341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04751089607826854</v>
+        <v>0.04751089607826861</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06862160849906582</v>
+        <v>0.0686216084990658</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4711140543954598</v>
+        <v>0.03739342052692862</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1312012110722148</v>
+        <v>0.1312012110722149</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08908895578024305</v>
+        <v>0.08908895578024302</v>
       </c>
       <c r="Q5" t="n">
         <v>0.029277060451551</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0271699336104926</v>
+        <v>0.02716993361049263</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0555984339467083</v>
+        <v>0.05559843394670825</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06913137011092123</v>
+        <v>0.06913137011092128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05222532323795506</v>
+        <v>0.05222532323795503</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02560821233970856</v>
+        <v>0.0256082123397085</v>
       </c>
       <c r="W5" t="n">
         <v>0.05704665078663605</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04773045905410356</v>
+        <v>0.04773045905410352</v>
       </c>
       <c r="Y5" t="n">
         <v>0.04929833016509001</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01862715749045721</v>
+        <v>0.01862715749045715</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02450617081134437</v>
+        <v>0.02450617081134438</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04248747065515863</v>
+        <v>0.04248747065515857</v>
       </c>
     </row>
     <row r="6">
@@ -1534,43 +1534,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01940714043607668</v>
+        <v>0.01940714043607667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02639701206142929</v>
+        <v>0.02639701206142926</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02599948791458269</v>
+        <v>0.02599948791458268</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03608328935439348</v>
+        <v>0.03608328935439346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08926105804545265</v>
+        <v>0.08926105804545252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05587614459731879</v>
+        <v>0.05587614459731876</v>
       </c>
       <c r="H6" t="n">
-        <v>0.041806309595896</v>
+        <v>0.04180630959589594</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03478369137867633</v>
+        <v>0.0347836913786763</v>
       </c>
       <c r="J6" t="n">
         <v>0.05562583433722789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06787537047029839</v>
+        <v>0.06787537047029833</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05551795806600355</v>
+        <v>0.05551795806600357</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0766286704867857</v>
+        <v>0.07662867048678564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4711140543954598</v>
+        <v>0.04854311219333483</v>
       </c>
       <c r="O6" t="n">
         <v>0.1428112979972561</v>
@@ -1579,40 +1579,40 @@
         <v>0.1011986891469659</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04213497879714188</v>
+        <v>0.04213497879714185</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0351769955982276</v>
+        <v>0.03517699559822759</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06360549593444324</v>
+        <v>0.06360549593444319</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07713843209865621</v>
+        <v>0.07713843209865623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06224175743145813</v>
+        <v>0.06224175743145809</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03936750604870342</v>
+        <v>0.03936750604870336</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06505291602646804</v>
+        <v>0.06505291602646798</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06021681202746008</v>
+        <v>0.06021681202746006</v>
       </c>
       <c r="Y6" t="n">
         <v>0.05332681839076592</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02835487305956024</v>
+        <v>0.02835487305956022</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03251323279907936</v>
+        <v>0.03251323279907932</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04625965393696242</v>
+        <v>0.04625965393696236</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05230576440450132</v>
+        <v>0.05230576440450124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04896556330623313</v>
+        <v>0.04896556330623315</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05240992019875994</v>
+        <v>0.05240992019875989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05792409886938536</v>
+        <v>0.05792409886938524</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05319409355419891</v>
+        <v>0.05319409355419884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05304782053717547</v>
+        <v>0.05304782053717535</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05447462810846709</v>
+        <v>0.05447462810846707</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05317159413674233</v>
+        <v>0.05317159413674225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05438515393324154</v>
+        <v>0.05438515393324145</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0536283323814454</v>
+        <v>0.05362833238144531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05235328494830092</v>
+        <v>0.05235328494830085</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05343898439644616</v>
+        <v>0.05343898439644613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05319698488936452</v>
+        <v>0.0531969848893644</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06402786277469433</v>
+        <v>0.06402786277469429</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05658288924070595</v>
+        <v>0.05658288924070581</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05451781654421281</v>
+        <v>0.05451781654421276</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0539944941599227</v>
+        <v>0.05399449415992262</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05235774216839514</v>
+        <v>0.0523577421683951</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05505572169615713</v>
+        <v>0.05505572169615704</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196072760032522</v>
+        <v>0.2196072760032521</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0564065338939411</v>
+        <v>0.05640653389394099</v>
       </c>
       <c r="W2" t="n">
-        <v>0.242199576461823</v>
+        <v>0.2421995764618227</v>
       </c>
       <c r="X2" t="n">
         <v>0.05239050758248791</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.058651051789976</v>
+        <v>0.0586510517899759</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2050397011808698</v>
+        <v>0.2050397011808699</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0530708543065041</v>
+        <v>0.05307085430650397</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05268737558977458</v>
+        <v>0.05268737558977457</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07582924081833661</v>
+        <v>0.07428817029922997</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0834023511710721</v>
+        <v>0.07440651463046546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07828982969543445</v>
+        <v>0.07516655383127592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.15141967171201</v>
+        <v>0.06456316535200921</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09668479478089224</v>
+        <v>0.08157848184687458</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09292819391746496</v>
+        <v>0.08009945717559816</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1268038892159578</v>
+        <v>0.09230096971888793</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09610968141569526</v>
+        <v>0.08142095751162585</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1239075140548233</v>
+        <v>0.09067377968818285</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1066597592535756</v>
+        <v>0.08479453609182351</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0769414998273636</v>
+        <v>0.07467874260633366</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1031813595059065</v>
+        <v>0.08384909779408682</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09658033695035555</v>
+        <v>0.08149725968649069</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2216858719834116</v>
+        <v>0.1267477665720551</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1741800746243439</v>
+        <v>0.1077141508788136</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1273742609572553</v>
+        <v>0.0921748313940671</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1154295019290097</v>
+        <v>0.088247432775027</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07703477458748849</v>
+        <v>0.07469993822174188</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1400932570002583</v>
+        <v>0.0967519126903056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2968881238591021</v>
+        <v>0.2583960584221127</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1703252218772072</v>
+        <v>0.1058336031154615</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4038593056773255</v>
+        <v>0.3078186458583651</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07783258643219387</v>
+        <v>0.07500047701321644</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2231744915635587</v>
+        <v>0.1249181592833051</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3153343216766405</v>
+        <v>0.2539133884097307</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09360172161740085</v>
+        <v>0.08042857608706527</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08571530094667693</v>
+        <v>0.07780837365947704</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02725832682068659</v>
+        <v>0.02725832682068681</v>
       </c>
       <c r="C4" t="n">
         <v>0.134634375794182</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05276550386670113</v>
+        <v>0.05276550386669927</v>
       </c>
       <c r="E4" t="n">
-        <v>1.220437869739907</v>
+        <v>1.220437869739912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.230303112104242</v>
+        <v>0.2303031121042427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.177031951948881</v>
+        <v>0.1770319519488805</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5385076600569649</v>
+        <v>0.538507660056965</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2272208548482061</v>
+        <v>0.2272208548482066</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4541977130832601</v>
+        <v>0.4541977130832602</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3045014638219368</v>
+        <v>0.3045014638219372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03816823042406829</v>
+        <v>0.03816823042409548</v>
       </c>
       <c r="M4" t="n">
         <v>0.2950428495478353</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2235747660128173</v>
+        <v>0.2235747660128166</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19098380390412</v>
+        <v>1.190983803904124</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8857867753098483</v>
+        <v>0.8857867753098451</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5139736427226985</v>
+        <v>0.5139736427226974</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4206564749386446</v>
+        <v>0.4206564749386437</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03808098628571582</v>
+        <v>0.03808098628571581</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6486628604952752</v>
+        <v>0.6486628604952741</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5329748304653931</v>
+        <v>0.5329748304653926</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8140837112994332</v>
+        <v>0.8140837112994318</v>
       </c>
       <c r="W4" t="n">
-        <v>1.363899469095701</v>
+        <v>1.363899469095702</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04783643068868811</v>
+        <v>0.04783643068868817</v>
       </c>
       <c r="Y4" t="n">
         <v>1.374675481085584</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.822199935541634</v>
+        <v>0.8221999355416364</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1923202404714384</v>
+        <v>0.1923202404714388</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1304145591547357</v>
+        <v>0.1304145591547362</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01547971820063666</v>
+        <v>0.0154797182006365</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02543864147703359</v>
+        <v>0.02543864147703363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02110334321786649</v>
+        <v>0.02110334321786645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08102055846465187</v>
+        <v>0.08102055846465211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02620661663043132</v>
+        <v>0.02620661663043134</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02923086390011673</v>
+        <v>0.02923086390011674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04442516887057284</v>
+        <v>0.04442516887057283</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02970680073469963</v>
+        <v>0.02970680073469964</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04352699949283391</v>
+        <v>0.0435269994928339</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03486586931859443</v>
+        <v>0.03486586931859448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02046362201042901</v>
+        <v>0.02046362201042978</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03311940226588871</v>
+        <v>0.03311940226588869</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2235747660128173</v>
+        <v>0.02654632548365628</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08631845230522314</v>
+        <v>0.08631845230522306</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06550679772968593</v>
+        <v>0.06550679772968579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03959190071343961</v>
+        <v>0.03959190071343974</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03900183504923502</v>
+        <v>0.03900183504923506</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02051396836181595</v>
+        <v>0.02051396836181598</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05098888825978899</v>
+        <v>0.05098888825978904</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04520010869226438</v>
+        <v>0.04520010869226442</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06580227388042884</v>
+        <v>0.06580227388042889</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09022236651831791</v>
+        <v>0.09022236651831787</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01597055635576397</v>
+        <v>0.01597055635576409</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09605102145154409</v>
+        <v>0.09605102145154402</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.059842993912304</v>
+        <v>0.05984299391230413</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02856889800954707</v>
+        <v>0.02856889800954715</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02935559197596456</v>
+        <v>0.02935559197596455</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02804180959485834</v>
+        <v>0.02804180959485843</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03896332799256509</v>
+        <v>0.03896332799256507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03462802973339787</v>
+        <v>0.03462802973339794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09566467795321421</v>
+        <v>0.09566467795321436</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03101470553872767</v>
+        <v>0.03101470553872766</v>
       </c>
       <c r="G6" t="n">
         <v>0.04183341750080902</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05794985538610427</v>
+        <v>0.05794985538610425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04323148725023115</v>
+        <v>0.04323148725023116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05705168600836542</v>
+        <v>0.05705168600836539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04839055583412596</v>
+        <v>0.04839055583412599</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03398830852596051</v>
+        <v>0.0339883085259605</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04664408878141831</v>
+        <v>0.04664408878141825</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2235747660128173</v>
+        <v>0.04351828748142215</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1041358646576282</v>
+        <v>0.104135864657628</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08394632554507671</v>
+        <v>0.08394632554507662</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05843769863186909</v>
+        <v>0.05843769863186905</v>
       </c>
       <c r="R6" t="n">
         <v>0.05252652156476659</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03403865487734741</v>
+        <v>0.03403865487734742</v>
       </c>
       <c r="T6" t="n">
         <v>0.06451357477532048</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06087811689600704</v>
+        <v>0.06087811689600708</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08676611372605675</v>
+        <v>0.08676611372605676</v>
       </c>
       <c r="W6" t="n">
         <v>0.1037461790512158</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03440875530236082</v>
+        <v>0.03440875530236118</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1051244821185612</v>
+        <v>0.1051244821185611</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.07463584200179946</v>
+        <v>0.07463584200179944</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04209358452507861</v>
+        <v>0.04209358452507863</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03823487161301709</v>
+        <v>0.03823487161301708</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05104623505724652</v>
+        <v>0.0510462350572466</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04743170785351843</v>
+        <v>0.0474317078535185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05108792843960023</v>
+        <v>0.05108792843960031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05402455334535601</v>
+        <v>0.05402455334535607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05449114739057599</v>
+        <v>0.05449114739057603</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05151388060432718</v>
+        <v>0.05151388060432726</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05298408314552197</v>
+        <v>0.05298408314552198</v>
       </c>
       <c r="I2" t="n">
-        <v>0.051478805742748</v>
+        <v>0.05147880574274805</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05253953157436855</v>
+        <v>0.05253953157436864</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05106312771699079</v>
+        <v>0.05106312771699085</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091687981853241</v>
+        <v>0.05091687981853244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05187939947752037</v>
+        <v>0.05187939947752036</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05167788316386051</v>
+        <v>0.05167788316386055</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0659179306260565</v>
+        <v>0.0659179306260566</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05480682152970029</v>
+        <v>0.05480682152970034</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05521530985741263</v>
+        <v>0.05521530985741271</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05244454949954774</v>
+        <v>0.05244454949954781</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05095951986796593</v>
+        <v>0.05095951986796596</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0546484437448273</v>
+        <v>0.05464844374482738</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2171369908740652</v>
+        <v>0.2171369908740654</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05399173999074443</v>
+        <v>0.05399173999074453</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2389454631694079</v>
+        <v>0.2389454631694082</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05112010561143612</v>
+        <v>0.05112010561143619</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05551332622583102</v>
+        <v>0.05551332622583111</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2008988278507526</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05167147323924703</v>
+        <v>0.05167147323924709</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05122274192705087</v>
+        <v>0.05122274192705088</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07700733920576264</v>
+        <v>0.07381285054348233</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07921666244637485</v>
+        <v>0.07203170956013222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07804415724311196</v>
+        <v>0.07421688837946805</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09127251210162925</v>
+        <v>0.04288971060894576</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1577983076519907</v>
+        <v>0.1018526639584898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08778145084624867</v>
+        <v>0.0774517120850742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1226132117182435</v>
+        <v>0.09001237056858814</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08719411852448948</v>
+        <v>0.0774295434726142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1115961400817108</v>
+        <v>0.08557724566136804</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07745326489632678</v>
+        <v>0.07396580293278711</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07403768887751624</v>
+        <v>0.07281237419474204</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09715157786460706</v>
+        <v>0.08089308677315125</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0917469082597252</v>
+        <v>0.07896255895231259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2727171016492141</v>
+        <v>0.1433773729042478</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1634587144488948</v>
+        <v>0.1030670170635976</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1741254571912559</v>
+        <v>0.1072517980763148</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1098477747053297</v>
+        <v>0.08542724289167283</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07501711114630177</v>
+        <v>0.07313958227112217</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1612184496390146</v>
+        <v>0.1032971701895373</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2842122628278191</v>
+        <v>0.2527005893936106</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1448687271265848</v>
+        <v>0.09634149582995237</v>
       </c>
       <c r="W3" t="n">
-        <v>0.375342036364806</v>
+        <v>0.2966235528672166</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07878909786682212</v>
+        <v>0.07446711820347335</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1807701104214832</v>
+        <v>0.1095214697987172</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2761027124361281</v>
+        <v>0.2385347305420804</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0915547957566578</v>
+        <v>0.07886274599150885</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08189087196434371</v>
+        <v>0.0756086215525253</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04496506333546786</v>
+        <v>0.0449650633354719</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09814148354347658</v>
+        <v>0.09814148354347661</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0580031240866705</v>
+        <v>0.05800312408667296</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6404039019205607</v>
+        <v>0.6404039019205603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7656634488128377</v>
+        <v>0.7656634488128385</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1316827389446931</v>
+        <v>0.1316827389446934</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4791836444850541</v>
+        <v>0.4791836444850553</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1419231617850396</v>
+        <v>0.1419231617850405</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3315560950233141</v>
+        <v>0.3315560950233142</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04947557768329455</v>
+        <v>0.04947557768329422</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02137523664997364</v>
+        <v>0.02137523664997242</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2326938971281435</v>
+        <v>0.2326938971281431</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1777972287123821</v>
+        <v>0.1777972287123825</v>
       </c>
       <c r="O4" t="n">
         <v>1.497269763462614</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7420638567696373</v>
+        <v>0.7420638567696385</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8844356774642327</v>
+        <v>0.8844356774642328</v>
       </c>
       <c r="R4" t="n">
-        <v>0.353292236865743</v>
+        <v>0.3532922368657423</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02897441687411777</v>
+        <v>0.02897441687411861</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8101702701087095</v>
+        <v>0.8101702701087123</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4029869754383247</v>
+        <v>0.4029869754383255</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5652436917128041</v>
+        <v>0.5652436917128034</v>
       </c>
       <c r="W4" t="n">
-        <v>1.046494534117901</v>
+        <v>1.046494534117898</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06395423277672184</v>
+        <v>0.0639542327767242</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.936682096582943</v>
+        <v>0.9366820965829457</v>
       </c>
       <c r="Z4" t="n">
         <v>0.4398183893075685</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1732748393626937</v>
+        <v>0.173274839362694</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09773763619582901</v>
+        <v>0.09773763619582922</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01378778502828126</v>
+        <v>0.01378778502828158</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02019450751935039</v>
+        <v>0.02019450751935049</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01774354834382961</v>
+        <v>0.01774354834382987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04905851510947768</v>
+        <v>0.04905851510947781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05324254839072694</v>
+        <v>0.05324254839072711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02327747357727962</v>
+        <v>0.02327747357727963</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03916148802147497</v>
+        <v>0.03916148802147502</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02215868729532678</v>
+        <v>0.02215868729532688</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03424768332779132</v>
+        <v>0.03424768332779139</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01746341277305996</v>
+        <v>0.01746341277306001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01581147548261488</v>
+        <v>0.01581147548261511</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02696263643494877</v>
+        <v>0.02696263643494892</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1777972287123821</v>
+        <v>0.02170604187718768</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1082089400259781</v>
+        <v>0.1082089400259782</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05760921856997325</v>
+        <v>0.05760921856997345</v>
       </c>
       <c r="Q5" t="n">
         <v>0.06019455661422071</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03306720729245734</v>
+        <v>0.03306720729245739</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01629311445635836</v>
+        <v>0.01629311445635851</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05796120663433216</v>
+        <v>0.05796120663433235</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03654748235415413</v>
+        <v>0.03654748235415424</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05031207908111897</v>
+        <v>0.05031207908111911</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07346032595230224</v>
+        <v>0.07346032595230226</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01425673120287704</v>
+        <v>0.01425673120287719</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07119904745720841</v>
+        <v>0.07119904745720863</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03897202796851153</v>
+        <v>0.03897202796851166</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02433495529971053</v>
+        <v>0.02433495529971064</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02325441333014047</v>
+        <v>0.02325441333014049</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02240619893313669</v>
+        <v>0.02240619893313707</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02922834313363009</v>
+        <v>0.02922834313363016</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02677738395810933</v>
+        <v>0.02677738395810951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0590477586696747</v>
+        <v>0.05904775866967481</v>
       </c>
       <c r="F6" t="n">
         <v>0.05622718390764279</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03158871579505979</v>
+        <v>0.03158871579505997</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04819532363575466</v>
+        <v>0.04819532363575468</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03119252290960655</v>
+        <v>0.03119252290960656</v>
       </c>
       <c r="J6" t="n">
-        <v>0.043281518942071</v>
+        <v>0.04328151894207109</v>
       </c>
       <c r="K6" t="n">
         <v>0.0264972483873397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02484531109689484</v>
+        <v>0.02484531109689481</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03599647204922312</v>
+        <v>0.03599647204922322</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1777972287123821</v>
+        <v>0.03344119396121027</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1204942892594774</v>
+        <v>0.1204942892594775</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07035763899641533</v>
+        <v>0.07035763899641546</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07339806195024157</v>
+        <v>0.07339806195024165</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0421010429067371</v>
+        <v>0.04210104290673708</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02532695007063806</v>
+        <v>0.0253269500706382</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06699504224861197</v>
+        <v>0.06699504224861208</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04728003585948804</v>
+        <v>0.04728003585948806</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06479676844763002</v>
+        <v>0.06479676844763022</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08249347670582219</v>
+        <v>0.0824934767058223</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02714083991622618</v>
+        <v>0.02714083991622615</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.07676428773714687</v>
+        <v>0.07676428773714709</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04920391834438562</v>
+        <v>0.04920391834438573</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03336879091399025</v>
+        <v>0.03336879091399034</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02864806579857791</v>
+        <v>0.028648065798578</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04934018498054481</v>
+        <v>0.04934018498054468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04548133966150088</v>
+        <v>0.04548133966150082</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04990737021542397</v>
+        <v>0.0499073702154239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05005741331310273</v>
+        <v>0.05005741331310266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05430311111966976</v>
+        <v>0.05430311111966965</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04979122983576258</v>
+        <v>0.04979122983576249</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05110246139033985</v>
+        <v>0.05110246139033977</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05173418337068881</v>
+        <v>0.05173418337068868</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05065326127654899</v>
+        <v>0.05065326127654889</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05115343002782567</v>
+        <v>0.05115343002782556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05091753770488419</v>
+        <v>0.05091753770488407</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05137169661301522</v>
+        <v>0.05137169661301529</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04969576800240507</v>
+        <v>0.04969576800240498</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05963831087621437</v>
+        <v>0.05963831087621427</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05199599145735109</v>
+        <v>0.05199599145735095</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05424912180568774</v>
+        <v>0.05424912180568767</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05123987606366982</v>
+        <v>0.05123987606366975</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05081304729419103</v>
+        <v>0.05081304729419099</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05329119132761098</v>
+        <v>0.0532911913276109</v>
       </c>
       <c r="U2" t="n">
         <v>0.2133775794532431</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04998314245609585</v>
+        <v>0.04998314245609574</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2348917361953768</v>
+        <v>0.2348917361953769</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04982363514680769</v>
+        <v>0.04982363514680757</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05023624151764032</v>
+        <v>0.05023624151764021</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1959733264791282</v>
+        <v>0.1959733264791279</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04993036868846026</v>
+        <v>0.04993036868846017</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04934835397608787</v>
+        <v>0.04934835397608782</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07768605712946818</v>
+        <v>0.07280815074295997</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07445855301905163</v>
+        <v>0.06918673061359315</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09101376803454911</v>
+        <v>0.07743848852180188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03962100005393891</v>
+        <v>0.02374521357761604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1940713603012179</v>
+        <v>0.1130941257243644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08807285803809202</v>
+        <v>0.0762720945792663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1192253589232928</v>
+        <v>0.08765189733570226</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1337611175218255</v>
+        <v>0.09239578681190644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1082453917933169</v>
+        <v>0.08326824338893986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1199698734687182</v>
+        <v>0.08697536228006106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1142332180353434</v>
+        <v>0.08523754135761404</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1252803747199554</v>
+        <v>0.0892648856136322</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08603382265022616</v>
+        <v>0.07578938164735204</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2149589302303508</v>
+        <v>0.1215438079961427</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1386998208419247</v>
+        <v>0.09320722048037321</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1920095142838376</v>
+        <v>0.1118248558067928</v>
       </c>
       <c r="R3" t="n">
-        <v>0.122320465600913</v>
+        <v>0.08862971698470416</v>
       </c>
       <c r="S3" t="n">
-        <v>0.111696187160674</v>
+        <v>0.08427494637515927</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1700869507017279</v>
+        <v>0.1052222333421574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2570202346753827</v>
+        <v>0.2415484346563398</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09250200525268554</v>
+        <v>0.07769533414094038</v>
       </c>
       <c r="W3" t="n">
-        <v>0.342945765248988</v>
+        <v>0.2836248633573013</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08904575246516397</v>
+        <v>0.07675901278846459</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09856430375615768</v>
+        <v>0.08011399239681212</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2341071514376004</v>
+        <v>0.2222873096145086</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09144510871193295</v>
+        <v>0.07763934198225883</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.078403791263912</v>
+        <v>0.07318177214082978</v>
       </c>
     </row>
     <row r="4">
@@ -3146,43 +3146,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06157372873287875</v>
+        <v>0.06157372873287925</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07086072603703301</v>
+        <v>0.07086072603703329</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1811289775066867</v>
+        <v>0.1811289775066872</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1973417857229485</v>
+        <v>0.1973417857229483</v>
       </c>
       <c r="F4" t="n">
-        <v>1.092387659433047</v>
+        <v>1.092387659433048</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1421040704365018</v>
+        <v>0.1421040704365009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4639763221475695</v>
+        <v>0.4639763221475698</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5694510430293896</v>
+        <v>0.5694510430293894</v>
       </c>
       <c r="J4" t="n">
         <v>0.3212231131587298</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4009771850922157</v>
+        <v>0.4009771850922153</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3643555414158214</v>
+        <v>0.3643555414158209</v>
       </c>
       <c r="M4" t="n">
         <v>0.4820050187820999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1418759121484608</v>
+        <v>0.1418759121484601</v>
       </c>
       <c r="O4" t="n">
         <v>1.083716017082199</v>
@@ -3194,37 +3194,37 @@
         <v>1.025780796979891</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4833371366290503</v>
+        <v>0.4833371366290504</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3349913963330063</v>
+        <v>0.3349913963330054</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9059160681444347</v>
+        <v>0.9059160681444346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1909695939662134</v>
+        <v>0.1909695939662127</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1735351176632623</v>
+        <v>0.1735351176632625</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7893963201739133</v>
+        <v>0.7893963201739131</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1637595852306495</v>
+        <v>0.1637595852306505</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2500890794448275</v>
+        <v>0.2500890794448274</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1324913586643736</v>
+        <v>0.1324913586643728</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1870368815846624</v>
+        <v>0.1870368815846623</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07886180222333171</v>
+        <v>0.07886180222333158</v>
       </c>
     </row>
     <row r="5">
@@ -3234,61 +3234,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01177224130797985</v>
+        <v>0.01177224130797987</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01499712486342326</v>
+        <v>0.01499712486342324</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0211283069505958</v>
+        <v>0.02112830695059587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02125261897444074</v>
+        <v>0.02125261897444056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06829026455668626</v>
+        <v>0.06829026455668621</v>
       </c>
       <c r="G5" t="n">
         <v>0.02042803508700117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03462741154037256</v>
+        <v>0.03462741154037247</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04176300191488296</v>
+        <v>0.04176300191488291</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0296480942631482</v>
+        <v>0.0296480942631483</v>
       </c>
       <c r="K5" t="n">
         <v>0.0352031257475063</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03253861344405239</v>
+        <v>0.03253861344405231</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03763534395849583</v>
+        <v>0.03763534395849576</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1418759121484608</v>
+        <v>0.01645184736979946</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07828902059622035</v>
+        <v>0.07828902059622032</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04290821739183474</v>
+        <v>0.04290821739183467</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06664130722087108</v>
+        <v>0.06664130722087092</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03617957348950752</v>
+        <v>0.03617957348950741</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03135834618731025</v>
+        <v>0.03135834618731017</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05935012304736589</v>
+        <v>0.05935012304736587</v>
       </c>
       <c r="U5" t="n">
         <v>0.02104650685738218</v>
@@ -3297,22 +3297,22 @@
         <v>0.02177403644657567</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05525891129259784</v>
+        <v>0.05525891129259754</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01692372230505107</v>
+        <v>0.0169237223050511</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0277220471909853</v>
+        <v>0.02772204719098527</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01674102838409875</v>
+        <v>0.01674102838409859</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02138808528336099</v>
+        <v>0.02138808528336097</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01810605069697829</v>
+        <v>0.01810605069697808</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01693293570529763</v>
+        <v>0.01693293570529743</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01991934511306228</v>
+        <v>0.01991934511306222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02605052720023494</v>
+        <v>0.02605052720023486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02711965172875655</v>
+        <v>0.02711965172875647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06945290886765909</v>
+        <v>0.06945290886765906</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02473866858524637</v>
+        <v>0.02473866858524632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03954963179001158</v>
+        <v>0.03954963179001155</v>
       </c>
       <c r="I6" t="n">
         <v>0.04668522216452194</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03457031451278732</v>
+        <v>0.03457031451278734</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04012534599714531</v>
+        <v>0.04012534599714534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03746083369369142</v>
+        <v>0.03746083369369131</v>
       </c>
       <c r="M6" t="n">
         <v>0.04255756420812296</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1418759121484608</v>
+        <v>0.02366038286235894</v>
       </c>
       <c r="O6" t="n">
         <v>0.0857676703621473</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05073626793850166</v>
+        <v>0.05073626793850156</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07509260911717472</v>
+        <v>0.07509260911717455</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04110179373914657</v>
+        <v>0.04110179373914646</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03628056643694922</v>
+        <v>0.03628056643694919</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06427234329700492</v>
+        <v>0.06427234329700486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02743963394962334</v>
+        <v>0.02743963394962331</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0306653299021745</v>
+        <v>0.03066532990217448</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06018055189621311</v>
+        <v>0.06018055189621304</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02510470108017896</v>
+        <v>0.02510470108017893</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02976527984704172</v>
+        <v>0.02976527984704166</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02303300793018999</v>
+        <v>0.02303300793018986</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02631030553300003</v>
+        <v>0.02631030553299997</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01994732641223951</v>
+        <v>0.01994732641223941</v>
       </c>
     </row>
   </sheetData>
@@ -3566,85 +3566,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05461387539358899</v>
+        <v>0.05461387539358905</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05089850950633485</v>
+        <v>0.05089850950633484</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05491160711280151</v>
+        <v>0.05491160711280157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06088657307094902</v>
+        <v>0.0608865730709491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0559410178173749</v>
+        <v>0.055941017817375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05698406665450173</v>
+        <v>0.05698406665450177</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05551178296907999</v>
+        <v>0.05551178296908008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05515388668779538</v>
+        <v>0.05515388668779544</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05836096857683355</v>
+        <v>0.05836096857683359</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05529667593216653</v>
+        <v>0.05529667593216655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05472137999673721</v>
+        <v>0.05472137999673725</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05966166827010844</v>
+        <v>0.05966166827010849</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05808888194999558</v>
+        <v>0.05808888194999559</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07834697445995603</v>
+        <v>0.07834697445995607</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06314398363361408</v>
+        <v>0.06314398363361415</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0594744224775531</v>
+        <v>0.05947442247755315</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05527470314285392</v>
+        <v>0.05527470314285396</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05479497547810925</v>
+        <v>0.05479497547810927</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05995054754569194</v>
+        <v>0.059950547545692</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2236383541501464</v>
+        <v>0.2236383541501465</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05898107277762748</v>
+        <v>0.05898107277762749</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2478375437361286</v>
+        <v>0.2478375437361283</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05473438767241054</v>
+        <v>0.05473438767241053</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06244052514519881</v>
+        <v>0.06244052514519887</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2083010079203376</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05536859626170623</v>
+        <v>0.05536859626170628</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0581785414156564</v>
+        <v>0.05817854141565641</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07833470878053574</v>
+        <v>0.0764108156030216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08170091497329858</v>
+        <v>0.07494581769781226</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08531973263210207</v>
+        <v>0.07886038067621605</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1688617609223047</v>
+        <v>0.07167723577378253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1094705473899594</v>
+        <v>0.08719922848941815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328662922209316</v>
+        <v>0.09434456809863442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09947112136063774</v>
+        <v>0.08389095579565467</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09100040941309702</v>
+        <v>0.08085589245927111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1649509363119434</v>
+        <v>0.1054873274382038</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09426267050783321</v>
+        <v>0.08179356104933613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08083576507695606</v>
+        <v>0.07725746828270785</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1964743204416356</v>
+        <v>0.1162107369766142</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1591461874953632</v>
+        <v>0.1041251127648936</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3882831229955631</v>
+        <v>0.186488369777365</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2744501076104357</v>
+        <v>0.1428183075164256</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1914764715105139</v>
+        <v>0.1149639539722985</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0938614786360091</v>
+        <v>0.08190144191000327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08251366235627129</v>
+        <v>0.07776764932372858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2029093396684298</v>
+        <v>0.1190869593393993</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3320382696122789</v>
+        <v>0.2716087400764932</v>
       </c>
       <c r="V3" t="n">
-        <v>0.178962172652831</v>
+        <v>0.1099480649891628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4725887079496212</v>
+        <v>0.3331228997873912</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08117801466015238</v>
+        <v>0.07741317404670799</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2600712113679677</v>
+        <v>0.1388004871695108</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.336541593524626</v>
+        <v>0.2616718815584749</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09586986181168458</v>
+        <v>0.08246739275906211</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1618843951555285</v>
+        <v>0.1056814910776656</v>
       </c>
     </row>
     <row r="4">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03346326432199945</v>
+        <v>0.03346326432199948</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1037619962702293</v>
+        <v>0.1037619962702294</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1019733338655024</v>
+        <v>0.1019733338655026</v>
       </c>
       <c r="E4" t="n">
-        <v>1.364657189723323</v>
+        <v>1.364657189723322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3293024953227215</v>
+        <v>0.3293024953227219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4660759414700795</v>
+        <v>0.4660759414700791</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2467369102879716</v>
+        <v>0.2467369102879714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1578881164218009</v>
+        <v>0.157888116421801</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7698070245076436</v>
+        <v>0.7698070245076433</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1735526462219273</v>
+        <v>0.1735526462219276</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0554694108393252</v>
+        <v>0.05546941083932523</v>
       </c>
       <c r="M4" t="n">
         <v>1.067838526337109</v>
@@ -3784,34 +3784,34 @@
         <v>2.47321522242051</v>
       </c>
       <c r="P4" t="n">
-        <v>1.727022846142502</v>
+        <v>1.727022846142507</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.048336971996211</v>
+        <v>1.048336971996207</v>
       </c>
       <c r="R4" t="n">
         <v>0.1894133113454376</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06551526750957258</v>
+        <v>0.06551526750957276</v>
       </c>
       <c r="T4" t="n">
         <v>1.172504815740471</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8076111423314885</v>
+        <v>0.8076111423314905</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8671098035863541</v>
+        <v>0.8671098035863543</v>
       </c>
       <c r="W4" t="n">
-        <v>1.977437439206566</v>
+        <v>1.977437439206568</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06196107789316041</v>
+        <v>0.06196107789316067</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.691048651218506</v>
+        <v>1.691048651218504</v>
       </c>
       <c r="Z4" t="n">
         <v>0.9298877105478708</v>
@@ -3820,7 +3820,7 @@
         <v>0.1962377427843338</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8465494075480429</v>
+        <v>0.8465494075480426</v>
       </c>
     </row>
     <row r="5">
@@ -3830,82 +3830,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0190628202004274</v>
+        <v>0.01906282020042745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02848995916867082</v>
+        <v>0.02848995916867081</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02828396338608829</v>
+        <v>0.02828396338608824</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09265467297214387</v>
+        <v>0.09265467297214386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03496613202808029</v>
+        <v>0.03496613202808033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05290806796989616</v>
+        <v>0.05290806796989615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0350632257772883</v>
+        <v>0.03506322577728827</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03102062263975484</v>
+        <v>0.03102062263975481</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0673520694415219</v>
+        <v>0.06735206944152194</v>
       </c>
       <c r="K5" t="n">
         <v>0.03263349284122435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02613526060134558</v>
+        <v>0.02613526060134555</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0819860220927526</v>
+        <v>0.08198602209275253</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7702123175005281</v>
+        <v>0.05963171624414421</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1686679894817833</v>
+        <v>0.1686679894817834</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1176734352966952</v>
+        <v>0.1176734352966953</v>
       </c>
       <c r="Q5" t="n">
         <v>0.07281367992436302</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03238530007795616</v>
+        <v>0.03238530007795617</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0269665554190365</v>
+        <v>0.02696655541903648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08520111360270785</v>
+        <v>0.08520111360270788</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06528101167901562</v>
+        <v>0.06528101167901554</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0733510461780764</v>
+        <v>0.07335104617807643</v>
       </c>
       <c r="W5" t="n">
-        <v>0.127224791879081</v>
+        <v>0.1272247918790811</v>
       </c>
       <c r="X5" t="n">
         <v>0.01980971520209255</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1191414345977349</v>
+        <v>0.1191414345977346</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0725482881221271</v>
+        <v>0.07254828812212712</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03344586604836159</v>
+        <v>0.03344586604836148</v>
       </c>
       <c r="AB5" t="n">
         <v>0.07143911676606055</v>
@@ -3918,43 +3918,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03553677938442205</v>
+        <v>0.03553677938442198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04621151549740332</v>
+        <v>0.04621151549740337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04600551971482075</v>
+        <v>0.0460055197148208</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1118555397514798</v>
+        <v>0.1118555397514797</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04125254995226951</v>
+        <v>0.04125254995226953</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06941490744163684</v>
+        <v>0.06941490744163693</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05278478210602076</v>
+        <v>0.05278478210602082</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0487421789684873</v>
+        <v>0.04874217896848733</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08507362577025443</v>
+        <v>0.08507362577025449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05035504916995691</v>
+        <v>0.05035504916995688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04385681693007808</v>
+        <v>0.04385681693007811</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09970757842147991</v>
+        <v>0.09970757842147987</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7702123175005281</v>
+        <v>0.08189430061956438</v>
       </c>
       <c r="O6" t="n">
         <v>0.1920374925131789</v>
@@ -3963,13 +3963,13 @@
         <v>0.141860967040568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09754462208328055</v>
+        <v>0.09754462208328067</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05010685640668869</v>
+        <v>0.05010685640668872</v>
       </c>
       <c r="S6" t="n">
-        <v>0.044688111747769</v>
+        <v>0.04468811174776906</v>
       </c>
       <c r="T6" t="n">
         <v>0.1029226699314405</v>
@@ -3981,22 +3981,22 @@
         <v>0.1008798324184936</v>
       </c>
       <c r="W6" t="n">
-        <v>0.144945196924975</v>
+        <v>0.1449451969249752</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0440037446106338</v>
+        <v>0.04400374461063386</v>
       </c>
       <c r="Y6" t="n">
         <v>0.1310481123641575</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.09195267066501228</v>
+        <v>0.09195267066501249</v>
       </c>
       <c r="AA6" t="n">
         <v>0.05116742237709402</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.08304137017157542</v>
+        <v>0.08304137017157541</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05201607054781596</v>
+        <v>0.05201607054781594</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04840047481821481</v>
+        <v>0.04840047481821474</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05210945655800225</v>
+        <v>0.05210945655800223</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05408004584823452</v>
+        <v>0.05408004584823447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05547992541265061</v>
+        <v>0.05547992541265056</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05436413987932378</v>
+        <v>0.05436413987932372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05262224585738371</v>
+        <v>0.05262224585738364</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05238355452013729</v>
+        <v>0.05238355452013727</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05483351395095377</v>
+        <v>0.05483351395095378</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05223501236869</v>
+        <v>0.05223501236868994</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0520907991101159</v>
+        <v>0.05209079911011587</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05628853548812306</v>
+        <v>0.0562885354881231</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05489399039308923</v>
+        <v>0.05489399039308925</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0754241087300233</v>
+        <v>0.07542410873002334</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06037873132797721</v>
+        <v>0.06037873132797718</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05455580050608921</v>
+        <v>0.05455580050608923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05217518652540645</v>
+        <v>0.0521751865254064</v>
       </c>
       <c r="S2" t="n">
         <v>0.0522598376142449</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05607853771391701</v>
+        <v>0.05607853771391702</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2196967063557353</v>
+        <v>0.2196967063557352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05502748850177065</v>
+        <v>0.05502748850177059</v>
       </c>
       <c r="W2" t="n">
         <v>0.2403547298806271</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05589618719471575</v>
+        <v>0.05589618719471567</v>
       </c>
       <c r="Y2" t="n">
         <v>0.05772242130740744</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2004405355587046</v>
+        <v>0.2004405355587045</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05265529199044715</v>
+        <v>0.052655291990447</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05603854726890283</v>
+        <v>0.0560385472689028</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07486665056488034</v>
+        <v>0.0736598466797064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07947186934283698</v>
+        <v>0.07261372289093068</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07706684886132208</v>
+        <v>0.07442840472752063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06766579549780029</v>
+        <v>0.03508984497105354</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1560015000394613</v>
+        <v>0.1014531588672291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1288648279412322</v>
+        <v>0.09124283560954961</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08912896328136871</v>
+        <v>0.07867970494359787</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08347890801221533</v>
+        <v>0.07665082552917117</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1400372582489937</v>
+        <v>0.09531258473290856</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07998270076776706</v>
+        <v>0.07538963480635423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07660367425956716</v>
+        <v>0.07424498184948497</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1742877782149258</v>
+        <v>0.106377662038669</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1417642157036855</v>
+        <v>0.0964314101890493</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3897415660281802</v>
+        <v>0.1848610626399196</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2670813729126017</v>
+        <v>0.1383643325608011</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.133905283308812</v>
+        <v>0.09317582783325695</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07862001623518468</v>
+        <v>0.07498414118557246</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08048838679412372</v>
+        <v>0.07549579836714747</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1696497011843989</v>
+        <v>0.1058202984983173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3220133950633333</v>
+        <v>0.2647888607083609</v>
       </c>
       <c r="V3" t="n">
-        <v>0.144227278179473</v>
+        <v>0.09658005781692852</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3871995990099651</v>
+        <v>0.3001873148177732</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1652747048895977</v>
+        <v>0.1043010304510253</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2073942758428089</v>
+        <v>0.1193551999469244</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.259224863182586</v>
+        <v>0.2328873589141459</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08971335493862291</v>
+        <v>0.0787835709992738</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1681981642151316</v>
+        <v>0.1058427855751267</v>
       </c>
     </row>
     <row r="4">
@@ -4338,40 +4338,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02106190890276049</v>
+        <v>0.02106190890276051</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09422021239720196</v>
+        <v>0.09422021239720192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04115865552352877</v>
+        <v>0.04115865552352869</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4282438773126972</v>
+        <v>0.4282438773126977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7185794993098757</v>
+        <v>0.7185794993098756</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4097624728573127</v>
+        <v>0.4097624728573125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.153659337501549</v>
+        <v>0.1536593375015489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09794098382262383</v>
+        <v>0.09794098382262337</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5247909864320441</v>
+        <v>0.5247909864320436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06333247604049405</v>
+        <v>0.06333247604049401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03514456629249631</v>
+        <v>0.03514456629249625</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7799466135381917</v>
+        <v>0.7799466135381918</v>
       </c>
       <c r="N4" t="n">
         <v>0.5795547819009182</v>
@@ -4383,40 +4383,40 @@
         <v>1.547457676038024</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4744308848400534</v>
+        <v>0.4744308848400542</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05630408320253368</v>
+        <v>0.05630408320253371</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06211007807045597</v>
+        <v>0.06211007807045599</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8099910697189073</v>
+        <v>0.8099910697189072</v>
       </c>
       <c r="U4" t="n">
         <v>0.6231849737861637</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5452871613139201</v>
+        <v>0.5452871613139197</v>
       </c>
       <c r="W4" t="n">
         <v>1.075058843546289</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7696069955402063</v>
+        <v>0.7696069955402074</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.165672479936286</v>
+        <v>1.165672479936284</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3058740058109601</v>
+        <v>0.3058740058109594</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1496168683842609</v>
+        <v>0.149616868384261</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8321730772903904</v>
+        <v>0.8321730772903922</v>
       </c>
     </row>
     <row r="5">
@@ -4429,82 +4429,82 @@
         <v>0.01395080040358909</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02235879729959748</v>
+        <v>0.0223587972995974</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01925916027961863</v>
+        <v>0.01925916027961851</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03925299787225581</v>
+        <v>0.03925299787225574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05373928355822566</v>
+        <v>0.05373928355822555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04560884108072209</v>
+        <v>0.04560884108072202</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0250513513108645</v>
+        <v>0.02505135131086436</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0223552228532266</v>
+        <v>0.02235522285322653</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05013039213955822</v>
+        <v>0.05013039213955818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02067737091986355</v>
+        <v>0.0206773709198634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01904841582289251</v>
+        <v>0.01904841582289238</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06627483867188323</v>
+        <v>0.06627483867188318</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5795547819009182</v>
+        <v>0.04741455979906062</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1655603511302616</v>
+        <v>0.1655603511302614</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1100512222989805</v>
+        <v>0.1100512222989804</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04180230447568252</v>
+        <v>0.04180230447568244</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02000161049872817</v>
+        <v>0.0200016104987281</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02095778348858343</v>
+        <v>0.02095778348858337</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06409175780321601</v>
+        <v>0.06409175780321591</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05675983033772104</v>
+        <v>0.05675983033772098</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0517229249963389</v>
+        <v>0.05172292499633886</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08137242726793818</v>
+        <v>0.08137242726793809</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05733243246597645</v>
+        <v>0.0573324324659764</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08686890722535638</v>
+        <v>0.08686890722535635</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03230077834561002</v>
+        <v>0.03230077834560994</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02542462258578806</v>
+        <v>0.02542462258578797</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06780158882198782</v>
+        <v>0.06780158882198783</v>
       </c>
     </row>
     <row r="6">
@@ -4514,82 +4514,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0243322979965985</v>
+        <v>0.02433229799659847</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03320919326884644</v>
+        <v>0.03320919326884642</v>
       </c>
       <c r="D6" t="n">
         <v>0.03010955624886751</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05127835045870567</v>
+        <v>0.05127835045870565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05729408985637122</v>
+        <v>0.05729408985637128</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05557723767562418</v>
+        <v>0.05557723767562405</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0359017472801134</v>
+        <v>0.03590174728011339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03320561882247559</v>
+        <v>0.03320561882247556</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06098078810880724</v>
+        <v>0.06098078810880721</v>
       </c>
       <c r="K6" t="n">
         <v>0.03152776688911244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0298988117921414</v>
+        <v>0.02989881179214139</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07712523464113111</v>
+        <v>0.07712523464113112</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5795547819009182</v>
+        <v>0.06156214686502587</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1803668401794023</v>
+        <v>0.1803668401794022</v>
       </c>
       <c r="P6" t="n">
         <v>0.125420178771292</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05774213262318469</v>
+        <v>0.05774213262318462</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03085200646797719</v>
+        <v>0.0308520064679771</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03180817945783245</v>
+        <v>0.03180817945783238</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07494215377246499</v>
+        <v>0.07494215377246496</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06969826888682185</v>
+        <v>0.06969826888682182</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06919861735326666</v>
+        <v>0.0691986173532666</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09222198730308045</v>
+        <v>0.0922219873030804</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07288242077270297</v>
+        <v>0.07288242077270296</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09351057518475378</v>
+        <v>0.09351057518475367</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04463650654201445</v>
+        <v>0.04463650654201435</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03627501855503699</v>
+        <v>0.03627501855503698</v>
       </c>
       <c r="AB6" t="n">
         <v>0.07420882546474522</v>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04957258291737526</v>
+        <v>0.04957258291737523</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04580594567377765</v>
+        <v>0.04580594567377769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04985954102733288</v>
+        <v>0.04985954102733287</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04971814823926574</v>
+        <v>0.04971814823926572</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05481944654007414</v>
+        <v>0.05481944654007411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05063189714887713</v>
+        <v>0.05063189714887708</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05064934688268772</v>
+        <v>0.05064934688268771</v>
       </c>
       <c r="I2" t="n">
         <v>0.05024335044254739</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05149135122217425</v>
+        <v>0.05149135122217419</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05048215686570202</v>
+        <v>0.05048215686570199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05012071949388727</v>
+        <v>0.05012071949388723</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05323903276581285</v>
+        <v>0.05323903276581288</v>
       </c>
       <c r="N2" t="n">
         <v>0.05109735768353069</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06664931125795404</v>
+        <v>0.06664931125795398</v>
       </c>
       <c r="P2" t="n">
         <v>0.0571157006724405</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05069292818852596</v>
+        <v>0.05069292818852594</v>
       </c>
       <c r="R2" t="n">
         <v>0.04988374671285796</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05227240222220507</v>
+        <v>0.05227240222220505</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05297132783443435</v>
+        <v>0.05297132783443437</v>
       </c>
       <c r="U2" t="n">
         <v>0.2158004262289117</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0510271611423995</v>
+        <v>0.05102716114239954</v>
       </c>
       <c r="W2" t="n">
         <v>0.2329087091914709</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05368947919086831</v>
+        <v>0.05368947919086827</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05346032766584277</v>
+        <v>0.05346032766584275</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1957603394782083</v>
+        <v>0.1957603394782081</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05051125258849832</v>
+        <v>0.05051125258849831</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05266530292786546</v>
+        <v>0.05266530292786541</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07257483007154157</v>
+        <v>0.07135946806036966</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07364179936281659</v>
+        <v>0.06911447091228902</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07929089116832852</v>
+        <v>0.07367359913172616</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02107674752313458</v>
+        <v>0.01763682462827113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1955158791636112</v>
+        <v>0.1138709309442447</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09695500317892262</v>
+        <v>0.07943609232616131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09788163449060029</v>
+        <v>0.08021719820142099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08827859663329801</v>
+        <v>0.07682194042013146</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1171023050668571</v>
+        <v>0.08639162630570547</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09377467616523159</v>
+        <v>0.07854083463064666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08524898551183141</v>
+        <v>0.0755090249267385</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1578075162649292</v>
+        <v>0.1003254548721381</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1080403843221099</v>
+        <v>0.08353720022132521</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3069285510848885</v>
+        <v>0.1540431523660674</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2458774390242188</v>
+        <v>0.1291532785895946</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09865372757455493</v>
+        <v>0.08016420227138051</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07989122257200064</v>
+        <v>0.07393448096788779</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1348473620470071</v>
+        <v>0.09205427878438643</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1519294339679171</v>
+        <v>0.09866913729201363</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3100276148135069</v>
+        <v>0.2589227582207116</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1060913555069109</v>
+        <v>0.08253026430746013</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2995492059981102</v>
+        <v>0.2682464511533456</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1684758993354236</v>
+        <v>0.1036886824745096</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1628918401398965</v>
+        <v>0.1026553199997499</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2260919599523269</v>
+        <v>0.219729077387782</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09437332355926138</v>
+        <v>0.07889281376735165</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1442203190877256</v>
+        <v>0.09646260906824464</v>
       </c>
     </row>
     <row r="4">
@@ -4934,82 +4934,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0190646540841613</v>
+        <v>0.01906465408416132</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06292754748610255</v>
+        <v>0.06292754748610246</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07765045385143413</v>
+        <v>0.07765045385143397</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04629555479501018</v>
+        <v>0.04629555479501014</v>
       </c>
       <c r="F4" t="n">
-        <v>1.103605851857838</v>
+        <v>1.103605851857839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2042176820430193</v>
+        <v>0.2042176820430202</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2506123374572386</v>
+        <v>0.250612337457239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1596242217945032</v>
+        <v>0.1596242217945034</v>
       </c>
       <c r="J4" t="n">
-        <v>0.381408771143069</v>
+        <v>0.3814087711430691</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1944248017376506</v>
+        <v>0.1944248017376503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112760839167532</v>
+        <v>0.1127608391675321</v>
       </c>
       <c r="M4" t="n">
         <v>0.733346004883762</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3226250321204202</v>
+        <v>0.3226250321204207</v>
       </c>
       <c r="O4" t="n">
-        <v>1.75663049939684</v>
+        <v>1.756630499396842</v>
       </c>
       <c r="P4" t="n">
-        <v>1.357181349221783</v>
+        <v>1.357181349221782</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2323363134421485</v>
+        <v>0.2323363134421488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08701494457917204</v>
+        <v>0.08701494457917133</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4982626884727435</v>
+        <v>0.4982626884727445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7065055964589498</v>
+        <v>0.7065055964589499</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5809534666843359</v>
+        <v>0.5809534666843362</v>
       </c>
       <c r="V4" t="n">
         <v>0.2793815340061147</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3977961457294567</v>
+        <v>0.397796145729457</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8009392056750716</v>
+        <v>0.8009392056750698</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8099918377980839</v>
+        <v>0.8099918377980855</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07566381315875179</v>
+        <v>0.07566381315875176</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.208485768727179</v>
+        <v>0.2084857687271792</v>
       </c>
       <c r="AB4" t="n">
         <v>0.6692064258295777</v>
@@ -5025,79 +5025,79 @@
         <v>0.01003643786935891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01560759136385466</v>
+        <v>0.01560759136385464</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01641122147273271</v>
+        <v>0.01641122147273269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01314565000588899</v>
+        <v>0.01314565000588901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06979033257043359</v>
+        <v>0.06979033257043347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.025785082457198</v>
+        <v>0.02578508245719804</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02533244193760956</v>
+        <v>0.02533244193760953</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0207465253786349</v>
+        <v>0.02074652537863496</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03494104484370107</v>
+        <v>0.03494104484370111</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02344395378454847</v>
+        <v>0.02344395378454849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01936135240049505</v>
+        <v>0.01936135240049508</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05431289275955594</v>
+        <v>0.05431289275955595</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3226250321204203</v>
+        <v>0.02796397450918524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1230279329571122</v>
+        <v>0.1230279329571121</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09644780530392653</v>
+        <v>0.09644780530392649</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02207545673484479</v>
+        <v>0.02207545673484486</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0166846358259043</v>
+        <v>0.01668463582590428</v>
       </c>
       <c r="S5" t="n">
         <v>0.04366559863980245</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05156028495159842</v>
+        <v>0.0515602849515984</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0480274509278449</v>
+        <v>0.04802745092784475</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02937474806596928</v>
+        <v>0.02937474806596932</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03539013435355164</v>
+        <v>0.03539013435355159</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05621006659737874</v>
+        <v>0.05621006659737875</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06016708542611125</v>
+        <v>0.0601670854261112</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01373809397052023</v>
+        <v>0.01373809397052022</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02377260335822649</v>
+        <v>0.02377260335822644</v>
       </c>
       <c r="AB5" t="n">
         <v>0.05107271769402704</v>
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01575306537604179</v>
+        <v>0.01575306537604169</v>
       </c>
       <c r="C6" t="n">
         <v>0.02113557728956076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02193920739843883</v>
+        <v>0.02193920739843873</v>
       </c>
       <c r="E6" t="n">
         <v>0.01966245394341922</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07117502048012021</v>
+        <v>0.0711750204801202</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03066331878803013</v>
+        <v>0.03066331878803008</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03086042786331564</v>
+        <v>0.03086042786331567</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02627451130434098</v>
+        <v>0.02627451130434096</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0404690307694072</v>
+        <v>0.04046903076940718</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02897193971025458</v>
+        <v>0.02897193971025459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02488933832620116</v>
+        <v>0.02488933832620112</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05984087868526061</v>
+        <v>0.05984087868526056</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3226250321204202</v>
+        <v>0.03592091595398821</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1312932768263382</v>
+        <v>0.131293276826338</v>
       </c>
       <c r="P6" t="n">
         <v>0.105089012061643</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.031352692456529</v>
+        <v>0.03135269245652891</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02221262175161039</v>
+        <v>0.02221262175161033</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04919358456550851</v>
+        <v>0.04919358456550849</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05708827087730457</v>
+        <v>0.05708827087730451</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05510366242184266</v>
+        <v>0.05510366242184262</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03917815991731413</v>
+        <v>0.0391781599173141</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04091750446841923</v>
+        <v>0.04091750446841921</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06520012081417199</v>
+        <v>0.06520012081417198</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.06261174892409904</v>
+        <v>0.06261174892409907</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02068227927109501</v>
+        <v>0.02068227927109498</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02930058928393261</v>
+        <v>0.02930058928393264</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0533275429047983</v>
+        <v>0.05332754290479818</v>
       </c>
     </row>
   </sheetData>
@@ -5354,82 +5354,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05285523631409007</v>
+        <v>0.05285523631408998</v>
       </c>
       <c r="C2" t="n">
-        <v>0.049345542550164</v>
+        <v>0.04934554255016413</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05308105280135939</v>
+        <v>0.05308105280135941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0588664991866677</v>
+        <v>0.05886649918666761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05402583911912798</v>
+        <v>0.05402583911912788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05376611024714323</v>
+        <v>0.05376611024714324</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05475272756706617</v>
+        <v>0.05475272756706623</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05366558709445881</v>
+        <v>0.05366558709445877</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05529998164979825</v>
+        <v>0.05529998164979823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0539199198360773</v>
+        <v>0.05391991983607725</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05289080638599421</v>
+        <v>0.05289080638599435</v>
       </c>
       <c r="M2" t="n">
         <v>0.05444873848901613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05422884595204163</v>
+        <v>0.05422884595204177</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06641735925318511</v>
+        <v>0.06641735925318513</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05792468284676209</v>
+        <v>0.05792468284676206</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05452090987311228</v>
+        <v>0.05452090987311237</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05407180750838145</v>
+        <v>0.05407180750838143</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05291132033908919</v>
+        <v>0.05291132033908915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.055949045506006</v>
+        <v>0.05594904550600603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2208799047181118</v>
+        <v>0.2208799047181119</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05706261650994381</v>
+        <v>0.05706261650994374</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2452061961098659</v>
+        <v>0.2452061961098657</v>
       </c>
       <c r="X2" t="n">
         <v>0.05301178444977696</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05955495731133886</v>
+        <v>0.05955495731133878</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2061217388922285</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05361177419819515</v>
+        <v>0.05361177419819519</v>
       </c>
       <c r="AB2" t="n">
         <v>0.05355286702823787</v>
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07661840587907792</v>
+        <v>0.0748865130008316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08115859272902748</v>
+        <v>0.07393165339187124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08192326379010427</v>
+        <v>0.07676218109865077</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1612604017311564</v>
+        <v>0.06824255666346192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1040874634647981</v>
+        <v>0.08443796742789846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09759260265033896</v>
+        <v>0.08190780239570367</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1212243147049732</v>
+        <v>0.09064640770503543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09560149685024633</v>
+        <v>0.08153712151398287</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1331252161374002</v>
+        <v>0.09402515172248561</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1014307777013588</v>
+        <v>0.0832377545126636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07745513435172924</v>
+        <v>0.07518134376132911</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1146855398259741</v>
+        <v>0.08780409030051597</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1085922737401311</v>
+        <v>0.08598536419110429</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2468179923028097</v>
+        <v>0.13587261181421</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931863559844823</v>
+        <v>0.1144877985975787</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.115423675489822</v>
+        <v>0.08823334007019558</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1051615533826536</v>
+        <v>0.08495800648617913</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07791772452723571</v>
+        <v>0.07531783501590862</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1489166948325158</v>
+        <v>0.1001489014940445</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3076968087070198</v>
+        <v>0.2625680403185207</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1735647751544123</v>
+        <v>0.1072034904103923</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4517829752084631</v>
+        <v>0.324977203952635</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08029989164721972</v>
+        <v>0.07618383041249725</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.232186753481895</v>
+        <v>0.1282804244551945</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3251952220370719</v>
+        <v>0.2573944128957249</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09419414293817305</v>
+        <v>0.08095775566753707</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.09389963105160515</v>
+        <v>0.08102948366582083</v>
       </c>
     </row>
     <row r="4">
@@ -5530,13 +5530,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02999125868930568</v>
+        <v>0.02999125868930597</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1095847391342091</v>
+        <v>0.1095847391342092</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08324155376287713</v>
+        <v>0.08324155376287733</v>
       </c>
       <c r="E4" t="n">
         <v>1.306329771737979</v>
@@ -5545,70 +5545,70 @@
         <v>0.2935260339628764</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2056691472340669</v>
+        <v>0.2056691472340672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4773219362835543</v>
+        <v>0.4773219362835548</v>
       </c>
       <c r="I4" t="n">
         <v>0.2152995055445746</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5227452635570828</v>
+        <v>0.5227452635570826</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2453986411281467</v>
+        <v>0.2453986411281468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03833194088334194</v>
+        <v>0.03833194088334336</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3725376904529245</v>
+        <v>0.3725376904529247</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3316841556672366</v>
+        <v>0.3316841556672364</v>
       </c>
       <c r="O4" t="n">
-        <v>1.377902435619591</v>
+        <v>1.377902435619589</v>
       </c>
       <c r="P4" t="n">
-        <v>1.046338681459238</v>
+        <v>1.046338681459237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3875944194353334</v>
+        <v>0.3875944194353337</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3144812546413336</v>
+        <v>0.3144812546413334</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04072259478865174</v>
+        <v>0.0407225947886518</v>
       </c>
       <c r="T4" t="n">
-        <v>0.728352028802309</v>
+        <v>0.7283520288023098</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6189821729346445</v>
+        <v>0.6189821729346459</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8337066815747229</v>
+        <v>0.8337066815747227</v>
       </c>
       <c r="W4" t="n">
-        <v>1.798139774508386</v>
+        <v>1.798139774508389</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0666817454936285</v>
+        <v>0.06668174549362837</v>
       </c>
       <c r="Y4" t="n">
         <v>1.447993413762017</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8810232330496174</v>
+        <v>0.8810232330496162</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1931664629098238</v>
+        <v>0.1931664629098243</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2074787115324275</v>
+        <v>0.2074787115324273</v>
       </c>
     </row>
     <row r="5">
@@ -5621,82 +5621,82 @@
         <v>0.01635119135306205</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02516002090219722</v>
+        <v>0.02516002090219724</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02365018311248327</v>
+        <v>0.02365018311248328</v>
       </c>
       <c r="E5" t="n">
         <v>0.08647113676482107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03031341672861496</v>
+        <v>0.03031341672861497</v>
       </c>
       <c r="G5" t="n">
         <v>0.03237281110359935</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04253251859952647</v>
+        <v>0.0425325185995265</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03025276685209939</v>
+        <v>0.03025276685209935</v>
       </c>
       <c r="J5" t="n">
         <v>0.04882568331674204</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03312557216752176</v>
+        <v>0.03312557216752177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0215012623332581</v>
+        <v>0.02150126233325811</v>
       </c>
       <c r="M5" t="n">
         <v>0.03948376711797294</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3316841556672366</v>
+        <v>0.03293431512917282</v>
       </c>
       <c r="O5" t="n">
         <v>0.09888962440142472</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07544404518505773</v>
+        <v>0.07544404518505772</v>
       </c>
       <c r="Q5" t="n">
         <v>0.03423259296366615</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0348412132979781</v>
+        <v>0.03484121329797805</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02173297687034901</v>
+        <v>0.02173297687034902</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05604548005329278</v>
+        <v>0.05604548005329276</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05096547824817279</v>
+        <v>0.05096547824817289</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06808336654413526</v>
+        <v>0.06808336654413527</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1141324639967961</v>
+        <v>0.1141324639967962</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01762151734423455</v>
+        <v>0.01762151734423459</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1015140912426831</v>
+        <v>0.101514091242683</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06510351104730684</v>
+        <v>0.06510351104730688</v>
       </c>
       <c r="AA5" t="n">
         <v>0.02964492543364681</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03441588097035352</v>
+        <v>0.03441588097035354</v>
       </c>
     </row>
     <row r="6">
@@ -5712,22 +5712,22 @@
         <v>0.03958967758337497</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03807983979366103</v>
+        <v>0.03807983979366104</v>
       </c>
       <c r="E6" t="n">
         <v>0.1020965774591772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03544164516961083</v>
+        <v>0.03544164516961078</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0458178891891322</v>
+        <v>0.04581788918913222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05696217528070417</v>
+        <v>0.05696217528070423</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0446824235332771</v>
+        <v>0.04468242353327711</v>
       </c>
       <c r="J6" t="n">
         <v>0.06325533999791977</v>
@@ -5736,55 +5736,55 @@
         <v>0.04755522884869948</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03593091901443588</v>
+        <v>0.03593091901443587</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0539134237991507</v>
+        <v>0.05391342379915072</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3316841556672366</v>
+        <v>0.05104469144155316</v>
       </c>
       <c r="O6" t="n">
-        <v>0.117901920757358</v>
+        <v>0.1179019207573579</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09512041549028646</v>
+        <v>0.09512041549028639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05434369818943551</v>
+        <v>0.05434369818943553</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04927086997915585</v>
+        <v>0.0492708699791558</v>
       </c>
       <c r="S6" t="n">
         <v>0.0361626335515268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07047513673447056</v>
+        <v>0.07047513673447049</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06770273903637819</v>
+        <v>0.06770273903637822</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09046255204882464</v>
+        <v>0.09046255204882461</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1285611875099617</v>
+        <v>0.1285611875099616</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03729742189752044</v>
+        <v>0.03729742189752045</v>
       </c>
       <c r="Y6" t="n">
         <v>0.1112055693770889</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.08088863079590783</v>
+        <v>0.0808886307959078</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04407458211482454</v>
+        <v>0.04407458211482458</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04388555102340971</v>
+        <v>0.04388555102340969</v>
       </c>
     </row>
   </sheetData>
@@ -5950,85 +5950,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05144005559020468</v>
+        <v>0.05144005559020464</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04775679134635796</v>
+        <v>0.04775679134635792</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05150526485450798</v>
+        <v>0.05150526485450785</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0551716563707183</v>
+        <v>0.05517165637071817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05535646192174699</v>
+        <v>0.05535646192174695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0523221601001457</v>
+        <v>0.05232216010014561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05289453754970481</v>
+        <v>0.0528945375497048</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0517195120527978</v>
+        <v>0.05171951205279771</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05419920037611543</v>
+        <v>0.05419920037611521</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05203253830393967</v>
+        <v>0.05203253830393959</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05152221026042203</v>
+        <v>0.05152221026042196</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05927952771273234</v>
+        <v>0.05927952771273212</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05327924239682773</v>
+        <v>0.05327924239682753</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07227810920974842</v>
+        <v>0.07227810920974832</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0576942228040494</v>
+        <v>0.05769422280404924</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05439499252099817</v>
+        <v>0.05439499252099802</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05187400636777569</v>
+        <v>0.05187400636777559</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05162870142709009</v>
+        <v>0.05162870142708991</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05520606080550636</v>
+        <v>0.05520606080550618</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2198700303989291</v>
+        <v>0.2198700303989288</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05428732777596904</v>
+        <v>0.05428732777596885</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2402243948895544</v>
+        <v>0.2402243948895542</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05344177066018126</v>
+        <v>0.05344177066018108</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05657188251563849</v>
+        <v>0.0565718825156384</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2008175000182142</v>
+        <v>0.200817500018214</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0521075887036312</v>
+        <v>0.05210758870363105</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05353875954540254</v>
+        <v>0.05353875954540235</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07397225394209712</v>
+        <v>0.07311417473822424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07771555212459823</v>
+        <v>0.07175116916340089</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07550921051011751</v>
+        <v>0.07365625402839536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1057269997577248</v>
+        <v>0.04820873128167318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1657142575950207</v>
+        <v>0.1046752228424083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09427163296647136</v>
+        <v>0.07982319921616265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1081544210325655</v>
+        <v>0.08521549943373918</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08052323425531795</v>
+        <v>0.07541274247431126</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1379763655617139</v>
+        <v>0.09467850588591836</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08777285004896598</v>
+        <v>0.07772469819912672</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07587957409413248</v>
+        <v>0.07376358855867048</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2560479331107878</v>
+        <v>0.1344538330285288</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1167641935009923</v>
+        <v>0.08796499531913671</v>
       </c>
       <c r="O3" t="n">
-        <v>0.35315837766837</v>
+        <v>0.171865142423162</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2177252882525862</v>
+        <v>0.1215171353645084</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1426967820553968</v>
+        <v>0.09613700050300446</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08415680101739388</v>
+        <v>0.07670159611039151</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07832580950137616</v>
+        <v>0.07456034601670164</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1619330280316525</v>
+        <v>0.1036847699011978</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3357128702711414</v>
+        <v>0.2699574803037986</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1395628744815365</v>
+        <v>0.09486832469734965</v>
       </c>
       <c r="W3" t="n">
-        <v>0.393866182641545</v>
+        <v>0.3033124975735007</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1206446689591734</v>
+        <v>0.08913988231401587</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.193133227211516</v>
+        <v>0.1140474372222011</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2710052738989045</v>
+        <v>0.2368379775539096</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08947308968935243</v>
+        <v>0.07846732855482041</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.123124099821573</v>
+        <v>0.09041555415999725</v>
       </c>
     </row>
     <row r="4">
@@ -6126,82 +6126,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01653863497456282</v>
+        <v>0.01653863497456269</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08251928774976118</v>
+        <v>0.08251928774976119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03093957829024534</v>
+        <v>0.03093957829024518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7575305709088751</v>
+        <v>0.7575305709088757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8144789027238154</v>
+        <v>0.814478902723816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1695984200096809</v>
+        <v>0.1695984200096578</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3386061532128335</v>
+        <v>0.3386061532128337</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07663795067888501</v>
+        <v>0.07663795067888525</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5340713522473967</v>
+        <v>0.5340713522473991</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1261931677570884</v>
+        <v>0.1261931677570883</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03244201932645058</v>
+        <v>0.03244201932645041</v>
       </c>
       <c r="M4" t="n">
         <v>1.504127496251208</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.3937110344914035</v>
       </c>
       <c r="O4" t="n">
-        <v>2.075909551700038</v>
+        <v>2.075909551700039</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158932923769634</v>
+        <v>1.158932923769635</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5655219441467371</v>
+        <v>0.5655219441467367</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1110790974254619</v>
+        <v>0.1110790974254623</v>
       </c>
       <c r="S4" t="n">
         <v>0.05002863917028949</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7993282347175857</v>
+        <v>0.7993282347175864</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7847847411102834</v>
+        <v>0.7847847411102835</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5179056603710159</v>
+        <v>0.5179056603710155</v>
       </c>
       <c r="W4" t="n">
-        <v>1.202950748848594</v>
+        <v>1.202950748848593</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4175236304310028</v>
+        <v>0.4175236304310012</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.034947406102086</v>
+        <v>1.034947406102084</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3955919447845406</v>
+        <v>0.3955919447845402</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1509626954811443</v>
+        <v>0.1509626954811427</v>
       </c>
       <c r="AB4" t="n">
         <v>0.4694014990419108</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01305401176752504</v>
+        <v>0.01305401176752507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02091454504575505</v>
+        <v>0.02091454504575498</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01789598652699484</v>
+        <v>0.01789598652699471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05712355766931905</v>
+        <v>0.05712355766931892</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05793119721042913</v>
+        <v>0.05793119721042899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02797447681995655</v>
+        <v>0.02797447681995609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03358846071625757</v>
+        <v>0.03358846071625728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02031600719025869</v>
+        <v>0.02031600719025879</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04843023143469998</v>
+        <v>0.04843023143469965</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02385178269609589</v>
+        <v>0.02385178269609574</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01808739268206556</v>
+        <v>0.01808739268206521</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1051030321970178</v>
+        <v>0.1051030321970176</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.0347515023725443</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1475764059182932</v>
+        <v>0.1475764059182934</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08528090973293964</v>
+        <v>0.08528090973293961</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04562457773620654</v>
+        <v>0.04562457773620645</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02206109154883019</v>
+        <v>0.02206109154882993</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01929025939793836</v>
+        <v>0.01929025939793841</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05969817924376929</v>
+        <v>0.05969817924376889</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06281621833404502</v>
+        <v>0.06281621833404492</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04889519833785642</v>
+        <v>0.04889519833785626</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08388223482113566</v>
+        <v>0.08388223482113584</v>
       </c>
       <c r="X5" t="n">
-        <v>0.035233766939938</v>
+        <v>0.03523376693993788</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07920058594538183</v>
+        <v>0.07920058594538218</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03741748433102704</v>
+        <v>0.03741748433102693</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02469951148550165</v>
+        <v>0.02469951148550125</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04521066712674086</v>
+        <v>0.04521066712674061</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02106167765553526</v>
+        <v>0.02106167765553525</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02881827026688053</v>
+        <v>0.02881827026688001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02579971174812052</v>
+        <v>0.02579971174811969</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06628975927099166</v>
+        <v>0.06628975927099158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06007630018616972</v>
+        <v>0.0600763001861696</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03502690715535355</v>
+        <v>0.03502690715535276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04149218593738303</v>
+        <v>0.04149218593738273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02821973241138422</v>
+        <v>0.02821973241138385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05633395665582556</v>
+        <v>0.05633395665582486</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03175550791722143</v>
+        <v>0.03175550791722159</v>
       </c>
       <c r="L6" t="n">
         <v>0.02599111790319109</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1130067574181301</v>
+        <v>0.1130067574181294</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3937110344914039</v>
+        <v>0.04583760415860958</v>
       </c>
       <c r="O6" t="n">
         <v>0.1591140271871234</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0973213019016331</v>
+        <v>0.09732130190163311</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05844050289890672</v>
+        <v>0.05844050289890596</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02996481676995579</v>
+        <v>0.02996481676995505</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0271939846190639</v>
+        <v>0.02719398461906388</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06760190446489488</v>
+        <v>0.06760190446489397</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07272788178715774</v>
+        <v>0.07272788178715694</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06254313652101688</v>
+        <v>0.0625431365210169</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09178515321756639</v>
+        <v>0.09178515321756593</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04767343565988263</v>
+        <v>0.04767343565988252</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08302948898986572</v>
+        <v>0.08302948898986491</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04709034301707349</v>
+        <v>0.04709034301707361</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03260323670662717</v>
+        <v>0.03260323670662674</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04882595237042353</v>
+        <v>0.04882595237042292</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ionising radiation results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07479581901467773</v>
+        <v>0.07444253511515574</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07311291485936069</v>
+        <v>0.07206680627158088</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07835489420330448</v>
+        <v>0.07686103436027696</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06952250322906517</v>
+        <v>0.05436596707015174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08182996241107299</v>
+        <v>0.0792070929272702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08186033605563112</v>
+        <v>0.07944211049701978</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09235192991918161</v>
+        <v>0.08631070321676799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07977156944962593</v>
+        <v>0.07781891783229619</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09302761449309484</v>
+        <v>0.08727253677699727</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08816807196144469</v>
+        <v>0.083629180181142</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07564531549593859</v>
+        <v>0.07502404463766618</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08924321133771509</v>
+        <v>0.08429162397688647</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0842461285386094</v>
+        <v>0.08097659557904162</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09497145453103038</v>
+        <v>0.08982681654545124</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1110691456543142</v>
+        <v>0.1002135115337958</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0837208424950688</v>
+        <v>0.08059463550513782</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08498368338122252</v>
+        <v>0.08135475446919053</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07499696587041743</v>
+        <v>0.0745794793681947</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09963231015286902</v>
+        <v>0.0914580350845451</v>
       </c>
       <c r="U3" t="n">
-        <v>0.260231936480928</v>
+        <v>0.2537981244174643</v>
       </c>
       <c r="V3" t="n">
-        <v>0.102948627436956</v>
+        <v>0.0945005951206187</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3122538804860946</v>
+        <v>0.2956563794948068</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07493851956032214</v>
+        <v>0.07451653542903772</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1244100523573837</v>
+        <v>0.1090301412092466</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.255150550609981</v>
+        <v>0.245593321597912</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0786302328300834</v>
+        <v>0.07709479280810569</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.07809535292242918</v>
+        <v>0.07662447554442373</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07219364259750741</v>
+        <v>0.07208032806233816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07034047270947977</v>
+        <v>0.06959171345864452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07404290858177554</v>
+        <v>0.07336651519846443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02672597655324678</v>
+        <v>0.02395456649494327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1257535599072874</v>
+        <v>0.109276829475414</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0941458511611097</v>
+        <v>0.08799164615832321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08560797697802107</v>
+        <v>0.08123792257410165</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08036430541311602</v>
+        <v>0.07772548802398183</v>
       </c>
       <c r="J3" t="n">
-        <v>0.094477564244701</v>
+        <v>0.08790812098177174</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1026581852714896</v>
+        <v>0.09394208100116688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09412958526742939</v>
+        <v>0.0878514298753207</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1099997300754911</v>
+        <v>0.09845151135066953</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09017816883034871</v>
+        <v>0.08453671895698879</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1600654451759067</v>
+        <v>0.1379493516602287</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1239083445629329</v>
+        <v>0.1094309150251632</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08525922448570725</v>
+        <v>0.08131883297108772</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08074900864004936</v>
+        <v>0.07793475820794157</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0995377252292053</v>
+        <v>0.09180382785284398</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1108809330015805</v>
+        <v>0.09874502523825995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2618213895158682</v>
+        <v>0.2544156633610695</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07952056437228625</v>
+        <v>0.07736925680124329</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2834672071208117</v>
+        <v>0.2744885453627194</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09802522028244468</v>
+        <v>0.09025827048788614</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09351045393381917</v>
+        <v>0.08689349076509237</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2230081702242256</v>
+        <v>0.2215621808339111</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0786716519125886</v>
+        <v>0.07658863410541775</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08884253354150776</v>
+        <v>0.08344648737223961</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07428817029922997</v>
+        <v>0.07406434649306423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07440651463046546</v>
+        <v>0.07296850296710083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07516655383127592</v>
+        <v>0.07465271636605025</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06456316535200921</v>
+        <v>0.05087348336639227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08157848184687458</v>
+        <v>0.07905403523389214</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08009945717559816</v>
+        <v>0.07819029100734026</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09230096971888793</v>
+        <v>0.08627523698096534</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08142095751162585</v>
+        <v>0.078930221092816</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09067377968818285</v>
+        <v>0.08564228736802913</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08479453609182351</v>
+        <v>0.08144413509669142</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07467874260633366</v>
+        <v>0.07433127448324742</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08384909779408682</v>
+        <v>0.08059062300765434</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08149725968649069</v>
+        <v>0.07905340198650561</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1267477665720551</v>
+        <v>0.1134738892678687</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1077141508788136</v>
+        <v>0.09783281980712989</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0921748313940671</v>
+        <v>0.08644735072431368</v>
       </c>
       <c r="R3" t="n">
-        <v>0.088247432775027</v>
+        <v>0.08356180232318454</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07469993822174188</v>
+        <v>0.07435411013115426</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0967519126903056</v>
+        <v>0.08949140423648322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2583960584221127</v>
+        <v>0.2524711790527908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1058336031154615</v>
+        <v>0.09679216516609884</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3078186458583651</v>
+        <v>0.2925003963631202</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07500047701321644</v>
+        <v>0.07454277876967809</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1249181592833051</v>
+        <v>0.1094878922491166</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2539133884097307</v>
+        <v>0.2447439072298473</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08042857608706527</v>
+        <v>0.07834027986920766</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.07780837365947704</v>
+        <v>0.07641197783962307</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07381285054348233</v>
+        <v>0.07334387118934958</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07203170956013222</v>
+        <v>0.07091987267787349</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07421688837946805</v>
+        <v>0.07358715004972034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04288971060894576</v>
+        <v>0.03523419958398664</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1018526639584898</v>
+        <v>0.09266224746620695</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0774517120850742</v>
+        <v>0.07594100817282064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09001237056858814</v>
+        <v>0.08426885521853365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0774295434726142</v>
+        <v>0.07578277567632516</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08557724566136804</v>
+        <v>0.08165932956365228</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07396580293278711</v>
+        <v>0.0734415657730508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07281237419474204</v>
+        <v>0.07262646594773257</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08089308677315125</v>
+        <v>0.07814662881825765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07896255895231259</v>
+        <v>0.07688565390701435</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1433773729042478</v>
+        <v>0.1255187807112146</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1030670170635976</v>
+        <v>0.0942240997476843</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1072517980763148</v>
+        <v>0.09664667867671742</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08542724289167283</v>
+        <v>0.08121617661047785</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07313958227112217</v>
+        <v>0.07286262618561372</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1032971701895373</v>
+        <v>0.09356014892346083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2527005893936106</v>
+        <v>0.2479200761257015</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09634149582995237</v>
+        <v>0.08965188920377512</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2966235528672166</v>
+        <v>0.2840617198075571</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07446711820347335</v>
+        <v>0.07376590242306852</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1095214697987172</v>
+        <v>0.09829107332263579</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2385347305420804</v>
+        <v>0.233337759308077</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07886274599150885</v>
+        <v>0.0768427653278104</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0756086215525253</v>
+        <v>0.07449452777165026</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07280815074295997</v>
+        <v>0.07211170824904256</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06918673061359315</v>
+        <v>0.06837501191065672</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07743848852180188</v>
+        <v>0.07529464475751006</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02374521357761604</v>
+        <v>0.02141565501494486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1130941257243644</v>
+        <v>0.0999285778426942</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0762720945792663</v>
+        <v>0.07461067745470665</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08765189733570226</v>
+        <v>0.08206254139278155</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09239578681190644</v>
+        <v>0.08554847324604214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08326824338893986</v>
+        <v>0.07944129592397824</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08697536228006106</v>
+        <v>0.08219925807488278</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08523754135761404</v>
+        <v>0.08089581797361567</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0892648856136322</v>
+        <v>0.08348338352551984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07578938164735204</v>
+        <v>0.0741170896678105</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1215438079961427</v>
+        <v>0.1086064502761863</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09320722048037321</v>
+        <v>0.08682346562931566</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1118248558067928</v>
+        <v>0.09950354423708417</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08862971698470416</v>
+        <v>0.08281255213100848</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08427494637515927</v>
+        <v>0.08029375214951842</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1052222333421574</v>
+        <v>0.09429582239121601</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2415484346563398</v>
+        <v>0.2392964788820026</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07769533414094038</v>
+        <v>0.07566764543157924</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2836248633573013</v>
+        <v>0.2741366347887875</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07675901278846459</v>
+        <v>0.07482525986121036</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08011399239681212</v>
+        <v>0.07713552782512413</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2222873096145086</v>
+        <v>0.220747948042377</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07763934198225883</v>
+        <v>0.07542324719439293</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.07318177214082978</v>
+        <v>0.0722680613271235</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0764108156030216</v>
+        <v>0.07612927073620442</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07494581769781226</v>
+        <v>0.07386887695238424</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07886038067621605</v>
+        <v>0.077802304786195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07167723577378253</v>
+        <v>0.05637284978665874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08719922848941815</v>
+        <v>0.08357006312395769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09434456809863442</v>
+        <v>0.08922554322961165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08389095579565467</v>
+        <v>0.08118815315382494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08085589245927111</v>
+        <v>0.07916395117215139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1054873274382038</v>
+        <v>0.0969345766291773</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08179356104933613</v>
+        <v>0.07993412869186198</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07725746828270785</v>
+        <v>0.07672809174395442</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1162107369766142</v>
+        <v>0.1042799824154742</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1041251127648936</v>
+        <v>0.09552963450965601</v>
       </c>
       <c r="O3" t="n">
-        <v>0.186488369777365</v>
+        <v>0.1588784690751472</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1428183075164256</v>
+        <v>0.1234985778792182</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1149639539722985</v>
+        <v>0.1032398696394618</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08190144191000327</v>
+        <v>0.07984999736843794</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07776764932372858</v>
+        <v>0.07712843829768945</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1190869593393993</v>
+        <v>0.1059469405198561</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2716087400764932</v>
+        <v>0.2626148398738303</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1099480649891628</v>
+        <v>0.1003261629437519</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3331228997873912</v>
+        <v>0.3108892484509742</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07741317404670799</v>
+        <v>0.07680817034226003</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1388004871695108</v>
+        <v>0.1198148455610048</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2616718815584749</v>
+        <v>0.2513440838106747</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08246739275906211</v>
+        <v>0.08034724487395802</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1056814910776656</v>
+        <v>0.09618977299222546</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0736598466797064</v>
+        <v>0.07348324657967077</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07261372289093068</v>
+        <v>0.07155442338463175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07442840472752063</v>
+        <v>0.07400821986065977</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03508984497105354</v>
+        <v>0.03000278654142128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1014531588672291</v>
+        <v>0.09285438821927597</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09124283560954961</v>
+        <v>0.08643324124976948</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07867970494359787</v>
+        <v>0.07689450130011379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07665082552917117</v>
+        <v>0.07554388405923336</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09531258473290856</v>
+        <v>0.08910066393161122</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07538963480635423</v>
+        <v>0.07470394344651789</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07424498184948497</v>
+        <v>0.0738990335734884</v>
       </c>
       <c r="M3" t="n">
-        <v>0.106377662038669</v>
+        <v>0.09710830179266122</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0964314101890493</v>
+        <v>0.08952638574792177</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1848610626399196</v>
+        <v>0.1569754079801434</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1383643325608011</v>
+        <v>0.1198703609517503</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09317582783325695</v>
+        <v>0.08756668628092421</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07498414118557246</v>
+        <v>0.07437971292348039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07549579836714747</v>
+        <v>0.07482933101268234</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1058202984983173</v>
+        <v>0.09613868246266789</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2647888607083609</v>
+        <v>0.2574297948747207</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09658005781692852</v>
+        <v>0.09014136104287253</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3001873148177732</v>
+        <v>0.2873359867177423</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1043010304510253</v>
+        <v>0.09510966073829548</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1193551999469244</v>
+        <v>0.1053612226785394</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2328873589141459</v>
+        <v>0.2293031767141223</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0787835709992738</v>
+        <v>0.07705485366249848</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1058427855751267</v>
+        <v>0.0958680357553687</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07135946806036966</v>
+        <v>0.07118089403958787</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06911447091228902</v>
+        <v>0.06840598427773019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07367359913172616</v>
+        <v>0.07278705662477622</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01763682462827113</v>
+        <v>0.01713094497920615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1138709309442447</v>
+        <v>0.1005769971148627</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07943609232616131</v>
+        <v>0.07704209659691011</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08021719820142099</v>
+        <v>0.07723224175074089</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07682194042013146</v>
+        <v>0.07494224394522055</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08639162630570547</v>
+        <v>0.08185643085300338</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07854083463064666</v>
+        <v>0.07625047350994879</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0755090249267385</v>
+        <v>0.07421108731231812</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1003254548721381</v>
+        <v>0.09153607128428248</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08353720022132521</v>
+        <v>0.07969578878475815</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1540431523660674</v>
+        <v>0.1330654153051835</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1291532785895946</v>
+        <v>0.112947388236387</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08016420227138051</v>
+        <v>0.07741933051062568</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07393448096788779</v>
+        <v>0.0729316450915828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09205427878438643</v>
+        <v>0.08613588870285879</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09866913729201363</v>
+        <v>0.09018788569850852</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2589227582207116</v>
+        <v>0.2520221867144696</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08253026430746013</v>
+        <v>0.07924022159709088</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2682464511533456</v>
+        <v>0.2635073647188015</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1036886824745096</v>
+        <v>0.09410319989430534</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1026553199997499</v>
+        <v>0.09292092528597849</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.219729077387782</v>
+        <v>0.2188745812132263</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07889281376735165</v>
+        <v>0.07642678835834008</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.09646260906824464</v>
+        <v>0.08841038241510886</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0748865130008316</v>
+        <v>0.07463485170145816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07393165339187124</v>
+        <v>0.07277966475831117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07676218109865077</v>
+        <v>0.07590619764068778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06824255666346192</v>
+        <v>0.05358671327963969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443796742789846</v>
+        <v>0.08120266771305867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08190780239570367</v>
+        <v>0.079684757908166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09064640770503543</v>
+        <v>0.085318189344758</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08153712151398287</v>
+        <v>0.07918575213896523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09402515172248561</v>
+        <v>0.08823051494638454</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0832377545126636</v>
+        <v>0.0805618564108847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07518134376132911</v>
+        <v>0.07483505341389801</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08780409030051597</v>
+        <v>0.08368852491705807</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08598536419110429</v>
+        <v>0.08232256491482476</v>
       </c>
       <c r="O3" t="n">
-        <v>0.13587261181421</v>
+        <v>0.120513349981444</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1144877985975787</v>
+        <v>0.1028041574663986</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08823334007019558</v>
+        <v>0.08394343212880731</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08495800648617913</v>
+        <v>0.08147911666433323</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07531783501590862</v>
+        <v>0.07494581083518384</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1001489014940445</v>
+        <v>0.09198955858009593</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2625680403185207</v>
+        <v>0.2556793033597284</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1072034904103923</v>
+        <v>0.09794718091278831</v>
       </c>
       <c r="W3" t="n">
-        <v>0.324977203952635</v>
+        <v>0.3047587160975782</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07618383041249725</v>
+        <v>0.0755159081570163</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1282804244551945</v>
+        <v>0.1120286906545636</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2573944128957249</v>
+        <v>0.2475808984854378</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08095775566753707</v>
+        <v>0.07886295947279025</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08102948366582083</v>
+        <v>0.07876183707971954</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07311417473822424</v>
+        <v>0.07298694672546918</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07175116916340089</v>
+        <v>0.07082795003409353</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07365625402839536</v>
+        <v>0.07335423085322836</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04820873128167318</v>
+        <v>0.03914189448311301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1046752228424083</v>
+        <v>0.09490660388578616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07982319921616265</v>
+        <v>0.07786548201600885</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08521549943373918</v>
+        <v>0.08117853327275582</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07541274247431126</v>
+        <v>0.07455710109873401</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09467850588591836</v>
+        <v>0.08833099846470367</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07772469819912672</v>
+        <v>0.07628037450521996</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07376358855867048</v>
+        <v>0.07344479457910288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1344538330285288</v>
+        <v>0.116422293692725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08796499531913671</v>
+        <v>0.08327871231794833</v>
       </c>
       <c r="O3" t="n">
-        <v>0.171865142423162</v>
+        <v>0.1470921896441612</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1215171353645084</v>
+        <v>0.1076800359966435</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09613700050300446</v>
+        <v>0.08941412317150374</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07670159611039151</v>
+        <v>0.07542770555253006</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07456034601670164</v>
+        <v>0.07403197048975392</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1036847699011978</v>
+        <v>0.09408822707716785</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2699574803037986</v>
+        <v>0.2606125500450566</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09486832469734965</v>
+        <v>0.08874796927345142</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3033124975735007</v>
+        <v>0.2888621542952224</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08913988231401587</v>
+        <v>0.08417247176766632</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1140474372222011</v>
+        <v>0.1016341958594609</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2368379775539096</v>
+        <v>0.2321745201646843</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07846732855482041</v>
+        <v>0.07671699636593177</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.09041555415999725</v>
+        <v>0.08479926312456465</v>
       </c>
     </row>
     <row r="4">
